--- a/data/OldInventorySystem.xlsx
+++ b/data/OldInventorySystem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rosehulman-my.sharepoint.com/personal/lucasja_rose-hulman_edu/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96303D34-571E-4205-A343-0BD2D91829A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{929C0295-FFF7-4442-A7F8-B9615CC42371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="3" activeTab="3" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="3" activeTab="4" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Laptops" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="258">
   <si>
     <t>LAPTOPS</t>
   </si>
@@ -403,7 +403,10 @@
     <t>OS</t>
   </si>
   <si>
-    <t>RAM</t>
+    <t>RAM Amount</t>
+  </si>
+  <si>
+    <t>RAM Generation</t>
   </si>
   <si>
     <t>Storage</t>
@@ -430,10 +433,7 @@
     <t>Vanilla OS</t>
   </si>
   <si>
-    <t>4GB DDR3</t>
-  </si>
-  <si>
-    <t>256GB</t>
+    <t>DDR3</t>
   </si>
   <si>
     <t>SSD</t>
@@ -445,16 +445,13 @@
     <t>Inspiron 15-3552</t>
   </si>
   <si>
-    <t>8GB DDR3</t>
-  </si>
-  <si>
     <t>Asus Chromebox Thin Cilent 3</t>
   </si>
   <si>
     <t>Intel Celeron 3865U</t>
   </si>
   <si>
-    <t>8GB DDR4</t>
+    <t>DDR4</t>
   </si>
   <si>
     <t>intel core i3-7100</t>
@@ -514,9 +511,6 @@
     <t>Intel Core i5-8265U</t>
   </si>
   <si>
-    <t xml:space="preserve"> 8GB DDR4</t>
-  </si>
-  <si>
     <t>HP ProBook 450 G8</t>
   </si>
   <si>
@@ -526,12 +520,6 @@
     <t>Intel Core i7-6700</t>
   </si>
   <si>
-    <t>16GB DDR4</t>
-  </si>
-  <si>
-    <t>500GB</t>
-  </si>
-  <si>
     <t>HP Elitebook 850 G6</t>
   </si>
   <si>
@@ -577,18 +565,12 @@
     <t>Intel core i7-8665U</t>
   </si>
   <si>
-    <t>16gb DDR4 2400 MT/s</t>
-  </si>
-  <si>
     <t>HP 15-AC113CL</t>
   </si>
   <si>
     <t>Intel core i3-5005U</t>
   </si>
   <si>
-    <t>8gb DDR3 1600 MT/s</t>
-  </si>
-  <si>
     <t>Toshiba Satellite C55-B5296</t>
   </si>
   <si>
@@ -604,18 +586,12 @@
     <t>Intel core i7-8565U</t>
   </si>
   <si>
-    <t>16GB DDR4 2400 MT/s</t>
-  </si>
-  <si>
     <t>Dell Latitude 5420</t>
   </si>
   <si>
     <t>Intel core i5-1145G7</t>
   </si>
   <si>
-    <t>16GB DDR4 3200 MT/s</t>
-  </si>
-  <si>
     <t>Apple iPad Mini A1455</t>
   </si>
   <si>
@@ -625,10 +601,10 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>iOS 9.3.6</t>
-  </si>
-  <si>
-    <t>64GB</t>
+    <t>iOS</t>
+  </si>
+  <si>
+    <t>DDR2</t>
   </si>
   <si>
     <t>Flash Storage</t>
@@ -640,12 +616,6 @@
     <t>Apple iPad Air 2 A1566</t>
   </si>
   <si>
-    <t>iOS 15.8.5</t>
-  </si>
-  <si>
-    <t>128GB</t>
-  </si>
-  <si>
     <t>Dell OptiPlex 5060</t>
   </si>
   <si>
@@ -664,9 +634,6 @@
     <t>Wifi included</t>
   </si>
   <si>
-    <t>SFF Desktop</t>
-  </si>
-  <si>
     <t>Intel i7-6700</t>
   </si>
   <si>
@@ -685,19 +652,10 @@
     <t>Intel i7-4770</t>
   </si>
   <si>
-    <t>16GB DDR3</t>
-  </si>
-  <si>
     <t>ThinkPad P1 Gen 1</t>
   </si>
   <si>
     <t>Intel i7 10750H</t>
-  </si>
-  <si>
-    <t>512GB</t>
-  </si>
-  <si>
-    <t>Mini Desktop</t>
   </si>
   <si>
     <t>Intel i3-7100</t>
@@ -1059,7 +1017,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="49">
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1073,6 +1031,118 @@
           <color theme="4" tint="0.39997558519241921"/>
         </top>
       </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1113,6 +1183,142 @@
           <color theme="4" tint="0.39997558519241921"/>
         </top>
       </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1239,7 +1445,7 @@
     <tableColumn id="13" xr3:uid="{5BEE40AD-E450-4A13-BFB5-1D0CED084DB3}" name="ID"/>
     <tableColumn id="8" xr3:uid="{E9AB9B46-3541-4715-8E5B-024096D78342}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{F7DAC8DD-8096-40F1-8780-1DB9CB4EC72F}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="48"/>
     <tableColumn id="5" xr3:uid="{5338F6FB-43B0-44AF-AF8B-542FAC6CEDF0}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{64D6C993-8518-4A7C-9BDA-A54D7DBFBA8E}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{E5D987A3-C54A-4907-B710-79DB224E0008}" name="Current Status" totalsRowFunction="count"/>
@@ -1258,7 +1464,7 @@
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F96A3CC8-25D1-4CF8-877D-2816B26B7DC4}" name="Item Name" totalsRowLabel="Total"/>
-    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="45"/>
     <tableColumn id="8" xr3:uid="{7D8F815E-A974-42A8-AC0B-AB8B951599A2}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{FEA94C75-B538-448A-A9F5-46F5A27E863D}" name="Year released"/>
     <tableColumn id="4" xr3:uid="{24998D92-36B7-4553-81E7-CB33711B31BB}" name="Special Reqs/Notes"/>
@@ -1280,7 +1486,7 @@
     <tableColumn id="13" xr3:uid="{EFFF3477-1A58-41CD-BFF3-45CE299505A7}" name="ID"/>
     <tableColumn id="8" xr3:uid="{C694899F-E385-4DE2-972A-7395A9633019}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{13C54556-A90A-4F9C-800D-3D838462DF46}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="44"/>
     <tableColumn id="5" xr3:uid="{6DE19FBC-9BD8-456E-9FC5-F633F61E4A34}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{68546225-0A78-43C1-A4F9-4D2E1DC008A3}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{0D7FD365-4F73-4A57-B8A1-CFAC47267923}" name="Current Status" totalsRowFunction="count"/>
@@ -1291,19 +1497,20 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:K33" totalsRowShown="0" tableBorderDxfId="8">
-  <autoFilter ref="A2:K33" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:L33" totalsRowShown="0" tableBorderDxfId="21">
+  <autoFilter ref="A2:L33" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}"/>
+  <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{73648E04-2EA1-4ADB-8E24-E7DDE01C0462}" name="Item"/>
     <tableColumn id="10" xr3:uid="{2C0BEEB0-DF56-4C3E-A199-8338A12BCED4}" name="Type of Device"/>
     <tableColumn id="3" xr3:uid="{6E6AE907-D46F-4E72-8A6E-4086D6ED467F}" name="Est. Year"/>
     <tableColumn id="4" xr3:uid="{21962421-D6C5-44DF-8B4E-CE81A5E85189}" name="CPU"/>
     <tableColumn id="5" xr3:uid="{CA276052-8A68-41FA-B502-833DDEE2F0F8}" name="OS"/>
-    <tableColumn id="6" xr3:uid="{38C5F018-4493-43C4-9328-52082FCC36C1}" name="RAM"/>
+    <tableColumn id="6" xr3:uid="{38C5F018-4493-43C4-9328-52082FCC36C1}" name="RAM Amount"/>
+    <tableColumn id="2" xr3:uid="{C85B34EB-06B2-40A8-BBCB-B5F170EF3F82}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{A686D1B3-031E-4544-A98D-8F3144FA62B0}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{AB29939A-0AF4-4451-A6F4-2144F8957E73}" name="SSD/HDD"/>
-    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="19"/>
     <tableColumn id="12" xr3:uid="{67EC036F-98F6-4C6B-BDD7-99DB9B6ADF97}" name="ID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1311,15 +1518,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:L59" totalsRowShown="0" tableBorderDxfId="2">
-  <autoFilter ref="A2:L59" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:M59" totalsRowShown="0" tableBorderDxfId="2">
+  <autoFilter ref="A2:M59" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}"/>
+  <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{D71C6020-33AC-4F3C-BC88-69BADE52FD9C}" name="Item"/>
     <tableColumn id="11" xr3:uid="{3694AE3D-BABD-4C86-8092-3A4D6CE18FE9}" name="Type of Device"/>
     <tableColumn id="3" xr3:uid="{DBF01EDE-E989-4722-BA17-4F2F168FA1B7}" name="Est. Year"/>
     <tableColumn id="4" xr3:uid="{8A83BF41-D4B3-47AF-9A4E-D470FED11493}" name="CPU"/>
     <tableColumn id="5" xr3:uid="{5A855548-F141-4612-89D9-87C3C3042FDB}" name="OS"/>
-    <tableColumn id="6" xr3:uid="{7C6B1539-F50D-45A7-A8CD-94746983CE20}" name="RAM"/>
+    <tableColumn id="6" xr3:uid="{7C6B1539-F50D-45A7-A8CD-94746983CE20}" name="RAM Amount"/>
+    <tableColumn id="13" xr3:uid="{D6E0079E-D628-428A-8C40-CC4B7F920E56}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{7319329B-DA0F-470E-AE1F-CAF023744072}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{96CAC308-4A56-4EA5-AF3F-FCAC656EEA09}" name="SSD/HDD"/>
     <tableColumn id="10" xr3:uid="{6EFEA34D-1A93-4407-A41E-DD47A214B1DA}" name="Est. Value" dataDxfId="1"/>
@@ -3741,12 +3949,12 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:G63">
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="47" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:G63">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3993,21 +4201,23 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFE86381-3E33-4CB8-A62B-E48A74AB9667}">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" style="19" customWidth="1"/>
-    <col min="10" max="10" width="21.28515625" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="4" max="5" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" style="19" customWidth="1"/>
+    <col min="11" max="11" width="21.28515625" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="23" t="s">
         <v>114</v>
       </c>
@@ -4021,8 +4231,9 @@
       <c r="I1" s="24"/>
       <c r="J1" s="24"/>
       <c r="K1" s="24"/>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="24"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -4047,50 +4258,56 @@
       <c r="H2" t="s">
         <v>122</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" t="s">
         <v>123</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="19" t="s">
         <v>124</v>
       </c>
       <c r="K2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C3">
         <v>2013</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F3" t="s">
         <v>129</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
       </c>
       <c r="G3" t="s">
         <v>130</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3">
+        <v>256</v>
+      </c>
+      <c r="I3" t="s">
         <v>131</v>
       </c>
-      <c r="I3" s="19">
+      <c r="J3" s="19">
         <v>100</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="K3">
+      <c r="K3" s="1"/>
+      <c r="L3">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -4104,166 +4321,181 @@
         <v>133</v>
       </c>
       <c r="E4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F4" t="s">
-        <v>134</v>
+        <v>129</v>
+      </c>
+      <c r="F4">
+        <v>8</v>
       </c>
       <c r="G4" t="s">
         <v>130</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4">
+        <v>256</v>
+      </c>
+      <c r="I4" t="s">
         <v>131</v>
       </c>
-      <c r="I4" s="19">
+      <c r="J4" s="19">
         <v>200</v>
       </c>
-      <c r="J4" s="1"/>
-      <c r="K4">
+      <c r="K4" s="1"/>
+      <c r="L4">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>2018</v>
       </c>
       <c r="D5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5" t="s">
         <v>136</v>
       </c>
-      <c r="E5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F5" t="s">
-        <v>137</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="H5">
+        <v>256</v>
+      </c>
+      <c r="I5" t="s">
         <v>131</v>
       </c>
-      <c r="I5" s="19">
+      <c r="J5" s="19">
         <v>175</v>
       </c>
-      <c r="J5" s="1"/>
-      <c r="K5">
+      <c r="K5" s="1"/>
+      <c r="L5">
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:11">
+    <row r="6" spans="1:12">
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C7">
         <v>2018</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
-        <v>128</v>
-      </c>
-      <c r="F7" t="s">
-        <v>137</v>
+        <v>129</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>130</v>
-      </c>
-      <c r="H7" t="s">
+        <v>136</v>
+      </c>
+      <c r="H7">
+        <v>256</v>
+      </c>
+      <c r="I7" t="s">
         <v>131</v>
       </c>
-      <c r="I7" s="19">
+      <c r="J7" s="19">
         <v>175</v>
       </c>
-      <c r="J7" s="1"/>
-      <c r="K7">
+      <c r="K7" s="1"/>
+      <c r="L7">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>92</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8">
         <v>2018</v>
       </c>
       <c r="D8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H8">
+        <v>256</v>
+      </c>
+      <c r="I8" t="s">
+        <v>131</v>
+      </c>
+      <c r="J8" s="19">
+        <v>175</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
         <v>139</v>
       </c>
-      <c r="E8" t="s">
-        <v>128</v>
-      </c>
-      <c r="F8" t="s">
-        <v>137</v>
-      </c>
-      <c r="G8" t="s">
-        <v>130</v>
-      </c>
-      <c r="H8" t="s">
-        <v>131</v>
-      </c>
-      <c r="I8" s="19">
-        <v>175</v>
-      </c>
-      <c r="J8" s="1"/>
-      <c r="K8">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>140</v>
-      </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C9">
         <v>2018</v>
       </c>
       <c r="D9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9" t="s">
+        <v>136</v>
+      </c>
+      <c r="H9">
+        <v>256</v>
+      </c>
+      <c r="I9" t="s">
+        <v>131</v>
+      </c>
+      <c r="J9" s="19">
+        <v>150</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
         <v>141</v>
-      </c>
-      <c r="E9" t="s">
-        <v>128</v>
-      </c>
-      <c r="F9" t="s">
-        <v>137</v>
-      </c>
-      <c r="G9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H9" t="s">
-        <v>131</v>
-      </c>
-      <c r="I9" s="19">
-        <v>150</v>
-      </c>
-      <c r="J9" s="1"/>
-      <c r="K9">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>142</v>
       </c>
       <c r="B11" t="s">
         <v>132</v>
@@ -4272,63 +4504,69 @@
         <v>2020</v>
       </c>
       <c r="D11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" t="s">
         <v>143</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11" t="s">
+        <v>136</v>
+      </c>
+      <c r="H11">
+        <v>256</v>
+      </c>
+      <c r="I11" t="s">
+        <v>131</v>
+      </c>
+      <c r="J11" s="19">
+        <v>300</v>
+      </c>
+      <c r="K11" s="1"/>
+      <c r="L11">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
         <v>144</v>
       </c>
-      <c r="F11" t="s">
-        <v>137</v>
-      </c>
-      <c r="G11" t="s">
-        <v>130</v>
-      </c>
-      <c r="H11" t="s">
-        <v>131</v>
-      </c>
-      <c r="I11" s="19">
-        <v>300</v>
-      </c>
-      <c r="J11" s="1"/>
-      <c r="K11">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>145</v>
-      </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C12">
         <v>2014</v>
       </c>
       <c r="D12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+      <c r="G12" t="s">
+        <v>130</v>
+      </c>
+      <c r="H12">
+        <v>256</v>
+      </c>
+      <c r="I12" t="s">
+        <v>131</v>
+      </c>
+      <c r="J12" s="2">
+        <v>175</v>
+      </c>
+      <c r="L12">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
         <v>146</v>
-      </c>
-      <c r="E12" t="s">
-        <v>128</v>
-      </c>
-      <c r="F12" t="s">
-        <v>134</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="H12" t="s">
-        <v>131</v>
-      </c>
-      <c r="I12" s="2">
-        <v>175</v>
-      </c>
-      <c r="K12">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>147</v>
       </c>
       <c r="B13" t="s">
         <v>132</v>
@@ -4337,31 +4575,34 @@
         <v>2018</v>
       </c>
       <c r="D13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E13" t="s">
-        <v>144</v>
-      </c>
-      <c r="F13" t="s">
-        <v>137</v>
+        <v>143</v>
+      </c>
+      <c r="F13">
+        <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>130</v>
-      </c>
-      <c r="H13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H13">
+        <v>256</v>
+      </c>
+      <c r="I13" t="s">
         <v>131</v>
       </c>
-      <c r="I13" s="19">
+      <c r="J13" s="19">
         <v>120</v>
       </c>
-      <c r="J13" s="1"/>
-      <c r="K13">
+      <c r="K13" s="1"/>
+      <c r="L13">
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15" customHeight="1">
+    <row r="14" spans="1:12" ht="15" customHeight="1">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B14" t="s">
         <v>132</v>
@@ -4370,31 +4611,34 @@
         <v>2018</v>
       </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E14" t="s">
-        <v>128</v>
-      </c>
-      <c r="F14" t="s">
-        <v>137</v>
+        <v>129</v>
+      </c>
+      <c r="F14">
+        <v>8</v>
       </c>
       <c r="G14" t="s">
-        <v>130</v>
-      </c>
-      <c r="H14" t="s">
+        <v>136</v>
+      </c>
+      <c r="H14">
+        <v>256</v>
+      </c>
+      <c r="I14" t="s">
         <v>131</v>
       </c>
-      <c r="I14" s="19">
+      <c r="J14" s="19">
         <v>175</v>
       </c>
-      <c r="J14" s="1"/>
-      <c r="K14">
+      <c r="K14" s="1"/>
+      <c r="L14">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" customHeight="1">
+    <row r="15" spans="1:12" ht="15" customHeight="1">
       <c r="A15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B15" t="s">
         <v>132</v>
@@ -4403,29 +4647,32 @@
         <v>2013</v>
       </c>
       <c r="D15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E15" t="s">
-        <v>128</v>
-      </c>
-      <c r="F15" t="s">
-        <v>134</v>
+        <v>129</v>
+      </c>
+      <c r="F15">
+        <v>8</v>
       </c>
       <c r="G15" t="s">
         <v>130</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15">
+        <v>256</v>
+      </c>
+      <c r="I15" t="s">
         <v>131</v>
       </c>
-      <c r="I15" s="19">
+      <c r="J15" s="19">
         <v>150</v>
       </c>
-      <c r="J15" s="1"/>
-      <c r="K15">
+      <c r="K15" s="1"/>
+      <c r="L15">
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1">
+    <row r="16" spans="1:12" ht="15" customHeight="1">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -4436,31 +4683,34 @@
         <v>2019</v>
       </c>
       <c r="D16" t="s">
+        <v>150</v>
+      </c>
+      <c r="E16" t="s">
+        <v>143</v>
+      </c>
+      <c r="F16">
+        <v>8</v>
+      </c>
+      <c r="G16" t="s">
+        <v>136</v>
+      </c>
+      <c r="H16">
+        <v>256</v>
+      </c>
+      <c r="I16" t="s">
+        <v>131</v>
+      </c>
+      <c r="J16" s="19">
+        <v>265</v>
+      </c>
+      <c r="K16" s="1"/>
+      <c r="L16">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15" customHeight="1">
+      <c r="A17" t="s">
         <v>151</v>
-      </c>
-      <c r="E16" t="s">
-        <v>144</v>
-      </c>
-      <c r="F16" t="s">
-        <v>137</v>
-      </c>
-      <c r="G16" t="s">
-        <v>130</v>
-      </c>
-      <c r="H16" t="s">
-        <v>131</v>
-      </c>
-      <c r="I16" s="19">
-        <v>265</v>
-      </c>
-      <c r="J16" s="1"/>
-      <c r="K16">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1">
-      <c r="A17" t="s">
-        <v>152</v>
       </c>
       <c r="B17" t="s">
         <v>132</v>
@@ -4469,31 +4719,34 @@
         <v>2014</v>
       </c>
       <c r="D17" t="s">
+        <v>152</v>
+      </c>
+      <c r="E17" t="s">
         <v>153</v>
       </c>
-      <c r="E17" t="s">
-        <v>154</v>
-      </c>
-      <c r="F17" t="s">
-        <v>134</v>
+      <c r="F17">
+        <v>8</v>
       </c>
       <c r="G17" t="s">
         <v>130</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17">
+        <v>256</v>
+      </c>
+      <c r="I17" t="s">
         <v>131</v>
       </c>
-      <c r="I17" s="19">
+      <c r="J17" s="19">
         <v>100</v>
       </c>
-      <c r="J17" s="1"/>
-      <c r="K17">
+      <c r="K17" s="1"/>
+      <c r="L17">
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1">
+    <row r="18" spans="1:12" ht="15" customHeight="1">
       <c r="A18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B18" t="s">
         <v>132</v>
@@ -4502,31 +4755,34 @@
         <v>2019</v>
       </c>
       <c r="D18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E18" t="s">
-        <v>128</v>
-      </c>
-      <c r="F18" t="s">
-        <v>137</v>
+        <v>129</v>
+      </c>
+      <c r="F18">
+        <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>130</v>
-      </c>
-      <c r="H18" t="s">
+        <v>136</v>
+      </c>
+      <c r="H18">
+        <v>256</v>
+      </c>
+      <c r="I18" t="s">
         <v>131</v>
       </c>
-      <c r="I18" s="19">
+      <c r="J18" s="19">
         <v>300</v>
       </c>
-      <c r="J18" s="1"/>
-      <c r="K18">
+      <c r="K18" s="1"/>
+      <c r="L18">
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1">
+    <row r="19" spans="1:12" ht="15" customHeight="1">
       <c r="A19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B19" t="s">
         <v>132</v>
@@ -4535,31 +4791,34 @@
         <v>2019</v>
       </c>
       <c r="D19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19" t="s">
+        <v>143</v>
+      </c>
+      <c r="F19">
+        <v>8</v>
+      </c>
+      <c r="G19" t="s">
+        <v>136</v>
+      </c>
+      <c r="H19">
+        <v>256</v>
+      </c>
+      <c r="I19" t="s">
+        <v>131</v>
+      </c>
+      <c r="J19" s="19">
+        <v>300</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15" customHeight="1">
+      <c r="A20" t="s">
         <v>156</v>
-      </c>
-      <c r="E19" t="s">
-        <v>144</v>
-      </c>
-      <c r="F19" t="s">
-        <v>157</v>
-      </c>
-      <c r="G19" t="s">
-        <v>130</v>
-      </c>
-      <c r="H19" t="s">
-        <v>131</v>
-      </c>
-      <c r="I19" s="19">
-        <v>300</v>
-      </c>
-      <c r="J19" s="1"/>
-      <c r="K19">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1">
-      <c r="A20" t="s">
-        <v>158</v>
       </c>
       <c r="B20" t="s">
         <v>132</v>
@@ -4568,31 +4827,34 @@
         <v>2021</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E20" t="s">
-        <v>144</v>
-      </c>
-      <c r="F20" t="s">
-        <v>137</v>
+        <v>143</v>
+      </c>
+      <c r="F20">
+        <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>130</v>
-      </c>
-      <c r="H20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H20">
+        <v>256</v>
+      </c>
+      <c r="I20" t="s">
         <v>131</v>
       </c>
-      <c r="I20" s="19">
+      <c r="J20" s="19">
         <v>350</v>
       </c>
-      <c r="J20" s="1"/>
-      <c r="K20">
+      <c r="K20" s="1"/>
+      <c r="L20">
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1">
+    <row r="21" spans="1:12" ht="15" customHeight="1">
       <c r="A21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B21" t="s">
         <v>132</v>
@@ -4601,64 +4863,70 @@
         <v>2021</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E21" t="s">
-        <v>144</v>
-      </c>
-      <c r="F21" t="s">
-        <v>137</v>
+        <v>143</v>
+      </c>
+      <c r="F21">
+        <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>130</v>
-      </c>
-      <c r="H21" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21">
+        <v>256</v>
+      </c>
+      <c r="I21" t="s">
         <v>131</v>
       </c>
-      <c r="I21" s="19">
+      <c r="J21" s="19">
         <v>350</v>
       </c>
-      <c r="J21" s="1"/>
-      <c r="K21">
+      <c r="K21" s="1"/>
+      <c r="L21">
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1">
+    <row r="22" spans="1:12" ht="15" customHeight="1">
       <c r="A22" t="s">
         <v>68</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C22">
         <v>2016</v>
       </c>
       <c r="D22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E22" t="s">
-        <v>128</v>
-      </c>
-      <c r="F22" t="s">
-        <v>161</v>
+        <v>129</v>
+      </c>
+      <c r="F22">
+        <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>162</v>
-      </c>
-      <c r="H22" t="s">
+        <v>136</v>
+      </c>
+      <c r="H22">
+        <v>256</v>
+      </c>
+      <c r="I22" t="s">
         <v>131</v>
       </c>
-      <c r="I22" s="19">
+      <c r="J22" s="19">
         <v>255</v>
       </c>
-      <c r="J22" s="1"/>
-      <c r="K22">
+      <c r="K22" s="1"/>
+      <c r="L22">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1">
+    <row r="23" spans="1:12" ht="15" customHeight="1">
       <c r="A23" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B23" t="s">
         <v>132</v>
@@ -4667,97 +4935,106 @@
         <v>2019</v>
       </c>
       <c r="D23" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E23" t="s">
-        <v>144</v>
-      </c>
-      <c r="F23" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F23">
+        <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>130</v>
-      </c>
-      <c r="H23" t="s">
+        <v>136</v>
+      </c>
+      <c r="H23">
+        <v>256</v>
+      </c>
+      <c r="I23" t="s">
         <v>131</v>
       </c>
-      <c r="I23" s="19">
+      <c r="J23" s="19">
         <v>300</v>
       </c>
-      <c r="J23" s="1"/>
-      <c r="K23">
+      <c r="K23" s="1"/>
+      <c r="L23">
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1">
+    <row r="24" spans="1:12" ht="15" customHeight="1">
       <c r="A24" t="s">
         <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C24">
         <v>2015</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E24" t="s">
-        <v>144</v>
-      </c>
-      <c r="F24" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F24">
+        <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>130</v>
-      </c>
-      <c r="H24" t="s">
+        <v>136</v>
+      </c>
+      <c r="H24">
+        <v>256</v>
+      </c>
+      <c r="I24" t="s">
         <v>131</v>
       </c>
-      <c r="I24" s="19">
+      <c r="J24" s="19">
         <v>255</v>
       </c>
-      <c r="J24" s="1"/>
-      <c r="K24">
+      <c r="K24" s="1"/>
+      <c r="L24">
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1">
+    <row r="25" spans="1:12" ht="15" customHeight="1">
       <c r="A25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C25">
         <v>2018</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
-      </c>
-      <c r="F25" t="s">
-        <v>137</v>
+        <v>129</v>
+      </c>
+      <c r="F25">
+        <v>8</v>
       </c>
       <c r="G25" t="s">
-        <v>130</v>
-      </c>
-      <c r="H25" t="s">
+        <v>136</v>
+      </c>
+      <c r="H25">
+        <v>256</v>
+      </c>
+      <c r="I25" t="s">
         <v>131</v>
       </c>
-      <c r="I25" s="19">
+      <c r="J25" s="19">
         <v>175</v>
       </c>
-      <c r="J25" s="1"/>
-      <c r="K25">
+      <c r="K25" s="1"/>
+      <c r="L25">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15" customHeight="1">
+    <row r="26" spans="1:12" ht="15" customHeight="1">
       <c r="A26" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s">
         <v>132</v>
@@ -4766,29 +5043,32 @@
         <v>2017</v>
       </c>
       <c r="D26" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E26" t="s">
-        <v>128</v>
-      </c>
-      <c r="F26" t="s">
-        <v>137</v>
+        <v>129</v>
+      </c>
+      <c r="F26">
+        <v>8</v>
       </c>
       <c r="G26" t="s">
-        <v>130</v>
-      </c>
-      <c r="H26" t="s">
+        <v>136</v>
+      </c>
+      <c r="H26">
+        <v>256</v>
+      </c>
+      <c r="I26" t="s">
         <v>131</v>
       </c>
-      <c r="I26" s="19">
+      <c r="J26" s="19">
         <v>150</v>
       </c>
-      <c r="J26" s="1"/>
-      <c r="K26">
+      <c r="K26" s="1"/>
+      <c r="L26">
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1">
+    <row r="27" spans="1:12" ht="15" customHeight="1">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -4799,62 +5079,68 @@
         <v>2017</v>
       </c>
       <c r="D27" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E27" t="s">
-        <v>144</v>
-      </c>
-      <c r="F27" t="s">
-        <v>137</v>
+        <v>143</v>
+      </c>
+      <c r="F27">
+        <v>8</v>
       </c>
       <c r="G27" t="s">
-        <v>130</v>
-      </c>
-      <c r="H27" t="s">
+        <v>136</v>
+      </c>
+      <c r="H27">
+        <v>256</v>
+      </c>
+      <c r="I27" t="s">
         <v>131</v>
       </c>
-      <c r="I27" s="19">
+      <c r="J27" s="19">
         <v>200</v>
       </c>
-      <c r="J27" s="1"/>
-      <c r="K27">
+      <c r="K27" s="1"/>
+      <c r="L27">
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1">
+    <row r="28" spans="1:12" ht="15" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>71</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C28">
         <v>2013</v>
       </c>
       <c r="D28" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E28" t="s">
-        <v>128</v>
-      </c>
-      <c r="F28" t="s">
-        <v>134</v>
+        <v>129</v>
+      </c>
+      <c r="F28">
+        <v>8</v>
       </c>
       <c r="G28" t="s">
         <v>130</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28">
+        <v>256</v>
+      </c>
+      <c r="I28" t="s">
         <v>131</v>
       </c>
-      <c r="I28" s="19">
+      <c r="J28" s="19">
         <v>200</v>
       </c>
-      <c r="J28" s="1"/>
-      <c r="K28">
+      <c r="K28" s="1"/>
+      <c r="L28">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15" customHeight="1">
+    <row r="29" spans="1:12" ht="15" customHeight="1">
       <c r="A29" t="s">
         <v>55</v>
       </c>
@@ -4865,76 +5151,159 @@
         <v>2018</v>
       </c>
       <c r="D29" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E29" t="s">
-        <v>144</v>
-      </c>
-      <c r="F29" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F29">
+        <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>130</v>
-      </c>
-      <c r="H29" t="s">
+        <v>136</v>
+      </c>
+      <c r="H29">
+        <v>256</v>
+      </c>
+      <c r="I29" t="s">
         <v>131</v>
       </c>
-      <c r="I29" s="19">
+      <c r="J29" s="19">
         <v>325</v>
       </c>
-      <c r="J29" s="1"/>
-      <c r="K29">
+      <c r="K29" s="1"/>
+      <c r="L29">
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15" customHeight="1">
-      <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="1:11" ht="15" customHeight="1">
-      <c r="J31" s="1"/>
-    </row>
-    <row r="32" spans="1:11" ht="15" customHeight="1">
-      <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="10:10" ht="15" customHeight="1">
-      <c r="J33" s="1"/>
+    <row r="30" spans="1:12" ht="15" customHeight="1">
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" spans="1:12" ht="15" customHeight="1">
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" spans="1:12" ht="15" customHeight="1">
+      <c r="K32" s="1"/>
+    </row>
+    <row r="33" spans="11:11" ht="15" customHeight="1">
+      <c r="K33" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:J9 A11:J14 A15:C15 E15:J15 A16:J25">
-    <cfRule type="expression" dxfId="14" priority="5">
+  <conditionalFormatting sqref="A15:C15 A3:K9 A11:K14 E15:K15 A16:K25">
+    <cfRule type="expression" dxfId="43" priority="21">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:K9 A11:K14 A15:C15 E15:K15 A16:K25">
-    <cfRule type="expression" dxfId="13" priority="6">
+  <conditionalFormatting sqref="A15:C15 A3:L9 A11:L14 E15:L15 A16:L25">
+    <cfRule type="expression" dxfId="42" priority="22">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
-    <cfRule type="expression" dxfId="12" priority="4">
+    <cfRule type="expression" dxfId="41" priority="20">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
-    <cfRule type="expression" dxfId="11" priority="3">
+    <cfRule type="expression" dxfId="40" priority="19">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28">
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="39" priority="18">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="38" priority="17">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G28">
+    <cfRule type="expression" dxfId="37" priority="15">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28">
+    <cfRule type="expression" dxfId="36" priority="16">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="expression" dxfId="35" priority="13">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="expression" dxfId="34" priority="14">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27">
+    <cfRule type="expression" dxfId="33" priority="11">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27">
+    <cfRule type="expression" dxfId="32" priority="12">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
+    <cfRule type="expression" dxfId="31" priority="9">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
+    <cfRule type="expression" dxfId="30" priority="10">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26">
+    <cfRule type="expression" dxfId="29" priority="7">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26">
+    <cfRule type="expression" dxfId="28" priority="8">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="expression" dxfId="27" priority="5">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="expression" dxfId="26" priority="6">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
+    <cfRule type="expression" dxfId="25" priority="3">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
+    <cfRule type="expression" dxfId="24" priority="4">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="expression" dxfId="23" priority="1">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K12:K25 K3:K4" xr:uid="{BD4480FF-AB8D-4446-AB7A-01C4C2A99ADB}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12:L25 L3:L4" xr:uid="{BD4480FF-AB8D-4446-AB7A-01C4C2A99ADB}">
       <formula1>1</formula1>
       <formula2>2000</formula2>
     </dataValidation>
@@ -4951,7 +5320,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19592962-4FD3-47C5-914B-6346C180BC2C}">
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
@@ -4960,19 +5329,20 @@
     <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.28515625" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" style="16" customWidth="1"/>
-    <col min="12" max="12" width="29.140625" customWidth="1"/>
-    <col min="13" max="13" width="27.7109375" customWidth="1"/>
-    <col min="14" max="14" width="28.28515625" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.28515625" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" style="16" customWidth="1"/>
+    <col min="13" max="13" width="29.140625" customWidth="1"/>
+    <col min="14" max="14" width="27.7109375" customWidth="1"/>
+    <col min="15" max="15" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" customHeight="1">
+    <row r="1" spans="1:15" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
@@ -4980,18 +5350,19 @@
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
       <c r="H1" s="18"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="18"/>
-      <c r="M1" t="s">
-        <v>170</v>
-      </c>
+      <c r="I1" s="18"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="18"/>
       <c r="N1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>166</v>
+      </c>
+      <c r="O1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -5016,135 +5387,138 @@
       <c r="H2" t="s">
         <v>122</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" t="s">
         <v>123</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="M2" t="s">
+        <v>169</v>
+      </c>
+      <c r="N2" s="2">
+        <f>SUM(J3:J38)</f>
+        <v>9870</v>
+      </c>
+      <c r="O2">
+        <f>COUNTIF(M3:M42,"*International*")</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J3" s="19">
+        <v>225</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="15">
+        <v>45970</v>
+      </c>
+      <c r="M3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>170</v>
+      </c>
+      <c r="J4" s="19">
+        <v>225</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="15">
+        <v>45970</v>
+      </c>
+      <c r="M4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>170</v>
+      </c>
+      <c r="J5" s="19">
+        <v>225</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="15">
+        <v>45970</v>
+      </c>
+      <c r="M5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>170</v>
+      </c>
+      <c r="J6" s="19">
+        <v>225</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="15">
+        <v>45970</v>
+      </c>
+      <c r="M6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>170</v>
+      </c>
+      <c r="J7" s="19">
+        <v>225</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="15">
+        <v>45970</v>
+      </c>
+      <c r="M7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>170</v>
+      </c>
+      <c r="J8" s="19">
+        <v>225</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="15">
+        <v>45970</v>
+      </c>
+      <c r="M8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>170</v>
+      </c>
+      <c r="J9" s="19">
+        <v>225</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="15">
+        <v>45970</v>
+      </c>
+      <c r="M9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
         <v>172</v>
-      </c>
-      <c r="L2" t="s">
-        <v>173</v>
-      </c>
-      <c r="M2" s="2">
-        <f>SUM(I3:I38)</f>
-        <v>9870</v>
-      </c>
-      <c r="N2">
-        <f>COUNTIF(L3:L42,"*International*")</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I3" s="19">
-        <v>225</v>
-      </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="15">
-        <v>45970</v>
-      </c>
-      <c r="L3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>174</v>
-      </c>
-      <c r="I4" s="19">
-        <v>225</v>
-      </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="15">
-        <v>45970</v>
-      </c>
-      <c r="L4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>174</v>
-      </c>
-      <c r="I5" s="19">
-        <v>225</v>
-      </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="15">
-        <v>45970</v>
-      </c>
-      <c r="L5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>174</v>
-      </c>
-      <c r="I6" s="19">
-        <v>225</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="15">
-        <v>45970</v>
-      </c>
-      <c r="L6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>174</v>
-      </c>
-      <c r="I7" s="19">
-        <v>225</v>
-      </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="15">
-        <v>45970</v>
-      </c>
-      <c r="L7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>174</v>
-      </c>
-      <c r="I8" s="19">
-        <v>225</v>
-      </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="15">
-        <v>45970</v>
-      </c>
-      <c r="L8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>174</v>
-      </c>
-      <c r="I9" s="19">
-        <v>225</v>
-      </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="15">
-        <v>45970</v>
-      </c>
-      <c r="L9" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>176</v>
       </c>
       <c r="B10" t="s">
         <v>132</v>
@@ -5153,34 +5527,37 @@
         <v>2018</v>
       </c>
       <c r="D10" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E10" t="s">
-        <v>144</v>
-      </c>
-      <c r="F10" t="s">
-        <v>178</v>
+        <v>143</v>
+      </c>
+      <c r="F10">
+        <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>130</v>
-      </c>
-      <c r="H10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10">
+        <v>256</v>
+      </c>
+      <c r="I10" t="s">
         <v>131</v>
       </c>
-      <c r="I10" s="21">
+      <c r="J10" s="21">
         <v>325</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="15">
+      <c r="K10" s="3"/>
+      <c r="L10" s="15">
         <v>45999</v>
       </c>
-      <c r="L10" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="M10" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B11" t="s">
         <v>132</v>
@@ -5189,34 +5566,37 @@
         <v>2015</v>
       </c>
       <c r="D11" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E11" t="s">
-        <v>144</v>
-      </c>
-      <c r="F11" t="s">
-        <v>181</v>
+        <v>143</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
       </c>
       <c r="G11" t="s">
         <v>130</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11">
+        <v>256</v>
+      </c>
+      <c r="I11" t="s">
         <v>131</v>
       </c>
-      <c r="I11" s="19">
+      <c r="J11" s="19">
         <v>225</v>
       </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="15">
+      <c r="K11" s="2"/>
+      <c r="L11" s="15">
         <v>45999</v>
       </c>
-      <c r="L11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="M11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B12" t="s">
         <v>132</v>
@@ -5225,36 +5605,39 @@
         <v>2014</v>
       </c>
       <c r="D12" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E12" t="s">
-        <v>128</v>
-      </c>
-      <c r="F12" t="s">
-        <v>181</v>
+        <v>129</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
       </c>
       <c r="G12" t="s">
         <v>130</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12">
+        <v>256</v>
+      </c>
+      <c r="I12" t="s">
         <v>131</v>
       </c>
-      <c r="I12" s="19">
+      <c r="J12" s="19">
         <v>175</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="K12" s="15">
+      <c r="K12" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="L12" s="15">
         <v>45999</v>
       </c>
-      <c r="L12" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="M12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B13" t="s">
         <v>132</v>
@@ -5263,34 +5646,37 @@
         <v>2019</v>
       </c>
       <c r="D13" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E13" t="s">
-        <v>144</v>
-      </c>
-      <c r="F13" t="s">
-        <v>178</v>
+        <v>143</v>
+      </c>
+      <c r="F13">
+        <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>130</v>
-      </c>
-      <c r="H13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H13">
+        <v>256</v>
+      </c>
+      <c r="I13" t="s">
         <v>131</v>
       </c>
-      <c r="I13" s="19">
+      <c r="J13" s="19">
         <v>325</v>
       </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="15">
+      <c r="K13" s="2"/>
+      <c r="L13" s="15">
         <v>45999</v>
       </c>
-      <c r="L13" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="M13" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s">
         <v>132</v>
@@ -5299,34 +5685,37 @@
         <v>2018</v>
       </c>
       <c r="D14" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E14" t="s">
-        <v>144</v>
-      </c>
-      <c r="F14" t="s">
-        <v>187</v>
+        <v>143</v>
+      </c>
+      <c r="F14">
+        <v>16</v>
       </c>
       <c r="G14" t="s">
-        <v>130</v>
-      </c>
-      <c r="H14" t="s">
+        <v>136</v>
+      </c>
+      <c r="H14">
+        <v>256</v>
+      </c>
+      <c r="I14" t="s">
         <v>131</v>
       </c>
-      <c r="I14" s="19">
+      <c r="J14" s="19">
         <v>325</v>
       </c>
-      <c r="J14" s="2"/>
-      <c r="K14" s="15">
+      <c r="K14" s="2"/>
+      <c r="L14" s="15">
         <v>45999</v>
       </c>
-      <c r="L14" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="M14" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s">
         <v>132</v>
@@ -5335,476 +5724,515 @@
         <v>2021</v>
       </c>
       <c r="D15" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="E15" t="s">
-        <v>144</v>
-      </c>
-      <c r="F15" t="s">
-        <v>190</v>
+        <v>143</v>
+      </c>
+      <c r="F15">
+        <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>130</v>
-      </c>
-      <c r="H15" t="s">
+        <v>136</v>
+      </c>
+      <c r="H15">
+        <v>256</v>
+      </c>
+      <c r="I15" t="s">
         <v>131</v>
       </c>
-      <c r="I15" s="19">
+      <c r="J15" s="19">
         <v>205</v>
       </c>
-      <c r="J15" s="2"/>
-      <c r="K15" s="15">
+      <c r="K15" s="2"/>
+      <c r="L15" s="15">
         <v>45999</v>
       </c>
-      <c r="L15" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="M15" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C16">
         <v>2012</v>
       </c>
       <c r="D16" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E16" t="s">
-        <v>194</v>
-      </c>
-      <c r="F16" t="s">
-        <v>193</v>
+        <v>186</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>195</v>
-      </c>
-      <c r="H16" t="s">
-        <v>196</v>
-      </c>
-      <c r="I16" s="19">
+        <v>187</v>
+      </c>
+      <c r="H16" s="1">
+        <v>64</v>
+      </c>
+      <c r="I16" t="s">
+        <v>188</v>
+      </c>
+      <c r="J16" s="19">
         <v>50</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="K16" s="15">
+      <c r="K16" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="L16" s="15">
         <v>45999</v>
       </c>
-      <c r="L16" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C17">
         <v>2014</v>
       </c>
       <c r="D17" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E17" t="s">
-        <v>199</v>
-      </c>
-      <c r="F17" t="s">
-        <v>193</v>
+        <v>186</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>200</v>
-      </c>
-      <c r="H17" t="s">
-        <v>196</v>
-      </c>
-      <c r="I17" s="19">
+        <v>130</v>
+      </c>
+      <c r="H17">
+        <v>128</v>
+      </c>
+      <c r="I17" t="s">
+        <v>188</v>
+      </c>
+      <c r="J17" s="19">
         <v>60</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="K17" s="15">
+      <c r="K17" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="L17" s="15">
         <v>45999</v>
       </c>
-      <c r="L17" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="M17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C18">
         <v>2018</v>
       </c>
       <c r="D18" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="E18" t="s">
-        <v>144</v>
-      </c>
-      <c r="F18" t="s">
-        <v>137</v>
+        <v>143</v>
+      </c>
+      <c r="F18">
+        <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>130</v>
-      </c>
-      <c r="H18" t="s">
+        <v>136</v>
+      </c>
+      <c r="H18">
+        <v>256</v>
+      </c>
+      <c r="I18" t="s">
         <v>131</v>
       </c>
-      <c r="I18" s="19">
+      <c r="J18" s="19">
         <v>250</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="K18" s="16">
+      <c r="K18" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="L18" s="16">
         <v>46043</v>
       </c>
-      <c r="L18" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="M18" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C19">
         <v>2013</v>
       </c>
       <c r="D19" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="E19" t="s">
-        <v>128</v>
-      </c>
-      <c r="F19" t="s">
-        <v>134</v>
+        <v>129</v>
+      </c>
+      <c r="F19">
+        <v>8</v>
       </c>
       <c r="G19" t="s">
         <v>130</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19">
+        <v>256</v>
+      </c>
+      <c r="I19" t="s">
         <v>131</v>
       </c>
-      <c r="I19" s="19">
+      <c r="J19" s="19">
         <v>290</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="K19" s="16">
+      <c r="K19" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L19" s="16">
         <v>46043</v>
       </c>
-      <c r="L19" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="45">
+      <c r="M19" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="43.5">
       <c r="A20" t="s">
         <v>68</v>
       </c>
       <c r="B20" t="s">
-        <v>207</v>
+        <v>127</v>
       </c>
       <c r="C20">
         <v>2016</v>
       </c>
       <c r="D20" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="E20" t="s">
-        <v>128</v>
-      </c>
-      <c r="F20" t="s">
-        <v>161</v>
+        <v>129</v>
+      </c>
+      <c r="F20">
+        <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>130</v>
-      </c>
-      <c r="H20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H20">
+        <v>256</v>
+      </c>
+      <c r="I20" t="s">
         <v>131</v>
       </c>
-      <c r="I20" s="19">
+      <c r="J20" s="19">
         <v>300</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="K20" s="15">
+      <c r="K20" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L20" s="15">
         <v>46056</v>
       </c>
-      <c r="L20" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="M20" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C21">
         <v>2013</v>
       </c>
       <c r="D21" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="E21" t="s">
-        <v>128</v>
-      </c>
-      <c r="F21" t="s">
-        <v>134</v>
+        <v>129</v>
+      </c>
+      <c r="F21">
+        <v>8</v>
       </c>
       <c r="G21" t="s">
         <v>130</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21">
+        <v>256</v>
+      </c>
+      <c r="I21" t="s">
         <v>131</v>
       </c>
-      <c r="I21" s="19">
+      <c r="J21" s="19">
         <v>200</v>
       </c>
-      <c r="J21" s="1"/>
-      <c r="K21" s="15">
+      <c r="K21" s="1"/>
+      <c r="L21" s="15">
         <v>46056</v>
       </c>
-      <c r="L21" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="M21" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C22">
         <v>2013</v>
       </c>
       <c r="D22" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E22" t="s">
-        <v>128</v>
-      </c>
-      <c r="F22" t="s">
-        <v>134</v>
+        <v>129</v>
+      </c>
+      <c r="F22">
+        <v>8</v>
       </c>
       <c r="G22" t="s">
         <v>130</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22">
+        <v>256</v>
+      </c>
+      <c r="I22" t="s">
         <v>131</v>
       </c>
-      <c r="I22" s="19">
+      <c r="J22" s="19">
         <v>200</v>
       </c>
-      <c r="J22" s="1"/>
-      <c r="K22" s="15">
+      <c r="K22" s="1"/>
+      <c r="L22" s="15">
         <v>46056</v>
       </c>
-      <c r="L22" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="M22" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>71</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C23">
         <v>2013</v>
       </c>
       <c r="D23" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E23" t="s">
-        <v>128</v>
-      </c>
-      <c r="F23" t="s">
-        <v>134</v>
+        <v>129</v>
+      </c>
+      <c r="F23">
+        <v>8</v>
       </c>
       <c r="G23" t="s">
         <v>130</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23">
+        <v>256</v>
+      </c>
+      <c r="I23" t="s">
         <v>131</v>
       </c>
-      <c r="I23" s="19">
+      <c r="J23" s="19">
         <v>200</v>
       </c>
-      <c r="J23" s="1"/>
-      <c r="K23" s="15">
+      <c r="K23" s="1"/>
+      <c r="L23" s="15">
         <v>46056</v>
       </c>
-      <c r="L23" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="M23" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
         <v>71</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C24">
         <v>2013</v>
       </c>
       <c r="D24" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E24" t="s">
-        <v>128</v>
-      </c>
-      <c r="F24" t="s">
-        <v>134</v>
+        <v>129</v>
+      </c>
+      <c r="F24">
+        <v>8</v>
       </c>
       <c r="G24" t="s">
         <v>130</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24">
+        <v>256</v>
+      </c>
+      <c r="I24" t="s">
         <v>131</v>
       </c>
-      <c r="I24" s="19">
+      <c r="J24" s="19">
         <v>200</v>
       </c>
-      <c r="J24" s="1"/>
-      <c r="K24" s="15">
+      <c r="K24" s="1"/>
+      <c r="L24" s="15">
         <v>46056</v>
       </c>
-      <c r="L24" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="M24" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
         <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C25">
         <v>2013</v>
       </c>
       <c r="D25" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
-      </c>
-      <c r="F25" t="s">
-        <v>214</v>
+        <v>129</v>
+      </c>
+      <c r="F25">
+        <v>16</v>
       </c>
       <c r="G25" t="s">
         <v>130</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25">
+        <v>256</v>
+      </c>
+      <c r="I25" t="s">
         <v>131</v>
       </c>
-      <c r="I25" s="19">
+      <c r="J25" s="19">
         <v>200</v>
       </c>
-      <c r="J25" s="1"/>
-      <c r="K25" s="15">
+      <c r="K25" s="1"/>
+      <c r="L25" s="15">
         <v>46056</v>
       </c>
-      <c r="L25" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="M25" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
         <v>68</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C26">
         <v>2016</v>
       </c>
       <c r="D26" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="E26" t="s">
-        <v>128</v>
-      </c>
-      <c r="F26" t="s">
-        <v>161</v>
+        <v>129</v>
+      </c>
+      <c r="F26">
+        <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>130</v>
-      </c>
-      <c r="H26" t="s">
+        <v>136</v>
+      </c>
+      <c r="H26">
+        <v>256</v>
+      </c>
+      <c r="I26" t="s">
         <v>131</v>
       </c>
-      <c r="I26" s="19">
+      <c r="J26" s="19">
         <v>300</v>
       </c>
-      <c r="J26" s="1"/>
-      <c r="K26" s="15">
+      <c r="K26" s="1"/>
+      <c r="L26" s="15">
         <v>46056</v>
       </c>
-      <c r="L26" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="M26" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
         <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C27">
         <v>2016</v>
       </c>
       <c r="D27" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="E27" t="s">
-        <v>128</v>
-      </c>
-      <c r="F27" t="s">
-        <v>134</v>
+        <v>129</v>
+      </c>
+      <c r="F27">
+        <v>8</v>
       </c>
       <c r="G27" t="s">
         <v>130</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27">
+        <v>256</v>
+      </c>
+      <c r="I27" t="s">
         <v>131</v>
       </c>
-      <c r="I27" s="19">
+      <c r="J27" s="19">
         <v>300</v>
       </c>
-      <c r="J27" s="1"/>
-      <c r="K27" s="15">
+      <c r="K27" s="1"/>
+      <c r="L27" s="15">
         <v>46056</v>
       </c>
-      <c r="L27" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="M27" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B28" t="s">
         <v>132</v>
@@ -5813,34 +6241,37 @@
         <v>2018</v>
       </c>
       <c r="D28" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E28" t="s">
-        <v>144</v>
-      </c>
-      <c r="F28" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F28">
+        <v>16</v>
       </c>
       <c r="G28" t="s">
-        <v>217</v>
-      </c>
-      <c r="H28" t="s">
+        <v>136</v>
+      </c>
+      <c r="H28">
+        <v>512</v>
+      </c>
+      <c r="I28" t="s">
         <v>131</v>
       </c>
-      <c r="I28" s="19">
+      <c r="J28" s="19">
         <v>445</v>
       </c>
-      <c r="J28" s="1"/>
-      <c r="K28" s="15">
+      <c r="K28" s="1"/>
+      <c r="L28" s="15">
         <v>46056</v>
       </c>
-      <c r="L28" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="M28" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B29" t="s">
         <v>132</v>
@@ -5849,176 +6280,191 @@
         <v>2018</v>
       </c>
       <c r="D29" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E29" t="s">
-        <v>144</v>
-      </c>
-      <c r="F29" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F29">
+        <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>217</v>
-      </c>
-      <c r="H29" t="s">
+        <v>136</v>
+      </c>
+      <c r="H29">
+        <v>512</v>
+      </c>
+      <c r="I29" t="s">
         <v>131</v>
       </c>
-      <c r="I29" s="19">
+      <c r="J29" s="19">
         <v>445</v>
       </c>
-      <c r="J29" s="1"/>
-      <c r="K29" s="15">
+      <c r="K29" s="1"/>
+      <c r="L29" s="15">
         <v>46056</v>
       </c>
-      <c r="L29" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="M29" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B30" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="C30">
         <v>2018</v>
       </c>
       <c r="D30" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="E30" t="s">
-        <v>128</v>
-      </c>
-      <c r="F30" t="s">
-        <v>137</v>
+        <v>129</v>
+      </c>
+      <c r="F30">
+        <v>8</v>
       </c>
       <c r="G30" t="s">
-        <v>130</v>
-      </c>
-      <c r="H30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H30">
+        <v>256</v>
+      </c>
+      <c r="I30" t="s">
         <v>131</v>
       </c>
-      <c r="I30" s="19">
+      <c r="J30" s="19">
         <v>150</v>
       </c>
-      <c r="J30" s="1"/>
-      <c r="K30" s="15">
+      <c r="K30" s="1"/>
+      <c r="L30" s="15">
         <v>46056</v>
       </c>
-      <c r="L30" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="M30" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="8" t="s">
         <v>68</v>
       </c>
       <c r="B31" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C31">
         <v>2016</v>
       </c>
       <c r="D31" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="E31" t="s">
-        <v>128</v>
-      </c>
-      <c r="F31" t="s">
-        <v>137</v>
+        <v>129</v>
+      </c>
+      <c r="F31">
+        <v>8</v>
       </c>
       <c r="G31" t="s">
-        <v>162</v>
-      </c>
-      <c r="H31" t="s">
-        <v>220</v>
-      </c>
-      <c r="I31" s="19">
+        <v>136</v>
+      </c>
+      <c r="H31">
+        <v>500</v>
+      </c>
+      <c r="I31" t="s">
+        <v>206</v>
+      </c>
+      <c r="J31" s="19">
         <v>300</v>
       </c>
-      <c r="J31" s="1"/>
-      <c r="K31" s="16">
+      <c r="K31" s="1"/>
+      <c r="L31" s="16">
         <v>46058</v>
       </c>
-      <c r="L31" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="M31" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" t="s">
         <v>68</v>
       </c>
       <c r="B32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C32">
         <v>2016</v>
       </c>
       <c r="D32" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="E32" t="s">
-        <v>128</v>
-      </c>
-      <c r="F32" t="s">
-        <v>137</v>
+        <v>129</v>
+      </c>
+      <c r="F32">
+        <v>8</v>
       </c>
       <c r="G32" t="s">
-        <v>130</v>
-      </c>
-      <c r="H32" t="s">
+        <v>136</v>
+      </c>
+      <c r="H32">
+        <v>256</v>
+      </c>
+      <c r="I32" t="s">
         <v>131</v>
       </c>
-      <c r="I32" s="19">
+      <c r="J32" s="19">
         <v>300</v>
       </c>
-      <c r="K32" s="16">
+      <c r="L32" s="16">
         <v>46058</v>
       </c>
-      <c r="L32" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
+      <c r="M32" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" t="s">
         <v>68</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C33">
         <v>2016</v>
       </c>
       <c r="D33" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="E33" t="s">
-        <v>128</v>
-      </c>
-      <c r="F33" t="s">
-        <v>137</v>
+        <v>129</v>
+      </c>
+      <c r="F33">
+        <v>8</v>
       </c>
       <c r="G33" t="s">
-        <v>130</v>
-      </c>
-      <c r="H33" t="s">
+        <v>136</v>
+      </c>
+      <c r="H33">
+        <v>256</v>
+      </c>
+      <c r="I33" t="s">
         <v>131</v>
       </c>
-      <c r="I33" s="19">
+      <c r="J33" s="19">
         <v>300</v>
       </c>
-      <c r="K33" s="16">
+      <c r="L33" s="16">
         <v>46058</v>
       </c>
-      <c r="L33" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="M33" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B34" t="s">
         <v>132</v>
@@ -6027,33 +6473,36 @@
         <v>2020</v>
       </c>
       <c r="D34" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E34" t="s">
-        <v>144</v>
-      </c>
-      <c r="F34" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F34">
+        <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>217</v>
-      </c>
-      <c r="H34" t="s">
+        <v>136</v>
+      </c>
+      <c r="H34">
+        <v>512</v>
+      </c>
+      <c r="I34" t="s">
         <v>131</v>
       </c>
-      <c r="I34" s="19">
+      <c r="J34" s="19">
         <v>445</v>
       </c>
-      <c r="K34" s="16">
+      <c r="L34" s="16">
         <v>46058</v>
       </c>
-      <c r="L34" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="M34" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B35" t="s">
         <v>132</v>
@@ -6062,33 +6511,36 @@
         <v>2020</v>
       </c>
       <c r="D35" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E35" t="s">
-        <v>144</v>
-      </c>
-      <c r="F35" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F35">
+        <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>217</v>
-      </c>
-      <c r="H35" t="s">
+        <v>136</v>
+      </c>
+      <c r="H35">
+        <v>512</v>
+      </c>
+      <c r="I35" t="s">
         <v>131</v>
       </c>
-      <c r="I35" s="19">
+      <c r="J35" s="19">
         <v>445</v>
       </c>
-      <c r="K35" s="16">
+      <c r="L35" s="16">
         <v>46058</v>
       </c>
-      <c r="L35" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="M35" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B36" t="s">
         <v>132</v>
@@ -6097,33 +6549,36 @@
         <v>2020</v>
       </c>
       <c r="D36" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E36" t="s">
-        <v>144</v>
-      </c>
-      <c r="F36" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F36">
+        <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>217</v>
-      </c>
-      <c r="H36" t="s">
+        <v>136</v>
+      </c>
+      <c r="H36">
+        <v>512</v>
+      </c>
+      <c r="I36" t="s">
         <v>131</v>
       </c>
-      <c r="I36" s="19">
+      <c r="J36" s="19">
         <v>445</v>
       </c>
-      <c r="K36" s="16">
+      <c r="L36" s="16">
         <v>46058</v>
       </c>
-      <c r="L36" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
+      <c r="M36" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B37" t="s">
         <v>132</v>
@@ -6132,33 +6587,36 @@
         <v>2020</v>
       </c>
       <c r="D37" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E37" t="s">
-        <v>144</v>
-      </c>
-      <c r="F37" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F37">
+        <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>217</v>
-      </c>
-      <c r="H37" t="s">
+        <v>136</v>
+      </c>
+      <c r="H37">
+        <v>512</v>
+      </c>
+      <c r="I37" t="s">
         <v>131</v>
       </c>
-      <c r="I37" s="19">
+      <c r="J37" s="19">
         <v>445</v>
       </c>
-      <c r="K37" s="16">
+      <c r="L37" s="16">
         <v>46058</v>
       </c>
-      <c r="L37" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="M37" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B38" t="s">
         <v>132</v>
@@ -6167,33 +6625,36 @@
         <v>2020</v>
       </c>
       <c r="D38" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E38" t="s">
-        <v>144</v>
-      </c>
-      <c r="F38" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F38">
+        <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>217</v>
-      </c>
-      <c r="H38" t="s">
+        <v>136</v>
+      </c>
+      <c r="H38">
+        <v>512</v>
+      </c>
+      <c r="I38" t="s">
         <v>131</v>
       </c>
-      <c r="I38" s="19">
+      <c r="J38" s="19">
         <v>445</v>
       </c>
-      <c r="K38" s="16">
+      <c r="L38" s="16">
         <v>46058</v>
       </c>
-      <c r="L38" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="M38" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B39" t="s">
         <v>132</v>
@@ -6202,33 +6663,36 @@
         <v>2020</v>
       </c>
       <c r="D39" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E39" t="s">
-        <v>144</v>
-      </c>
-      <c r="F39" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F39">
+        <v>16</v>
       </c>
       <c r="G39" t="s">
-        <v>217</v>
-      </c>
-      <c r="H39" t="s">
+        <v>136</v>
+      </c>
+      <c r="H39">
+        <v>512</v>
+      </c>
+      <c r="I39" t="s">
         <v>131</v>
       </c>
-      <c r="I39" s="19">
+      <c r="J39" s="19">
         <v>445</v>
       </c>
-      <c r="K39" s="16">
+      <c r="L39" s="16">
         <v>46058</v>
       </c>
-      <c r="L39" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="15" customHeight="1">
+      <c r="M39" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15" customHeight="1">
       <c r="A40" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B40" t="s">
         <v>132</v>
@@ -6237,33 +6701,36 @@
         <v>2020</v>
       </c>
       <c r="D40" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E40" t="s">
-        <v>144</v>
-      </c>
-      <c r="F40" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F40">
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>217</v>
-      </c>
-      <c r="H40" t="s">
+        <v>136</v>
+      </c>
+      <c r="H40">
+        <v>512</v>
+      </c>
+      <c r="I40" t="s">
         <v>131</v>
       </c>
-      <c r="I40" s="19">
+      <c r="J40" s="19">
         <v>445</v>
       </c>
-      <c r="K40" s="16">
+      <c r="L40" s="16">
         <v>46058</v>
       </c>
-      <c r="L40" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="15" customHeight="1">
+      <c r="M40" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="15" customHeight="1">
       <c r="A41" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B41" t="s">
         <v>132</v>
@@ -6272,33 +6739,36 @@
         <v>2020</v>
       </c>
       <c r="D41" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E41" t="s">
-        <v>144</v>
-      </c>
-      <c r="F41" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F41">
+        <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>217</v>
-      </c>
-      <c r="H41" t="s">
+        <v>136</v>
+      </c>
+      <c r="H41">
+        <v>512</v>
+      </c>
+      <c r="I41" t="s">
         <v>131</v>
       </c>
-      <c r="I41" s="19">
+      <c r="J41" s="19">
         <v>445</v>
       </c>
-      <c r="K41" s="16">
+      <c r="L41" s="16">
         <v>46058</v>
       </c>
-      <c r="L41" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="15" customHeight="1">
+      <c r="M41" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="15" customHeight="1">
       <c r="A42" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B42" t="s">
         <v>132</v>
@@ -6307,33 +6777,36 @@
         <v>2020</v>
       </c>
       <c r="D42" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E42" t="s">
-        <v>144</v>
-      </c>
-      <c r="F42" t="s">
-        <v>161</v>
+        <v>143</v>
+      </c>
+      <c r="F42">
+        <v>16</v>
       </c>
       <c r="G42" t="s">
-        <v>217</v>
-      </c>
-      <c r="H42" t="s">
+        <v>136</v>
+      </c>
+      <c r="H42">
+        <v>512</v>
+      </c>
+      <c r="I42" t="s">
         <v>131</v>
       </c>
-      <c r="I42" s="19">
+      <c r="J42" s="19">
         <v>445</v>
       </c>
-      <c r="K42" s="16">
+      <c r="L42" s="16">
         <v>46058</v>
       </c>
-      <c r="L42" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="15" customHeight="1">
+      <c r="M42" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="15" customHeight="1">
       <c r="A43" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B43" t="s">
         <v>132</v>
@@ -6342,128 +6815,202 @@
         <v>2018</v>
       </c>
       <c r="D43" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="E43" t="s">
-        <v>144</v>
-      </c>
-      <c r="F43" t="s">
-        <v>137</v>
+        <v>143</v>
+      </c>
+      <c r="F43">
+        <v>8</v>
       </c>
       <c r="G43" t="s">
-        <v>130</v>
-      </c>
-      <c r="H43" t="s">
+        <v>136</v>
+      </c>
+      <c r="H43">
+        <v>256</v>
+      </c>
+      <c r="I43" t="s">
         <v>131</v>
       </c>
-      <c r="I43" s="19">
+      <c r="J43" s="19">
         <v>300</v>
       </c>
-      <c r="J43" s="1"/>
-      <c r="K43" s="16">
+      <c r="K43" s="1"/>
+      <c r="L43" s="16">
         <v>46078</v>
       </c>
-      <c r="L43" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="15" customHeight="1">
+      <c r="M43" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="15" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>68</v>
       </c>
       <c r="B44" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C44" s="5">
         <v>2016</v>
       </c>
       <c r="D44" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E44" t="s">
-        <v>128</v>
-      </c>
-      <c r="F44" t="s">
-        <v>137</v>
+        <v>129</v>
+      </c>
+      <c r="F44">
+        <v>8</v>
       </c>
       <c r="G44" t="s">
-        <v>130</v>
-      </c>
-      <c r="H44" t="s">
+        <v>136</v>
+      </c>
+      <c r="H44">
+        <v>256</v>
+      </c>
+      <c r="I44" t="s">
         <v>131</v>
       </c>
-      <c r="I44" s="19">
+      <c r="J44" s="19">
         <v>300</v>
       </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="16">
+      <c r="K44" s="1"/>
+      <c r="L44" s="16">
         <v>46099</v>
       </c>
-      <c r="L44" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="15" customHeight="1">
-      <c r="K45" s="15"/>
-    </row>
-    <row r="46" spans="1:12" ht="15" customHeight="1">
-      <c r="K46" s="15"/>
-    </row>
-    <row r="47" spans="1:12" ht="15" customHeight="1">
-      <c r="K47" s="15"/>
-    </row>
-    <row r="48" spans="1:12" ht="15" customHeight="1">
-      <c r="K48" s="15"/>
-    </row>
-    <row r="49" spans="11:11" ht="15" customHeight="1">
-      <c r="K49" s="15"/>
-    </row>
-    <row r="50" spans="11:11" ht="15" customHeight="1">
-      <c r="K50" s="15"/>
-    </row>
-    <row r="51" spans="11:11" ht="15" customHeight="1">
-      <c r="K51" s="15"/>
-    </row>
-    <row r="52" spans="11:11" ht="15" customHeight="1">
-      <c r="K52" s="15"/>
-    </row>
-    <row r="53" spans="11:11" ht="15" customHeight="1">
-      <c r="K53" s="15"/>
-    </row>
-    <row r="54" spans="11:11" ht="15" customHeight="1">
-      <c r="K54" s="15"/>
-    </row>
-    <row r="55" spans="11:11" ht="15" customHeight="1">
-      <c r="K55" s="15"/>
-    </row>
-    <row r="56" spans="11:11" ht="15" customHeight="1">
-      <c r="K56" s="15"/>
-    </row>
-    <row r="57" spans="11:11" ht="15" customHeight="1">
-      <c r="K57" s="15"/>
-    </row>
-    <row r="58" spans="11:11" ht="15" customHeight="1">
-      <c r="K58" s="15"/>
-    </row>
-    <row r="59" spans="11:11" ht="15" customHeight="1">
-      <c r="K59" s="15"/>
+      <c r="M44" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="15" customHeight="1">
+      <c r="L45" s="15"/>
+    </row>
+    <row r="46" spans="1:13" ht="15" customHeight="1">
+      <c r="L46" s="15"/>
+    </row>
+    <row r="47" spans="1:13" ht="15" customHeight="1">
+      <c r="L47" s="15"/>
+    </row>
+    <row r="48" spans="1:13" ht="15" customHeight="1">
+      <c r="L48" s="15"/>
+    </row>
+    <row r="49" spans="12:12" ht="15" customHeight="1">
+      <c r="L49" s="15"/>
+    </row>
+    <row r="50" spans="12:12" ht="15" customHeight="1">
+      <c r="L50" s="15"/>
+    </row>
+    <row r="51" spans="12:12" ht="15" customHeight="1">
+      <c r="L51" s="15"/>
+    </row>
+    <row r="52" spans="12:12" ht="15" customHeight="1">
+      <c r="L52" s="15"/>
+    </row>
+    <row r="53" spans="12:12" ht="15" customHeight="1">
+      <c r="L53" s="15"/>
+    </row>
+    <row r="54" spans="12:12" ht="15" customHeight="1">
+      <c r="L54" s="15"/>
+    </row>
+    <row r="55" spans="12:12" ht="15" customHeight="1">
+      <c r="L55" s="15"/>
+    </row>
+    <row r="56" spans="12:12" ht="15" customHeight="1">
+      <c r="L56" s="15"/>
+    </row>
+    <row r="57" spans="12:12" ht="15" customHeight="1">
+      <c r="L57" s="15"/>
+    </row>
+    <row r="58" spans="12:12" ht="15" customHeight="1">
+      <c r="L58" s="15"/>
+    </row>
+    <row r="59" spans="12:12" ht="15" customHeight="1">
+      <c r="L59" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A44:J44">
-    <cfRule type="expression" dxfId="5" priority="1">
+  <conditionalFormatting sqref="A44:F44 H44:K44">
+    <cfRule type="expression" dxfId="18" priority="15">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A44:K44">
-    <cfRule type="expression" dxfId="4" priority="2">
+  <conditionalFormatting sqref="A44:F44 H44:L44">
+    <cfRule type="expression" dxfId="17" priority="16">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:L43 L44 A45:L59">
-    <cfRule type="expression" priority="3">
+  <conditionalFormatting sqref="M44 A45:M59 A3:M9 A10:G15 I10:M15 A16:M43">
+    <cfRule type="expression" priority="17">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="16" priority="18">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G44">
+    <cfRule type="expression" priority="13">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="14">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="expression" dxfId="14" priority="11">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="expression" dxfId="13" priority="12">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="expression" dxfId="12" priority="9">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="expression" dxfId="11" priority="10">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="expression" dxfId="10" priority="7">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="expression" dxfId="9" priority="8">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="expression" dxfId="8" priority="5">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="expression" dxfId="7" priority="6">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
+    <cfRule type="expression" dxfId="6" priority="3">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
+    <cfRule type="expression" dxfId="5" priority="4">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6471,8 +7018,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B17 B19 B21:B29 B31:B42" xr:uid="{1DFA3251-7984-4A3C-A048-50097DB9AAD3}">
       <formula1>"Desktop,Laptop,Tablet,All-In-One"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1 K1:K42 K45:K1048576" xr:uid="{A67DFFE0-1B96-49B5-A6E2-5C17E92A136C}"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J32:J42" xr:uid="{BD4480FF-AB8D-4446-AB7A-01C4C2A99ADB}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M1 L1:L42 L45:L1048576" xr:uid="{A67DFFE0-1B96-49B5-A6E2-5C17E92A136C}"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K32:K42" xr:uid="{BD4480FF-AB8D-4446-AB7A-01C4C2A99ADB}">
       <formula1>1</formula1>
       <formula2>2000</formula2>
     </dataValidation>
@@ -6495,7 +7042,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="23" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B1" s="24"/>
     </row>
@@ -6504,12 +7051,12 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -6517,7 +7064,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="B4">
         <v>9</v>
@@ -6525,7 +7072,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -6533,7 +7080,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -6541,7 +7088,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -6549,7 +7096,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="B8">
         <v>18</v>
@@ -6557,7 +7104,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -6565,7 +7112,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -6573,7 +7120,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="B11">
         <v>16</v>
@@ -6581,7 +7128,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -6589,7 +7136,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -6597,7 +7144,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -6605,7 +7152,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="B15">
         <v>11</v>
@@ -6613,7 +7160,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="B16">
         <v>14</v>
@@ -6621,7 +7168,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="B17">
         <v>17</v>
@@ -6629,7 +7176,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -6637,7 +7184,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="B19">
         <v>2</v>
@@ -6645,7 +7192,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -6653,7 +7200,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -6661,7 +7208,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -6669,7 +7216,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="B23">
         <v>12</v>
@@ -6677,7 +7224,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -6685,7 +7232,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -6693,7 +7240,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -6701,7 +7248,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -6709,7 +7256,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -6717,7 +7264,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B29">
         <v>9</v>
@@ -6725,7 +7272,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -6733,7 +7280,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B31">
         <v>5</v>
@@ -6741,7 +7288,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -6749,7 +7296,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="B33">
         <v>6</v>
@@ -6757,7 +7304,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -6765,7 +7312,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="B35">
         <v>2</v>
@@ -6773,7 +7320,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -6781,7 +7328,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="B37">
         <v>14</v>
@@ -6789,7 +7336,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="B38">
         <v>5</v>
@@ -6797,7 +7344,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="B39">
         <v>2</v>
@@ -6805,7 +7352,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -6813,7 +7360,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -6821,7 +7368,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="B42">
         <v>2</v>
@@ -6829,7 +7376,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -6837,7 +7384,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -6845,7 +7392,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="B45">
         <v>11</v>
@@ -6853,7 +7400,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="B46">
         <v>16</v>
@@ -6861,7 +7408,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="B47">
         <v>6</v>

--- a/data/OldInventorySystem.xlsx
+++ b/data/OldInventorySystem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rosehulman-my.sharepoint.com/personal/lucasja_rose-hulman_edu/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{929C0295-FFF7-4442-A7F8-B9615CC42371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6F62A0D-D864-413C-A038-AF10FB8B133F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="3" activeTab="4" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="4" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Laptops" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="254">
   <si>
     <t>LAPTOPS</t>
   </si>
@@ -76,463 +76,451 @@
     <t>Column1</t>
   </si>
   <si>
+    <t>Lenovo 100e Chromebook 2nd Gen</t>
+  </si>
+  <si>
+    <t>Lenovo</t>
+  </si>
+  <si>
+    <t>ARM, ARM bad, has charger</t>
+  </si>
+  <si>
+    <t>Included</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Toshiba Satellite C655-S5547</t>
+  </si>
+  <si>
+    <t>Toshiba</t>
+  </si>
+  <si>
+    <t>Won't turn on, has missing SSD</t>
+  </si>
+  <si>
+    <t>Apple MacBook Air A1369</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>bv</t>
+  </si>
+  <si>
+    <t>Apple MacBook Air A2179</t>
+  </si>
+  <si>
+    <t>Toshiba Satellite Click W35Dt-A3300</t>
+  </si>
+  <si>
+    <t>Not Included</t>
+  </si>
+  <si>
+    <t>Toshiba Satellite C55t-C5300</t>
+  </si>
+  <si>
+    <t>Dell Precision M6700</t>
+  </si>
+  <si>
+    <t>Dell</t>
+  </si>
+  <si>
+    <t>Samsung 500C Chromebook</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>Dell Inspiron N7110</t>
+  </si>
+  <si>
+    <t>Needs OS installed, need to change to UEFI (if possible)</t>
+  </si>
+  <si>
+    <t>Lenovo Ideapad 3 Chromebook 11AST5</t>
+  </si>
+  <si>
+    <t>Battery issue</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>HP Elitebook 8560p</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>Needs Vanilla but isn't installing easily (Claims to be in legacy mode even after factory reset)</t>
+  </si>
+  <si>
+    <t>HP 15-db0004dx</t>
+  </si>
+  <si>
+    <t>HP ProBook 450 G7</t>
+  </si>
+  <si>
+    <t>Screen does not turn on but power light does, SSD installed</t>
+  </si>
+  <si>
+    <t>ThinkPad P15s Gen 1</t>
+  </si>
+  <si>
+    <t>Thinkpad S230u</t>
+  </si>
+  <si>
+    <t>Might need to scrap 4gb of ram soldered</t>
+  </si>
+  <si>
+    <t>Macbook Pro A1708</t>
+  </si>
+  <si>
+    <t>Surface Pro 1796</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>Windows 11 w/ all updates, battery no work :(</t>
+  </si>
+  <si>
+    <t>Thinkpad Yoga 11e</t>
+  </si>
+  <si>
+    <t>Lenovo Edge 15</t>
+  </si>
+  <si>
+    <t>Dell Precision 5540</t>
+  </si>
+  <si>
+    <t>Broken hinges; attempted to be superglued</t>
+  </si>
+  <si>
+    <t>Acer C731 Series</t>
+  </si>
+  <si>
+    <t>Acer</t>
+  </si>
+  <si>
+    <t>Arc Linux Minecraft Installed</t>
+  </si>
+  <si>
+    <t>DESKTOPS</t>
+  </si>
+  <si>
+    <t>Dell Optiplex 7040</t>
+  </si>
+  <si>
+    <t>Vanilla OS installs but can't boot to it - has SSD</t>
+  </si>
+  <si>
+    <t>Windows 11 installed (somehow, it shouldn't work bc tpm 1.2) should be fully working but needs to be tested</t>
+  </si>
+  <si>
+    <t>Boot issues (no boot device found after installation)</t>
+  </si>
+  <si>
+    <t>Dell Precision Tower 3420</t>
+  </si>
+  <si>
+    <t>Being used as a 2.5" SSD eraser; Tal accidentally ripped the sata power port off the motherboard, so if it doesn't work that's why</t>
+  </si>
+  <si>
+    <t>Has SSD, no bootable device found</t>
+  </si>
+  <si>
+    <t>Dell Optiplex 9020</t>
+  </si>
+  <si>
+    <t>Dell Optiplex 7050</t>
+  </si>
+  <si>
+    <t>Done???</t>
+  </si>
+  <si>
+    <t>Needs SSD and OS install</t>
+  </si>
+  <si>
+    <t>Dell Optiplex 960</t>
+  </si>
+  <si>
+    <t>Dell Optiplex 5060</t>
+  </si>
+  <si>
+    <t>Ram switched out</t>
+  </si>
+  <si>
+    <t>Dell Precision T3600</t>
+  </si>
+  <si>
+    <t>No OS, needs Vanilla; Ready to install</t>
+  </si>
+  <si>
+    <t>Dell Precision 7920</t>
+  </si>
+  <si>
+    <t>Dell Precision 5810</t>
+  </si>
+  <si>
+    <t>Dell Precision 5820</t>
+  </si>
+  <si>
+    <t>HP Ryzen 4000 Desktop</t>
+  </si>
+  <si>
+    <t>Dell OptiPlex 5050 Micro</t>
+  </si>
+  <si>
+    <t>Installed SSD</t>
+  </si>
+  <si>
+    <t>Vanilla OS installed, needs to go through out-of-box experience</t>
+  </si>
+  <si>
+    <t>Dell Inspiron D16M001</t>
+  </si>
+  <si>
+    <t>Asus Chromebox CN60</t>
+  </si>
+  <si>
+    <t>Asus</t>
+  </si>
+  <si>
+    <t>has like 4 Vanilla installations</t>
+  </si>
+  <si>
+    <t>Asus Chromebox Thin Client 3</t>
+  </si>
+  <si>
+    <t>Doesnt display video</t>
+  </si>
+  <si>
+    <t>Dell Precision T7810</t>
+  </si>
+  <si>
+    <t>"No bootable devices" still a problem</t>
+  </si>
+  <si>
+    <t>HP EliteDesk 800 G4 TWR</t>
+  </si>
+  <si>
+    <t>CoolerMaster custom build</t>
+  </si>
+  <si>
+    <t>CoolerMaster</t>
+  </si>
+  <si>
+    <t>Lenovo ThinkCentre M700</t>
+  </si>
+  <si>
+    <t>HP ProDesk 400 G5 Desktop Mini</t>
+  </si>
+  <si>
+    <t>HP ProDesk 600 G3 Desktop Mini</t>
+  </si>
+  <si>
+    <t>Zotac Mini PC ZBox-CI323NANO</t>
+  </si>
+  <si>
+    <t>Zotac</t>
+  </si>
+  <si>
+    <t>Has Vanilla OS, can discover eduroam but not rhit open, ethernet works</t>
+  </si>
+  <si>
+    <t>HP ProDesk 600 G5 Desktop Mini</t>
+  </si>
+  <si>
+    <t>HP Z2 Mini G5 Workstation</t>
+  </si>
+  <si>
+    <t>Needs power supply; expensive!!!! MXM P620</t>
+  </si>
+  <si>
+    <t>Dell Optiplex 7070 micro</t>
+  </si>
+  <si>
+    <t>Needs to play dugdug video, make clinky when moved</t>
+  </si>
+  <si>
+    <t>TABLETS</t>
+  </si>
+  <si>
+    <t>Apple iPad A1397</t>
+  </si>
+  <si>
+    <t>Wifi + Cellular, Cracked screen</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Wifi + Cellular</t>
+  </si>
+  <si>
+    <t>READY TO DONATE</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Type of Device</t>
+  </si>
+  <si>
+    <t>Est. Year</t>
+  </si>
+  <si>
+    <t>CPU</t>
+  </si>
+  <si>
+    <t>OS</t>
+  </si>
+  <si>
+    <t>RAM Amount</t>
+  </si>
+  <si>
+    <t>RAM Generation</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>SSD/HDD</t>
+  </si>
+  <si>
+    <t>Est. Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Lenovo Thinkcenter E73</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>Intel i3-4130</t>
+  </si>
+  <si>
+    <t>Vanilla OS</t>
+  </si>
+  <si>
+    <t>DDR3</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>Dell Inspiron 15 3552</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Inspiron 15-3552</t>
+  </si>
+  <si>
+    <t>Asus Chromebox Thin Cilent 3</t>
+  </si>
+  <si>
+    <t>Intel Celeron 3865U</t>
+  </si>
+  <si>
+    <t>DDR4</t>
+  </si>
+  <si>
+    <t>intel core i3-7100</t>
+  </si>
+  <si>
+    <t>Intel core i3-7100</t>
+  </si>
+  <si>
+    <t>Lenovo ThinkCentre M625q</t>
+  </si>
+  <si>
+    <t>AMD A9-9420e</t>
+  </si>
+  <si>
+    <t>Dell Latitude 5510</t>
+  </si>
+  <si>
+    <t>Intel Core i7-10610U</t>
+  </si>
+  <si>
+    <t>Windows 11</t>
+  </si>
+  <si>
+    <t>Dell Inspiron 3847</t>
+  </si>
+  <si>
+    <t>Intel Core i3-4170</t>
+  </si>
+  <si>
+    <t>Dell Latitude 5490</t>
+  </si>
+  <si>
+    <t>Intel Core i7-8650U</t>
+  </si>
+  <si>
+    <t>Dell Inspiron 15 3537</t>
+  </si>
+  <si>
+    <t>Intel Core i3 ULV (4th generation)</t>
+  </si>
+  <si>
     <t>Dell Latitude 5410</t>
   </si>
   <si>
-    <t>Dell</t>
-  </si>
-  <si>
-    <t>Has windows 11, double check battery health, needs to finish windows updates</t>
-  </si>
-  <si>
-    <t>Included</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>Lenovo 100e Chromebook 2nd Gen</t>
-  </si>
-  <si>
-    <t>Lenovo</t>
-  </si>
-  <si>
-    <t>ARM, ARM bad, has charger</t>
-  </si>
-  <si>
-    <t>Dell Inspiron 15 3552</t>
-  </si>
-  <si>
-    <t>Toshiba Satellite C655-S5547</t>
-  </si>
-  <si>
-    <t>Toshiba</t>
-  </si>
-  <si>
-    <t>Won't turn on, has missing SSD</t>
-  </si>
-  <si>
-    <t>Apple MacBook Air A1369</t>
-  </si>
-  <si>
-    <t>Apple</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>bv</t>
-  </si>
-  <si>
-    <t>Apple MacBook Air A2179</t>
-  </si>
-  <si>
-    <t>Toshiba Satellite Click W35Dt-A3300</t>
-  </si>
-  <si>
-    <t>Not Included</t>
-  </si>
-  <si>
-    <t>Toshiba Satellite C55t-C5300</t>
-  </si>
-  <si>
-    <t>Dell Precision M6700</t>
-  </si>
-  <si>
-    <t>Samsung 500C Chromebook</t>
-  </si>
-  <si>
-    <t>Samsung</t>
-  </si>
-  <si>
-    <t>Dell Inspiron N7110</t>
-  </si>
-  <si>
-    <t>Needs OS installed, need to change to UEFI (if possible)</t>
-  </si>
-  <si>
-    <t>Lenovo Ideapad 3 Chromebook 11AST5</t>
-  </si>
-  <si>
-    <t>Battery issue</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>HP Elitebook 8560p</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>Needs Vanilla but isn't installing easily (Claims to be in legacy mode even after factory reset)</t>
-  </si>
-  <si>
-    <t>HP 15-db0004dx</t>
-  </si>
-  <si>
-    <t>HP ProBook 450 G7</t>
-  </si>
-  <si>
-    <t>Screen does not turn on but power light does, SSD installed</t>
-  </si>
-  <si>
-    <t>ThinkPad P15s Gen 1</t>
-  </si>
-  <si>
-    <t>Thinkpad S230u</t>
-  </si>
-  <si>
-    <t>Might need to scrap 4gb of ram soldered</t>
-  </si>
-  <si>
-    <t>Macbook Pro A1708</t>
-  </si>
-  <si>
-    <t>Surface Pro 1796</t>
-  </si>
-  <si>
-    <t>Microsoft</t>
-  </si>
-  <si>
-    <t>Windows 11 w/ all updates, battery no work :(</t>
-  </si>
-  <si>
-    <t>Need to remove stickers, has windows 11 fully updated</t>
-  </si>
-  <si>
-    <t>Thinkpad Yoga 11e</t>
-  </si>
-  <si>
-    <t>Lenovo Edge 15</t>
+    <t>Intel Core i5-10210U</t>
+  </si>
+  <si>
+    <t>MacBook Pro A1502</t>
+  </si>
+  <si>
+    <t>2.6 GHz Dual-Core Intel Core i5</t>
+  </si>
+  <si>
+    <t>macOS</t>
+  </si>
+  <si>
+    <t>HP ProBook 450 G6</t>
+  </si>
+  <si>
+    <t>Intel Core i5-8265U</t>
+  </si>
+  <si>
+    <t>HP ProBook 450 G8</t>
+  </si>
+  <si>
+    <t>Intel Core i5-1135G7</t>
+  </si>
+  <si>
+    <t>Intel Core i7-6700</t>
+  </si>
+  <si>
+    <t>HP Elitebook 850 G6</t>
+  </si>
+  <si>
+    <t>Intel Core i7-8565U</t>
+  </si>
+  <si>
+    <t>HP ProBook 650 G3</t>
+  </si>
+  <si>
+    <t>Intel Core i5-7300u</t>
+  </si>
+  <si>
+    <t>Intel Core i7-4770</t>
   </si>
   <si>
     <t>Dell Latitude 5580</t>
-  </si>
-  <si>
-    <t>Has windows 11 updated, needs to be cleaned</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Dell Precision 5540</t>
-  </si>
-  <si>
-    <t>Broken hinges; attempted to be superglued</t>
-  </si>
-  <si>
-    <t>Acer C731 Series</t>
-  </si>
-  <si>
-    <t>Acer</t>
-  </si>
-  <si>
-    <t>Arc Linux Minecraft Installed</t>
-  </si>
-  <si>
-    <t>DESKTOPS</t>
-  </si>
-  <si>
-    <t>Dell Optiplex 7040</t>
-  </si>
-  <si>
-    <t>Vanilla OS installs but can't boot to it - has SSD</t>
-  </si>
-  <si>
-    <t>Windows 11 installed (somehow, it shouldn't work bc tpm 1.2) should be fully working but needs to be tested</t>
-  </si>
-  <si>
-    <t>Boot issues (no boot device found after installation)</t>
-  </si>
-  <si>
-    <t>Dell Precision Tower 3420</t>
-  </si>
-  <si>
-    <t>Being used as a 2.5" SSD eraser; Tal accidentally ripped the sata power port off the motherboard, so if it doesn't work that's why</t>
-  </si>
-  <si>
-    <t>Has SSD, no bootable device found</t>
-  </si>
-  <si>
-    <t>Dell Optiplex 9020</t>
-  </si>
-  <si>
-    <t>Dell Optiplex 7050</t>
-  </si>
-  <si>
-    <t>Done???</t>
-  </si>
-  <si>
-    <t>Needs OS install</t>
-  </si>
-  <si>
-    <t>Needs SSD and OS install</t>
-  </si>
-  <si>
-    <t>Dell Optiplex 960</t>
-  </si>
-  <si>
-    <t>Dell Optiplex 5060</t>
-  </si>
-  <si>
-    <t>Ram switched out</t>
-  </si>
-  <si>
-    <t>Dell Precision T3600</t>
-  </si>
-  <si>
-    <t>No OS, needs Vanilla; Ready to install</t>
-  </si>
-  <si>
-    <t>Dell Precision 7920</t>
-  </si>
-  <si>
-    <t>Dell Precision 5810</t>
-  </si>
-  <si>
-    <t>Dell Precision 5820</t>
-  </si>
-  <si>
-    <t>HP Ryzen 4000 Desktop</t>
-  </si>
-  <si>
-    <t>Dell OptiPlex 5050 Micro</t>
-  </si>
-  <si>
-    <t>Installed SSD</t>
-  </si>
-  <si>
-    <t>Vanilla OS installed, needs to go through out-of-box experience</t>
-  </si>
-  <si>
-    <t>Dell Inspiron D16M001</t>
-  </si>
-  <si>
-    <t>Asus Chromebox CN60</t>
-  </si>
-  <si>
-    <t>Asus</t>
-  </si>
-  <si>
-    <t>has like 4 Vanilla installations</t>
-  </si>
-  <si>
-    <t>Asus Chromebox Thin Client 3</t>
-  </si>
-  <si>
-    <t>Doesnt display video</t>
-  </si>
-  <si>
-    <t>Dell Precision T7810</t>
-  </si>
-  <si>
-    <t>"No bootable devices" still a problem</t>
-  </si>
-  <si>
-    <t>HP EliteDesk 800 G4 TWR</t>
-  </si>
-  <si>
-    <t>CoolerMaster custom build</t>
-  </si>
-  <si>
-    <t>CoolerMaster</t>
-  </si>
-  <si>
-    <t>Lenovo ThinkCentre M700</t>
-  </si>
-  <si>
-    <t>HP ProDesk 400 G5 Desktop Mini</t>
-  </si>
-  <si>
-    <t>HP ProDesk 600 G3 Desktop Mini</t>
-  </si>
-  <si>
-    <t>Zotac Mini PC ZBox-CI323NANO</t>
-  </si>
-  <si>
-    <t>Zotac</t>
-  </si>
-  <si>
-    <t>Has Vanilla OS, can discover eduroam but not rhit open, ethernet works</t>
-  </si>
-  <si>
-    <t>HP ProDesk 600 G5 Desktop Mini</t>
-  </si>
-  <si>
-    <t>HP Z2 Mini G5 Workstation</t>
-  </si>
-  <si>
-    <t>Needs power supply; expensive!!!! MXM P620</t>
-  </si>
-  <si>
-    <t>Dell Optiplex 7070 micro</t>
-  </si>
-  <si>
-    <t>Needs to play dugdug video, make clinky when moved</t>
-  </si>
-  <si>
-    <t>TABLETS</t>
-  </si>
-  <si>
-    <t>Apple iPad A1397</t>
-  </si>
-  <si>
-    <t>Wifi + Cellular, Cracked screen</t>
-  </si>
-  <si>
-    <t>Wifi + Cellular</t>
-  </si>
-  <si>
-    <t>READY TO DONATE</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Type of Device</t>
-  </si>
-  <si>
-    <t>Est. Year</t>
-  </si>
-  <si>
-    <t>CPU</t>
-  </si>
-  <si>
-    <t>OS</t>
-  </si>
-  <si>
-    <t>RAM Amount</t>
-  </si>
-  <si>
-    <t>RAM Generation</t>
-  </si>
-  <si>
-    <t>Storage</t>
-  </si>
-  <si>
-    <t>SSD/HDD</t>
-  </si>
-  <si>
-    <t>Est. Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Lenovo Thinkcenter E73</t>
-  </si>
-  <si>
-    <t>Desktop</t>
-  </si>
-  <si>
-    <t>Intel i3-4130</t>
-  </si>
-  <si>
-    <t>Vanilla OS</t>
-  </si>
-  <si>
-    <t>DDR3</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>Inspiron 15-3552</t>
-  </si>
-  <si>
-    <t>Asus Chromebox Thin Cilent 3</t>
-  </si>
-  <si>
-    <t>Intel Celeron 3865U</t>
-  </si>
-  <si>
-    <t>DDR4</t>
-  </si>
-  <si>
-    <t>intel core i3-7100</t>
-  </si>
-  <si>
-    <t>Intel core i3-7100</t>
-  </si>
-  <si>
-    <t>Lenovo ThinkCentre M625q</t>
-  </si>
-  <si>
-    <t>AMD A9-9420e</t>
-  </si>
-  <si>
-    <t>Dell Latitude 5510</t>
-  </si>
-  <si>
-    <t>Intel Core i7-10610U</t>
-  </si>
-  <si>
-    <t>Windows 11</t>
-  </si>
-  <si>
-    <t>Dell Inspiron 3847</t>
-  </si>
-  <si>
-    <t>Intel Core i3-4170</t>
-  </si>
-  <si>
-    <t>Dell Latitude 5490</t>
-  </si>
-  <si>
-    <t>Intel Core i7-8650U</t>
-  </si>
-  <si>
-    <t>Dell Inspiron 15 3537</t>
-  </si>
-  <si>
-    <t>Intel Core i3 ULV (4th generation)</t>
-  </si>
-  <si>
-    <t>Intel Core i5-10210U</t>
-  </si>
-  <si>
-    <t>MacBook Pro A1502</t>
-  </si>
-  <si>
-    <t>2.6 GHz Dual-Core Intel Core i5</t>
-  </si>
-  <si>
-    <t>macOS</t>
-  </si>
-  <si>
-    <t>HP ProBook 450 G6</t>
-  </si>
-  <si>
-    <t>Intel Core i5-8265U</t>
-  </si>
-  <si>
-    <t>HP ProBook 450 G8</t>
-  </si>
-  <si>
-    <t>Intel Core i5-1135G7</t>
-  </si>
-  <si>
-    <t>Intel Core i7-6700</t>
-  </si>
-  <si>
-    <t>HP Elitebook 850 G6</t>
-  </si>
-  <si>
-    <t>Intel Core i7-8565U</t>
-  </si>
-  <si>
-    <t>HP ProBook 650 G3</t>
-  </si>
-  <si>
-    <t>Intel Core i5-7300u</t>
-  </si>
-  <si>
-    <t>Intel Core i7-4770</t>
   </si>
   <si>
     <t>Intel Core i7-7820</t>
@@ -1001,16 +989,16 @@
     <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1882,17 +1870,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
@@ -1926,47 +1914,25 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="45">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
-        <v>56</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3">
-        <v>2019</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="16">
-        <v>46094</v>
-      </c>
+    <row r="3" spans="1:10">
+      <c r="E3" s="1"/>
+      <c r="I3" s="16"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>2019</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
@@ -1979,44 +1945,24 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>2017</v>
-      </c>
       <c r="E5" s="1"/>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="16">
-        <v>46057</v>
-      </c>
+      <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>2010</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
@@ -2030,13 +1976,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>2010</v>
@@ -2046,24 +1992,24 @@
         <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I7" s="16">
         <v>46001</v>
       </c>
       <c r="J7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>2020</v>
@@ -2073,7 +2019,7 @@
         <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I8" s="16">
         <v>46001</v>
@@ -2081,23 +2027,23 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D9">
         <v>2013</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I9" s="16">
         <v>46001</v>
@@ -2105,13 +2051,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D10">
         <v>2014</v>
@@ -2121,7 +2067,7 @@
         <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I10" s="16">
         <v>46001</v>
@@ -2129,23 +2075,23 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2012</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I11" s="16">
         <v>46001</v>
@@ -2153,23 +2099,23 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B12">
         <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D12">
         <v>2016</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I12" s="16">
         <v>46001</v>
@@ -2177,19 +2123,19 @@
     </row>
     <row r="13" spans="1:10" ht="30">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B13">
         <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2011</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
@@ -2203,25 +2149,25 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B14">
         <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D14">
         <v>2023</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -2232,19 +2178,19 @@
     </row>
     <row r="15" spans="1:10" ht="45">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B15">
         <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D15">
         <v>2011</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
@@ -2258,13 +2204,13 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B16">
         <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D16">
         <v>2018</v>
@@ -2274,7 +2220,7 @@
         <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I16" s="16">
         <v>46001</v>
@@ -2282,19 +2228,19 @@
     </row>
     <row r="17" spans="1:9" ht="30">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B17">
         <v>116</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D17">
         <v>2020</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
@@ -2308,23 +2254,23 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B18">
         <v>118</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D18">
         <v>2020</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H18" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I18" s="16">
         <v>46094</v>
@@ -2332,19 +2278,19 @@
     </row>
     <row r="19" spans="1:9" ht="30">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B19">
         <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D19">
         <v>2012</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
@@ -2358,13 +2304,13 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B20">
         <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D20">
         <v>2017</v>
@@ -2374,7 +2320,7 @@
         <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I20" s="16">
         <v>46094</v>
@@ -2382,25 +2328,25 @@
     </row>
     <row r="21" spans="1:9" ht="29.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B21">
         <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D21">
         <v>2017</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -2409,51 +2355,29 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="29.25">
-      <c r="A22" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22">
-        <v>125</v>
-      </c>
-      <c r="C22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22">
-        <v>2017</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="16">
-        <v>46115</v>
-      </c>
+    <row r="22" spans="1:9">
+      <c r="E22" s="1"/>
+      <c r="I22" s="16"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B23">
         <v>123</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D23">
         <v>2014</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I23" s="16">
         <v>46094</v>
@@ -2461,75 +2385,50 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B24">
         <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D24">
         <v>2015</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I24" s="16">
         <v>46094</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="29.25">
-      <c r="A25" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25">
-        <v>126</v>
-      </c>
-      <c r="C25" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25">
-        <v>2018</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" t="s">
-        <v>57</v>
-      </c>
-      <c r="H25" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="16">
-        <v>46108</v>
-      </c>
+    <row r="25" spans="1:9">
+      <c r="E25" s="1"/>
+      <c r="I25" s="16"/>
     </row>
     <row r="26" spans="1:9" ht="30">
       <c r="A26" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B26">
         <v>134</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2019</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F26" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -2540,13 +2439,13 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B27">
         <v>137</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D27">
         <v>2017</v>
@@ -2556,7 +2455,7 @@
         <v>14</v>
       </c>
       <c r="H27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I27" s="16">
         <v>46108</v>
@@ -2564,13 +2463,13 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B28">
         <v>138</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D28">
         <v>2017</v>
@@ -2580,7 +2479,7 @@
         <v>14</v>
       </c>
       <c r="H28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I28" s="16">
         <v>46108</v>
@@ -2588,19 +2487,19 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B29">
         <v>136</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D29">
         <v>2017</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
@@ -2684,15 +2583,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="A1" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
@@ -2719,20 +2618,20 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B3" s="13">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D3" s="5">
         <v>2015</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G3" s="7">
         <v>46000</v>
@@ -2740,20 +2639,20 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="8" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B4" s="14">
         <v>2</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D4" s="9">
         <v>2015</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G4" s="11">
         <v>46000</v>
@@ -2761,19 +2660,19 @@
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B5" s="13">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D5" s="5">
         <v>2015</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>15</v>
@@ -2784,19 +2683,19 @@
     </row>
     <row r="6" spans="1:7" ht="43.5">
       <c r="A6" s="8" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B6" s="14">
         <v>4</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D6" s="9">
         <v>2015</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>15</v>
@@ -2807,20 +2706,20 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B7" s="13">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D7" s="5">
         <v>2015</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G7" s="7">
         <v>46000</v>
@@ -2828,19 +2727,19 @@
     </row>
     <row r="8" spans="1:7" ht="30">
       <c r="A8" s="8" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B8" s="14">
         <v>6</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D8" s="9">
         <v>2015</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>15</v>
@@ -2851,62 +2750,50 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B9" s="13">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D9" s="5">
         <v>2015</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G9" s="7">
         <v>46000</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="14">
-        <v>8</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="9">
-        <v>2015</v>
-      </c>
+      <c r="A10" s="8"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
       <c r="E10" s="10"/>
-      <c r="F10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="11">
-        <v>46000</v>
-      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B11" s="13">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D11" s="5">
         <v>2015</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G11" s="7">
         <v>46000</v>
@@ -2914,19 +2801,19 @@
     </row>
     <row r="12" spans="1:7" ht="60">
       <c r="A12" s="8" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B12" s="14">
         <v>12</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D12" s="9">
         <v>2016</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>15</v>
@@ -2937,19 +2824,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="8" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B13" s="14">
         <v>14</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D13" s="9">
         <v>2016</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>15</v>
@@ -2960,20 +2847,20 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B14" s="13">
         <v>18</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D14" s="5">
         <v>2016</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G14" s="7">
         <v>46000</v>
@@ -2981,20 +2868,20 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="8" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B15" s="14">
         <v>19</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D15" s="9">
         <v>2016</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G15" s="11">
         <v>46000</v>
@@ -3002,20 +2889,20 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B16" s="13">
         <v>20</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D16" s="5">
         <v>2016</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G16" s="7">
         <v>46000</v>
@@ -3023,20 +2910,20 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B17" s="14">
         <v>21</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D17" s="9">
         <v>2016</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G17" s="11">
         <v>46000</v>
@@ -3044,13 +2931,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B18" s="13">
         <v>23</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D18" s="5">
         <v>2016</v>
@@ -3065,20 +2952,20 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="8" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B19" s="14">
         <v>24</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D19" s="9">
         <v>2016</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G19" s="11">
         <v>46000</v>
@@ -3086,20 +2973,20 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B20" s="13">
         <v>25</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D20" s="5">
         <v>2016</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G20" s="7">
         <v>46000</v>
@@ -3107,20 +2994,20 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="8" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B21" s="14">
         <v>27</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D21" s="9">
         <v>2016</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G21" s="11">
         <v>46000</v>
@@ -3128,20 +3015,20 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B22" s="13">
         <v>28</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D22" s="5">
         <v>2013</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G22" s="7">
         <v>46000</v>
@@ -3149,19 +3036,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B23" s="14">
         <v>31</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D23" s="9">
         <v>2017</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>15</v>
@@ -3172,13 +3059,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B24" s="13">
         <v>32</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D24" s="5">
         <v>2013</v>
@@ -3193,7 +3080,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B25" s="14">
         <v>33</v>
@@ -3204,50 +3091,36 @@
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G25" s="11">
         <v>46000</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="13">
-        <v>34</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="5">
-        <v>2013</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" s="7">
-        <v>46122</v>
-      </c>
+      <c r="A26" s="4"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B27" s="14">
         <v>37</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D27" s="9">
         <v>2013</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>15</v>
@@ -3258,20 +3131,20 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B28" s="13">
         <v>38</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D28" s="5">
         <v>2009</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G28" s="7">
         <v>46000</v>
@@ -3279,19 +3152,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="8" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B29" s="14">
         <v>39</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D29" s="9">
         <v>2018</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>15</v>
@@ -3302,19 +3175,19 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="8" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B30" s="14">
         <v>41</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D30" s="9">
         <v>2012</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>15</v>
@@ -3325,20 +3198,20 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="8" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B31" s="14">
         <v>42</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D31" s="9">
         <v>2017</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G31" s="11">
         <v>46000</v>
@@ -3346,20 +3219,20 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="8" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B32" s="14">
         <v>43</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D32" s="9">
         <v>2014</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G32" s="11">
         <v>46000</v>
@@ -3367,20 +3240,20 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="8" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B33" s="14">
         <v>44</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D33" s="9">
         <v>2017</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G33" s="11">
         <v>46000</v>
@@ -3388,20 +3261,20 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="8" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B34" s="14">
         <v>45</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D34" s="9">
         <v>2017</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G34" s="11">
         <v>46000</v>
@@ -3409,20 +3282,20 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B35" s="14">
         <v>46</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D35" s="9">
         <v>2020</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G35" s="11">
         <v>46000</v>
@@ -3430,19 +3303,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B36" s="12">
         <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D36">
         <v>2017</v>
       </c>
       <c r="E36" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F36" t="s">
         <v>15</v>
@@ -3453,19 +3326,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B37" s="12">
         <v>80</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D37">
         <v>2013</v>
       </c>
       <c r="E37" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F37" t="s">
         <v>15</v>
@@ -3476,19 +3349,19 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B38" s="12">
         <v>82</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D38">
         <v>2014</v>
       </c>
       <c r="F38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G38" s="16">
         <v>46001</v>
@@ -3496,19 +3369,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B39" s="12">
         <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D39">
         <v>2014</v>
       </c>
       <c r="F39" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G39" s="16">
         <v>46031</v>
@@ -3516,19 +3389,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B40" s="12">
         <v>35</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D40">
         <v>2013</v>
       </c>
       <c r="E40" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F40" t="s">
         <v>15</v>
@@ -3539,19 +3412,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B41" s="12">
         <v>102</v>
       </c>
       <c r="C41" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D41">
         <v>2018</v>
       </c>
       <c r="E41" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F41" t="s">
         <v>15</v>
@@ -3561,40 +3434,23 @@
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" t="s">
-        <v>92</v>
-      </c>
-      <c r="B42" s="12">
-        <v>103</v>
-      </c>
-      <c r="C42" t="s">
-        <v>90</v>
-      </c>
-      <c r="D42">
-        <v>2018</v>
-      </c>
-      <c r="F42" t="s">
-        <v>25</v>
-      </c>
-      <c r="G42" s="16">
-        <v>46066</v>
-      </c>
+      <c r="G42" s="16"/>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B43" s="12">
         <v>104</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D43">
         <v>2014</v>
       </c>
       <c r="F43" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G43" s="16">
         <v>46066</v>
@@ -3602,19 +3458,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B44" s="12">
         <v>105</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D44">
         <v>2014</v>
       </c>
       <c r="F44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G44" s="16">
         <v>46066</v>
@@ -3622,19 +3478,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B45" s="12">
         <v>106</v>
       </c>
       <c r="C45" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D45">
         <v>2014</v>
       </c>
       <c r="F45" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G45" s="16">
         <v>46066</v>
@@ -3642,19 +3498,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B46" s="12">
         <v>107</v>
       </c>
       <c r="C46" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D46">
         <v>2014</v>
       </c>
       <c r="E46" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F46" t="s">
         <v>15</v>
@@ -3665,19 +3521,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B47" s="12">
         <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D47">
         <v>2014</v>
       </c>
       <c r="E47" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F47" t="s">
         <v>15</v>
@@ -3688,19 +3544,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B48" s="12">
         <v>111</v>
       </c>
       <c r="C48" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D48">
         <v>2018</v>
       </c>
       <c r="F48" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G48" s="16">
         <v>46092</v>
@@ -3708,16 +3564,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B49" s="12">
         <v>112</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G49" s="16">
         <v>46092</v>
@@ -3725,19 +3581,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B50" s="12">
         <v>127</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D50">
         <v>2016</v>
       </c>
       <c r="F50" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G50" s="16">
         <v>46094</v>
@@ -3745,19 +3601,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B51" s="12">
         <v>128</v>
       </c>
       <c r="C51" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D51">
         <v>2018</v>
       </c>
       <c r="F51" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G51" s="16">
         <v>46094</v>
@@ -3765,13 +3621,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B52" s="12">
         <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D52">
         <v>2017</v>
@@ -3785,19 +3641,19 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B53" s="12">
         <v>130</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D53">
         <v>2015</v>
       </c>
       <c r="E53" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F53" t="s">
         <v>15</v>
@@ -3808,19 +3664,19 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B54" s="12">
         <v>131</v>
       </c>
       <c r="C54" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D54">
         <v>2019</v>
       </c>
       <c r="F54" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G54" s="16">
         <v>46094</v>
@@ -3828,19 +3684,19 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B55" s="12">
         <v>132</v>
       </c>
       <c r="C55" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D55">
         <v>2020</v>
       </c>
       <c r="E55" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F55" t="s">
         <v>15</v>
@@ -3851,19 +3707,19 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B56" s="12">
         <v>133</v>
       </c>
       <c r="C56" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D56">
         <v>2019</v>
       </c>
       <c r="F56" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G56" s="16">
         <v>46094</v>
@@ -3871,19 +3727,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B57" s="12">
         <v>135</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D57">
         <v>2016</v>
       </c>
       <c r="F57" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G57" s="16">
         <v>46094</v>
@@ -3891,19 +3747,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B58" s="12">
         <v>139</v>
       </c>
       <c r="C58" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D58">
         <v>2018</v>
       </c>
       <c r="F58" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G58" s="16">
         <v>46115</v>
@@ -3911,19 +3767,19 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B59" s="12">
         <v>142</v>
       </c>
       <c r="C59" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D59">
         <v>2013</v>
       </c>
       <c r="E59" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F59" t="s">
         <v>15</v>
@@ -3987,17 +3843,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="A1" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
@@ -4030,28 +3886,28 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B3">
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>2011</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I3" s="16">
         <v>46001</v>
@@ -4059,28 +3915,28 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B4">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>2011</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I4" s="16">
         <v>46001</v>
@@ -4218,54 +4074,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
+      <c r="A1" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H2" t="s">
         <v>115</v>
       </c>
-      <c r="B2" t="s">
+      <c r="I2" t="s">
         <v>116</v>
       </c>
-      <c r="C2" t="s">
+      <c r="J2" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="D2" t="s">
+      <c r="K2" t="s">
         <v>118</v>
-      </c>
-      <c r="E2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="K2" t="s">
-        <v>125</v>
       </c>
       <c r="L2" t="s">
         <v>2</v>
@@ -4273,31 +4129,31 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C3">
         <v>2013</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F3">
         <v>4</v>
       </c>
       <c r="G3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H3">
         <v>256</v>
       </c>
       <c r="I3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J3" s="19">
         <v>100</v>
@@ -4309,31 +4165,31 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>2017</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F4">
         <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H4">
         <v>256</v>
       </c>
       <c r="I4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J4" s="19">
         <v>200</v>
@@ -4345,31 +4201,31 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C5">
         <v>2018</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F5">
         <v>8</v>
       </c>
       <c r="G5" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H5">
         <v>256</v>
       </c>
       <c r="I5" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J5" s="19">
         <v>175</v>
@@ -4384,31 +4240,31 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C7">
         <v>2018</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F7">
         <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H7">
         <v>256</v>
       </c>
       <c r="I7" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J7" s="19">
         <v>175</v>
@@ -4420,31 +4276,31 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C8">
         <v>2018</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F8">
         <v>8</v>
       </c>
       <c r="G8" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H8">
         <v>256</v>
       </c>
       <c r="I8" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J8" s="19">
         <v>175</v>
@@ -4456,31 +4312,31 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C9">
         <v>2018</v>
       </c>
       <c r="D9" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E9" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F9">
         <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H9">
         <v>256</v>
       </c>
       <c r="I9" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J9" s="19">
         <v>150</v>
@@ -4495,31 +4351,31 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C11">
         <v>2020</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E11" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F11">
         <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H11">
         <v>256</v>
       </c>
       <c r="I11" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J11" s="19">
         <v>300</v>
@@ -4531,31 +4387,31 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B12" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C12">
         <v>2014</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E12" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F12">
         <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H12">
         <v>256</v>
       </c>
       <c r="I12" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J12" s="2">
         <v>175</v>
@@ -4566,31 +4422,31 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B13" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C13">
         <v>2018</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E13" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F13">
         <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H13">
         <v>256</v>
       </c>
       <c r="I13" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J13" s="19">
         <v>120</v>
@@ -4602,31 +4458,31 @@
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1">
       <c r="A14" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C14">
         <v>2018</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E14" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F14">
         <v>8</v>
       </c>
       <c r="G14" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H14">
         <v>256</v>
       </c>
       <c r="I14" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J14" s="19">
         <v>175</v>
@@ -4638,31 +4494,31 @@
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1">
       <c r="A15" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C15">
         <v>2013</v>
       </c>
       <c r="D15" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E15" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F15">
         <v>8</v>
       </c>
       <c r="G15" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H15">
         <v>256</v>
       </c>
       <c r="I15" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J15" s="19">
         <v>150</v>
@@ -4674,31 +4530,31 @@
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>144</v>
       </c>
       <c r="B16" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C16">
         <v>2019</v>
       </c>
       <c r="D16" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F16">
         <v>8</v>
       </c>
       <c r="G16" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H16">
         <v>256</v>
       </c>
       <c r="I16" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J16" s="19">
         <v>265</v>
@@ -4710,31 +4566,31 @@
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1">
       <c r="A17" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C17">
         <v>2014</v>
       </c>
       <c r="D17" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E17" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F17">
         <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H17">
         <v>256</v>
       </c>
       <c r="I17" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J17" s="19">
         <v>100</v>
@@ -4746,31 +4602,31 @@
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1">
       <c r="A18" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B18" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C18">
         <v>2019</v>
       </c>
       <c r="D18" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E18" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F18">
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H18">
         <v>256</v>
       </c>
       <c r="I18" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J18" s="19">
         <v>300</v>
@@ -4782,31 +4638,31 @@
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1">
       <c r="A19" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B19" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C19">
         <v>2019</v>
       </c>
       <c r="D19" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E19" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F19">
         <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H19">
         <v>256</v>
       </c>
       <c r="I19" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J19" s="19">
         <v>300</v>
@@ -4818,31 +4674,31 @@
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1">
       <c r="A20" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C20">
         <v>2021</v>
       </c>
       <c r="D20" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E20" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F20">
         <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H20">
         <v>256</v>
       </c>
       <c r="I20" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J20" s="19">
         <v>350</v>
@@ -4854,31 +4710,31 @@
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1">
       <c r="A21" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C21">
         <v>2021</v>
       </c>
       <c r="D21" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E21" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F21">
         <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H21">
         <v>256</v>
       </c>
       <c r="I21" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J21" s="19">
         <v>350</v>
@@ -4890,31 +4746,31 @@
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C22">
         <v>2016</v>
       </c>
       <c r="D22" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E22" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F22">
         <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H22">
         <v>256</v>
       </c>
       <c r="I22" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J22" s="19">
         <v>255</v>
@@ -4926,31 +4782,31 @@
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1">
       <c r="A23" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C23">
         <v>2019</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E23" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F23">
         <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H23">
         <v>256</v>
       </c>
       <c r="I23" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J23" s="19">
         <v>300</v>
@@ -4962,31 +4818,31 @@
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1">
       <c r="A24" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C24">
         <v>2015</v>
       </c>
       <c r="D24" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E24" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F24">
         <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H24">
         <v>256</v>
       </c>
       <c r="I24" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J24" s="19">
         <v>255</v>
@@ -4998,31 +4854,31 @@
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1">
       <c r="A25" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C25">
         <v>2018</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E25" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F25">
         <v>8</v>
       </c>
       <c r="G25" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H25">
         <v>256</v>
       </c>
       <c r="I25" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J25" s="19">
         <v>175</v>
@@ -5034,31 +4890,31 @@
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1">
       <c r="A26" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C26">
         <v>2017</v>
       </c>
       <c r="D26" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E26" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F26">
         <v>8</v>
       </c>
       <c r="G26" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H26">
         <v>256</v>
       </c>
       <c r="I26" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J26" s="19">
         <v>150</v>
@@ -5070,31 +4926,31 @@
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C27">
         <v>2017</v>
       </c>
       <c r="D27" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E27" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F27">
         <v>8</v>
       </c>
       <c r="G27" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H27">
         <v>256</v>
       </c>
       <c r="I27" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J27" s="19">
         <v>200</v>
@@ -5106,31 +4962,31 @@
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C28">
         <v>2013</v>
       </c>
       <c r="D28" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E28" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F28">
         <v>8</v>
       </c>
       <c r="G28" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H28">
         <v>256</v>
       </c>
       <c r="I28" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J28" s="19">
         <v>200</v>
@@ -5142,31 +4998,31 @@
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>159</v>
       </c>
       <c r="B29" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C29">
         <v>2018</v>
       </c>
       <c r="D29" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E29" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F29">
         <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H29">
         <v>256</v>
       </c>
       <c r="I29" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J29" s="19">
         <v>325</v>
@@ -5342,7 +5198,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
@@ -5356,51 +5212,51 @@
       <c r="L1" s="22"/>
       <c r="M1" s="18"/>
       <c r="N1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="O1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H2" t="s">
         <v>115</v>
       </c>
-      <c r="B2" t="s">
+      <c r="I2" t="s">
         <v>116</v>
       </c>
-      <c r="C2" t="s">
+      <c r="J2" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="D2" t="s">
+      <c r="K2" t="s">
         <v>118</v>
       </c>
-      <c r="E2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="K2" t="s">
-        <v>125</v>
-      </c>
       <c r="L2" s="16" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="N2" s="2">
         <f>SUM(J3:J38)</f>
@@ -5413,7 +5269,10 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>166</v>
+      </c>
+      <c r="B3" t="s">
+        <v>126</v>
       </c>
       <c r="J3" s="19">
         <v>225</v>
@@ -5423,12 +5282,15 @@
         <v>45970</v>
       </c>
       <c r="M3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>166</v>
+      </c>
+      <c r="B4" t="s">
+        <v>126</v>
       </c>
       <c r="J4" s="19">
         <v>225</v>
@@ -5438,12 +5300,15 @@
         <v>45970</v>
       </c>
       <c r="M4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>166</v>
+      </c>
+      <c r="B5" t="s">
+        <v>126</v>
       </c>
       <c r="J5" s="19">
         <v>225</v>
@@ -5453,12 +5318,15 @@
         <v>45970</v>
       </c>
       <c r="M5" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>166</v>
+      </c>
+      <c r="B6" t="s">
+        <v>126</v>
       </c>
       <c r="J6" s="19">
         <v>225</v>
@@ -5468,12 +5336,15 @@
         <v>45970</v>
       </c>
       <c r="M6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>166</v>
+      </c>
+      <c r="B7" t="s">
+        <v>126</v>
       </c>
       <c r="J7" s="19">
         <v>225</v>
@@ -5483,12 +5354,15 @@
         <v>45970</v>
       </c>
       <c r="M7" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>166</v>
+      </c>
+      <c r="B8" t="s">
+        <v>126</v>
       </c>
       <c r="J8" s="19">
         <v>225</v>
@@ -5498,12 +5372,15 @@
         <v>45970</v>
       </c>
       <c r="M8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>166</v>
+      </c>
+      <c r="B9" t="s">
+        <v>126</v>
       </c>
       <c r="J9" s="19">
         <v>225</v>
@@ -5513,36 +5390,36 @@
         <v>45970</v>
       </c>
       <c r="M9" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B10" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C10">
         <v>2018</v>
       </c>
       <c r="D10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E10" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F10">
         <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H10">
         <v>256</v>
       </c>
       <c r="I10" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J10" s="21">
         <v>325</v>
@@ -5552,36 +5429,36 @@
         <v>45999</v>
       </c>
       <c r="M10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C11">
         <v>2015</v>
       </c>
       <c r="D11" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E11" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F11">
         <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H11">
         <v>256</v>
       </c>
       <c r="I11" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J11" s="19">
         <v>225</v>
@@ -5591,77 +5468,77 @@
         <v>45999</v>
       </c>
       <c r="M11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C12">
         <v>2014</v>
       </c>
       <c r="D12" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E12" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F12">
         <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H12">
         <v>256</v>
       </c>
       <c r="I12" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J12" s="19">
         <v>175</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="L12" s="15">
         <v>45999</v>
       </c>
       <c r="M12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B13" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C13">
         <v>2019</v>
       </c>
       <c r="D13" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E13" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F13">
         <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H13">
         <v>256</v>
       </c>
       <c r="I13" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J13" s="19">
         <v>325</v>
@@ -5671,36 +5548,36 @@
         <v>45999</v>
       </c>
       <c r="M13" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C14">
         <v>2018</v>
       </c>
       <c r="D14" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E14" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F14">
         <v>16</v>
       </c>
       <c r="G14" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H14">
         <v>256</v>
       </c>
       <c r="I14" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J14" s="19">
         <v>325</v>
@@ -5710,36 +5587,36 @@
         <v>45999</v>
       </c>
       <c r="M14" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C15">
         <v>2021</v>
       </c>
       <c r="D15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E15" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F15">
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H15">
         <v>256</v>
       </c>
       <c r="I15" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J15" s="19">
         <v>205</v>
@@ -5749,241 +5626,241 @@
         <v>45999</v>
       </c>
       <c r="M15" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C16">
         <v>2012</v>
       </c>
       <c r="D16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E16" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="H16" s="1">
         <v>64</v>
       </c>
       <c r="I16" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J16" s="19">
         <v>50</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L16" s="15">
         <v>45999</v>
       </c>
       <c r="M16" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C17">
         <v>2014</v>
       </c>
       <c r="D17" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E17" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F17">
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H17">
         <v>128</v>
       </c>
       <c r="I17" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J17" s="19">
         <v>60</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L17" s="15">
         <v>45999</v>
       </c>
       <c r="M17" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C18">
         <v>2018</v>
       </c>
       <c r="D18" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E18" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F18">
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H18">
         <v>256</v>
       </c>
       <c r="I18" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J18" s="19">
         <v>250</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="L18" s="16">
         <v>46043</v>
       </c>
       <c r="M18" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C19">
         <v>2013</v>
       </c>
       <c r="D19" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E19" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F19">
         <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H19">
         <v>256</v>
       </c>
       <c r="I19" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J19" s="19">
         <v>290</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L19" s="16">
         <v>46043</v>
       </c>
       <c r="M19" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="43.5">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C20">
         <v>2016</v>
       </c>
       <c r="D20" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F20">
         <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H20">
         <v>256</v>
       </c>
       <c r="I20" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J20" s="19">
         <v>300</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="L20" s="15">
         <v>46056</v>
       </c>
       <c r="M20" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B21" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C21">
         <v>2013</v>
       </c>
       <c r="D21" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E21" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F21">
         <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H21">
         <v>256</v>
       </c>
       <c r="I21" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J21" s="19">
         <v>200</v>
@@ -5993,36 +5870,36 @@
         <v>46056</v>
       </c>
       <c r="M21" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B22" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C22">
         <v>2013</v>
       </c>
       <c r="D22" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E22" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F22">
         <v>8</v>
       </c>
       <c r="G22" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H22">
         <v>256</v>
       </c>
       <c r="I22" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J22" s="19">
         <v>200</v>
@@ -6032,36 +5909,36 @@
         <v>46056</v>
       </c>
       <c r="M22" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C23">
         <v>2013</v>
       </c>
       <c r="D23" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E23" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F23">
         <v>8</v>
       </c>
       <c r="G23" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H23">
         <v>256</v>
       </c>
       <c r="I23" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J23" s="19">
         <v>200</v>
@@ -6071,36 +5948,36 @@
         <v>46056</v>
       </c>
       <c r="M23" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C24">
         <v>2013</v>
       </c>
       <c r="D24" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E24" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F24">
         <v>8</v>
       </c>
       <c r="G24" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H24">
         <v>256</v>
       </c>
       <c r="I24" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J24" s="19">
         <v>200</v>
@@ -6110,36 +5987,36 @@
         <v>46056</v>
       </c>
       <c r="M24" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C25">
         <v>2013</v>
       </c>
       <c r="D25" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E25" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F25">
         <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H25">
         <v>256</v>
       </c>
       <c r="I25" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J25" s="19">
         <v>200</v>
@@ -6149,36 +6026,36 @@
         <v>46056</v>
       </c>
       <c r="M25" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C26">
         <v>2016</v>
       </c>
       <c r="D26" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E26" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F26">
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H26">
         <v>256</v>
       </c>
       <c r="I26" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J26" s="19">
         <v>300</v>
@@ -6188,36 +6065,36 @@
         <v>46056</v>
       </c>
       <c r="M26" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C27">
         <v>2016</v>
       </c>
       <c r="D27" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E27" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F27">
         <v>8</v>
       </c>
       <c r="G27" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H27">
         <v>256</v>
       </c>
       <c r="I27" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J27" s="19">
         <v>300</v>
@@ -6227,36 +6104,36 @@
         <v>46056</v>
       </c>
       <c r="M27" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B28" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C28">
         <v>2018</v>
       </c>
       <c r="D28" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E28" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F28">
         <v>16</v>
       </c>
       <c r="G28" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H28">
         <v>512</v>
       </c>
       <c r="I28" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J28" s="19">
         <v>445</v>
@@ -6266,36 +6143,36 @@
         <v>46056</v>
       </c>
       <c r="M28" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B29" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C29">
         <v>2018</v>
       </c>
       <c r="D29" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E29" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F29">
         <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H29">
         <v>512</v>
       </c>
       <c r="I29" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J29" s="19">
         <v>445</v>
@@ -6305,36 +6182,36 @@
         <v>46056</v>
       </c>
       <c r="M29" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C30">
         <v>2018</v>
       </c>
       <c r="D30" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E30" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F30">
         <v>8</v>
       </c>
       <c r="G30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H30">
         <v>256</v>
       </c>
       <c r="I30" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J30" s="19">
         <v>150</v>
@@ -6344,36 +6221,36 @@
         <v>46056</v>
       </c>
       <c r="M30" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="8" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C31">
         <v>2016</v>
       </c>
       <c r="D31" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E31" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F31">
         <v>8</v>
       </c>
       <c r="G31" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H31">
         <v>500</v>
       </c>
       <c r="I31" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="J31" s="19">
         <v>300</v>
@@ -6383,36 +6260,36 @@
         <v>46058</v>
       </c>
       <c r="M31" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B32" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C32">
         <v>2016</v>
       </c>
       <c r="D32" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E32" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F32">
         <v>8</v>
       </c>
       <c r="G32" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H32">
         <v>256</v>
       </c>
       <c r="I32" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J32" s="19">
         <v>300</v>
@@ -6421,36 +6298,36 @@
         <v>46058</v>
       </c>
       <c r="M32" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C33">
         <v>2016</v>
       </c>
       <c r="D33" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E33" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F33">
         <v>8</v>
       </c>
       <c r="G33" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H33">
         <v>256</v>
       </c>
       <c r="I33" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J33" s="19">
         <v>300</v>
@@ -6459,36 +6336,36 @@
         <v>46058</v>
       </c>
       <c r="M33" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C34">
         <v>2020</v>
       </c>
       <c r="D34" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E34" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F34">
         <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H34">
         <v>512</v>
       </c>
       <c r="I34" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J34" s="19">
         <v>445</v>
@@ -6497,36 +6374,36 @@
         <v>46058</v>
       </c>
       <c r="M34" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C35">
         <v>2020</v>
       </c>
       <c r="D35" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E35" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F35">
         <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H35">
         <v>512</v>
       </c>
       <c r="I35" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J35" s="19">
         <v>445</v>
@@ -6535,36 +6412,36 @@
         <v>46058</v>
       </c>
       <c r="M35" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C36">
         <v>2020</v>
       </c>
       <c r="D36" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E36" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F36">
         <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H36">
         <v>512</v>
       </c>
       <c r="I36" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J36" s="19">
         <v>445</v>
@@ -6573,36 +6450,36 @@
         <v>46058</v>
       </c>
       <c r="M36" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C37">
         <v>2020</v>
       </c>
       <c r="D37" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E37" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F37">
         <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H37">
         <v>512</v>
       </c>
       <c r="I37" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J37" s="19">
         <v>445</v>
@@ -6611,36 +6488,36 @@
         <v>46058</v>
       </c>
       <c r="M37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B38" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C38">
         <v>2020</v>
       </c>
       <c r="D38" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E38" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F38">
         <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H38">
         <v>512</v>
       </c>
       <c r="I38" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J38" s="19">
         <v>445</v>
@@ -6649,36 +6526,36 @@
         <v>46058</v>
       </c>
       <c r="M38" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C39">
         <v>2020</v>
       </c>
       <c r="D39" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E39" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F39">
         <v>16</v>
       </c>
       <c r="G39" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H39">
         <v>512</v>
       </c>
       <c r="I39" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J39" s="19">
         <v>445</v>
@@ -6687,36 +6564,36 @@
         <v>46058</v>
       </c>
       <c r="M39" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15" customHeight="1">
       <c r="A40" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C40">
         <v>2020</v>
       </c>
       <c r="D40" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E40" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F40">
         <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H40">
         <v>512</v>
       </c>
       <c r="I40" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J40" s="19">
         <v>445</v>
@@ -6725,36 +6602,36 @@
         <v>46058</v>
       </c>
       <c r="M40" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="15" customHeight="1">
       <c r="A41" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B41" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C41">
         <v>2020</v>
       </c>
       <c r="D41" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E41" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F41">
         <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H41">
         <v>512</v>
       </c>
       <c r="I41" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J41" s="19">
         <v>445</v>
@@ -6763,36 +6640,36 @@
         <v>46058</v>
       </c>
       <c r="M41" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1">
       <c r="A42" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C42">
         <v>2020</v>
       </c>
       <c r="D42" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E42" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F42">
         <v>16</v>
       </c>
       <c r="G42" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H42">
         <v>512</v>
       </c>
       <c r="I42" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J42" s="19">
         <v>445</v>
@@ -6801,36 +6678,36 @@
         <v>46058</v>
       </c>
       <c r="M42" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="15" customHeight="1">
       <c r="A43" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B43" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C43">
         <v>2018</v>
       </c>
       <c r="D43" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E43" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F43">
         <v>8</v>
       </c>
       <c r="G43" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H43">
         <v>256</v>
       </c>
       <c r="I43" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J43" s="19">
         <v>300</v>
@@ -6840,36 +6717,36 @@
         <v>46078</v>
       </c>
       <c r="M43" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="15" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C44" s="5">
         <v>2016</v>
       </c>
       <c r="D44" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E44" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F44">
         <v>8</v>
       </c>
       <c r="G44" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H44">
         <v>256</v>
       </c>
       <c r="I44" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J44" s="19">
         <v>300</v>
@@ -6879,7 +6756,7 @@
         <v>46099</v>
       </c>
       <c r="M44" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="15" customHeight="1">
@@ -7041,22 +6918,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="B1" s="24"/>
+      <c r="A1" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" s="26"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -7064,7 +6941,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B4">
         <v>9</v>
@@ -7072,7 +6949,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -7080,7 +6957,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -7088,7 +6965,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -7096,7 +6973,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B8">
         <v>18</v>
@@ -7104,7 +6981,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -7112,7 +6989,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -7120,7 +6997,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B11">
         <v>16</v>
@@ -7128,7 +7005,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -7136,7 +7013,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -7144,7 +7021,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -7152,7 +7029,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B15">
         <v>11</v>
@@ -7160,7 +7037,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B16">
         <v>14</v>
@@ -7168,7 +7045,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B17">
         <v>17</v>
@@ -7176,7 +7053,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -7184,7 +7061,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B19">
         <v>2</v>
@@ -7192,7 +7069,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -7200,7 +7077,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -7208,7 +7085,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -7216,7 +7093,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B23">
         <v>12</v>
@@ -7224,7 +7101,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -7232,7 +7109,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -7240,7 +7117,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -7248,7 +7125,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -7256,7 +7133,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -7264,7 +7141,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B29">
         <v>9</v>
@@ -7272,7 +7149,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -7280,7 +7157,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B31">
         <v>5</v>
@@ -7288,7 +7165,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -7296,7 +7173,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B33">
         <v>6</v>
@@ -7304,7 +7181,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -7312,7 +7189,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B35">
         <v>2</v>
@@ -7320,7 +7197,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -7328,7 +7205,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B37">
         <v>14</v>
@@ -7336,7 +7213,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B38">
         <v>5</v>
@@ -7344,7 +7221,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B39">
         <v>2</v>
@@ -7352,7 +7229,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -7360,7 +7237,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -7368,7 +7245,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B42">
         <v>2</v>
@@ -7376,7 +7253,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -7384,7 +7261,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -7392,7 +7269,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B45">
         <v>11</v>
@@ -7400,7 +7277,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B46">
         <v>16</v>
@@ -7408,7 +7285,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B47">
         <v>6</v>

--- a/data/OldInventorySystem.xlsx
+++ b/data/OldInventorySystem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rosehulman-my.sharepoint.com/personal/lucasja_rose-hulman_edu/Documents/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucasja\git\Inventory-System\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6F62A0D-D864-413C-A038-AF10FB8B133F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1769F4D0-9B06-4025-9E21-BBB42E246945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="4" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Laptops" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="255">
   <si>
     <t>LAPTOPS</t>
   </si>
@@ -803,6 +803,9 @@
   </si>
   <si>
     <t>WiFi Adapters</t>
+  </si>
+  <si>
+    <t>Intel core i7-i8850H</t>
   </si>
 </sst>
 </file>
@@ -814,7 +817,7 @@
     <numFmt numFmtId="164" formatCode="00000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1005,21 +1008,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="49">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
+  <dxfs count="25">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1038,9 +1027,12 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1050,7 +1042,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="0"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1138,182 +1130,6 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
           <bgColor theme="0"/>
         </patternFill>
       </fill>
@@ -1349,62 +1165,37 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="00000"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1433,7 +1224,7 @@
     <tableColumn id="13" xr3:uid="{5BEE40AD-E450-4A13-BFB5-1D0CED084DB3}" name="ID"/>
     <tableColumn id="8" xr3:uid="{E9AB9B46-3541-4715-8E5B-024096D78342}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{F7DAC8DD-8096-40F1-8780-1DB9CB4EC72F}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="24"/>
     <tableColumn id="5" xr3:uid="{5338F6FB-43B0-44AF-AF8B-542FAC6CEDF0}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{64D6C993-8518-4A7C-9BDA-A54D7DBFBA8E}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{E5D987A3-C54A-4907-B710-79DB224E0008}" name="Current Status" totalsRowFunction="count"/>
@@ -1452,7 +1243,7 @@
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F96A3CC8-25D1-4CF8-877D-2816B26B7DC4}" name="Item Name" totalsRowLabel="Total"/>
-    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="45"/>
+    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="23"/>
     <tableColumn id="8" xr3:uid="{7D8F815E-A974-42A8-AC0B-AB8B951599A2}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{FEA94C75-B538-448A-A9F5-46F5A27E863D}" name="Year released"/>
     <tableColumn id="4" xr3:uid="{24998D92-36B7-4553-81E7-CB33711B31BB}" name="Special Reqs/Notes"/>
@@ -1474,7 +1265,7 @@
     <tableColumn id="13" xr3:uid="{EFFF3477-1A58-41CD-BFF3-45CE299505A7}" name="ID"/>
     <tableColumn id="8" xr3:uid="{C694899F-E385-4DE2-972A-7395A9633019}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{13C54556-A90A-4F9C-800D-3D838462DF46}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="22"/>
     <tableColumn id="5" xr3:uid="{6DE19FBC-9BD8-456E-9FC5-F633F61E4A34}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{68546225-0A78-43C1-A4F9-4D2E1DC008A3}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{0D7FD365-4F73-4A57-B8A1-CFAC47267923}" name="Current Status" totalsRowFunction="count"/>
@@ -1506,7 +1297,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:M59" totalsRowShown="0" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:M59" totalsRowShown="0" tableBorderDxfId="18">
   <autoFilter ref="A2:M59" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{D71C6020-33AC-4F3C-BC88-69BADE52FD9C}" name="Item"/>
@@ -1518,9 +1309,9 @@
     <tableColumn id="13" xr3:uid="{D6E0079E-D628-428A-8C40-CC4B7F920E56}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{7319329B-DA0F-470E-AE1F-CAF023744072}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{96CAC308-4A56-4EA5-AF3F-FCAC656EEA09}" name="SSD/HDD"/>
-    <tableColumn id="10" xr3:uid="{6EFEA34D-1A93-4407-A41E-DD47A214B1DA}" name="Est. Value" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{6EFEA34D-1A93-4407-A41E-DD47A214B1DA}" name="Est. Value" dataDxfId="17"/>
     <tableColumn id="12" xr3:uid="{04505084-FFBB-491E-B658-CE08D38C3E7B}" name="Notes"/>
-    <tableColumn id="9" xr3:uid="{6814BC74-3E15-43D3-BC09-F23C9C777339}" name="Date Donated" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{6814BC74-3E15-43D3-BC09-F23C9C777339}" name="Date Donated" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{45D6EFC2-97A5-4C00-9305-6B4ED43BEBB2}" name="Recipient"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1856,20 +1647,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5AA6A1-7D43-4966-8813-F497D895A5C2}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.109375" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="7" max="7" width="19.44140625" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1882,7 +1673,7 @@
       <c r="H1" s="23"/>
       <c r="I1" s="23"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1914,11 +1705,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E3" s="1"/>
       <c r="I3" s="16"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1944,11 +1735,11 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E5" s="1"/>
       <c r="I5" s="16"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1974,7 +1765,7 @@
         <v>45673</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -2001,7 +1792,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -2025,7 +1816,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2049,7 +1840,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -2073,7 +1864,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2097,7 +1888,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -2121,7 +1912,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="30">
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -2147,7 +1938,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -2176,7 +1967,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="45">
+    <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2202,7 +1993,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -2226,7 +2017,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="30">
+    <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2252,7 +2043,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2276,7 +2067,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="30">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -2302,7 +2093,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -2326,7 +2117,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="29.25">
+    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -2355,11 +2146,11 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E22" s="1"/>
       <c r="I22" s="16"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -2383,7 +2174,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -2407,11 +2198,11 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E25" s="1"/>
       <c r="I25" s="16"/>
     </row>
-    <row r="26" spans="1:9" ht="30">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -2437,7 +2228,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -2461,7 +2252,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -2485,7 +2276,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>53</v>
       </c>
@@ -2511,34 +2302,34 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="5:5">
+    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="5:5">
+    <row r="34" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="5:5">
+    <row r="35" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="5:5">
+    <row r="36" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="5:5">
+    <row r="37" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="5:5">
+    <row r="38" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="5:5">
+    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E39" s="1"/>
     </row>
   </sheetData>
@@ -2571,18 +2362,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEA6183-B753-401C-B21E-C502785DFA3D}">
   <dimension ref="A1:G63"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>56</v>
       </c>
@@ -2593,7 +2384,7 @@
       <c r="F1" s="24"/>
       <c r="G1" s="24"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2616,7 +2407,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>57</v>
       </c>
@@ -2637,7 +2428,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>57</v>
       </c>
@@ -2658,7 +2449,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1">
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>57</v>
       </c>
@@ -2681,7 +2472,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="43.5">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>57</v>
       </c>
@@ -2704,7 +2495,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>57</v>
       </c>
@@ -2725,7 +2516,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>57</v>
       </c>
@@ -2748,7 +2539,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>57</v>
       </c>
@@ -2769,7 +2560,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="B10" s="14"/>
       <c r="C10" s="9"/>
@@ -2778,7 +2569,7 @@
       <c r="F10" s="9"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>57</v>
       </c>
@@ -2799,7 +2590,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="60">
+    <row r="12" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>61</v>
       </c>
@@ -2822,7 +2613,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>61</v>
       </c>
@@ -2845,7 +2636,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>61</v>
       </c>
@@ -2866,7 +2657,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>61</v>
       </c>
@@ -2887,7 +2678,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>61</v>
       </c>
@@ -2908,7 +2699,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>61</v>
       </c>
@@ -2929,7 +2720,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>61</v>
       </c>
@@ -2950,7 +2741,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>61</v>
       </c>
@@ -2971,7 +2762,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>61</v>
       </c>
@@ -2992,7 +2783,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>61</v>
       </c>
@@ -3013,7 +2804,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>64</v>
       </c>
@@ -3034,7 +2825,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>65</v>
       </c>
@@ -3057,7 +2848,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>64</v>
       </c>
@@ -3078,7 +2869,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>64</v>
       </c>
@@ -3097,7 +2888,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="13"/>
       <c r="C26" s="5"/>
@@ -3106,7 +2897,7 @@
       <c r="F26" s="5"/>
       <c r="G26" s="7"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>64</v>
       </c>
@@ -3129,7 +2920,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>68</v>
       </c>
@@ -3150,7 +2941,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>69</v>
       </c>
@@ -3173,7 +2964,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>71</v>
       </c>
@@ -3196,7 +2987,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>73</v>
       </c>
@@ -3217,7 +3008,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>74</v>
       </c>
@@ -3238,7 +3029,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>75</v>
       </c>
@@ -3259,7 +3050,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>73</v>
       </c>
@@ -3280,7 +3071,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>76</v>
       </c>
@@ -3301,7 +3092,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>77</v>
       </c>
@@ -3324,7 +3115,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>64</v>
       </c>
@@ -3347,7 +3138,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>80</v>
       </c>
@@ -3367,7 +3158,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -3387,7 +3178,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>64</v>
       </c>
@@ -3410,7 +3201,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -3433,10 +3224,10 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G42" s="16"/>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>81</v>
       </c>
@@ -3456,7 +3247,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>81</v>
       </c>
@@ -3476,7 +3267,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>81</v>
       </c>
@@ -3496,7 +3287,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>86</v>
       </c>
@@ -3519,7 +3310,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>86</v>
       </c>
@@ -3542,7 +3333,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>88</v>
       </c>
@@ -3562,7 +3353,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>89</v>
       </c>
@@ -3579,7 +3370,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>91</v>
       </c>
@@ -3599,7 +3390,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>92</v>
       </c>
@@ -3619,7 +3410,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>93</v>
       </c>
@@ -3639,7 +3430,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>94</v>
       </c>
@@ -3662,7 +3453,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>97</v>
       </c>
@@ -3682,7 +3473,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>98</v>
       </c>
@@ -3705,7 +3496,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>100</v>
       </c>
@@ -3725,7 +3516,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>91</v>
       </c>
@@ -3745,7 +3536,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>75</v>
       </c>
@@ -3765,7 +3556,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -3788,16 +3579,16 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G60" s="16"/>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G61" s="16"/>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G62" s="16"/>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G63" s="16"/>
     </row>
   </sheetData>
@@ -3805,13 +3596,11 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:G63">
-    <cfRule type="expression" dxfId="47" priority="2">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3:G63">
-    <cfRule type="expression" dxfId="46" priority="1">
-      <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -3829,20 +3618,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F948288C-1730-49D1-BD4C-FC704F167D22}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5703125" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.109375" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>102</v>
       </c>
@@ -3855,7 +3644,7 @@
       <c r="H1" s="24"/>
       <c r="I1" s="24"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3884,7 +3673,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>103</v>
       </c>
@@ -3913,7 +3702,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -3942,91 +3731,91 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="5:5">
+    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="5:5">
+    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="5:5">
+    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="5:5">
+    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="5:5">
+    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="5:5">
+    <row r="22" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="5:5">
+    <row r="23" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="5:5">
+    <row r="24" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="5:5">
+    <row r="25" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="5:5">
+    <row r="26" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="5:5">
+    <row r="27" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="5:5">
+    <row r="28" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="5:5">
+    <row r="29" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="5:5">
+    <row r="30" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="5:5">
+    <row r="31" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="5:5">
+    <row r="32" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="5:5">
+    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E33" s="1"/>
     </row>
   </sheetData>
@@ -4058,22 +3847,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFE86381-3E33-4CB8-A62B-E48A74AB9667}">
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.33203125" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" customWidth="1"/>
-    <col min="10" max="10" width="18.7109375" style="19" customWidth="1"/>
-    <col min="11" max="11" width="21.28515625" customWidth="1"/>
+    <col min="7" max="7" width="17.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" style="19" customWidth="1"/>
+    <col min="11" max="11" width="21.33203125" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>107</v>
       </c>
@@ -4089,7 +3878,7 @@
       <c r="K1" s="26"/>
       <c r="L1" s="26"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>108</v>
       </c>
@@ -4127,7 +3916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>119</v>
       </c>
@@ -4163,7 +3952,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -4199,7 +3988,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -4235,10 +4024,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>128</v>
       </c>
@@ -4274,7 +4063,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -4310,7 +4099,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>133</v>
       </c>
@@ -4346,10 +4135,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -4385,7 +4174,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>138</v>
       </c>
@@ -4420,7 +4209,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>140</v>
       </c>
@@ -4456,7 +4245,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1">
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -4492,7 +4281,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1">
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>142</v>
       </c>
@@ -4528,7 +4317,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1">
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>144</v>
       </c>
@@ -4564,7 +4353,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1">
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>146</v>
       </c>
@@ -4600,7 +4389,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1">
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>149</v>
       </c>
@@ -4636,7 +4425,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1">
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>149</v>
       </c>
@@ -4672,7 +4461,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1">
+    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>151</v>
       </c>
@@ -4708,7 +4497,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1">
+    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>151</v>
       </c>
@@ -4744,7 +4533,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1">
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -4780,7 +4569,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1">
+    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>154</v>
       </c>
@@ -4816,7 +4605,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1">
+    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -4852,7 +4641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1">
+    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>128</v>
       </c>
@@ -4888,7 +4677,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1">
+    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>156</v>
       </c>
@@ -4924,7 +4713,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1">
+    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -4960,7 +4749,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1">
+    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>64</v>
       </c>
@@ -4996,7 +4785,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1">
+    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>159</v>
       </c>
@@ -5032,129 +4821,53 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1">
+    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="K30" s="1"/>
     </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1">
+    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1">
+    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="K32" s="1"/>
     </row>
-    <row r="33" spans="11:11" ht="15" customHeight="1">
+    <row r="33" spans="11:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="K33" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A15:C15 A3:K9 A11:K14 E15:K15 A16:K25">
-    <cfRule type="expression" dxfId="43" priority="21">
+  <conditionalFormatting sqref="A27:A28">
+    <cfRule type="expression" dxfId="13" priority="17">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="18">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:K9 A11:K14 A15:C15 E15:K15 A16:K25">
+    <cfRule type="expression" dxfId="11" priority="21">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A15:C15 A3:L9 A11:L14 E15:L15 A16:L25">
-    <cfRule type="expression" dxfId="42" priority="22">
+  <conditionalFormatting sqref="A3:L9 A11:L14 A15:C15 E15:L15 A16:L25">
+    <cfRule type="expression" dxfId="10" priority="22">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A27">
-    <cfRule type="expression" dxfId="41" priority="20">
+  <conditionalFormatting sqref="G26:G29">
+    <cfRule type="expression" dxfId="9" priority="9">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="10">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A27">
-    <cfRule type="expression" dxfId="40" priority="19">
+  <conditionalFormatting sqref="H26:H29">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A28">
-    <cfRule type="expression" dxfId="39" priority="18">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A28">
-    <cfRule type="expression" dxfId="38" priority="17">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G28">
-    <cfRule type="expression" dxfId="37" priority="15">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G28">
-    <cfRule type="expression" dxfId="36" priority="16">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G26">
-    <cfRule type="expression" dxfId="35" priority="13">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G26">
-    <cfRule type="expression" dxfId="34" priority="14">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G27">
-    <cfRule type="expression" dxfId="33" priority="11">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G27">
-    <cfRule type="expression" dxfId="32" priority="12">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
-    <cfRule type="expression" dxfId="31" priority="9">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
-    <cfRule type="expression" dxfId="30" priority="10">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H26">
-    <cfRule type="expression" dxfId="29" priority="7">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H26">
-    <cfRule type="expression" dxfId="28" priority="8">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
-    <cfRule type="expression" dxfId="27" priority="5">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
-    <cfRule type="expression" dxfId="26" priority="6">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
-    <cfRule type="expression" dxfId="25" priority="3">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
-    <cfRule type="expression" dxfId="24" priority="4">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="expression" dxfId="23" priority="1">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="expression" dxfId="22" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5177,26 +4890,26 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19592962-4FD3-47C5-914B-6346C180BC2C}">
   <dimension ref="A1:O59"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.28515625" customWidth="1"/>
-    <col min="12" max="12" width="16.85546875" style="16" customWidth="1"/>
-    <col min="13" max="13" width="29.140625" customWidth="1"/>
-    <col min="14" max="14" width="27.7109375" customWidth="1"/>
-    <col min="15" max="15" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.109375" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.33203125" customWidth="1"/>
+    <col min="12" max="12" width="16.88671875" style="16" customWidth="1"/>
+    <col min="13" max="13" width="29.109375" customWidth="1"/>
+    <col min="14" max="14" width="27.6640625" customWidth="1"/>
+    <col min="15" max="15" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="17" t="s">
         <v>161</v>
       </c>
@@ -5218,7 +4931,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>108</v>
       </c>
@@ -5267,12 +4980,33 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>166</v>
       </c>
       <c r="B3" t="s">
         <v>126</v>
+      </c>
+      <c r="C3">
+        <v>2019</v>
+      </c>
+      <c r="D3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H3">
+        <v>256</v>
+      </c>
+      <c r="I3" t="s">
+        <v>124</v>
       </c>
       <c r="J3" s="19">
         <v>225</v>
@@ -5285,12 +5019,33 @@
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>166</v>
       </c>
       <c r="B4" t="s">
         <v>126</v>
+      </c>
+      <c r="C4">
+        <v>2019</v>
+      </c>
+      <c r="D4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H4">
+        <v>256</v>
+      </c>
+      <c r="I4" t="s">
+        <v>124</v>
       </c>
       <c r="J4" s="19">
         <v>225</v>
@@ -5303,12 +5058,33 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>166</v>
       </c>
       <c r="B5" t="s">
         <v>126</v>
+      </c>
+      <c r="C5">
+        <v>2019</v>
+      </c>
+      <c r="D5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5" t="s">
+        <v>130</v>
+      </c>
+      <c r="H5">
+        <v>256</v>
+      </c>
+      <c r="I5" t="s">
+        <v>124</v>
       </c>
       <c r="J5" s="19">
         <v>225</v>
@@ -5321,12 +5097,33 @@
         <v>167</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>166</v>
       </c>
       <c r="B6" t="s">
         <v>126</v>
+      </c>
+      <c r="C6">
+        <v>2019</v>
+      </c>
+      <c r="D6" t="s">
+        <v>254</v>
+      </c>
+      <c r="E6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H6">
+        <v>256</v>
+      </c>
+      <c r="I6" t="s">
+        <v>124</v>
       </c>
       <c r="J6" s="19">
         <v>225</v>
@@ -5339,12 +5136,33 @@
         <v>167</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>166</v>
       </c>
       <c r="B7" t="s">
         <v>126</v>
+      </c>
+      <c r="C7">
+        <v>2019</v>
+      </c>
+      <c r="D7" t="s">
+        <v>254</v>
+      </c>
+      <c r="E7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H7">
+        <v>256</v>
+      </c>
+      <c r="I7" t="s">
+        <v>124</v>
       </c>
       <c r="J7" s="19">
         <v>225</v>
@@ -5357,12 +5175,33 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>166</v>
       </c>
       <c r="B8" t="s">
         <v>126</v>
+      </c>
+      <c r="C8">
+        <v>2019</v>
+      </c>
+      <c r="D8" t="s">
+        <v>254</v>
+      </c>
+      <c r="E8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8" t="s">
+        <v>130</v>
+      </c>
+      <c r="H8">
+        <v>256</v>
+      </c>
+      <c r="I8" t="s">
+        <v>124</v>
       </c>
       <c r="J8" s="19">
         <v>225</v>
@@ -5375,12 +5214,33 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>166</v>
       </c>
       <c r="B9" t="s">
         <v>126</v>
+      </c>
+      <c r="C9">
+        <v>2019</v>
+      </c>
+      <c r="D9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9" t="s">
+        <v>130</v>
+      </c>
+      <c r="H9">
+        <v>256</v>
+      </c>
+      <c r="I9" t="s">
+        <v>124</v>
       </c>
       <c r="J9" s="19">
         <v>225</v>
@@ -5393,7 +5253,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>168</v>
       </c>
@@ -5432,7 +5292,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>170</v>
       </c>
@@ -5471,7 +5331,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>172</v>
       </c>
@@ -5512,7 +5372,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>175</v>
       </c>
@@ -5551,7 +5411,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>168</v>
       </c>
@@ -5590,7 +5450,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>177</v>
       </c>
@@ -5629,7 +5489,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>179</v>
       </c>
@@ -5670,7 +5530,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>186</v>
       </c>
@@ -5711,7 +5571,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>187</v>
       </c>
@@ -5752,7 +5612,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -5793,7 +5653,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="43.5">
+    <row r="20" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -5834,7 +5694,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>196</v>
       </c>
@@ -5873,7 +5733,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>64</v>
       </c>
@@ -5912,7 +5772,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>64</v>
       </c>
@@ -5951,7 +5811,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>64</v>
       </c>
@@ -5990,7 +5850,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>64</v>
       </c>
@@ -6029,7 +5889,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -6068,7 +5928,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -6107,7 +5967,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>199</v>
       </c>
@@ -6146,7 +6006,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>199</v>
       </c>
@@ -6185,7 +6045,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>128</v>
       </c>
@@ -6224,7 +6084,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>61</v>
       </c>
@@ -6263,7 +6123,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -6301,7 +6161,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -6339,7 +6199,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>203</v>
       </c>
@@ -6377,7 +6237,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>203</v>
       </c>
@@ -6415,7 +6275,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>203</v>
       </c>
@@ -6453,7 +6313,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>203</v>
       </c>
@@ -6491,7 +6351,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>203</v>
       </c>
@@ -6529,7 +6389,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>203</v>
       </c>
@@ -6567,7 +6427,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="15" customHeight="1">
+    <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>203</v>
       </c>
@@ -6605,7 +6465,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="15" customHeight="1">
+    <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>203</v>
       </c>
@@ -6643,7 +6503,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="15" customHeight="1">
+    <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>203</v>
       </c>
@@ -6681,7 +6541,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="15" customHeight="1">
+    <row r="43" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>140</v>
       </c>
@@ -6720,7 +6580,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="15" customHeight="1">
+    <row r="44" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>61</v>
       </c>
@@ -6759,67 +6619,67 @@
         <v>206</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="15" customHeight="1">
+    <row r="45" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L45" s="15"/>
     </row>
-    <row r="46" spans="1:13" ht="15" customHeight="1">
+    <row r="46" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L46" s="15"/>
     </row>
-    <row r="47" spans="1:13" ht="15" customHeight="1">
+    <row r="47" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L47" s="15"/>
     </row>
-    <row r="48" spans="1:13" ht="15" customHeight="1">
+    <row r="48" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L48" s="15"/>
     </row>
-    <row r="49" spans="12:12" ht="15" customHeight="1">
+    <row r="49" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L49" s="15"/>
     </row>
-    <row r="50" spans="12:12" ht="15" customHeight="1">
+    <row r="50" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L50" s="15"/>
     </row>
-    <row r="51" spans="12:12" ht="15" customHeight="1">
+    <row r="51" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L51" s="15"/>
     </row>
-    <row r="52" spans="12:12" ht="15" customHeight="1">
+    <row r="52" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L52" s="15"/>
     </row>
-    <row r="53" spans="12:12" ht="15" customHeight="1">
+    <row r="53" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L53" s="15"/>
     </row>
-    <row r="54" spans="12:12" ht="15" customHeight="1">
+    <row r="54" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L54" s="15"/>
     </row>
-    <row r="55" spans="12:12" ht="15" customHeight="1">
+    <row r="55" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L55" s="15"/>
     </row>
-    <row r="56" spans="12:12" ht="15" customHeight="1">
+    <row r="56" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L56" s="15"/>
     </row>
-    <row r="57" spans="12:12" ht="15" customHeight="1">
+    <row r="57" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L57" s="15"/>
     </row>
-    <row r="58" spans="12:12" ht="15" customHeight="1">
+    <row r="58" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L58" s="15"/>
     </row>
-    <row r="59" spans="12:12" ht="15" customHeight="1">
+    <row r="59" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L59" s="15"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A44:F44 H44:K44">
-    <cfRule type="expression" dxfId="18" priority="15">
+    <cfRule type="expression" dxfId="5" priority="15">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:F44 H44:L44">
-    <cfRule type="expression" dxfId="17" priority="16">
+    <cfRule type="expression" dxfId="4" priority="16">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M44 A45:M59 A3:M9 A10:G15 I10:M15 A16:M43">
+  <conditionalFormatting sqref="A3:M9 A10:G15 I10:M15 A16:M43 M44 A45:M59">
     <cfRule type="expression" priority="17">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="18">
+    <cfRule type="expression" dxfId="3" priority="18">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6827,67 +6687,15 @@
     <cfRule type="expression" priority="13">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="14">
+    <cfRule type="expression" dxfId="2" priority="14">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
-    <cfRule type="expression" dxfId="14" priority="11">
+  <conditionalFormatting sqref="H10:H15">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
-    <cfRule type="expression" dxfId="13" priority="12">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="expression" dxfId="12" priority="9">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="expression" dxfId="11" priority="10">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="expression" dxfId="10" priority="7">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="expression" dxfId="9" priority="8">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="expression" dxfId="8" priority="5">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="expression" dxfId="7" priority="6">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
-    <cfRule type="expression" dxfId="6" priority="3">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
-    <cfRule type="expression" dxfId="5" priority="4">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6911,19 +6719,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66F9EB6D-6D2E-43F3-A79F-D2A5CF3A037E}">
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="46.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" customWidth="1"/>
+    <col min="1" max="1" width="46.109375" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>207</v>
       </c>
       <c r="B1" s="26"/>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>108</v>
       </c>
@@ -6931,7 +6739,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>209</v>
       </c>
@@ -6939,7 +6747,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>210</v>
       </c>
@@ -6947,7 +6755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>211</v>
       </c>
@@ -6955,7 +6763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>212</v>
       </c>
@@ -6963,7 +6771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>213</v>
       </c>
@@ -6971,7 +6779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>214</v>
       </c>
@@ -6979,7 +6787,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>215</v>
       </c>
@@ -6987,7 +6795,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>216</v>
       </c>
@@ -6995,7 +6803,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>217</v>
       </c>
@@ -7003,7 +6811,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>218</v>
       </c>
@@ -7011,7 +6819,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>219</v>
       </c>
@@ -7019,7 +6827,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>220</v>
       </c>
@@ -7027,7 +6835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>221</v>
       </c>
@@ -7035,7 +6843,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>222</v>
       </c>
@@ -7043,7 +6851,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>223</v>
       </c>
@@ -7051,7 +6859,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>224</v>
       </c>
@@ -7059,7 +6867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>225</v>
       </c>
@@ -7067,7 +6875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>226</v>
       </c>
@@ -7075,7 +6883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>227</v>
       </c>
@@ -7083,7 +6891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>228</v>
       </c>
@@ -7091,7 +6899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>229</v>
       </c>
@@ -7099,7 +6907,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>230</v>
       </c>
@@ -7107,7 +6915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>231</v>
       </c>
@@ -7115,7 +6923,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>232</v>
       </c>
@@ -7123,7 +6931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>233</v>
       </c>
@@ -7131,7 +6939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>234</v>
       </c>
@@ -7139,7 +6947,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>235</v>
       </c>
@@ -7147,7 +6955,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>236</v>
       </c>
@@ -7155,7 +6963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>237</v>
       </c>
@@ -7163,7 +6971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>238</v>
       </c>
@@ -7171,7 +6979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>239</v>
       </c>
@@ -7179,7 +6987,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>240</v>
       </c>
@@ -7187,7 +6995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>241</v>
       </c>
@@ -7195,7 +7003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>242</v>
       </c>
@@ -7203,7 +7011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>243</v>
       </c>
@@ -7211,7 +7019,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>244</v>
       </c>
@@ -7219,7 +7027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>245</v>
       </c>
@@ -7227,7 +7035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>246</v>
       </c>
@@ -7235,7 +7043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>247</v>
       </c>
@@ -7243,7 +7051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>248</v>
       </c>
@@ -7251,7 +7059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>249</v>
       </c>
@@ -7259,7 +7067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>250</v>
       </c>
@@ -7267,7 +7075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>251</v>
       </c>
@@ -7275,7 +7083,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>252</v>
       </c>
@@ -7283,7 +7091,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>253</v>
       </c>

--- a/data/OldInventorySystem.xlsx
+++ b/data/OldInventorySystem.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucasja\git\Inventory-System\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\lucasja\Inventory-System\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1769F4D0-9B06-4025-9E21-BBB42E246945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39906191-F046-4C44-A76B-7AC87B711D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Laptops" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Ready To Donate" sheetId="2" r:id="rId4"/>
     <sheet name="Donated" sheetId="6" r:id="rId5"/>
     <sheet name="Parts" sheetId="3" r:id="rId6"/>
+    <sheet name="Tools" sheetId="12" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="257">
   <si>
     <t>LAPTOPS</t>
   </si>
@@ -670,45 +671,6 @@
     <t>Qty</t>
   </si>
   <si>
-    <t>2.5" SSDs</t>
-  </si>
-  <si>
-    <t>M.2 SSDs</t>
-  </si>
-  <si>
-    <t>1GB DDR3 SODIMM</t>
-  </si>
-  <si>
-    <t>2GB DDR4 SODIMM</t>
-  </si>
-  <si>
-    <t>2GB DDR3 SODIMM</t>
-  </si>
-  <si>
-    <t>8GB DDR4 SODIMM</t>
-  </si>
-  <si>
-    <t>8GB DDR3 SODIMM</t>
-  </si>
-  <si>
-    <t>4GB DDR4 SODIMM</t>
-  </si>
-  <si>
-    <t>4GB DDR3 SODIMM</t>
-  </si>
-  <si>
-    <t>8GB DDR4 DIMM</t>
-  </si>
-  <si>
-    <t>8GB DDR3 DIMM</t>
-  </si>
-  <si>
-    <t>16GB DDR4 DIMM</t>
-  </si>
-  <si>
-    <t>4GB DDR3 DIMM</t>
-  </si>
-  <si>
     <t>USB Keyboard</t>
   </si>
   <si>
@@ -806,6 +768,51 @@
   </si>
   <si>
     <t>Intel core i7-i8850H</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>SATA SSD</t>
+  </si>
+  <si>
+    <t>M.2 SSD</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>SODIMM</t>
+  </si>
+  <si>
+    <t>8GB DDR4</t>
+  </si>
+  <si>
+    <t>2GB DDR3</t>
+  </si>
+  <si>
+    <t>4GB DDR3</t>
+  </si>
+  <si>
+    <t>2GB DDR4</t>
+  </si>
+  <si>
+    <t>8GB DDR3</t>
+  </si>
+  <si>
+    <t>4GB DDR4</t>
+  </si>
+  <si>
+    <t>16GB DDR4</t>
+  </si>
+  <si>
+    <t>1GB DDR3</t>
+  </si>
+  <si>
+    <t>DIMM</t>
+  </si>
+  <si>
+    <t>TOOLS</t>
   </si>
 </sst>
 </file>
@@ -948,7 +955,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1002,6 +1009,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1165,20 +1175,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1199,6 +1195,20 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1224,7 +1234,7 @@
     <tableColumn id="13" xr3:uid="{5BEE40AD-E450-4A13-BFB5-1D0CED084DB3}" name="ID"/>
     <tableColumn id="8" xr3:uid="{E9AB9B46-3541-4715-8E5B-024096D78342}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{F7DAC8DD-8096-40F1-8780-1DB9CB4EC72F}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="21"/>
     <tableColumn id="5" xr3:uid="{5338F6FB-43B0-44AF-AF8B-542FAC6CEDF0}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{64D6C993-8518-4A7C-9BDA-A54D7DBFBA8E}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{E5D987A3-C54A-4907-B710-79DB224E0008}" name="Current Status" totalsRowFunction="count"/>
@@ -1243,7 +1253,7 @@
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F96A3CC8-25D1-4CF8-877D-2816B26B7DC4}" name="Item Name" totalsRowLabel="Total"/>
-    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="20"/>
     <tableColumn id="8" xr3:uid="{7D8F815E-A974-42A8-AC0B-AB8B951599A2}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{FEA94C75-B538-448A-A9F5-46F5A27E863D}" name="Year released"/>
     <tableColumn id="4" xr3:uid="{24998D92-36B7-4553-81E7-CB33711B31BB}" name="Special Reqs/Notes"/>
@@ -1265,7 +1275,7 @@
     <tableColumn id="13" xr3:uid="{EFFF3477-1A58-41CD-BFF3-45CE299505A7}" name="ID"/>
     <tableColumn id="8" xr3:uid="{C694899F-E385-4DE2-972A-7395A9633019}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{13C54556-A90A-4F9C-800D-3D838462DF46}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="19"/>
     <tableColumn id="5" xr3:uid="{6DE19FBC-9BD8-456E-9FC5-F633F61E4A34}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{68546225-0A78-43C1-A4F9-4D2E1DC008A3}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{0D7FD365-4F73-4A57-B8A1-CFAC47267923}" name="Current Status" totalsRowFunction="count"/>
@@ -1276,7 +1286,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:L33" totalsRowShown="0" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:L33" totalsRowShown="0" tableBorderDxfId="18">
   <autoFilter ref="A2:L33" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{73648E04-2EA1-4ADB-8E24-E7DDE01C0462}" name="Item"/>
@@ -1288,8 +1298,8 @@
     <tableColumn id="2" xr3:uid="{C85B34EB-06B2-40A8-BBCB-B5F170EF3F82}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{A686D1B3-031E-4544-A98D-8F3144FA62B0}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{AB29939A-0AF4-4451-A6F4-2144F8957E73}" name="SSD/HDD"/>
-    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="16"/>
     <tableColumn id="12" xr3:uid="{67EC036F-98F6-4C6B-BDD7-99DB9B6ADF97}" name="ID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1297,7 +1307,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:M59" totalsRowShown="0" tableBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:M59" totalsRowShown="0" tableBorderDxfId="24">
   <autoFilter ref="A2:M59" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{D71C6020-33AC-4F3C-BC88-69BADE52FD9C}" name="Item"/>
@@ -1309,9 +1319,9 @@
     <tableColumn id="13" xr3:uid="{D6E0079E-D628-428A-8C40-CC4B7F920E56}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{7319329B-DA0F-470E-AE1F-CAF023744072}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{96CAC308-4A56-4EA5-AF3F-FCAC656EEA09}" name="SSD/HDD"/>
-    <tableColumn id="10" xr3:uid="{6EFEA34D-1A93-4407-A41E-DD47A214B1DA}" name="Est. Value" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{6EFEA34D-1A93-4407-A41E-DD47A214B1DA}" name="Est. Value" dataDxfId="23"/>
     <tableColumn id="12" xr3:uid="{04505084-FFBB-491E-B658-CE08D38C3E7B}" name="Notes"/>
-    <tableColumn id="9" xr3:uid="{6814BC74-3E15-43D3-BC09-F23C9C777339}" name="Date Donated" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{6814BC74-3E15-43D3-BC09-F23C9C777339}" name="Date Donated" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{45D6EFC2-97A5-4C00-9305-6B4ED43BEBB2}" name="Recipient"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1319,11 +1329,24 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}" name="Parts" displayName="Parts" ref="A2:B47" totalsRowShown="0">
-  <autoFilter ref="A2:B47" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AE6A62C8-410E-43CA-9FCC-DB171FCD3CD1}" name="Item"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}" name="Parts" displayName="Parts" ref="A2:C15" totalsRowShown="0">
+  <autoFilter ref="A2:C15" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{AE6A62C8-410E-43CA-9FCC-DB171FCD3CD1}" name="Type"/>
+    <tableColumn id="3" xr3:uid="{8BE6192C-E1B9-4BD5-BEB2-D26E68C58775}" name="Description"/>
     <tableColumn id="2" xr3:uid="{675E5FD2-430E-4D35-9481-575A83791C4E}" name="Qty"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{42D1C34C-9303-4D46-A107-174D17AE2274}" name="Parts5" displayName="Parts5" ref="A2:C34" totalsRowShown="0">
+  <autoFilter ref="A2:C34" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{C29E963F-354B-4750-B17F-22461F6DC5F4}" name="Type"/>
+    <tableColumn id="3" xr3:uid="{7C7B0B32-2D9C-4EDB-8E56-4C2ADECB5869}" name="Description"/>
+    <tableColumn id="2" xr3:uid="{1155C0CA-025A-4922-8B0E-F2A817B3BB60}" name="Qty"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4991,7 +5014,7 @@
         <v>2019</v>
       </c>
       <c r="D3" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="E3" t="s">
         <v>137</v>
@@ -5030,7 +5053,7 @@
         <v>2019</v>
       </c>
       <c r="D4" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="E4" t="s">
         <v>137</v>
@@ -5069,7 +5092,7 @@
         <v>2019</v>
       </c>
       <c r="D5" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="E5" t="s">
         <v>137</v>
@@ -5108,7 +5131,7 @@
         <v>2019</v>
       </c>
       <c r="D6" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="E6" t="s">
         <v>137</v>
@@ -5147,7 +5170,7 @@
         <v>2019</v>
       </c>
       <c r="D7" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="E7" t="s">
         <v>137</v>
@@ -5186,7 +5209,7 @@
         <v>2019</v>
       </c>
       <c r="D8" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="E8" t="s">
         <v>137</v>
@@ -5225,7 +5248,7 @@
         <v>2019</v>
       </c>
       <c r="D9" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="E9" t="s">
         <v>137</v>
@@ -6718,390 +6741,467 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66F9EB6D-6D2E-43F3-A79F-D2A5CF3A037E}">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="46.109375" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" customWidth="1"/>
+    <col min="1" max="1" width="42.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B1" s="27"/>
+      <c r="C1" s="26"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B2" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" t="s">
+        <v>247</v>
+      </c>
+      <c r="C8">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" t="s">
+        <v>252</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>255</v>
+      </c>
+      <c r="B12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>255</v>
+      </c>
+      <c r="B13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>255</v>
+      </c>
+      <c r="B14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>255</v>
+      </c>
+      <c r="B15" t="s">
+        <v>249</v>
+      </c>
+      <c r="C15">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6AEFF60-27EE-498D-A491-C67356035C05}">
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="42.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="26"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>209</v>
       </c>
-      <c r="B3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>210</v>
       </c>
-      <c r="B4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>211</v>
       </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>212</v>
       </c>
-      <c r="B6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>213</v>
       </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>214</v>
       </c>
-      <c r="B8">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>215</v>
       </c>
-      <c r="B9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>216</v>
       </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>217</v>
       </c>
-      <c r="B11">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>218</v>
       </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>219</v>
       </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>220</v>
       </c>
-      <c r="B14">
+      <c r="C14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>221</v>
       </c>
-      <c r="B15">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>222</v>
       </c>
-      <c r="B16">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>223</v>
       </c>
-      <c r="B17">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>224</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>225</v>
       </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>226</v>
       </c>
-      <c r="B20">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>227</v>
       </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>228</v>
       </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>229</v>
       </c>
-      <c r="B23">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>230</v>
       </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C24">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>231</v>
       </c>
-      <c r="B25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>232</v>
       </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>233</v>
       </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>234</v>
       </c>
-      <c r="B28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>235</v>
       </c>
-      <c r="B29">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>236</v>
       </c>
-      <c r="B30">
+      <c r="C30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>237</v>
       </c>
-      <c r="B31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>238</v>
       </c>
-      <c r="B32">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C32">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>239</v>
       </c>
-      <c r="B33">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C33">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>240</v>
       </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>241</v>
-      </c>
-      <c r="B35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>242</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>243</v>
-      </c>
-      <c r="B37">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>244</v>
-      </c>
-      <c r="B38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>245</v>
-      </c>
-      <c r="B39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>246</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>247</v>
-      </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>248</v>
-      </c>
-      <c r="B42">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>249</v>
-      </c>
-      <c r="B43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>250</v>
-      </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>251</v>
-      </c>
-      <c r="B45">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>252</v>
-      </c>
-      <c r="B46">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>253</v>
-      </c>
-      <c r="B47">
+      <c r="C34">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/OldInventorySystem.xlsx
+++ b/data/OldInventorySystem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\lucasja\Inventory-System\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39906191-F046-4C44-A76B-7AC87B711D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843F4EDD-8E2F-4262-BF42-795457F9E7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Laptops" sheetId="1" r:id="rId1"/>
@@ -776,9 +776,6 @@
     <t>SATA SSD</t>
   </si>
   <si>
-    <t>M.2 SSD</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -813,6 +810,9 @@
   </si>
   <si>
     <t>TOOLS</t>
+  </si>
+  <si>
+    <t>M2 SSD</t>
   </si>
 </sst>
 </file>
@@ -955,7 +955,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -999,19 +999,16 @@
     <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1175,6 +1172,20 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1195,20 +1206,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1234,7 +1231,7 @@
     <tableColumn id="13" xr3:uid="{5BEE40AD-E450-4A13-BFB5-1D0CED084DB3}" name="ID"/>
     <tableColumn id="8" xr3:uid="{E9AB9B46-3541-4715-8E5B-024096D78342}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{F7DAC8DD-8096-40F1-8780-1DB9CB4EC72F}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="24"/>
     <tableColumn id="5" xr3:uid="{5338F6FB-43B0-44AF-AF8B-542FAC6CEDF0}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{64D6C993-8518-4A7C-9BDA-A54D7DBFBA8E}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{E5D987A3-C54A-4907-B710-79DB224E0008}" name="Current Status" totalsRowFunction="count"/>
@@ -1253,7 +1250,7 @@
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F96A3CC8-25D1-4CF8-877D-2816B26B7DC4}" name="Item Name" totalsRowLabel="Total"/>
-    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="23"/>
     <tableColumn id="8" xr3:uid="{7D8F815E-A974-42A8-AC0B-AB8B951599A2}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{FEA94C75-B538-448A-A9F5-46F5A27E863D}" name="Year released"/>
     <tableColumn id="4" xr3:uid="{24998D92-36B7-4553-81E7-CB33711B31BB}" name="Special Reqs/Notes"/>
@@ -1275,7 +1272,7 @@
     <tableColumn id="13" xr3:uid="{EFFF3477-1A58-41CD-BFF3-45CE299505A7}" name="ID"/>
     <tableColumn id="8" xr3:uid="{C694899F-E385-4DE2-972A-7395A9633019}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{13C54556-A90A-4F9C-800D-3D838462DF46}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="22"/>
     <tableColumn id="5" xr3:uid="{6DE19FBC-9BD8-456E-9FC5-F633F61E4A34}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{68546225-0A78-43C1-A4F9-4D2E1DC008A3}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{0D7FD365-4F73-4A57-B8A1-CFAC47267923}" name="Current Status" totalsRowFunction="count"/>
@@ -1286,7 +1283,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:L33" totalsRowShown="0" tableBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:L33" totalsRowShown="0" tableBorderDxfId="21">
   <autoFilter ref="A2:L33" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{73648E04-2EA1-4ADB-8E24-E7DDE01C0462}" name="Item"/>
@@ -1298,8 +1295,8 @@
     <tableColumn id="2" xr3:uid="{C85B34EB-06B2-40A8-BBCB-B5F170EF3F82}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{A686D1B3-031E-4544-A98D-8F3144FA62B0}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{AB29939A-0AF4-4451-A6F4-2144F8957E73}" name="SSD/HDD"/>
-    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="19"/>
     <tableColumn id="12" xr3:uid="{67EC036F-98F6-4C6B-BDD7-99DB9B6ADF97}" name="ID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1307,7 +1304,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:M59" totalsRowShown="0" tableBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:M59" totalsRowShown="0" tableBorderDxfId="18">
   <autoFilter ref="A2:M59" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{D71C6020-33AC-4F3C-BC88-69BADE52FD9C}" name="Item"/>
@@ -1319,9 +1316,9 @@
     <tableColumn id="13" xr3:uid="{D6E0079E-D628-428A-8C40-CC4B7F920E56}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{7319329B-DA0F-470E-AE1F-CAF023744072}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{96CAC308-4A56-4EA5-AF3F-FCAC656EEA09}" name="SSD/HDD"/>
-    <tableColumn id="10" xr3:uid="{6EFEA34D-1A93-4407-A41E-DD47A214B1DA}" name="Est. Value" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{6EFEA34D-1A93-4407-A41E-DD47A214B1DA}" name="Est. Value" dataDxfId="17"/>
     <tableColumn id="12" xr3:uid="{04505084-FFBB-491E-B658-CE08D38C3E7B}" name="Notes"/>
-    <tableColumn id="9" xr3:uid="{6814BC74-3E15-43D3-BC09-F23C9C777339}" name="Date Donated" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{6814BC74-3E15-43D3-BC09-F23C9C777339}" name="Date Donated" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{45D6EFC2-97A5-4C00-9305-6B4ED43BEBB2}" name="Recipient"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1684,17 +1681,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -2397,15 +2394,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -3655,17 +3652,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -3886,20 +3883,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
     </row>
     <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -6750,18 +6747,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="26"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>242</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>208</v>
@@ -6777,7 +6774,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -6785,10 +6782,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -6796,10 +6793,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -6807,10 +6804,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -6818,10 +6815,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" t="s">
         <v>246</v>
-      </c>
-      <c r="B8" t="s">
-        <v>247</v>
       </c>
       <c r="C8">
         <v>18</v>
@@ -6829,10 +6826,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -6840,10 +6837,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -6851,10 +6848,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C11">
         <v>16</v>
@@ -6862,10 +6859,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -6873,10 +6870,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -6884,10 +6881,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -6895,10 +6892,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C15">
         <v>11</v>
@@ -6926,18 +6923,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
-        <v>256</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="26"/>
+      <c r="A1" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>242</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>208</v>

--- a/data/OldInventorySystem.xlsx
+++ b/data/OldInventorySystem.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\lucasja\Inventory-System\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rosehulman-my.sharepoint.com/personal/lucasja_rose-hulman_edu/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843F4EDD-8E2F-4262-BF42-795457F9E7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3460" documentId="8_{A0F2C8DF-695D-4A53-BA74-C2F5D1F57A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73C00331-DB68-481F-98A9-F3303D7051BD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="4" activeTab="5" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Laptops" sheetId="1" r:id="rId1"/>
     <sheet name="Desktops" sheetId="7" r:id="rId2"/>
     <sheet name="Tablets" sheetId="10" r:id="rId3"/>
     <sheet name="Ready To Donate" sheetId="2" r:id="rId4"/>
-    <sheet name="Donated" sheetId="6" r:id="rId5"/>
-    <sheet name="Parts" sheetId="3" r:id="rId6"/>
-    <sheet name="Tools" sheetId="12" r:id="rId7"/>
+    <sheet name="Donated" sheetId="11" r:id="rId5"/>
+    <sheet name="Parts" sheetId="12" r:id="rId6"/>
+    <sheet name="Tools" sheetId="13" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="255">
   <si>
     <t>LAPTOPS</t>
   </si>
@@ -665,40 +665,133 @@
     <t>Wabash Activity Center</t>
   </si>
   <si>
-    <t>PARTS</t>
+    <t>y</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Description</t>
   </si>
   <si>
     <t>Qty</t>
   </si>
   <si>
-    <t>USB Keyboard</t>
-  </si>
-  <si>
-    <t>USB Mouse</t>
-  </si>
-  <si>
-    <t>Wireless Mouse</t>
-  </si>
-  <si>
-    <t>Wireless Keyboard/Mouse kit</t>
-  </si>
-  <si>
-    <t>iFixit Moray kit</t>
+    <t>Donated?</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>SATA SSD</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>M2 SSD</t>
+  </si>
+  <si>
+    <t>SODIMM</t>
+  </si>
+  <si>
+    <t>1GB DDR3</t>
+  </si>
+  <si>
+    <t>2GB DDR4</t>
+  </si>
+  <si>
+    <t>2GB DDR3</t>
+  </si>
+  <si>
+    <t>8GB DDR4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>8GB DDR3</t>
+  </si>
+  <si>
+    <t>4GB DDR4</t>
+  </si>
+  <si>
+    <t>4GB DDR3</t>
+  </si>
+  <si>
+    <t>DIMM</t>
+  </si>
+  <si>
+    <t>16GB DDR4</t>
+  </si>
+  <si>
+    <t>GPU</t>
+  </si>
+  <si>
+    <t>Nvidia P1000</t>
+  </si>
+  <si>
+    <t>TOOLS</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>iFixit Moray Kit (complete)</t>
+  </si>
+  <si>
+    <t>Screwdriver Kit</t>
+  </si>
+  <si>
+    <t>iFixit Pro Tech Toolkit (complete)</t>
   </si>
   <si>
     <t>iFixit Project Mat</t>
   </si>
   <si>
-    <t>iFixit Pro Tech Toolkit</t>
-  </si>
-  <si>
-    <t>Cleaning cloths</t>
-  </si>
-  <si>
-    <t>Thermal paste</t>
-  </si>
-  <si>
-    <t>Power Strips</t>
+    <t>Screw Organizer</t>
+  </si>
+  <si>
+    <t>Magnetic Parts Tray</t>
+  </si>
+  <si>
+    <t>Anker Power Strip</t>
+  </si>
+  <si>
+    <t>Power Strip</t>
+  </si>
+  <si>
+    <t>Generic Power Strip</t>
+  </si>
+  <si>
+    <t>USB A to Ethernet</t>
+  </si>
+  <si>
+    <t>Adapter</t>
+  </si>
+  <si>
+    <t>Duster</t>
+  </si>
+  <si>
+    <t>Miscellaneous</t>
+  </si>
+  <si>
+    <t>USB Drive</t>
+  </si>
+  <si>
+    <t>Goo Gone</t>
+  </si>
+  <si>
+    <t>Cleaning Supplies</t>
+  </si>
+  <si>
+    <t>Isopropyl Alcohol</t>
   </si>
   <si>
     <t>Monitors w/ HDMI</t>
@@ -713,106 +806,7 @@
     <t>Monitor Stands</t>
   </si>
   <si>
-    <t>4-in-1 monitor stand with Displayport monitors</t>
-  </si>
-  <si>
-    <t>USB A to Ethernet adapters</t>
-  </si>
-  <si>
-    <t>A3 Mesh bags (not in use)</t>
-  </si>
-  <si>
-    <t>A4 mesh bags (not in use)</t>
-  </si>
-  <si>
-    <t>Duster</t>
-  </si>
-  <si>
-    <t>AUX wired earbuds</t>
-  </si>
-  <si>
-    <t>Super Glue</t>
-  </si>
-  <si>
-    <t>USB drives</t>
-  </si>
-  <si>
-    <t>Sharpies</t>
-  </si>
-  <si>
-    <t>Dry Erase Markers</t>
-  </si>
-  <si>
-    <t>Goo Gone</t>
-  </si>
-  <si>
-    <t>Isopropyl Alcohol</t>
-  </si>
-  <si>
-    <t>Magnetic Parts Trays</t>
-  </si>
-  <si>
-    <t>30 Gallon Trash Bags (20/box)</t>
-  </si>
-  <si>
-    <t>Sandwich bags (200/box)</t>
-  </si>
-  <si>
-    <t>Mickey Mouse Power Cables</t>
-  </si>
-  <si>
-    <t>Ethernet cables</t>
-  </si>
-  <si>
     <t>WiFi Adapters</t>
-  </si>
-  <si>
-    <t>Intel core i7-i8850H</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>SATA SSD</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>SODIMM</t>
-  </si>
-  <si>
-    <t>8GB DDR4</t>
-  </si>
-  <si>
-    <t>2GB DDR3</t>
-  </si>
-  <si>
-    <t>4GB DDR3</t>
-  </si>
-  <si>
-    <t>2GB DDR4</t>
-  </si>
-  <si>
-    <t>8GB DDR3</t>
-  </si>
-  <si>
-    <t>4GB DDR4</t>
-  </si>
-  <si>
-    <t>16GB DDR4</t>
-  </si>
-  <si>
-    <t>1GB DDR3</t>
-  </si>
-  <si>
-    <t>DIMM</t>
-  </si>
-  <si>
-    <t>TOOLS</t>
-  </si>
-  <si>
-    <t>M2 SSD</t>
   </si>
 </sst>
 </file>
@@ -824,7 +818,7 @@
     <numFmt numFmtId="164" formatCode="00000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -955,7 +949,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -999,11 +993,8 @@
     <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1011,11 +1002,40 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="27">
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1069,6 +1089,19 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -1147,6 +1180,12 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="00000"/>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1170,39 +1209,6 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="00000"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1231,7 +1237,7 @@
     <tableColumn id="13" xr3:uid="{5BEE40AD-E450-4A13-BFB5-1D0CED084DB3}" name="ID"/>
     <tableColumn id="8" xr3:uid="{E9AB9B46-3541-4715-8E5B-024096D78342}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{F7DAC8DD-8096-40F1-8780-1DB9CB4EC72F}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="26"/>
     <tableColumn id="5" xr3:uid="{5338F6FB-43B0-44AF-AF8B-542FAC6CEDF0}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{64D6C993-8518-4A7C-9BDA-A54D7DBFBA8E}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{E5D987A3-C54A-4907-B710-79DB224E0008}" name="Current Status" totalsRowFunction="count"/>
@@ -1283,7 +1289,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:L33" totalsRowShown="0" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:L33" totalsRowShown="0" tableBorderDxfId="13">
   <autoFilter ref="A2:L33" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{73648E04-2EA1-4ADB-8E24-E7DDE01C0462}" name="Item"/>
@@ -1295,8 +1301,8 @@
     <tableColumn id="2" xr3:uid="{C85B34EB-06B2-40A8-BBCB-B5F170EF3F82}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{A686D1B3-031E-4544-A98D-8F3144FA62B0}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{AB29939A-0AF4-4451-A6F4-2144F8957E73}" name="SSD/HDD"/>
-    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="11"/>
     <tableColumn id="12" xr3:uid="{67EC036F-98F6-4C6B-BDD7-99DB9B6ADF97}" name="ID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1304,46 +1310,52 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:M59" totalsRowShown="0" tableBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10100501-D05A-423B-A036-4B5D9B2ECD20}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:M59" totalsRowShown="0" tableBorderDxfId="4">
   <autoFilter ref="A2:M59" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{D71C6020-33AC-4F3C-BC88-69BADE52FD9C}" name="Item"/>
-    <tableColumn id="11" xr3:uid="{3694AE3D-BABD-4C86-8092-3A4D6CE18FE9}" name="Type of Device"/>
-    <tableColumn id="3" xr3:uid="{DBF01EDE-E989-4722-BA17-4F2F168FA1B7}" name="Est. Year"/>
-    <tableColumn id="4" xr3:uid="{8A83BF41-D4B3-47AF-9A4E-D470FED11493}" name="CPU"/>
-    <tableColumn id="5" xr3:uid="{5A855548-F141-4612-89D9-87C3C3042FDB}" name="OS"/>
-    <tableColumn id="6" xr3:uid="{7C6B1539-F50D-45A7-A8CD-94746983CE20}" name="RAM Amount"/>
-    <tableColumn id="13" xr3:uid="{D6E0079E-D628-428A-8C40-CC4B7F920E56}" name="RAM Generation"/>
-    <tableColumn id="7" xr3:uid="{7319329B-DA0F-470E-AE1F-CAF023744072}" name="Storage"/>
-    <tableColumn id="8" xr3:uid="{96CAC308-4A56-4EA5-AF3F-FCAC656EEA09}" name="SSD/HDD"/>
-    <tableColumn id="10" xr3:uid="{6EFEA34D-1A93-4407-A41E-DD47A214B1DA}" name="Est. Value" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{04505084-FFBB-491E-B658-CE08D38C3E7B}" name="Notes"/>
-    <tableColumn id="9" xr3:uid="{6814BC74-3E15-43D3-BC09-F23C9C777339}" name="Date Donated" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{45D6EFC2-97A5-4C00-9305-6B4ED43BEBB2}" name="Recipient"/>
+    <tableColumn id="1" xr3:uid="{549BC727-085C-45F5-9520-711A34B50F51}" name="Item"/>
+    <tableColumn id="11" xr3:uid="{3C98AC72-613E-4EC8-8310-F9E3ED18CC90}" name="Type of Device"/>
+    <tableColumn id="3" xr3:uid="{50863EE7-CAD0-400D-9B34-779EE33CD648}" name="Est. Year"/>
+    <tableColumn id="4" xr3:uid="{00F5359B-A50E-41FF-A2BF-D2260FFBD06C}" name="CPU"/>
+    <tableColumn id="5" xr3:uid="{B2D873F2-431E-43E8-96DC-0380E528EA00}" name="OS"/>
+    <tableColumn id="6" xr3:uid="{67FB40A4-BE9A-4206-AF76-C81A6385AAC3}" name="RAM Amount"/>
+    <tableColumn id="13" xr3:uid="{A9DF335A-A163-4AA9-8879-B5B359D716CC}" name="RAM Generation"/>
+    <tableColumn id="7" xr3:uid="{03AC00D8-5308-407D-9BAC-3303A2B380B3}" name="Storage"/>
+    <tableColumn id="8" xr3:uid="{CFFC1B93-1DA0-40C5-BC8E-01F5CAD8DB66}" name="SSD/HDD"/>
+    <tableColumn id="10" xr3:uid="{71AF2E6E-D071-4784-865B-CA65E73CD28D}" name="Est. Value" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{EFA4DB39-7CD3-4AA7-9335-2FEE3F14CF55}" name="Notes"/>
+    <tableColumn id="9" xr3:uid="{2DC095C6-494B-405F-9E1B-C8849C64E6F1}" name="Date Donated" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{77D1B06F-E180-45FD-ACE9-4BA0C5955E95}" name="Recipient"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}" name="Parts" displayName="Parts" ref="A2:C15" totalsRowShown="0">
-  <autoFilter ref="A2:C15" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{AE6A62C8-410E-43CA-9FCC-DB171FCD3CD1}" name="Type"/>
-    <tableColumn id="3" xr3:uid="{8BE6192C-E1B9-4BD5-BEB2-D26E68C58775}" name="Description"/>
-    <tableColumn id="2" xr3:uid="{675E5FD2-430E-4D35-9481-575A83791C4E}" name="Qty"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5027EC0E-CEEE-4641-ADD0-AA27230F7EC3}" name="Parts5" displayName="Parts5" ref="A2:E19" totalsRowShown="0">
+  <autoFilter ref="A2:E19" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{A07F4B01-C838-4D46-AE29-85BAC951AA36}" name="Type"/>
+    <tableColumn id="3" xr3:uid="{9AC978C2-FD83-43AA-9C69-BC026B4E6411}" name="Description"/>
+    <tableColumn id="4" xr3:uid="{9B2129F6-659A-4DD2-94CF-8EC39B827718}" name="Qty"/>
+    <tableColumn id="5" xr3:uid="{C24221AA-BF54-4384-AC51-1C5D1D76BE99}" name="Donated?" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{1B36C5CD-E753-4327-9D04-48D37AAB944F}" name="Value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{42D1C34C-9303-4D46-A107-174D17AE2274}" name="Parts5" displayName="Parts5" ref="A2:C34" totalsRowShown="0">
-  <autoFilter ref="A2:C34" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C29E963F-354B-4750-B17F-22461F6DC5F4}" name="Type"/>
-    <tableColumn id="3" xr3:uid="{7C7B0B32-2D9C-4EDB-8E56-4C2ADECB5869}" name="Description"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1921E586-F6B8-46BF-BE64-CE91A4EEE8D6}" name="Parts56" displayName="Parts56" ref="A2:G34" totalsRowShown="0">
+  <autoFilter ref="A2:G34" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{C29E963F-354B-4750-B17F-22461F6DC5F4}" name="Name"/>
+    <tableColumn id="3" xr3:uid="{7C7B0B32-2D9C-4EDB-8E56-4C2ADECB5869}" name="Type"/>
     <tableColumn id="2" xr3:uid="{1155C0CA-025A-4922-8B0E-F2A817B3BB60}" name="Qty"/>
+    <tableColumn id="8" xr3:uid="{D743202E-D377-4920-815B-09F9ED9CC36B}" name="Value" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{B4A0A0AC-4FD4-4A43-8591-ABD2EBAA117A}" name="Column1"/>
+    <tableColumn id="5" xr3:uid="{829B96B7-C10C-454A-A528-8575C5865BFA}" name="Column2"/>
+    <tableColumn id="6" xr3:uid="{DDBE87C8-7522-4C92-862B-558811DEBA9D}" name="Column3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1667,33 +1679,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5AA6A1-7D43-4966-8813-F497D895A5C2}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.109375" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5546875" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
-    <col min="7" max="7" width="19.44140625" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1725,11 +1737,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="E3" s="1"/>
       <c r="I3" s="16"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1755,11 +1767,11 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="E5" s="1"/>
       <c r="I5" s="16"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1785,7 +1797,7 @@
         <v>45673</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1812,7 +1824,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1836,7 +1848,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1860,7 +1872,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1884,7 +1896,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1908,7 +1920,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1932,7 +1944,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="28.9">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -1958,7 +1970,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -1987,7 +1999,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="43.15">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2013,7 +2025,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -2037,7 +2049,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="28.9">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2063,7 +2075,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2087,7 +2099,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -2113,7 +2125,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -2137,7 +2149,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="28.9">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -2166,11 +2178,11 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9">
       <c r="E22" s="1"/>
       <c r="I22" s="16"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -2194,7 +2206,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -2218,11 +2230,11 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9">
       <c r="E25" s="1"/>
       <c r="I25" s="16"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -2248,7 +2260,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -2272,7 +2284,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -2296,7 +2308,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
         <v>53</v>
       </c>
@@ -2322,34 +2334,34 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9">
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:5">
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:5">
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="5:5">
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:5">
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="5:5">
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="5:5">
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="5:5">
       <c r="E39" s="1"/>
     </row>
   </sheetData>
@@ -2382,29 +2394,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEA6183-B753-401C-B21E-C502785DFA3D}">
   <dimension ref="A1:G63"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="2" width="7.5546875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5546875" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2427,7 +2439,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
         <v>57</v>
       </c>
@@ -2448,7 +2460,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="8" t="s">
         <v>57</v>
       </c>
@@ -2469,7 +2481,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>57</v>
       </c>
@@ -2492,7 +2504,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="43.15">
       <c r="A6" s="8" t="s">
         <v>57</v>
       </c>
@@ -2515,7 +2527,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
         <v>57</v>
       </c>
@@ -2536,7 +2548,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="28.9">
       <c r="A8" s="8" t="s">
         <v>57</v>
       </c>
@@ -2559,7 +2571,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" s="4" t="s">
         <v>57</v>
       </c>
@@ -2580,7 +2592,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" s="8"/>
       <c r="B10" s="14"/>
       <c r="C10" s="9"/>
@@ -2589,7 +2601,7 @@
       <c r="F10" s="9"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" s="4" t="s">
         <v>57</v>
       </c>
@@ -2610,7 +2622,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="57.6">
       <c r="A12" s="8" t="s">
         <v>61</v>
       </c>
@@ -2633,7 +2645,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" s="8" t="s">
         <v>61</v>
       </c>
@@ -2656,7 +2668,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" s="4" t="s">
         <v>61</v>
       </c>
@@ -2677,7 +2689,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" s="8" t="s">
         <v>61</v>
       </c>
@@ -2698,7 +2710,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" s="4" t="s">
         <v>61</v>
       </c>
@@ -2719,7 +2731,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
         <v>61</v>
       </c>
@@ -2740,7 +2752,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
         <v>61</v>
       </c>
@@ -2761,7 +2773,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19" s="8" t="s">
         <v>61</v>
       </c>
@@ -2782,7 +2794,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
         <v>61</v>
       </c>
@@ -2803,7 +2815,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21" s="8" t="s">
         <v>61</v>
       </c>
@@ -2824,7 +2836,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
         <v>64</v>
       </c>
@@ -2845,7 +2857,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23" s="8" t="s">
         <v>65</v>
       </c>
@@ -2868,7 +2880,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
         <v>64</v>
       </c>
@@ -2889,7 +2901,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25" s="8" t="s">
         <v>64</v>
       </c>
@@ -2908,7 +2920,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26" s="4"/>
       <c r="B26" s="13"/>
       <c r="C26" s="5"/>
@@ -2917,7 +2929,7 @@
       <c r="F26" s="5"/>
       <c r="G26" s="7"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27" s="8" t="s">
         <v>64</v>
       </c>
@@ -2940,7 +2952,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28" s="4" t="s">
         <v>68</v>
       </c>
@@ -2961,7 +2973,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29" s="8" t="s">
         <v>69</v>
       </c>
@@ -2984,7 +2996,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30" s="8" t="s">
         <v>71</v>
       </c>
@@ -3007,7 +3019,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31" s="8" t="s">
         <v>73</v>
       </c>
@@ -3028,7 +3040,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32" s="8" t="s">
         <v>74</v>
       </c>
@@ -3049,7 +3061,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33" s="8" t="s">
         <v>75</v>
       </c>
@@ -3070,7 +3082,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34" s="8" t="s">
         <v>73</v>
       </c>
@@ -3091,7 +3103,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35" s="8" t="s">
         <v>76</v>
       </c>
@@ -3112,7 +3124,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>77</v>
       </c>
@@ -3135,7 +3147,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>64</v>
       </c>
@@ -3158,7 +3170,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>80</v>
       </c>
@@ -3178,7 +3190,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -3198,7 +3210,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>64</v>
       </c>
@@ -3221,7 +3233,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -3244,10 +3256,10 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="G42" s="16"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>81</v>
       </c>
@@ -3267,7 +3279,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>81</v>
       </c>
@@ -3287,7 +3299,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>81</v>
       </c>
@@ -3307,7 +3319,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>86</v>
       </c>
@@ -3330,7 +3342,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>86</v>
       </c>
@@ -3353,7 +3365,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>88</v>
       </c>
@@ -3373,7 +3385,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>89</v>
       </c>
@@ -3390,7 +3402,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>91</v>
       </c>
@@ -3410,7 +3422,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>92</v>
       </c>
@@ -3430,7 +3442,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>93</v>
       </c>
@@ -3450,7 +3462,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>94</v>
       </c>
@@ -3473,7 +3485,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>97</v>
       </c>
@@ -3493,7 +3505,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>98</v>
       </c>
@@ -3516,7 +3528,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>100</v>
       </c>
@@ -3536,7 +3548,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>91</v>
       </c>
@@ -3556,7 +3568,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>75</v>
       </c>
@@ -3576,7 +3588,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -3599,16 +3611,16 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7">
       <c r="G60" s="16"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7">
       <c r="G61" s="16"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7">
       <c r="G62" s="16"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7">
       <c r="G63" s="16"/>
     </row>
   </sheetData>
@@ -3616,10 +3628,10 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:G63">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="24" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3638,33 +3650,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F948288C-1730-49D1-BD4C-FC704F167D22}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.109375" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5546875" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3693,7 +3705,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>103</v>
       </c>
@@ -3722,7 +3734,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -3751,91 +3763,91 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:5">
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:5">
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:5">
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:5">
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:5">
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:5">
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:5">
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="5:5">
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="5:5">
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="5:5">
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:5">
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="5:5">
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="5:5">
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="5:5">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="5:5">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="5:5">
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:5">
       <c r="E33" s="1"/>
     </row>
   </sheetData>
@@ -3867,38 +3879,38 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFE86381-3E33-4CB8-A62B-E48A74AB9667}">
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.28515625" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="17.109375" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" customWidth="1"/>
-    <col min="10" max="10" width="18.6640625" style="19" customWidth="1"/>
-    <col min="11" max="11" width="21.33203125" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" style="19" customWidth="1"/>
+    <col min="11" max="11" width="21.28515625" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:12" ht="14.45">
+      <c r="A1" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-    </row>
-    <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+    </row>
+    <row r="2" spans="1:12" ht="14.45">
       <c r="A2" t="s">
         <v>108</v>
       </c>
@@ -3936,7 +3948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="14.45">
       <c r="A3" t="s">
         <v>119</v>
       </c>
@@ -3972,7 +3984,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="14.45">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -4008,7 +4020,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="14.45">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -4044,10 +4056,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="14.45">
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="14.45">
       <c r="A7" t="s">
         <v>128</v>
       </c>
@@ -4083,7 +4095,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="14.45">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -4119,7 +4131,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="14.45">
       <c r="A9" t="s">
         <v>133</v>
       </c>
@@ -4155,10 +4167,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="14.45">
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="14.45">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -4194,7 +4206,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="14.45">
       <c r="A12" t="s">
         <v>138</v>
       </c>
@@ -4229,7 +4241,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="14.45">
       <c r="A13" t="s">
         <v>140</v>
       </c>
@@ -4265,7 +4277,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15" customHeight="1">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -4301,7 +4313,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" customHeight="1">
       <c r="A15" t="s">
         <v>142</v>
       </c>
@@ -4337,7 +4349,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="15" customHeight="1">
       <c r="A16" t="s">
         <v>144</v>
       </c>
@@ -4373,7 +4385,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="15" customHeight="1">
       <c r="A17" t="s">
         <v>146</v>
       </c>
@@ -4409,7 +4421,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="15" customHeight="1">
       <c r="A18" t="s">
         <v>149</v>
       </c>
@@ -4445,7 +4457,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="15" customHeight="1">
       <c r="A19" t="s">
         <v>149</v>
       </c>
@@ -4481,7 +4493,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="15" customHeight="1">
       <c r="A20" t="s">
         <v>151</v>
       </c>
@@ -4517,7 +4529,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="15" customHeight="1">
       <c r="A21" t="s">
         <v>151</v>
       </c>
@@ -4553,7 +4565,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="15" customHeight="1">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -4589,7 +4601,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="15" customHeight="1">
       <c r="A23" t="s">
         <v>154</v>
       </c>
@@ -4625,7 +4637,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="15" customHeight="1">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -4661,7 +4673,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="15" customHeight="1">
       <c r="A25" t="s">
         <v>128</v>
       </c>
@@ -4697,7 +4709,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="15" customHeight="1">
       <c r="A26" t="s">
         <v>156</v>
       </c>
@@ -4733,7 +4745,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="15" customHeight="1">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -4769,7 +4781,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="15" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>64</v>
       </c>
@@ -4805,7 +4817,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="15" customHeight="1">
       <c r="A29" t="s">
         <v>159</v>
       </c>
@@ -4841,16 +4853,16 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="15" customHeight="1">
       <c r="K30" s="1"/>
     </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="15" customHeight="1">
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="15" customHeight="1">
       <c r="K32" s="1"/>
     </row>
-    <row r="33" spans="11:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="11:11" ht="15" customHeight="1">
       <c r="K33" s="1"/>
     </row>
   </sheetData>
@@ -4858,36 +4870,36 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A27:A28">
-    <cfRule type="expression" dxfId="13" priority="17">
+    <cfRule type="expression" dxfId="21" priority="17">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="18">
+    <cfRule type="expression" dxfId="20" priority="18">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:K9 A11:K14 A15:C15 E15:K15 A16:K25">
-    <cfRule type="expression" dxfId="11" priority="21">
+    <cfRule type="expression" dxfId="19" priority="21">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:L9 A11:L14 A15:C15 E15:L15 A16:L25">
-    <cfRule type="expression" dxfId="10" priority="22">
+    <cfRule type="expression" dxfId="18" priority="22">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26:G29">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="17" priority="9">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10">
+    <cfRule type="expression" dxfId="16" priority="10">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H29">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4908,28 +4920,28 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19592962-4FD3-47C5-914B-6346C180BC2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1C144A-BB57-4446-B714-000D1D9FAB4A}">
   <dimension ref="A1:O59"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.109375" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.33203125" customWidth="1"/>
-    <col min="12" max="12" width="16.88671875" style="16" customWidth="1"/>
-    <col min="13" max="13" width="29.109375" customWidth="1"/>
-    <col min="14" max="14" width="27.6640625" customWidth="1"/>
-    <col min="15" max="15" width="28.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.28515625" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" style="16" customWidth="1"/>
+    <col min="13" max="13" width="29.140625" customWidth="1"/>
+    <col min="14" max="14" width="27.7109375" customWidth="1"/>
+    <col min="15" max="15" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
         <v>161</v>
       </c>
@@ -4951,7 +4963,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="14.45">
       <c r="A2" t="s">
         <v>108</v>
       </c>
@@ -5000,7 +5012,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="14.45">
       <c r="A3" t="s">
         <v>166</v>
       </c>
@@ -5009,18 +5021,6 @@
       </c>
       <c r="C3">
         <v>2019</v>
-      </c>
-      <c r="D3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F3">
-        <v>8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>130</v>
       </c>
       <c r="H3">
         <v>256</v>
@@ -5039,7 +5039,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="14.45">
       <c r="A4" t="s">
         <v>166</v>
       </c>
@@ -5048,18 +5048,6 @@
       </c>
       <c r="C4">
         <v>2019</v>
-      </c>
-      <c r="D4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F4">
-        <v>8</v>
-      </c>
-      <c r="G4" t="s">
-        <v>130</v>
       </c>
       <c r="H4">
         <v>256</v>
@@ -5078,7 +5066,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="14.45">
       <c r="A5" t="s">
         <v>166</v>
       </c>
@@ -5087,18 +5075,6 @@
       </c>
       <c r="C5">
         <v>2019</v>
-      </c>
-      <c r="D5" t="s">
-        <v>241</v>
-      </c>
-      <c r="E5" t="s">
-        <v>137</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5" t="s">
-        <v>130</v>
       </c>
       <c r="H5">
         <v>256</v>
@@ -5117,7 +5093,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="14.45">
       <c r="A6" t="s">
         <v>166</v>
       </c>
@@ -5126,18 +5102,6 @@
       </c>
       <c r="C6">
         <v>2019</v>
-      </c>
-      <c r="D6" t="s">
-        <v>241</v>
-      </c>
-      <c r="E6" t="s">
-        <v>137</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6" t="s">
-        <v>130</v>
       </c>
       <c r="H6">
         <v>256</v>
@@ -5156,7 +5120,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="14.45">
       <c r="A7" t="s">
         <v>166</v>
       </c>
@@ -5165,18 +5129,6 @@
       </c>
       <c r="C7">
         <v>2019</v>
-      </c>
-      <c r="D7" t="s">
-        <v>241</v>
-      </c>
-      <c r="E7" t="s">
-        <v>137</v>
-      </c>
-      <c r="F7">
-        <v>8</v>
-      </c>
-      <c r="G7" t="s">
-        <v>130</v>
       </c>
       <c r="H7">
         <v>256</v>
@@ -5195,7 +5147,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="14.45">
       <c r="A8" t="s">
         <v>166</v>
       </c>
@@ -5204,18 +5156,6 @@
       </c>
       <c r="C8">
         <v>2019</v>
-      </c>
-      <c r="D8" t="s">
-        <v>241</v>
-      </c>
-      <c r="E8" t="s">
-        <v>137</v>
-      </c>
-      <c r="F8">
-        <v>8</v>
-      </c>
-      <c r="G8" t="s">
-        <v>130</v>
       </c>
       <c r="H8">
         <v>256</v>
@@ -5234,7 +5174,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="14.45">
       <c r="A9" t="s">
         <v>166</v>
       </c>
@@ -5243,18 +5183,6 @@
       </c>
       <c r="C9">
         <v>2019</v>
-      </c>
-      <c r="D9" t="s">
-        <v>241</v>
-      </c>
-      <c r="E9" t="s">
-        <v>137</v>
-      </c>
-      <c r="F9">
-        <v>8</v>
-      </c>
-      <c r="G9" t="s">
-        <v>130</v>
       </c>
       <c r="H9">
         <v>256</v>
@@ -5273,7 +5201,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="14.45">
       <c r="A10" t="s">
         <v>168</v>
       </c>
@@ -5312,7 +5240,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="14.45">
       <c r="A11" t="s">
         <v>170</v>
       </c>
@@ -5351,7 +5279,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="14.45">
       <c r="A12" t="s">
         <v>172</v>
       </c>
@@ -5392,7 +5320,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="14.45">
       <c r="A13" t="s">
         <v>175</v>
       </c>
@@ -5431,7 +5359,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="14.45">
       <c r="A14" t="s">
         <v>168</v>
       </c>
@@ -5470,7 +5398,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="14.45">
       <c r="A15" t="s">
         <v>177</v>
       </c>
@@ -5509,7 +5437,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="14.45">
       <c r="A16" t="s">
         <v>179</v>
       </c>
@@ -5550,7 +5478,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="14.45">
       <c r="A17" t="s">
         <v>186</v>
       </c>
@@ -5591,7 +5519,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="14.45">
       <c r="A18" t="s">
         <v>187</v>
       </c>
@@ -5632,7 +5560,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="14.45">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -5673,7 +5601,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="28.9">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -5714,7 +5642,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="14.45">
       <c r="A21" t="s">
         <v>196</v>
       </c>
@@ -5753,7 +5681,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="14.45">
       <c r="A22" t="s">
         <v>64</v>
       </c>
@@ -5792,7 +5720,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="14.45">
       <c r="A23" t="s">
         <v>64</v>
       </c>
@@ -5831,7 +5759,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="14.45">
       <c r="A24" t="s">
         <v>64</v>
       </c>
@@ -5870,7 +5798,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="14.45">
       <c r="A25" t="s">
         <v>64</v>
       </c>
@@ -5909,7 +5837,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="14.45">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -5948,7 +5876,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="14.45">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -5987,7 +5915,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="14.45">
       <c r="A28" t="s">
         <v>199</v>
       </c>
@@ -6026,7 +5954,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" ht="14.45">
       <c r="A29" t="s">
         <v>199</v>
       </c>
@@ -6065,7 +5993,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="14.45">
       <c r="A30" t="s">
         <v>128</v>
       </c>
@@ -6104,7 +6032,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" ht="14.45">
       <c r="A31" s="8" t="s">
         <v>61</v>
       </c>
@@ -6143,7 +6071,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="14.45">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -6181,7 +6109,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" ht="14.45">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -6219,7 +6147,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" ht="14.45">
       <c r="A34" t="s">
         <v>203</v>
       </c>
@@ -6257,7 +6185,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" ht="14.45">
       <c r="A35" t="s">
         <v>203</v>
       </c>
@@ -6295,7 +6223,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" ht="14.45">
       <c r="A36" t="s">
         <v>203</v>
       </c>
@@ -6333,7 +6261,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" ht="14.45">
       <c r="A37" t="s">
         <v>203</v>
       </c>
@@ -6371,7 +6299,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" ht="14.45">
       <c r="A38" t="s">
         <v>203</v>
       </c>
@@ -6409,7 +6337,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" ht="14.45">
       <c r="A39" t="s">
         <v>203</v>
       </c>
@@ -6447,7 +6375,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" ht="15" customHeight="1">
       <c r="A40" t="s">
         <v>203</v>
       </c>
@@ -6485,7 +6413,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" ht="15" customHeight="1">
       <c r="A41" t="s">
         <v>203</v>
       </c>
@@ -6523,7 +6451,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" ht="15" customHeight="1">
       <c r="A42" t="s">
         <v>203</v>
       </c>
@@ -6561,7 +6489,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" ht="15" customHeight="1">
       <c r="A43" t="s">
         <v>140</v>
       </c>
@@ -6600,7 +6528,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" ht="15" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>61</v>
       </c>
@@ -6639,94 +6567,94 @@
         <v>206</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" ht="15" customHeight="1">
       <c r="L45" s="15"/>
     </row>
-    <row r="46" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" ht="15" customHeight="1">
       <c r="L46" s="15"/>
     </row>
-    <row r="47" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" ht="15" customHeight="1">
       <c r="L47" s="15"/>
     </row>
-    <row r="48" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" ht="15" customHeight="1">
       <c r="L48" s="15"/>
     </row>
-    <row r="49" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="12:12" ht="15" customHeight="1">
       <c r="L49" s="15"/>
     </row>
-    <row r="50" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="12:12" ht="15" customHeight="1">
       <c r="L50" s="15"/>
     </row>
-    <row r="51" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="12:12" ht="15" customHeight="1">
       <c r="L51" s="15"/>
     </row>
-    <row r="52" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="12:12" ht="15" customHeight="1">
       <c r="L52" s="15"/>
     </row>
-    <row r="53" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="12:12" ht="15" customHeight="1">
       <c r="L53" s="15"/>
     </row>
-    <row r="54" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="12:12" ht="15" customHeight="1">
       <c r="L54" s="15"/>
     </row>
-    <row r="55" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="12:12" ht="15" customHeight="1">
       <c r="L55" s="15"/>
     </row>
-    <row r="56" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="12:12" ht="15" customHeight="1">
       <c r="L56" s="15"/>
     </row>
-    <row r="57" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="12:12" ht="15" customHeight="1">
       <c r="L57" s="15"/>
     </row>
-    <row r="58" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="12:12" ht="15" customHeight="1">
       <c r="L58" s="15"/>
     </row>
-    <row r="59" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="12:12" ht="15" customHeight="1">
       <c r="L59" s="15"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A44:F44 H44:K44">
-    <cfRule type="expression" dxfId="5" priority="15">
+    <cfRule type="expression" dxfId="10" priority="5">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:F44 H44:L44">
-    <cfRule type="expression" dxfId="4" priority="16">
+    <cfRule type="expression" dxfId="9" priority="6">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:M9 A10:G15 I10:M15 A16:M43 M44 A45:M59">
-    <cfRule type="expression" priority="17">
+    <cfRule type="expression" priority="7">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="18">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G44">
-    <cfRule type="expression" priority="13">
+    <cfRule type="expression" priority="3">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="14">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H15">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B17 B19 B21:B29 B31:B42" xr:uid="{1DFA3251-7984-4A3C-A048-50097DB9AAD3}">
-      <formula1>"Desktop,Laptop,Tablet,All-In-One"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M1 L1:L42 L45:L1048576" xr:uid="{A67DFFE0-1B96-49B5-A6E2-5C17E92A136C}"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K32:K42" xr:uid="{BD4480FF-AB8D-4446-AB7A-01C4C2A99ADB}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K32:K42" xr:uid="{9E34EFD6-6288-43CE-B05D-35BC10E05685}">
       <formula1>1</formula1>
       <formula2>2000</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M1 L1:L42 L45:L1048576" xr:uid="{A9EBE1C3-8923-4578-8214-596FAC33FDB8}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B17 B19 B21:B29 B31:B42" xr:uid="{C7FD23E6-3E08-4DF7-8556-C07E455C4835}">
+      <formula1>"Desktop,Laptop,Tablet,All-In-One"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6737,173 +6665,287 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66F9EB6D-6D2E-43F3-A79F-D2A5CF3A037E}">
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6146040A-3AF4-440D-9E03-57379B2EC394}">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="42.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="B2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="C2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>243</v>
+        <v>213</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E3" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>215</v>
       </c>
       <c r="C4">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E4" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="B5" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="B6" t="s">
-        <v>249</v>
+        <v>218</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="B7" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="B8" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="C8">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="E8" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="B9" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="E9" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="B10" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E10" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="B11" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="C11">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E11" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="B12" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="C12">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E12" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="B13" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E13" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="B14" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E14" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="B15" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="C15">
         <v>11</v>
       </c>
+      <c r="D15" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E15" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1">
+      <c r="A16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B16" t="s">
+        <v>228</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E16" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" ht="15" customHeight="1">
+      <c r="D17" s="23"/>
+    </row>
+    <row r="18" spans="4:4" ht="15" customHeight="1">
+      <c r="D18" s="23"/>
+    </row>
+    <row r="19" spans="4:4" ht="15" customHeight="1">
+      <c r="D19" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -6913,286 +6955,222 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6AEFF60-27EE-498D-A491-C67356035C05}">
-  <dimension ref="A1:C34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F77F78-0898-4060-A2C7-C1A84336B28A}">
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="42.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="19" customWidth="1"/>
+    <col min="5" max="5" width="41.5703125" customWidth="1"/>
+    <col min="6" max="6" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15">
+      <c r="A1" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
+    </row>
+    <row r="2" spans="1:7" ht="15">
       <c r="A2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="B2" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15">
       <c r="A3" t="s">
-        <v>209</v>
+        <v>233</v>
+      </c>
+      <c r="B3" t="s">
+        <v>234</v>
       </c>
       <c r="C3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15">
       <c r="A4" t="s">
-        <v>210</v>
+        <v>235</v>
+      </c>
+      <c r="B4" t="s">
+        <v>234</v>
       </c>
       <c r="C4">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15">
       <c r="A5" t="s">
-        <v>211</v>
+        <v>236</v>
+      </c>
+      <c r="B5" t="s">
+        <v>237</v>
       </c>
       <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15">
       <c r="A6" t="s">
-        <v>212</v>
+        <v>238</v>
+      </c>
+      <c r="B6" t="s">
+        <v>237</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15">
       <c r="A7" t="s">
-        <v>213</v>
+        <v>239</v>
+      </c>
+      <c r="B7" t="s">
+        <v>240</v>
       </c>
       <c r="C7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15">
       <c r="A8" t="s">
-        <v>214</v>
+        <v>241</v>
+      </c>
+      <c r="B8" t="s">
+        <v>240</v>
       </c>
       <c r="C8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15">
       <c r="A9" t="s">
-        <v>215</v>
+        <v>242</v>
+      </c>
+      <c r="B9" t="s">
+        <v>243</v>
       </c>
       <c r="C9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
+      <c r="A10" t="s">
+        <v>244</v>
+      </c>
+      <c r="B10" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>216</v>
-      </c>
-      <c r="C10">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="15">
       <c r="A11" t="s">
-        <v>217</v>
+        <v>246</v>
+      </c>
+      <c r="B11" t="s">
+        <v>245</v>
       </c>
       <c r="C11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15">
+      <c r="A12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C12">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>218</v>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="15">
       <c r="A13" t="s">
-        <v>219</v>
+        <v>249</v>
+      </c>
+      <c r="B13" t="s">
+        <v>248</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>220</v>
-      </c>
-      <c r="C14">
+      <c r="E13" t="s">
+        <v>250</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15">
+      <c r="E14" t="s">
+        <v>251</v>
+      </c>
+      <c r="G14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>221</v>
-      </c>
-      <c r="C15">
+    <row r="15" spans="1:7" ht="15">
+      <c r="E15" t="s">
+        <v>252</v>
+      </c>
+      <c r="G15">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>222</v>
-      </c>
-      <c r="C16">
+    <row r="16" spans="1:7" ht="15">
+      <c r="E16" t="s">
+        <v>253</v>
+      </c>
+      <c r="G16">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>223</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>224</v>
-      </c>
-      <c r="C18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>225</v>
-      </c>
-      <c r="C19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>226</v>
-      </c>
-      <c r="C20">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>227</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>228</v>
-      </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>229</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>230</v>
-      </c>
-      <c r="C24">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>231</v>
-      </c>
-      <c r="C25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>232</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>233</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>234</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>235</v>
-      </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>236</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>237</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>238</v>
-      </c>
-      <c r="C32">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>239</v>
-      </c>
-      <c r="C33">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>240</v>
-      </c>
-      <c r="C34">
+    <row r="17" ht="15"/>
+    <row r="18" ht="15"/>
+    <row r="19" ht="15"/>
+    <row r="20" ht="15"/>
+    <row r="21" ht="15"/>
+    <row r="22" ht="15"/>
+    <row r="23" ht="15"/>
+    <row r="24" ht="15"/>
+    <row r="25" ht="15"/>
+    <row r="26" ht="15"/>
+    <row r="27" ht="15"/>
+    <row r="28" ht="15"/>
+    <row r="29" ht="15"/>
+    <row r="30" ht="15"/>
+    <row r="31" ht="15"/>
+    <row r="32" ht="15"/>
+    <row r="33" spans="5:7" ht="15"/>
+    <row r="34" spans="5:7" ht="15">
+      <c r="E34" t="s">
+        <v>254</v>
+      </c>
+      <c r="G34">
         <v>6</v>
       </c>
     </row>

--- a/data/OldInventorySystem.xlsx
+++ b/data/OldInventorySystem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rosehulman-my.sharepoint.com/personal/lucasja_rose-hulman_edu/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3460" documentId="8_{A0F2C8DF-695D-4A53-BA74-C2F5D1F57A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73C00331-DB68-481F-98A9-F3303D7051BD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97CF21FA-E5B5-40B6-91B6-79617555DD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="4" activeTab="5" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="4" activeTab="6" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Laptops" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="249">
   <si>
     <t>LAPTOPS</t>
   </si>
@@ -737,12 +737,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Column2</t>
-  </si>
-  <si>
-    <t>Column3</t>
-  </si>
-  <si>
     <t>iFixit Moray Kit (complete)</t>
   </si>
   <si>
@@ -752,7 +746,7 @@
     <t>iFixit Pro Tech Toolkit (complete)</t>
   </si>
   <si>
-    <t>iFixit Project Mat</t>
+    <t>iFixit Magnetic Screw Organizer</t>
   </si>
   <si>
     <t>Screw Organizer</t>
@@ -794,19 +788,7 @@
     <t>Isopropyl Alcohol</t>
   </si>
   <si>
-    <t>Monitors w/ HDMI</t>
-  </si>
-  <si>
-    <t>Monitors w/ No HDMI but DisplayPort</t>
-  </si>
-  <si>
-    <t>Monitors w/No HDMI and no DisplayPort</t>
-  </si>
-  <si>
-    <t>Monitor Stands</t>
-  </si>
-  <si>
-    <t>WiFi Adapters</t>
+    <t>USB Wifi Adapter</t>
   </si>
 </sst>
 </file>
@@ -1346,16 +1328,13 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1921E586-F6B8-46BF-BE64-CE91A4EEE8D6}" name="Parts56" displayName="Parts56" ref="A2:G34" totalsRowShown="0">
-  <autoFilter ref="A2:G34" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1921E586-F6B8-46BF-BE64-CE91A4EEE8D6}" name="Parts56" displayName="Parts56" ref="A2:D34" totalsRowShown="0">
+  <autoFilter ref="A2:D34" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}"/>
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{C29E963F-354B-4750-B17F-22461F6DC5F4}" name="Name"/>
     <tableColumn id="3" xr3:uid="{7C7B0B32-2D9C-4EDB-8E56-4C2ADECB5869}" name="Type"/>
     <tableColumn id="2" xr3:uid="{1155C0CA-025A-4922-8B0E-F2A817B3BB60}" name="Qty"/>
     <tableColumn id="8" xr3:uid="{D743202E-D377-4920-815B-09F9ED9CC36B}" name="Value" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{B4A0A0AC-4FD4-4A43-8591-ABD2EBAA117A}" name="Column1"/>
-    <tableColumn id="5" xr3:uid="{829B96B7-C10C-454A-A528-8575C5865BFA}" name="Column2"/>
-    <tableColumn id="6" xr3:uid="{DDBE87C8-7522-4C92-862B-558811DEBA9D}" name="Column3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6956,18 +6935,16 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F77F78-0898-4060-A2C7-C1A84336B28A}">
-  <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" customWidth="1"/>
     <col min="3" max="3" width="10.140625" customWidth="1"/>
     <col min="4" max="4" width="10.140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="41.5703125" customWidth="1"/>
-    <col min="6" max="6" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15">
+    <row r="1" spans="1:4">
       <c r="A1" s="26" t="s">
         <v>229</v>
       </c>
@@ -6975,7 +6952,7 @@
       <c r="C1" s="27"/>
       <c r="D1" s="28"/>
     </row>
-    <row r="2" spans="1:7" ht="15">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>230</v>
       </c>
@@ -6988,192 +6965,195 @@
       <c r="D2" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>231</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B3" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15">
-      <c r="A3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B3" t="s">
-        <v>234</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15">
+      <c r="D3" s="19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="15">
+      <c r="D4" s="19">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="15">
+      <c r="D5" s="19">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="15">
+      <c r="D6" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="15">
+      <c r="D7" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="15">
+      <c r="D8" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C9">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="15">
+      <c r="D9" s="19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="15">
+      <c r="D10" s="19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C11">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="15">
+      <c r="D11" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="15">
+      <c r="D12" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
-      <c r="E13" t="s">
-        <v>250</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15">
-      <c r="E14" t="s">
-        <v>251</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15">
-      <c r="E15" t="s">
-        <v>252</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15">
-      <c r="E16" t="s">
-        <v>253</v>
-      </c>
-      <c r="G16">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" ht="15"/>
-    <row r="18" ht="15"/>
-    <row r="19" ht="15"/>
-    <row r="20" ht="15"/>
-    <row r="21" ht="15"/>
-    <row r="22" ht="15"/>
-    <row r="23" ht="15"/>
-    <row r="24" ht="15"/>
-    <row r="25" ht="15"/>
-    <row r="26" ht="15"/>
-    <row r="27" ht="15"/>
-    <row r="28" ht="15"/>
-    <row r="29" ht="15"/>
-    <row r="30" ht="15"/>
-    <row r="31" ht="15"/>
-    <row r="32" ht="15"/>
-    <row r="33" spans="5:7" ht="15"/>
-    <row r="34" spans="5:7" ht="15">
-      <c r="E34" t="s">
-        <v>254</v>
-      </c>
-      <c r="G34">
+      <c r="D13" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>248</v>
+      </c>
+      <c r="B14" t="s">
+        <v>241</v>
+      </c>
+      <c r="C14">
         <v>6</v>
       </c>
-    </row>
+      <c r="D14" s="19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4"/>
+    <row r="16" spans="1:4"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/data/OldInventorySystem.xlsx
+++ b/data/OldInventorySystem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rosehulman-my.sharepoint.com/personal/lucasja_rose-hulman_edu/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97CF21FA-E5B5-40B6-91B6-79617555DD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3566" documentId="8_{A0F2C8DF-695D-4A53-BA74-C2F5D1F57A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A467ED7A-F1D3-41C0-9B3D-00F5C1CAE948}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="4" activeTab="6" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Laptops" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="250">
   <si>
     <t>LAPTOPS</t>
   </si>
@@ -789,6 +789,9 @@
   </si>
   <si>
     <t>USB Wifi Adapter</t>
+  </si>
+  <si>
+    <t>Org?</t>
   </si>
 </sst>
 </file>
@@ -800,7 +803,7 @@
     <numFmt numFmtId="164" formatCode="00000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -978,10 +981,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -990,33 +990,26 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="28">
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1046,16 +1039,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="4" tint="0.79998168889431442"/>
@@ -1071,19 +1054,6 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
     </dxf>
     <dxf>
       <fill>
@@ -1162,12 +1132,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="00000"/>
-    </dxf>
-    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1193,7 +1157,50 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="00000"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1238,7 +1245,7 @@
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F96A3CC8-25D1-4CF8-877D-2816B26B7DC4}" name="Item Name" totalsRowLabel="Total"/>
-    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="25"/>
     <tableColumn id="8" xr3:uid="{7D8F815E-A974-42A8-AC0B-AB8B951599A2}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{FEA94C75-B538-448A-A9F5-46F5A27E863D}" name="Year released"/>
     <tableColumn id="4" xr3:uid="{24998D92-36B7-4553-81E7-CB33711B31BB}" name="Special Reqs/Notes"/>
@@ -1260,7 +1267,7 @@
     <tableColumn id="13" xr3:uid="{EFFF3477-1A58-41CD-BFF3-45CE299505A7}" name="ID"/>
     <tableColumn id="8" xr3:uid="{C694899F-E385-4DE2-972A-7395A9633019}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{13C54556-A90A-4F9C-800D-3D838462DF46}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="24"/>
     <tableColumn id="5" xr3:uid="{6DE19FBC-9BD8-456E-9FC5-F633F61E4A34}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{68546225-0A78-43C1-A4F9-4D2E1DC008A3}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{0D7FD365-4F73-4A57-B8A1-CFAC47267923}" name="Current Status" totalsRowFunction="count"/>
@@ -1271,7 +1278,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:L33" totalsRowShown="0" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:L33" totalsRowShown="0" tableBorderDxfId="23">
   <autoFilter ref="A2:L33" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{73648E04-2EA1-4ADB-8E24-E7DDE01C0462}" name="Item"/>
@@ -1283,8 +1290,8 @@
     <tableColumn id="2" xr3:uid="{C85B34EB-06B2-40A8-BBCB-B5F170EF3F82}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{A686D1B3-031E-4544-A98D-8F3144FA62B0}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{AB29939A-0AF4-4451-A6F4-2144F8957E73}" name="SSD/HDD"/>
-    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="21"/>
     <tableColumn id="12" xr3:uid="{67EC036F-98F6-4C6B-BDD7-99DB9B6ADF97}" name="ID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1292,9 +1299,9 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10100501-D05A-423B-A036-4B5D9B2ECD20}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:M59" totalsRowShown="0" tableBorderDxfId="4">
-  <autoFilter ref="A2:M59" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10100501-D05A-423B-A036-4B5D9B2ECD20}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:N59" totalsRowShown="0" tableBorderDxfId="20">
+  <autoFilter ref="A2:N59" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}"/>
+  <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{549BC727-085C-45F5-9520-711A34B50F51}" name="Item"/>
     <tableColumn id="11" xr3:uid="{3C98AC72-613E-4EC8-8310-F9E3ED18CC90}" name="Type of Device"/>
     <tableColumn id="3" xr3:uid="{50863EE7-CAD0-400D-9B34-779EE33CD648}" name="Est. Year"/>
@@ -1304,10 +1311,11 @@
     <tableColumn id="13" xr3:uid="{A9DF335A-A163-4AA9-8879-B5B359D716CC}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{03AC00D8-5308-407D-9BAC-3303A2B380B3}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{CFFC1B93-1DA0-40C5-BC8E-01F5CAD8DB66}" name="SSD/HDD"/>
-    <tableColumn id="10" xr3:uid="{71AF2E6E-D071-4784-865B-CA65E73CD28D}" name="Est. Value" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{71AF2E6E-D071-4784-865B-CA65E73CD28D}" name="Est. Value" dataDxfId="19"/>
     <tableColumn id="12" xr3:uid="{EFA4DB39-7CD3-4AA7-9335-2FEE3F14CF55}" name="Notes"/>
-    <tableColumn id="9" xr3:uid="{2DC095C6-494B-405F-9E1B-C8849C64E6F1}" name="Date Donated" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{77D1B06F-E180-45FD-ACE9-4BA0C5955E95}" name="Recipient"/>
+    <tableColumn id="9" xr3:uid="{2DC095C6-494B-405F-9E1B-C8849C64E6F1}" name="Date Donated" dataDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{4D76F748-9FDA-4C94-B04F-D8250CE6CE08}" name="Recipient" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{77D1B06F-E180-45FD-ACE9-4BA0C5955E95}" name="Org?"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1320,7 +1328,7 @@
     <tableColumn id="1" xr3:uid="{A07F4B01-C838-4D46-AE29-85BAC951AA36}" name="Type"/>
     <tableColumn id="3" xr3:uid="{9AC978C2-FD83-43AA-9C69-BC026B4E6411}" name="Description"/>
     <tableColumn id="4" xr3:uid="{9B2129F6-659A-4DD2-94CF-8EC39B827718}" name="Qty"/>
-    <tableColumn id="5" xr3:uid="{C24221AA-BF54-4384-AC51-1C5D1D76BE99}" name="Donated?" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{C24221AA-BF54-4384-AC51-1C5D1D76BE99}" name="Donated?" dataDxfId="17"/>
     <tableColumn id="2" xr3:uid="{1B36C5CD-E753-4327-9D04-48D37AAB944F}" name="Value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1334,7 +1342,7 @@
     <tableColumn id="1" xr3:uid="{C29E963F-354B-4750-B17F-22461F6DC5F4}" name="Name"/>
     <tableColumn id="3" xr3:uid="{7C7B0B32-2D9C-4EDB-8E56-4C2ADECB5869}" name="Type"/>
     <tableColumn id="2" xr3:uid="{1155C0CA-025A-4922-8B0E-F2A817B3BB60}" name="Qty"/>
-    <tableColumn id="8" xr3:uid="{D743202E-D377-4920-815B-09F9ED9CC36B}" name="Value" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{D743202E-D377-4920-815B-09F9ED9CC36B}" name="Value" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1658,33 +1666,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5AA6A1-7D43-4966-8813-F497D895A5C2}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.109375" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="7" max="7" width="19.44140625" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1716,11 +1724,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E3" s="1"/>
       <c r="I3" s="16"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1746,11 +1754,11 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E5" s="1"/>
       <c r="I5" s="16"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1776,7 +1784,7 @@
         <v>45673</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1803,7 +1811,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1827,7 +1835,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1851,7 +1859,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1875,7 +1883,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1899,7 +1907,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1923,7 +1931,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="28.9">
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -1949,7 +1957,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -1978,7 +1986,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="43.15">
+    <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2004,7 +2012,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -2028,7 +2036,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="28.9">
+    <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2054,7 +2062,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2078,7 +2086,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -2104,7 +2112,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -2128,7 +2136,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="28.9">
+    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -2157,11 +2165,11 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E22" s="1"/>
       <c r="I22" s="16"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -2185,7 +2193,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -2209,11 +2217,11 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E25" s="1"/>
       <c r="I25" s="16"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -2239,7 +2247,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -2263,7 +2271,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -2287,7 +2295,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>53</v>
       </c>
@@ -2313,34 +2321,34 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="5:5">
+    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="5:5">
+    <row r="34" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="5:5">
+    <row r="35" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="5:5">
+    <row r="36" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="5:5">
+    <row r="37" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="5:5">
+    <row r="38" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="5:5">
+    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E39" s="1"/>
     </row>
   </sheetData>
@@ -2373,29 +2381,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEA6183-B753-401C-B21E-C502785DFA3D}">
   <dimension ref="A1:G63"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2418,7 +2426,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>57</v>
       </c>
@@ -2439,7 +2447,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>57</v>
       </c>
@@ -2460,7 +2468,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1">
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>57</v>
       </c>
@@ -2483,7 +2491,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="43.15">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>57</v>
       </c>
@@ -2506,7 +2514,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>57</v>
       </c>
@@ -2527,7 +2535,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.9">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>57</v>
       </c>
@@ -2550,7 +2558,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>57</v>
       </c>
@@ -2571,7 +2579,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="B10" s="14"/>
       <c r="C10" s="9"/>
@@ -2580,7 +2588,7 @@
       <c r="F10" s="9"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>57</v>
       </c>
@@ -2601,7 +2609,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="57.6">
+    <row r="12" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>61</v>
       </c>
@@ -2624,7 +2632,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>61</v>
       </c>
@@ -2647,7 +2655,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>61</v>
       </c>
@@ -2668,7 +2676,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>61</v>
       </c>
@@ -2689,7 +2697,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>61</v>
       </c>
@@ -2710,7 +2718,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>61</v>
       </c>
@@ -2731,7 +2739,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>61</v>
       </c>
@@ -2752,7 +2760,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>61</v>
       </c>
@@ -2773,7 +2781,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>61</v>
       </c>
@@ -2794,7 +2802,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>61</v>
       </c>
@@ -2815,7 +2823,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>64</v>
       </c>
@@ -2836,7 +2844,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>65</v>
       </c>
@@ -2859,7 +2867,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>64</v>
       </c>
@@ -2880,7 +2888,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>64</v>
       </c>
@@ -2899,7 +2907,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="13"/>
       <c r="C26" s="5"/>
@@ -2908,7 +2916,7 @@
       <c r="F26" s="5"/>
       <c r="G26" s="7"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>64</v>
       </c>
@@ -2931,7 +2939,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>68</v>
       </c>
@@ -2952,7 +2960,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>69</v>
       </c>
@@ -2975,7 +2983,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>71</v>
       </c>
@@ -2998,7 +3006,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>73</v>
       </c>
@@ -3019,7 +3027,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>74</v>
       </c>
@@ -3040,7 +3048,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>75</v>
       </c>
@@ -3061,7 +3069,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>73</v>
       </c>
@@ -3082,7 +3090,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>76</v>
       </c>
@@ -3103,7 +3111,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>77</v>
       </c>
@@ -3126,7 +3134,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>64</v>
       </c>
@@ -3149,7 +3157,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>80</v>
       </c>
@@ -3169,7 +3177,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -3189,7 +3197,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>64</v>
       </c>
@@ -3212,7 +3220,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -3235,10 +3243,10 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G42" s="16"/>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>81</v>
       </c>
@@ -3258,7 +3266,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>81</v>
       </c>
@@ -3278,7 +3286,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>81</v>
       </c>
@@ -3298,7 +3306,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>86</v>
       </c>
@@ -3321,7 +3329,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>86</v>
       </c>
@@ -3344,7 +3352,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>88</v>
       </c>
@@ -3364,7 +3372,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>89</v>
       </c>
@@ -3381,7 +3389,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>91</v>
       </c>
@@ -3401,7 +3409,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>92</v>
       </c>
@@ -3421,7 +3429,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>93</v>
       </c>
@@ -3441,7 +3449,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>94</v>
       </c>
@@ -3464,7 +3472,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>97</v>
       </c>
@@ -3484,7 +3492,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>98</v>
       </c>
@@ -3507,7 +3515,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>100</v>
       </c>
@@ -3527,7 +3535,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>91</v>
       </c>
@@ -3547,7 +3555,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>75</v>
       </c>
@@ -3567,7 +3575,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -3590,16 +3598,16 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G60" s="16"/>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G61" s="16"/>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G62" s="16"/>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G63" s="16"/>
     </row>
   </sheetData>
@@ -3607,10 +3615,10 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:G63">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="2">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3629,33 +3637,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F948288C-1730-49D1-BD4C-FC704F167D22}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5703125" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.109375" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3684,7 +3692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>103</v>
       </c>
@@ -3713,7 +3721,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -3742,91 +3750,91 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="5:5">
+    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="5:5">
+    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="5:5">
+    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="5:5">
+    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="5:5">
+    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="5:5">
+    <row r="22" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="5:5">
+    <row r="23" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="5:5">
+    <row r="24" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="5:5">
+    <row r="25" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="5:5">
+    <row r="26" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="5:5">
+    <row r="27" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="5:5">
+    <row r="28" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="5:5">
+    <row r="29" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="5:5">
+    <row r="30" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="5:5">
+    <row r="31" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="5:5">
+    <row r="32" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="5:5">
+    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E33" s="1"/>
     </row>
   </sheetData>
@@ -3858,38 +3866,38 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFE86381-3E33-4CB8-A62B-E48A74AB9667}">
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.33203125" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" customWidth="1"/>
-    <col min="10" max="10" width="18.7109375" style="19" customWidth="1"/>
-    <col min="11" max="11" width="21.28515625" customWidth="1"/>
+    <col min="7" max="7" width="17.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" style="19" customWidth="1"/>
+    <col min="11" max="11" width="21.33203125" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.45">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-    </row>
-    <row r="2" spans="1:12" ht="14.45">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+    </row>
+    <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>108</v>
       </c>
@@ -3927,7 +3935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="14.45">
+    <row r="3" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>119</v>
       </c>
@@ -3963,7 +3971,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="14.45">
+    <row r="4" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -3999,7 +4007,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="14.45">
+    <row r="5" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -4035,10 +4043,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="14.45">
+    <row r="6" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:12" ht="14.45">
+    <row r="7" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>128</v>
       </c>
@@ -4074,7 +4082,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="14.45">
+    <row r="8" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -4110,7 +4118,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="14.45">
+    <row r="9" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>133</v>
       </c>
@@ -4146,10 +4154,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="14.45">
+    <row r="10" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:12" ht="14.45">
+    <row r="11" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -4185,7 +4193,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="14.45">
+    <row r="12" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>138</v>
       </c>
@@ -4220,7 +4228,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="14.45">
+    <row r="13" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>140</v>
       </c>
@@ -4256,7 +4264,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1">
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -4292,7 +4300,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1">
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>142</v>
       </c>
@@ -4328,7 +4336,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1">
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>144</v>
       </c>
@@ -4364,7 +4372,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1">
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>146</v>
       </c>
@@ -4400,7 +4408,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1">
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>149</v>
       </c>
@@ -4436,7 +4444,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1">
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>149</v>
       </c>
@@ -4472,7 +4480,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1">
+    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>151</v>
       </c>
@@ -4508,7 +4516,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1">
+    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>151</v>
       </c>
@@ -4544,7 +4552,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1">
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -4580,7 +4588,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1">
+    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>154</v>
       </c>
@@ -4616,7 +4624,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1">
+    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -4652,7 +4660,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1">
+    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>128</v>
       </c>
@@ -4688,7 +4696,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1">
+    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>156</v>
       </c>
@@ -4724,7 +4732,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1">
+    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -4760,7 +4768,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1">
+    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>64</v>
       </c>
@@ -4796,7 +4804,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1">
+    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>159</v>
       </c>
@@ -4832,16 +4840,16 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1">
+    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="K30" s="1"/>
     </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1">
+    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1">
+    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="K32" s="1"/>
     </row>
-    <row r="33" spans="11:11" ht="15" customHeight="1">
+    <row r="33" spans="11:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="K33" s="1"/>
     </row>
   </sheetData>
@@ -4849,36 +4857,36 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A27:A28">
-    <cfRule type="expression" dxfId="21" priority="17">
+    <cfRule type="expression" dxfId="13" priority="17">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="18">
+    <cfRule type="expression" dxfId="12" priority="18">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:K9 A11:K14 A15:C15 E15:K15 A16:K25">
-    <cfRule type="expression" dxfId="19" priority="21">
+    <cfRule type="expression" dxfId="11" priority="21">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:L9 A11:L14 A15:C15 E15:L15 A16:L25">
-    <cfRule type="expression" dxfId="18" priority="22">
+    <cfRule type="expression" dxfId="10" priority="22">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26:G29">
-    <cfRule type="expression" dxfId="17" priority="9">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="10">
+    <cfRule type="expression" dxfId="8" priority="10">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H29">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4900,27 +4908,28 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1C144A-BB57-4446-B714-000D1D9FAB4A}">
-  <dimension ref="A1:O59"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:P59"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.28515625" customWidth="1"/>
-    <col min="12" max="12" width="16.85546875" style="16" customWidth="1"/>
-    <col min="13" max="13" width="29.140625" customWidth="1"/>
-    <col min="14" max="14" width="27.7109375" customWidth="1"/>
-    <col min="15" max="15" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.109375" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.33203125" customWidth="1"/>
+    <col min="12" max="12" width="16.88671875" style="16" customWidth="1"/>
+    <col min="13" max="13" width="33.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.6640625" customWidth="1"/>
+    <col min="16" max="16" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1">
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="17" t="s">
         <v>161</v>
       </c>
@@ -4934,15 +4943,16 @@
       <c r="J1" s="20"/>
       <c r="K1" s="18"/>
       <c r="L1" s="22"/>
-      <c r="M1" s="18"/>
-      <c r="N1" t="s">
+      <c r="M1" s="22"/>
+      <c r="N1" s="18"/>
+      <c r="O1" t="s">
         <v>162</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="14.45">
+    <row r="2" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>108</v>
       </c>
@@ -4979,19 +4989,22 @@
       <c r="L2" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" t="s">
+        <v>249</v>
+      </c>
+      <c r="O2" s="2">
         <f>SUM(J3:J38)</f>
         <v>9870</v>
       </c>
-      <c r="O2">
-        <f>COUNTIF(M3:M42,"*International*")</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="14.45">
+      <c r="P2">
+        <f>COUNTIF(N3:N42,"*International*")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>166</v>
       </c>
@@ -5014,11 +5027,14 @@
       <c r="L3" s="15">
         <v>45970</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="14.45">
+      <c r="N3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>166</v>
       </c>
@@ -5041,11 +5057,14 @@
       <c r="L4" s="15">
         <v>45970</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="14.45">
+      <c r="N4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>166</v>
       </c>
@@ -5068,11 +5087,14 @@
       <c r="L5" s="15">
         <v>45970</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="14.45">
+      <c r="N5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>166</v>
       </c>
@@ -5095,11 +5117,14 @@
       <c r="L6" s="15">
         <v>45970</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="14.45">
+      <c r="N6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>166</v>
       </c>
@@ -5122,11 +5147,14 @@
       <c r="L7" s="15">
         <v>45970</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="14.45">
+      <c r="N7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>166</v>
       </c>
@@ -5149,11 +5177,14 @@
       <c r="L8" s="15">
         <v>45970</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="14.45">
+      <c r="N8" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>166</v>
       </c>
@@ -5176,11 +5207,14 @@
       <c r="L9" s="15">
         <v>45970</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="14.45">
+      <c r="N9" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>168</v>
       </c>
@@ -5215,11 +5249,14 @@
       <c r="L10" s="15">
         <v>45999</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M10" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="14.45">
+      <c r="N10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>170</v>
       </c>
@@ -5254,11 +5291,14 @@
       <c r="L11" s="15">
         <v>45999</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" ht="14.45">
+      <c r="N11" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>172</v>
       </c>
@@ -5295,11 +5335,14 @@
       <c r="L12" s="15">
         <v>45999</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" ht="14.45">
+      <c r="N12" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>175</v>
       </c>
@@ -5334,11 +5377,14 @@
       <c r="L13" s="15">
         <v>45999</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" ht="14.45">
+      <c r="N13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>168</v>
       </c>
@@ -5373,11 +5419,14 @@
       <c r="L14" s="15">
         <v>45999</v>
       </c>
-      <c r="M14" t="s">
+      <c r="M14" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" ht="14.45">
+      <c r="N14" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>177</v>
       </c>
@@ -5412,11 +5461,14 @@
       <c r="L15" s="15">
         <v>45999</v>
       </c>
-      <c r="M15" t="s">
+      <c r="M15" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" ht="14.45">
+      <c r="N15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>179</v>
       </c>
@@ -5453,11 +5505,14 @@
       <c r="L16" s="15">
         <v>45999</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="14.45">
+      <c r="N16" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>186</v>
       </c>
@@ -5494,11 +5549,14 @@
       <c r="L17" s="15">
         <v>45999</v>
       </c>
-      <c r="M17" t="s">
+      <c r="M17" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="14.45">
+      <c r="N17" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>187</v>
       </c>
@@ -5535,11 +5593,14 @@
       <c r="L18" s="16">
         <v>46043</v>
       </c>
-      <c r="M18" t="s">
+      <c r="M18" s="16" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="14.45">
+      <c r="N18" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -5576,11 +5637,14 @@
       <c r="L19" s="16">
         <v>46043</v>
       </c>
-      <c r="M19" t="s">
+      <c r="M19" s="16" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="28.9">
+      <c r="N19" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -5617,11 +5681,14 @@
       <c r="L20" s="15">
         <v>46056</v>
       </c>
-      <c r="M20" t="s">
+      <c r="M20" s="15" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" ht="14.45">
+      <c r="N20" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>196</v>
       </c>
@@ -5656,11 +5723,14 @@
       <c r="L21" s="15">
         <v>46056</v>
       </c>
-      <c r="M21" t="s">
+      <c r="M21" s="15" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" ht="14.45">
+      <c r="N21" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>64</v>
       </c>
@@ -5695,11 +5765,14 @@
       <c r="L22" s="15">
         <v>46056</v>
       </c>
-      <c r="M22" t="s">
+      <c r="M22" s="15" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" ht="14.45">
+      <c r="N22" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>64</v>
       </c>
@@ -5734,11 +5807,14 @@
       <c r="L23" s="15">
         <v>46056</v>
       </c>
-      <c r="M23" t="s">
+      <c r="M23" s="15" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" ht="14.45">
+      <c r="N23" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>64</v>
       </c>
@@ -5773,11 +5849,14 @@
       <c r="L24" s="15">
         <v>46056</v>
       </c>
-      <c r="M24" t="s">
+      <c r="M24" s="15" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" ht="14.45">
+      <c r="N24" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>64</v>
       </c>
@@ -5812,11 +5891,14 @@
       <c r="L25" s="15">
         <v>46056</v>
       </c>
-      <c r="M25" t="s">
+      <c r="M25" s="15" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" ht="14.45">
+      <c r="N25" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -5851,11 +5933,14 @@
       <c r="L26" s="15">
         <v>46056</v>
       </c>
-      <c r="M26" t="s">
+      <c r="M26" s="15" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" ht="14.45">
+      <c r="N26" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -5890,11 +5975,14 @@
       <c r="L27" s="15">
         <v>46056</v>
       </c>
-      <c r="M27" t="s">
+      <c r="M27" s="15" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" ht="14.45">
+      <c r="N27" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>199</v>
       </c>
@@ -5929,11 +6017,14 @@
       <c r="L28" s="15">
         <v>46056</v>
       </c>
-      <c r="M28" t="s">
+      <c r="M28" s="15" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" ht="14.45">
+      <c r="N28" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>199</v>
       </c>
@@ -5968,11 +6059,14 @@
       <c r="L29" s="15">
         <v>46056</v>
       </c>
-      <c r="M29" t="s">
+      <c r="M29" s="15" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" ht="14.45">
+      <c r="N29" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>128</v>
       </c>
@@ -6007,11 +6101,14 @@
       <c r="L30" s="15">
         <v>46056</v>
       </c>
-      <c r="M30" t="s">
+      <c r="M30" s="15" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" ht="14.45">
+      <c r="N30" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>61</v>
       </c>
@@ -6046,11 +6143,14 @@
       <c r="L31" s="16">
         <v>46058</v>
       </c>
-      <c r="M31" t="s">
+      <c r="M31" s="16" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" ht="14.45">
+      <c r="N31" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -6084,11 +6184,14 @@
       <c r="L32" s="16">
         <v>46058</v>
       </c>
-      <c r="M32" t="s">
+      <c r="M32" s="16" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" ht="14.45">
+      <c r="N32" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -6122,11 +6225,14 @@
       <c r="L33" s="16">
         <v>46058</v>
       </c>
-      <c r="M33" t="s">
+      <c r="M33" s="16" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" ht="14.45">
+      <c r="N33" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>203</v>
       </c>
@@ -6160,11 +6266,14 @@
       <c r="L34" s="16">
         <v>46058</v>
       </c>
-      <c r="M34" t="s">
+      <c r="M34" s="16" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" ht="14.45">
+      <c r="N34" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>203</v>
       </c>
@@ -6198,11 +6307,14 @@
       <c r="L35" s="16">
         <v>46058</v>
       </c>
-      <c r="M35" t="s">
+      <c r="M35" s="16" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" ht="14.45">
+      <c r="N35" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>203</v>
       </c>
@@ -6236,11 +6348,14 @@
       <c r="L36" s="16">
         <v>46058</v>
       </c>
-      <c r="M36" t="s">
+      <c r="M36" s="16" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" ht="14.45">
+      <c r="N36" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>203</v>
       </c>
@@ -6274,11 +6389,14 @@
       <c r="L37" s="16">
         <v>46058</v>
       </c>
-      <c r="M37" t="s">
+      <c r="M37" s="16" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" ht="14.45">
+      <c r="N37" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>203</v>
       </c>
@@ -6312,11 +6430,14 @@
       <c r="L38" s="16">
         <v>46058</v>
       </c>
-      <c r="M38" t="s">
+      <c r="M38" s="16" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" ht="14.45">
+      <c r="N38" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>203</v>
       </c>
@@ -6350,11 +6471,14 @@
       <c r="L39" s="16">
         <v>46058</v>
       </c>
-      <c r="M39" t="s">
+      <c r="M39" s="16" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" ht="15" customHeight="1">
+      <c r="N39" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>203</v>
       </c>
@@ -6388,11 +6512,14 @@
       <c r="L40" s="16">
         <v>46058</v>
       </c>
-      <c r="M40" t="s">
+      <c r="M40" s="16" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" ht="15" customHeight="1">
+      <c r="N40" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>203</v>
       </c>
@@ -6426,11 +6553,14 @@
       <c r="L41" s="16">
         <v>46058</v>
       </c>
-      <c r="M41" t="s">
+      <c r="M41" s="16" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" ht="15" customHeight="1">
+      <c r="N41" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>203</v>
       </c>
@@ -6464,11 +6594,14 @@
       <c r="L42" s="16">
         <v>46058</v>
       </c>
-      <c r="M42" t="s">
+      <c r="M42" s="16" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" ht="15" customHeight="1">
+      <c r="N42" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>140</v>
       </c>
@@ -6503,11 +6636,14 @@
       <c r="L43" s="16">
         <v>46078</v>
       </c>
-      <c r="M43" t="s">
+      <c r="M43" s="16" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" ht="15" customHeight="1">
+      <c r="N43" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>61</v>
       </c>
@@ -6542,71 +6678,89 @@
       <c r="L44" s="16">
         <v>46099</v>
       </c>
-      <c r="M44" t="s">
+      <c r="M44" s="16" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" ht="15" customHeight="1">
+      <c r="N44" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L45" s="15"/>
-    </row>
-    <row r="46" spans="1:13" ht="15" customHeight="1">
+      <c r="M45" s="15"/>
+    </row>
+    <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L46" s="15"/>
-    </row>
-    <row r="47" spans="1:13" ht="15" customHeight="1">
+      <c r="M46" s="15"/>
+    </row>
+    <row r="47" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L47" s="15"/>
-    </row>
-    <row r="48" spans="1:13" ht="15" customHeight="1">
+      <c r="M47" s="15"/>
+    </row>
+    <row r="48" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L48" s="15"/>
-    </row>
-    <row r="49" spans="12:12" ht="15" customHeight="1">
+      <c r="M48" s="15"/>
+    </row>
+    <row r="49" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L49" s="15"/>
-    </row>
-    <row r="50" spans="12:12" ht="15" customHeight="1">
+      <c r="M49" s="15"/>
+    </row>
+    <row r="50" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L50" s="15"/>
-    </row>
-    <row r="51" spans="12:12" ht="15" customHeight="1">
+      <c r="M50" s="15"/>
+    </row>
+    <row r="51" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L51" s="15"/>
-    </row>
-    <row r="52" spans="12:12" ht="15" customHeight="1">
+      <c r="M51" s="15"/>
+    </row>
+    <row r="52" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L52" s="15"/>
-    </row>
-    <row r="53" spans="12:12" ht="15" customHeight="1">
+      <c r="M52" s="15"/>
+    </row>
+    <row r="53" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L53" s="15"/>
-    </row>
-    <row r="54" spans="12:12" ht="15" customHeight="1">
+      <c r="M53" s="15"/>
+    </row>
+    <row r="54" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L54" s="15"/>
-    </row>
-    <row r="55" spans="12:12" ht="15" customHeight="1">
+      <c r="M54" s="15"/>
+    </row>
+    <row r="55" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L55" s="15"/>
-    </row>
-    <row r="56" spans="12:12" ht="15" customHeight="1">
+      <c r="M55" s="15"/>
+    </row>
+    <row r="56" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L56" s="15"/>
-    </row>
-    <row r="57" spans="12:12" ht="15" customHeight="1">
+      <c r="M56" s="15"/>
+    </row>
+    <row r="57" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L57" s="15"/>
-    </row>
-    <row r="58" spans="12:12" ht="15" customHeight="1">
+      <c r="M57" s="15"/>
+    </row>
+    <row r="58" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L58" s="15"/>
-    </row>
-    <row r="59" spans="12:12" ht="15" customHeight="1">
+      <c r="M58" s="15"/>
+    </row>
+    <row r="59" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L59" s="15"/>
+      <c r="M59" s="15"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A44:F44 H44:K44">
-    <cfRule type="expression" dxfId="10" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A44:F44 H44:L44">
-    <cfRule type="expression" dxfId="9" priority="6">
+  <conditionalFormatting sqref="A44:F44 H44:M44">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:M9 A10:G15 I10:M15 A16:M43 M44 A45:M59">
+  <conditionalFormatting sqref="A3:N9 A10:G15 I10:N15 A16:N43 N44 A45:N59">
     <cfRule type="expression" priority="7">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6614,15 +6768,15 @@
     <cfRule type="expression" priority="3">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H15">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6631,7 +6785,7 @@
       <formula1>1</formula1>
       <formula2>2000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M1 L1:L42 L45:L1048576" xr:uid="{A9EBE1C3-8923-4578-8214-596FAC33FDB8}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1 L1:M42 L45:M1048576" xr:uid="{A9EBE1C3-8923-4578-8214-596FAC33FDB8}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B17 B19 B21:B29 B31:B42" xr:uid="{C7FD23E6-3E08-4DF7-8556-C07E455C4835}">
       <formula1>"Desktop,Laptop,Tablet,All-In-One"</formula1>
     </dataValidation>
@@ -6646,25 +6800,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6146040A-3AF4-440D-9E03-57379B2EC394}">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>208</v>
       </c>
@@ -6681,7 +6835,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>213</v>
       </c>
@@ -6695,7 +6849,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>215</v>
       </c>
@@ -6709,7 +6863,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>216</v>
       </c>
@@ -6726,7 +6880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>216</v>
       </c>
@@ -6743,7 +6897,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>216</v>
       </c>
@@ -6760,7 +6914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>216</v>
       </c>
@@ -6777,7 +6931,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>216</v>
       </c>
@@ -6794,7 +6948,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>216</v>
       </c>
@@ -6811,7 +6965,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>216</v>
       </c>
@@ -6828,7 +6982,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>225</v>
       </c>
@@ -6845,7 +6999,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>225</v>
       </c>
@@ -6862,7 +7016,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>225</v>
       </c>
@@ -6879,7 +7033,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>225</v>
       </c>
@@ -6896,7 +7050,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1">
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>227</v>
       </c>
@@ -6913,13 +7067,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="4:4" ht="15" customHeight="1">
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D17" s="23"/>
     </row>
-    <row r="18" spans="4:4" ht="15" customHeight="1">
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D18" s="23"/>
     </row>
-    <row r="19" spans="4:4" ht="15" customHeight="1">
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D19" s="23"/>
     </row>
   </sheetData>
@@ -6936,23 +7090,23 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F77F78-0898-4060-A2C7-C1A84336B28A}">
   <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="19" customWidth="1"/>
+    <col min="1" max="1" width="33.109375" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="28"/>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="24"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>230</v>
       </c>
@@ -6966,7 +7120,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>231</v>
       </c>
@@ -6980,7 +7134,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>233</v>
       </c>
@@ -6994,7 +7148,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>234</v>
       </c>
@@ -7008,7 +7162,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>236</v>
       </c>
@@ -7022,7 +7176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>237</v>
       </c>
@@ -7036,7 +7190,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>239</v>
       </c>
@@ -7050,7 +7204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>240</v>
       </c>
@@ -7064,7 +7218,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>242</v>
       </c>
@@ -7078,7 +7232,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>244</v>
       </c>
@@ -7092,7 +7246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>245</v>
       </c>
@@ -7106,7 +7260,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>247</v>
       </c>
@@ -7120,7 +7274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>248</v>
       </c>
@@ -7134,26 +7288,26 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:4"/>
-    <row r="16" spans="1:4"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3"/>
+    <row r="17" x14ac:dyDescent="0.3"/>
+    <row r="18" x14ac:dyDescent="0.3"/>
+    <row r="19" x14ac:dyDescent="0.3"/>
+    <row r="20" x14ac:dyDescent="0.3"/>
+    <row r="21" x14ac:dyDescent="0.3"/>
+    <row r="22" x14ac:dyDescent="0.3"/>
+    <row r="23" x14ac:dyDescent="0.3"/>
+    <row r="24" x14ac:dyDescent="0.3"/>
+    <row r="25" x14ac:dyDescent="0.3"/>
+    <row r="26" x14ac:dyDescent="0.3"/>
+    <row r="27" x14ac:dyDescent="0.3"/>
+    <row r="28" x14ac:dyDescent="0.3"/>
+    <row r="29" x14ac:dyDescent="0.3"/>
+    <row r="30" x14ac:dyDescent="0.3"/>
+    <row r="31" x14ac:dyDescent="0.3"/>
+    <row r="32" x14ac:dyDescent="0.3"/>
+    <row r="33" x14ac:dyDescent="0.3"/>
+    <row r="34" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/data/OldInventorySystem.xlsx
+++ b/data/OldInventorySystem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rosehulman-my.sharepoint.com/personal/lucasja_rose-hulman_edu/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3566" documentId="8_{A0F2C8DF-695D-4A53-BA74-C2F5D1F57A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A467ED7A-F1D3-41C0-9B3D-00F5C1CAE948}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{556398BC-9AA0-4613-9E16-7C15B14402EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
+    <workbookView xWindow="-315" yWindow="3510" windowWidth="19665" windowHeight="11055" firstSheet="1" activeTab="4" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Laptops" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="253">
   <si>
     <t>LAPTOPS</t>
   </si>
@@ -77,7 +77,7 @@
     <t>Column1</t>
   </si>
   <si>
-    <t>Lenovo 100e Chromebook 2nd Gen</t>
+    <t>100e Chromebook 2nd Gen</t>
   </si>
   <si>
     <t>Lenovo</t>
@@ -92,7 +92,7 @@
     <t>In Progress</t>
   </si>
   <si>
-    <t>Toshiba Satellite C655-S5547</t>
+    <t>Satellite C655-S5547</t>
   </si>
   <si>
     <t>Toshiba</t>
@@ -101,7 +101,7 @@
     <t>Won't turn on, has missing SSD</t>
   </si>
   <si>
-    <t>Apple MacBook Air A1369</t>
+    <t>MacBook Air A1369</t>
   </si>
   <si>
     <t>Apple</t>
@@ -113,37 +113,37 @@
     <t>bv</t>
   </si>
   <si>
-    <t>Apple MacBook Air A2179</t>
-  </si>
-  <si>
-    <t>Toshiba Satellite Click W35Dt-A3300</t>
+    <t>MacBook Air A2179</t>
+  </si>
+  <si>
+    <t>Satellite Click W35Dt-A3300</t>
   </si>
   <si>
     <t>Not Included</t>
   </si>
   <si>
-    <t>Toshiba Satellite C55t-C5300</t>
-  </si>
-  <si>
-    <t>Dell Precision M6700</t>
+    <t>Satellite C55t-C5300</t>
+  </si>
+  <si>
+    <t>Precision M6700</t>
   </si>
   <si>
     <t>Dell</t>
   </si>
   <si>
-    <t>Samsung 500C Chromebook</t>
+    <t>500C Chromebook</t>
   </si>
   <si>
     <t>Samsung</t>
   </si>
   <si>
-    <t>Dell Inspiron N7110</t>
+    <t>Inspiron N7110</t>
   </si>
   <si>
     <t>Needs OS installed, need to change to UEFI (if possible)</t>
   </si>
   <si>
-    <t>Lenovo Ideapad 3 Chromebook 11AST5</t>
+    <t>Ideapad 3 Chromebook 11AST5</t>
   </si>
   <si>
     <t>Battery issue</t>
@@ -152,7 +152,7 @@
     <t>No</t>
   </si>
   <si>
-    <t>HP Elitebook 8560p</t>
+    <t>Elitebook 8560p</t>
   </si>
   <si>
     <t>HP</t>
@@ -161,10 +161,10 @@
     <t>Needs Vanilla but isn't installing easily (Claims to be in legacy mode even after factory reset)</t>
   </si>
   <si>
-    <t>HP 15-db0004dx</t>
-  </si>
-  <si>
-    <t>HP ProBook 450 G7</t>
+    <t>15-db0004dx</t>
+  </si>
+  <si>
+    <t>ProBook 450 G7</t>
   </si>
   <si>
     <t>Screen does not turn on but power light does, SSD installed</t>
@@ -173,6 +173,9 @@
     <t>ThinkPad P15s Gen 1</t>
   </si>
   <si>
+    <t xml:space="preserve"> needs Windows updates needs usbc charger</t>
+  </si>
+  <si>
     <t>Thinkpad S230u</t>
   </si>
   <si>
@@ -191,19 +194,22 @@
     <t>Windows 11 w/ all updates, battery no work :(</t>
   </si>
   <si>
-    <t>Thinkpad Yoga 11e</t>
-  </si>
-  <si>
-    <t>Lenovo Edge 15</t>
-  </si>
-  <si>
-    <t>Dell Precision 5540</t>
+    <t>Edge 15</t>
+  </si>
+  <si>
+    <t>Needs Vinilla OS</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Precision 5540</t>
   </si>
   <si>
     <t>Broken hinges; attempted to be superglued</t>
   </si>
   <si>
-    <t>Acer C731 Series</t>
+    <t>C731 Series</t>
   </si>
   <si>
     <t>Acer</t>
@@ -215,7 +221,7 @@
     <t>DESKTOPS</t>
   </si>
   <si>
-    <t>Dell Optiplex 7040</t>
+    <t>Optiplex 7040</t>
   </si>
   <si>
     <t>Vanilla OS installs but can't boot to it - has SSD</t>
@@ -227,7 +233,7 @@
     <t>Boot issues (no boot device found after installation)</t>
   </si>
   <si>
-    <t>Dell Precision Tower 3420</t>
+    <t>Precision Tower 3420</t>
   </si>
   <si>
     <t>Being used as a 2.5" SSD eraser; Tal accidentally ripped the sata power port off the motherboard, so if it doesn't work that's why</t>
@@ -236,10 +242,10 @@
     <t>Has SSD, no bootable device found</t>
   </si>
   <si>
-    <t>Dell Optiplex 9020</t>
-  </si>
-  <si>
-    <t>Dell Optiplex 7050</t>
+    <t>Optiplex 9020</t>
+  </si>
+  <si>
+    <t>Optiplex 7050</t>
   </si>
   <si>
     <t>Done???</t>
@@ -248,46 +254,52 @@
     <t>Needs SSD and OS install</t>
   </si>
   <si>
-    <t>Dell Optiplex 960</t>
-  </si>
-  <si>
-    <t>Dell Optiplex 5060</t>
-  </si>
-  <si>
-    <t>Ram switched out</t>
-  </si>
-  <si>
-    <t>Dell Precision T3600</t>
+    <t>Optiplex 960</t>
+  </si>
+  <si>
+    <t>Precision T3600</t>
   </si>
   <si>
     <t>No OS, needs Vanilla; Ready to install</t>
   </si>
   <si>
-    <t>Dell Precision 7920</t>
-  </si>
-  <si>
-    <t>Dell Precision 5810</t>
-  </si>
-  <si>
-    <t>Dell Precision 5820</t>
-  </si>
-  <si>
-    <t>HP Ryzen 4000 Desktop</t>
-  </si>
-  <si>
-    <t>Dell OptiPlex 5050 Micro</t>
+    <t>Precision 7920</t>
+  </si>
+  <si>
+    <t>Precision 5810</t>
+  </si>
+  <si>
+    <t>Precision 5820</t>
+  </si>
+  <si>
+    <t>Ryzen 4000 Desktop</t>
+  </si>
+  <si>
+    <t>Optiplex 5050 Micro</t>
   </si>
   <si>
     <t>Installed SSD</t>
   </si>
   <si>
-    <t>Vanilla OS installed, needs to go through out-of-box experience</t>
-  </si>
-  <si>
-    <t>Dell Inspiron D16M001</t>
-  </si>
-  <si>
-    <t>Asus Chromebox CN60</t>
+    <r>
+      <t xml:space="preserve">Vanilla OS installed + DONE,  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CD Cover</t>
+    </r>
+  </si>
+  <si>
+    <t>Inspiron D16M001</t>
+  </si>
+  <si>
+    <t>Chromebox CN60</t>
   </si>
   <si>
     <t>Asus</t>
@@ -296,72 +308,75 @@
     <t>has like 4 Vanilla installations</t>
   </si>
   <si>
-    <t>Asus Chromebox Thin Client 3</t>
+    <t>Chromebox Thin Client 3</t>
   </si>
   <si>
     <t>Doesnt display video</t>
   </si>
   <si>
-    <t>Dell Precision T7810</t>
+    <t>Precision T7810</t>
   </si>
   <si>
     <t>"No bootable devices" still a problem</t>
   </si>
   <si>
-    <t>HP EliteDesk 800 G4 TWR</t>
-  </si>
-  <si>
-    <t>CoolerMaster custom build</t>
+    <t>EliteDesk 800 G4 TWR</t>
+  </si>
+  <si>
+    <t>Custom Build</t>
   </si>
   <si>
     <t>CoolerMaster</t>
   </si>
   <si>
-    <t>Lenovo ThinkCentre M700</t>
-  </si>
-  <si>
-    <t>HP ProDesk 400 G5 Desktop Mini</t>
-  </si>
-  <si>
-    <t>HP ProDesk 600 G3 Desktop Mini</t>
-  </si>
-  <si>
-    <t>Zotac Mini PC ZBox-CI323NANO</t>
-  </si>
-  <si>
-    <t>Zotac</t>
+    <t>ProDesk 400 G5 Desktop Mini</t>
+  </si>
+  <si>
+    <t>ProDesk 600 G3 Desktop Mini</t>
+  </si>
+  <si>
+    <t>Mini PC ZBox-CI323NANO</t>
   </si>
   <si>
     <t>Has Vanilla OS, can discover eduroam but not rhit open, ethernet works</t>
   </si>
   <si>
-    <t>HP ProDesk 600 G5 Desktop Mini</t>
-  </si>
-  <si>
-    <t>HP Z2 Mini G5 Workstation</t>
+    <t>ProDesk 600 G5 Desktop Mini</t>
+  </si>
+  <si>
+    <t>Windows Updates</t>
+  </si>
+  <si>
+    <t>Z2 Mini G5 Workstation</t>
   </si>
   <si>
     <t>Needs power supply; expensive!!!! MXM P620</t>
   </si>
   <si>
-    <t>Dell Optiplex 7070 micro</t>
+    <t>Optiplex 7070 micro</t>
+  </si>
+  <si>
+    <t>ThinkCentre M700</t>
   </si>
   <si>
     <t>Needs to play dugdug video, make clinky when moved</t>
   </si>
   <si>
+    <t>Optiplex 5060</t>
+  </si>
+  <si>
+    <t>Needs Windows 11, Has Vanilla OS</t>
+  </si>
+  <si>
     <t>TABLETS</t>
   </si>
   <si>
-    <t>Apple iPad A1397</t>
+    <t>iPad A1397</t>
   </si>
   <si>
     <t>Wifi + Cellular, Cracked screen</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>Wifi + Cellular</t>
   </si>
   <si>
@@ -401,7 +416,7 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Lenovo Thinkcenter E73</t>
+    <t>Thinkcenter E73</t>
   </si>
   <si>
     <t>Desktop</t>
@@ -419,7 +434,7 @@
     <t>SSD</t>
   </si>
   <si>
-    <t>Dell Inspiron 15 3552</t>
+    <t>Inspiron 15 3552</t>
   </si>
   <si>
     <t>Laptop</t>
@@ -428,7 +443,7 @@
     <t>Inspiron 15-3552</t>
   </si>
   <si>
-    <t>Asus Chromebox Thin Cilent 3</t>
+    <t>Chromebox Thin Cilent 3</t>
   </si>
   <si>
     <t>Intel Celeron 3865U</t>
@@ -443,13 +458,13 @@
     <t>Intel core i3-7100</t>
   </si>
   <si>
-    <t>Lenovo ThinkCentre M625q</t>
+    <t>ThinkCentre M625q</t>
   </si>
   <si>
     <t>AMD A9-9420e</t>
   </si>
   <si>
-    <t>Dell Latitude 5510</t>
+    <t>Latitude 5510</t>
   </si>
   <si>
     <t>Intel Core i7-10610U</t>
@@ -458,25 +473,25 @@
     <t>Windows 11</t>
   </si>
   <si>
-    <t>Dell Inspiron 3847</t>
+    <t>Inspiron 3847</t>
   </si>
   <si>
     <t>Intel Core i3-4170</t>
   </si>
   <si>
-    <t>Dell Latitude 5490</t>
+    <t>Latitude 5490</t>
   </si>
   <si>
     <t>Intel Core i7-8650U</t>
   </si>
   <si>
-    <t>Dell Inspiron 15 3537</t>
-  </si>
-  <si>
-    <t>Intel Core i3 ULV (4th generation)</t>
-  </si>
-  <si>
-    <t>Dell Latitude 5410</t>
+    <t>Inspiron 15 3537</t>
+  </si>
+  <si>
+    <t>Intel Core i3 ULV</t>
+  </si>
+  <si>
+    <t>Latitude 5410</t>
   </si>
   <si>
     <t>Intel Core i5-10210U</t>
@@ -491,13 +506,13 @@
     <t>macOS</t>
   </si>
   <si>
-    <t>HP ProBook 450 G6</t>
+    <t>ProBook 450 G6</t>
   </si>
   <si>
     <t>Intel Core i5-8265U</t>
   </si>
   <si>
-    <t>HP ProBook 450 G8</t>
+    <t>ProBook 450 G8</t>
   </si>
   <si>
     <t>Intel Core i5-1135G7</t>
@@ -506,13 +521,13 @@
     <t>Intel Core i7-6700</t>
   </si>
   <si>
-    <t>HP Elitebook 850 G6</t>
+    <t>Elitebook 850 G6</t>
   </si>
   <si>
     <t>Intel Core i7-8565U</t>
   </si>
   <si>
-    <t>HP ProBook 650 G3</t>
+    <t>ProBook 650 G3</t>
   </si>
   <si>
     <t>Intel Core i5-7300u</t>
@@ -521,12 +536,18 @@
     <t>Intel Core i7-4770</t>
   </si>
   <si>
-    <t>Dell Latitude 5580</t>
+    <t>Latitude 5580</t>
   </si>
   <si>
     <t>Intel Core i7-7820</t>
   </si>
   <si>
+    <t>Intel Core i5 6400t</t>
+  </si>
+  <si>
+    <t>Needs charger</t>
+  </si>
+  <si>
     <t>Donated Devices</t>
   </si>
   <si>
@@ -542,25 +563,34 @@
     <t>Recipient</t>
   </si>
   <si>
-    <t>Untracked Laptop given to Tarrant</t>
+    <t>Org?</t>
+  </si>
+  <si>
+    <t>Laptop given to Tarrant</t>
+  </si>
+  <si>
+    <t>Unknown</t>
   </si>
   <si>
     <t>International, via Wayne Tarrant</t>
   </si>
   <si>
-    <t>Dell Latitude 5500</t>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Latitude 5500</t>
   </si>
   <si>
     <t>Intel core i7-8665U</t>
   </si>
   <si>
-    <t>HP 15-AC113CL</t>
+    <t>15-AC113CL</t>
   </si>
   <si>
     <t>Intel core i3-5005U</t>
   </si>
   <si>
-    <t>Toshiba Satellite C55-B5296</t>
+    <t>Satellite C55-B5296</t>
   </si>
   <si>
     <t>Intel Celeron N2830</t>
@@ -569,19 +599,19 @@
     <t>Low battery health</t>
   </si>
   <si>
-    <t>HP EliteBook 850 G6</t>
+    <t>EliteBook 850 G6</t>
   </si>
   <si>
     <t>Intel core i7-8565U</t>
   </si>
   <si>
-    <t>Dell Latitude 5420</t>
+    <t>Latitude 5420</t>
   </si>
   <si>
     <t>Intel core i5-1145G7</t>
   </si>
   <si>
-    <t>Apple iPad Mini A1455</t>
+    <t>iPad Mini A1455</t>
   </si>
   <si>
     <t>Tablet</t>
@@ -596,16 +626,13 @@
     <t>DDR2</t>
   </si>
   <si>
-    <t>Flash Storage</t>
+    <t>eMMC</t>
   </si>
   <si>
     <t>WiFi + Cellular</t>
   </si>
   <si>
-    <t>Apple iPad Air 2 A1566</t>
-  </si>
-  <si>
-    <t>Dell OptiPlex 5060</t>
+    <t>iPad Air 2 A1566</t>
   </si>
   <si>
     <t>Intel core i5-8500</t>
@@ -617,6 +644,9 @@
     <t>The Learning Center, Terre Haute</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>Intel core i7-4770</t>
   </si>
   <si>
@@ -632,7 +662,7 @@
     <t>International, via Dr. Onyancha</t>
   </si>
   <si>
-    <t>Dell Optiplex 9010</t>
+    <t>Optiplex 9010</t>
   </si>
   <si>
     <t>Intel i7-3770</t>
@@ -665,7 +695,7 @@
     <t>Wabash Activity Center</t>
   </si>
   <si>
-    <t>y</t>
+    <t>PARTS</t>
   </si>
   <si>
     <t>Type</t>
@@ -686,9 +716,6 @@
     <t>SATA SSD</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>M2 SSD</t>
   </si>
   <si>
@@ -707,9 +734,6 @@
     <t>8GB DDR4</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>8GB DDR3</t>
   </si>
   <si>
@@ -789,9 +813,6 @@
   </si>
   <si>
     <t>USB Wifi Adapter</t>
-  </si>
-  <si>
-    <t>Org?</t>
   </si>
 </sst>
 </file>
@@ -803,7 +824,7 @@
     <numFmt numFmtId="164" formatCode="00000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -831,8 +852,15 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -849,6 +877,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC0E6F5"/>
         <bgColor rgb="FFC0E6F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -934,7 +968,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -984,32 +1018,60 @@
     <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="30">
     <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -1025,6 +1087,16 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1056,21 +1128,17 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -1132,6 +1200,23 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1157,50 +1242,38 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="00000"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1226,7 +1299,7 @@
     <tableColumn id="13" xr3:uid="{5BEE40AD-E450-4A13-BFB5-1D0CED084DB3}" name="ID"/>
     <tableColumn id="8" xr3:uid="{E9AB9B46-3541-4715-8E5B-024096D78342}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{F7DAC8DD-8096-40F1-8780-1DB9CB4EC72F}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="29"/>
     <tableColumn id="5" xr3:uid="{5338F6FB-43B0-44AF-AF8B-542FAC6CEDF0}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{64D6C993-8518-4A7C-9BDA-A54D7DBFBA8E}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{E5D987A3-C54A-4907-B710-79DB224E0008}" name="Current Status" totalsRowFunction="count"/>
@@ -1245,7 +1318,7 @@
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F96A3CC8-25D1-4CF8-877D-2816B26B7DC4}" name="Item Name" totalsRowLabel="Total"/>
-    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="25"/>
+    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="26"/>
     <tableColumn id="8" xr3:uid="{7D8F815E-A974-42A8-AC0B-AB8B951599A2}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{FEA94C75-B538-448A-A9F5-46F5A27E863D}" name="Year released"/>
     <tableColumn id="4" xr3:uid="{24998D92-36B7-4553-81E7-CB33711B31BB}" name="Special Reqs/Notes"/>
@@ -1267,7 +1340,7 @@
     <tableColumn id="13" xr3:uid="{EFFF3477-1A58-41CD-BFF3-45CE299505A7}" name="ID"/>
     <tableColumn id="8" xr3:uid="{C694899F-E385-4DE2-972A-7395A9633019}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{13C54556-A90A-4F9C-800D-3D838462DF46}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="25"/>
     <tableColumn id="5" xr3:uid="{6DE19FBC-9BD8-456E-9FC5-F633F61E4A34}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{68546225-0A78-43C1-A4F9-4D2E1DC008A3}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{0D7FD365-4F73-4A57-B8A1-CFAC47267923}" name="Current Status" totalsRowFunction="count"/>
@@ -1278,10 +1351,11 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:L33" totalsRowShown="0" tableBorderDxfId="23">
-  <autoFilter ref="A2:L33" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:M33" totalsRowShown="0" tableBorderDxfId="14">
+  <autoFilter ref="A2:M33" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}"/>
+  <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{73648E04-2EA1-4ADB-8E24-E7DDE01C0462}" name="Item"/>
+    <tableColumn id="13" xr3:uid="{DB867F70-87B5-4AE3-B35F-568639EAF10F}" name="Manufacturer"/>
     <tableColumn id="10" xr3:uid="{2C0BEEB0-DF56-4C3E-A199-8338A12BCED4}" name="Type of Device"/>
     <tableColumn id="3" xr3:uid="{6E6AE907-D46F-4E72-8A6E-4086D6ED467F}" name="Est. Year"/>
     <tableColumn id="4" xr3:uid="{21962421-D6C5-44DF-8B4E-CE81A5E85189}" name="CPU"/>
@@ -1290,8 +1364,8 @@
     <tableColumn id="2" xr3:uid="{C85B34EB-06B2-40A8-BBCB-B5F170EF3F82}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{A686D1B3-031E-4544-A98D-8F3144FA62B0}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{AB29939A-0AF4-4451-A6F4-2144F8957E73}" name="SSD/HDD"/>
-    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="12"/>
     <tableColumn id="12" xr3:uid="{67EC036F-98F6-4C6B-BDD7-99DB9B6ADF97}" name="ID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1299,10 +1373,11 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10100501-D05A-423B-A036-4B5D9B2ECD20}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:N59" totalsRowShown="0" tableBorderDxfId="20">
-  <autoFilter ref="A2:N59" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10100501-D05A-423B-A036-4B5D9B2ECD20}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:O59" totalsRowShown="0" tableBorderDxfId="5">
+  <autoFilter ref="A2:O59" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}"/>
+  <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{549BC727-085C-45F5-9520-711A34B50F51}" name="Item"/>
+    <tableColumn id="15" xr3:uid="{1796B66C-9564-4ED9-A973-A3E6CA0C2A0C}" name="Manufacturer"/>
     <tableColumn id="11" xr3:uid="{3C98AC72-613E-4EC8-8310-F9E3ED18CC90}" name="Type of Device"/>
     <tableColumn id="3" xr3:uid="{50863EE7-CAD0-400D-9B34-779EE33CD648}" name="Est. Year"/>
     <tableColumn id="4" xr3:uid="{00F5359B-A50E-41FF-A2BF-D2260FFBD06C}" name="CPU"/>
@@ -1311,10 +1386,10 @@
     <tableColumn id="13" xr3:uid="{A9DF335A-A163-4AA9-8879-B5B359D716CC}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{03AC00D8-5308-407D-9BAC-3303A2B380B3}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{CFFC1B93-1DA0-40C5-BC8E-01F5CAD8DB66}" name="SSD/HDD"/>
-    <tableColumn id="10" xr3:uid="{71AF2E6E-D071-4784-865B-CA65E73CD28D}" name="Est. Value" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{71AF2E6E-D071-4784-865B-CA65E73CD28D}" name="Est. Value" dataDxfId="4"/>
     <tableColumn id="12" xr3:uid="{EFA4DB39-7CD3-4AA7-9335-2FEE3F14CF55}" name="Notes"/>
-    <tableColumn id="9" xr3:uid="{2DC095C6-494B-405F-9E1B-C8849C64E6F1}" name="Date Donated" dataDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{4D76F748-9FDA-4C94-B04F-D8250CE6CE08}" name="Recipient" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{2DC095C6-494B-405F-9E1B-C8849C64E6F1}" name="Date Donated" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{4D76F748-9FDA-4C94-B04F-D8250CE6CE08}" name="Recipient" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{77D1B06F-E180-45FD-ACE9-4BA0C5955E95}" name="Org?"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1328,7 +1403,7 @@
     <tableColumn id="1" xr3:uid="{A07F4B01-C838-4D46-AE29-85BAC951AA36}" name="Type"/>
     <tableColumn id="3" xr3:uid="{9AC978C2-FD83-43AA-9C69-BC026B4E6411}" name="Description"/>
     <tableColumn id="4" xr3:uid="{9B2129F6-659A-4DD2-94CF-8EC39B827718}" name="Qty"/>
-    <tableColumn id="5" xr3:uid="{C24221AA-BF54-4384-AC51-1C5D1D76BE99}" name="Donated?" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{C24221AA-BF54-4384-AC51-1C5D1D76BE99}" name="Donated?" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{1B36C5CD-E753-4327-9D04-48D37AAB944F}" name="Value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1342,7 +1417,7 @@
     <tableColumn id="1" xr3:uid="{C29E963F-354B-4750-B17F-22461F6DC5F4}" name="Name"/>
     <tableColumn id="3" xr3:uid="{7C7B0B32-2D9C-4EDB-8E56-4C2ADECB5869}" name="Type"/>
     <tableColumn id="2" xr3:uid="{1155C0CA-025A-4922-8B0E-F2A817B3BB60}" name="Qty"/>
-    <tableColumn id="8" xr3:uid="{D743202E-D377-4920-815B-09F9ED9CC36B}" name="Value" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{D743202E-D377-4920-815B-09F9ED9CC36B}" name="Value" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1666,33 +1741,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5AA6A1-7D43-4966-8813-F497D895A5C2}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.109375" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5546875" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
-    <col min="7" max="7" width="19.44140625" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1724,11 +1799,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="E3" s="1"/>
       <c r="I3" s="16"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1754,11 +1829,11 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="E5" s="1"/>
       <c r="I5" s="16"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1784,7 +1859,7 @@
         <v>45673</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1811,7 +1886,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1835,7 +1910,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1859,7 +1934,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1883,7 +1958,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1907,7 +1982,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1931,7 +2006,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="30">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -1957,7 +2032,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -1986,7 +2061,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="45">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2012,7 +2087,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -2036,7 +2111,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="30">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2062,7 +2137,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="30">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2075,20 +2150,22 @@
       <c r="D18">
         <v>2020</v>
       </c>
-      <c r="E18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="F18" t="s">
         <v>25</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I18" s="16">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="30">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B19">
         <v>120</v>
@@ -2100,7 +2177,7 @@
         <v>2012</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
@@ -2112,9 +2189,9 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20">
         <v>121</v>
@@ -2136,21 +2213,21 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="30">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B21">
         <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D21">
         <v>2017</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F21" t="s">
         <v>14</v>
@@ -2165,35 +2242,11 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9">
       <c r="E22" s="1"/>
       <c r="I22" s="16"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23">
-        <v>123</v>
-      </c>
-      <c r="C23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23">
-        <v>2014</v>
-      </c>
-      <c r="E23" s="1"/>
-      <c r="F23" t="s">
-        <v>25</v>
-      </c>
-      <c r="H23" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="16">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -2206,24 +2259,29 @@
       <c r="D24">
         <v>2015</v>
       </c>
-      <c r="E24" s="1"/>
+      <c r="E24" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="F24" t="s">
         <v>25</v>
       </c>
+      <c r="G24" t="s">
+        <v>52</v>
+      </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I24" s="16">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="E25" s="1"/>
       <c r="I25" s="16"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="30">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B26">
         <v>134</v>
@@ -2235,7 +2293,7 @@
         <v>2019</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F26" t="s">
         <v>25</v>
@@ -2247,15 +2305,15 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B27">
         <v>137</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D27">
         <v>2017</v>
@@ -2271,15 +2329,15 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B28">
         <v>138</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D28">
         <v>2017</v>
@@ -2295,21 +2353,21 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B29">
         <v>136</v>
       </c>
       <c r="C29" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D29">
         <v>2017</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
@@ -2321,34 +2379,34 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9">
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:5">
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:5">
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="5:5">
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:5">
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="5:5">
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="5:5">
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="5:5">
       <c r="E39" s="1"/>
     </row>
   </sheetData>
@@ -2357,17 +2415,17 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21:H25 H3:H19" xr:uid="{BDBDE7E9-9FC3-44B3-919F-CEEE026A72CD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H19 H21:H22 H24:H25" xr:uid="{BDBDE7E9-9FC3-44B3-919F-CEEE026A72CD}">
       <formula1>"Not Started, In Progress, Scrapped, Unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G21:G25 G3:G19" xr:uid="{B3C7309D-E7FF-4409-A545-48D8D2AB8658}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G19 G21:G22 G24:G25" xr:uid="{B3C7309D-E7FF-4409-A545-48D8D2AB8658}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21:B25 B3:B19" xr:uid="{16B18C16-4889-4A0C-A4CE-D22AA5030E8B}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B19 B21:B22 B24:B25" xr:uid="{16B18C16-4889-4A0C-A4CE-D22AA5030E8B}">
       <formula1>0</formula1>
       <formula2>2000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F21:F25 F3:F19" xr:uid="{B98105AE-173E-4A15-99FD-BB956E15C3C9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F19 F21:F22 F24:F25" xr:uid="{B98105AE-173E-4A15-99FD-BB956E15C3C9}">
       <formula1>"Included, Not Included"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2381,29 +2439,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEA6183-B753-401C-B21E-C502785DFA3D}">
   <dimension ref="A1:G63"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="2" width="7.5546875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5546875" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
+      <c r="A1" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2426,9 +2484,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B3" s="13">
         <v>1</v>
@@ -2447,9 +2505,9 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B4" s="14">
         <v>2</v>
@@ -2468,9 +2526,9 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B5" s="13">
         <v>3</v>
@@ -2482,7 +2540,7 @@
         <v>2015</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>15</v>
@@ -2491,9 +2549,9 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="45">
       <c r="A6" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B6" s="14">
         <v>4</v>
@@ -2505,7 +2563,7 @@
         <v>2015</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>15</v>
@@ -2514,9 +2572,9 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="13">
         <v>5</v>
@@ -2535,9 +2593,9 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30">
       <c r="A8" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B8" s="14">
         <v>6</v>
@@ -2549,7 +2607,7 @@
         <v>2015</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>15</v>
@@ -2558,9 +2616,9 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B9" s="13">
         <v>7</v>
@@ -2579,7 +2637,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" s="8"/>
       <c r="B10" s="14"/>
       <c r="C10" s="9"/>
@@ -2588,9 +2646,9 @@
       <c r="F10" s="9"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B11" s="13">
         <v>9</v>
@@ -2609,9 +2667,9 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="60">
       <c r="A12" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B12" s="14">
         <v>12</v>
@@ -2623,7 +2681,7 @@
         <v>2016</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>15</v>
@@ -2632,9 +2690,9 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B13" s="14">
         <v>14</v>
@@ -2646,7 +2704,7 @@
         <v>2016</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>15</v>
@@ -2655,9 +2713,9 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B14" s="13">
         <v>18</v>
@@ -2676,9 +2734,9 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B15" s="14">
         <v>19</v>
@@ -2697,9 +2755,9 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B16" s="13">
         <v>20</v>
@@ -2718,9 +2776,9 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B17" s="14">
         <v>21</v>
@@ -2739,9 +2797,9 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B18" s="13">
         <v>23</v>
@@ -2760,9 +2818,9 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B19" s="14">
         <v>24</v>
@@ -2781,9 +2839,9 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B20" s="13">
         <v>25</v>
@@ -2802,9 +2860,9 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B21" s="14">
         <v>27</v>
@@ -2823,9 +2881,9 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B22" s="13">
         <v>28</v>
@@ -2844,9 +2902,9 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B23" s="14">
         <v>31</v>
@@ -2858,7 +2916,7 @@
         <v>2017</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>15</v>
@@ -2867,9 +2925,9 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B24" s="13">
         <v>32</v>
@@ -2888,14 +2946,16 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B25" s="14">
         <v>33</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="9" t="s">
+        <v>28</v>
+      </c>
       <c r="D25" s="9">
         <v>2013</v>
       </c>
@@ -2907,7 +2967,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26" s="4"/>
       <c r="B26" s="13"/>
       <c r="C26" s="5"/>
@@ -2916,9 +2976,9 @@
       <c r="F26" s="5"/>
       <c r="G26" s="7"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B27" s="14">
         <v>37</v>
@@ -2930,7 +2990,7 @@
         <v>2013</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>15</v>
@@ -2939,9 +2999,9 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B28" s="13">
         <v>38</v>
@@ -2960,30 +3020,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B29" s="14">
-        <v>39</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="9">
-        <v>2018</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" s="11">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30" s="8" t="s">
         <v>71</v>
       </c>
@@ -3006,7 +3043,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31" s="8" t="s">
         <v>73</v>
       </c>
@@ -3027,7 +3064,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32" s="8" t="s">
         <v>74</v>
       </c>
@@ -3048,7 +3085,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33" s="8" t="s">
         <v>75</v>
       </c>
@@ -3069,7 +3106,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34" s="8" t="s">
         <v>73</v>
       </c>
@@ -3090,7 +3127,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35" s="8" t="s">
         <v>76</v>
       </c>
@@ -3111,7 +3148,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>77</v>
       </c>
@@ -3134,9 +3171,9 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B37" s="12">
         <v>80</v>
@@ -3154,10 +3191,10 @@
         <v>15</v>
       </c>
       <c r="G37" s="16">
-        <v>46031</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>80</v>
       </c>
@@ -3177,7 +3214,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -3197,9 +3234,9 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B40" s="12">
         <v>35</v>
@@ -3220,7 +3257,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -3243,10 +3280,10 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="G42" s="16"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>81</v>
       </c>
@@ -3266,7 +3303,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>81</v>
       </c>
@@ -3286,7 +3323,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>81</v>
       </c>
@@ -3306,7 +3343,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>86</v>
       </c>
@@ -3320,7 +3357,7 @@
         <v>2014</v>
       </c>
       <c r="E46" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F46" t="s">
         <v>15</v>
@@ -3329,7 +3366,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>86</v>
       </c>
@@ -3352,7 +3389,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>88</v>
       </c>
@@ -3372,7 +3409,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>89</v>
       </c>
@@ -3389,35 +3426,18 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="50" spans="1:7">
+      <c r="G50" s="16"/>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
         <v>91</v>
-      </c>
-      <c r="B50" s="12">
-        <v>127</v>
-      </c>
-      <c r="C50" t="s">
-        <v>12</v>
-      </c>
-      <c r="D50">
-        <v>2016</v>
-      </c>
-      <c r="F50" t="s">
-        <v>21</v>
-      </c>
-      <c r="G50" s="16">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>92</v>
       </c>
       <c r="B51" s="12">
         <v>128</v>
       </c>
       <c r="C51" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D51">
         <v>2018</v>
@@ -3429,15 +3449,15 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B52" s="12">
         <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D52">
         <v>2017</v>
@@ -3449,21 +3469,21 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B53" s="12">
         <v>130</v>
       </c>
       <c r="C53" t="s">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="D53">
         <v>2015</v>
       </c>
       <c r="E53" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F53" t="s">
         <v>15</v>
@@ -3472,41 +3492,44 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B54" s="12">
         <v>131</v>
       </c>
       <c r="C54" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D54">
         <v>2019</v>
       </c>
+      <c r="E54" t="s">
+        <v>96</v>
+      </c>
       <c r="F54" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G54" s="16">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B55" s="12">
         <v>132</v>
       </c>
       <c r="C55" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D55">
         <v>2020</v>
       </c>
       <c r="E55" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F55" t="s">
         <v>15</v>
@@ -3515,29 +3538,32 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B56" s="12">
         <v>133</v>
       </c>
       <c r="C56" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D56">
         <v>2019</v>
       </c>
+      <c r="E56" t="s">
+        <v>96</v>
+      </c>
       <c r="F56" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G56" s="16">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B57" s="12">
         <v>135</v>
@@ -3555,7 +3581,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>75</v>
       </c>
@@ -3563,7 +3589,7 @@
         <v>139</v>
       </c>
       <c r="C58" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D58">
         <v>2018</v>
@@ -3575,15 +3601,15 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B59" s="12">
         <v>142</v>
       </c>
       <c r="C59" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D59">
         <v>2013</v>
@@ -3598,38 +3624,59 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G60" s="16"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>102</v>
+      </c>
+      <c r="B60" s="12">
+        <v>39</v>
+      </c>
+      <c r="C60" t="s">
+        <v>28</v>
+      </c>
+      <c r="D60">
+        <v>2018</v>
+      </c>
+      <c r="E60" t="s">
+        <v>103</v>
+      </c>
+      <c r="F60" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60" s="16">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="G61" s="16"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7">
       <c r="G62" s="16"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7">
       <c r="G63" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:G63">
-    <cfRule type="expression" dxfId="15" priority="1">
+  <conditionalFormatting sqref="A3:G28 A30:G59 A61:G63 B60:G60">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="27" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F44:F46 F49:F63 F3:F39" xr:uid="{6630553F-92E4-427F-9784-13858DB7D720}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F44:F46 F49:F63 F3:F28 F30:F39" xr:uid="{6630553F-92E4-427F-9784-13858DB7D720}">
       <formula1>"Not Started,In Progress,Scrapped,Unknown"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3637,33 +3684,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F948288C-1730-49D1-BD4C-FC704F167D22}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.109375" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5546875" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
+      <c r="A1" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3692,9 +3739,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B3">
         <v>74</v>
@@ -3706,13 +3753,13 @@
         <v>2011</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="H3" t="s">
         <v>21</v>
@@ -3721,9 +3768,9 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B4">
         <v>75</v>
@@ -3735,13 +3782,13 @@
         <v>2011</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="H4" t="s">
         <v>21</v>
@@ -3750,91 +3797,91 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:5">
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:5">
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:5">
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:5">
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:5">
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:5">
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:5">
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="5:5">
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="5:5">
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="5:5">
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:5">
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="5:5">
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="5:5">
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="5:5">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="5:5">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="5:5">
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:5">
       <c r="E33" s="1"/>
     </row>
   </sheetData>
@@ -3865,44 +3912,46 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFE86381-3E33-4CB8-A62B-E48A74AB9667}">
-  <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M36"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.33203125" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="17.109375" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" customWidth="1"/>
-    <col min="10" max="10" width="18.6640625" style="19" customWidth="1"/>
-    <col min="11" max="11" width="21.33203125" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" style="19" customWidth="1"/>
+    <col min="12" max="12" width="21.28515625" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-    </row>
-    <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13">
+      <c r="A1" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
         <v>110</v>
@@ -3925,978 +3974,1114 @@
       <c r="I2" t="s">
         <v>116</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" t="s">
         <v>117</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="19" t="s">
         <v>118</v>
       </c>
       <c r="L2" t="s">
+        <v>119</v>
+      </c>
+      <c r="M2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C3">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3">
         <v>2013</v>
-      </c>
-      <c r="D3" t="s">
-        <v>121</v>
       </c>
       <c r="E3" t="s">
         <v>122</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G3">
         <v>4</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3">
+        <v>256</v>
+      </c>
+      <c r="J3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K3" s="19">
+        <v>100</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4">
+        <v>2017</v>
+      </c>
+      <c r="E4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" t="s">
         <v>123</v>
       </c>
-      <c r="H3">
+      <c r="G4">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I4">
         <v>256</v>
       </c>
-      <c r="I3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J3" s="19">
-        <v>100</v>
-      </c>
-      <c r="K3" s="1"/>
-      <c r="L3">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="J4" t="s">
         <v>125</v>
       </c>
-      <c r="B4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4">
-        <v>2017</v>
-      </c>
-      <c r="D4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F4">
+      <c r="K4" s="19">
+        <v>200</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5">
+        <v>2018</v>
+      </c>
+      <c r="E5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G5">
         <v>8</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I5">
+        <v>256</v>
+      </c>
+      <c r="J5" t="s">
+        <v>125</v>
+      </c>
+      <c r="K5" s="19">
+        <v>175</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7">
+        <v>2018</v>
+      </c>
+      <c r="E7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" t="s">
         <v>123</v>
       </c>
-      <c r="H4">
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I7">
         <v>256</v>
       </c>
-      <c r="I4" t="s">
-        <v>124</v>
-      </c>
-      <c r="J4" s="19">
-        <v>200</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5">
-        <v>2018</v>
-      </c>
-      <c r="D5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E5" t="s">
-        <v>122</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5" t="s">
-        <v>130</v>
-      </c>
-      <c r="H5">
-        <v>256</v>
-      </c>
-      <c r="I5" t="s">
-        <v>124</v>
-      </c>
-      <c r="J5" s="19">
+      <c r="J7" t="s">
+        <v>125</v>
+      </c>
+      <c r="K7" s="19">
         <v>175</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C7">
-        <v>2018</v>
-      </c>
-      <c r="D7" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F7">
-        <v>8</v>
-      </c>
-      <c r="G7" t="s">
-        <v>130</v>
-      </c>
-      <c r="H7">
-        <v>256</v>
-      </c>
-      <c r="I7" t="s">
-        <v>124</v>
-      </c>
-      <c r="J7" s="19">
-        <v>175</v>
-      </c>
-      <c r="K7" s="1"/>
-      <c r="L7">
+      <c r="L7" s="1"/>
+      <c r="M7">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8">
+        <v>82</v>
+      </c>
+      <c r="C8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8">
         <v>2018</v>
       </c>
-      <c r="D8" t="s">
-        <v>132</v>
-      </c>
       <c r="E8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F8">
+        <v>133</v>
+      </c>
+      <c r="F8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G8">
         <v>8</v>
       </c>
-      <c r="G8" t="s">
-        <v>130</v>
-      </c>
-      <c r="H8">
+      <c r="H8" t="s">
+        <v>131</v>
+      </c>
+      <c r="I8">
         <v>256</v>
       </c>
-      <c r="I8" t="s">
-        <v>124</v>
-      </c>
-      <c r="J8" s="19">
+      <c r="J8" t="s">
+        <v>125</v>
+      </c>
+      <c r="K8" s="19">
         <v>175</v>
       </c>
-      <c r="K8" s="1"/>
-      <c r="L8">
+      <c r="L8" s="1"/>
+      <c r="M8">
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
-      </c>
-      <c r="C9">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9">
         <v>2018</v>
       </c>
-      <c r="D9" t="s">
-        <v>134</v>
-      </c>
       <c r="E9" t="s">
-        <v>122</v>
-      </c>
-      <c r="F9">
+        <v>135</v>
+      </c>
+      <c r="F9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G9">
         <v>8</v>
       </c>
-      <c r="G9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H9">
+      <c r="H9" t="s">
+        <v>131</v>
+      </c>
+      <c r="I9">
         <v>256</v>
       </c>
-      <c r="I9" t="s">
-        <v>124</v>
-      </c>
-      <c r="J9" s="19">
+      <c r="J9" t="s">
+        <v>125</v>
+      </c>
+      <c r="K9" s="19">
         <v>150</v>
       </c>
-      <c r="K9" s="1"/>
-      <c r="L9">
+      <c r="L9" s="1"/>
+      <c r="M9">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13">
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s">
-        <v>126</v>
-      </c>
-      <c r="C11">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11">
         <v>2020</v>
-      </c>
-      <c r="D11" t="s">
-        <v>136</v>
       </c>
       <c r="E11" t="s">
         <v>137</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="s">
+        <v>138</v>
+      </c>
+      <c r="G11">
         <v>8</v>
       </c>
-      <c r="G11" t="s">
-        <v>130</v>
-      </c>
-      <c r="H11">
+      <c r="H11" t="s">
+        <v>131</v>
+      </c>
+      <c r="I11">
         <v>256</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K11" s="19">
+        <v>300</v>
+      </c>
+      <c r="L11" s="1"/>
+      <c r="M11">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12">
+        <v>2014</v>
+      </c>
+      <c r="E12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G12">
+        <v>8</v>
+      </c>
+      <c r="H12" t="s">
         <v>124</v>
       </c>
-      <c r="J11" s="19">
-        <v>300</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="I12">
+        <v>256</v>
+      </c>
+      <c r="J12" t="s">
+        <v>125</v>
+      </c>
+      <c r="K12" s="2">
+        <v>175</v>
+      </c>
+      <c r="M12">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13">
+        <v>2018</v>
+      </c>
+      <c r="E13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F13" t="s">
         <v>138</v>
       </c>
-      <c r="B12" t="s">
+      <c r="G13">
+        <v>8</v>
+      </c>
+      <c r="H13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I13">
+        <v>256</v>
+      </c>
+      <c r="J13" t="s">
+        <v>125</v>
+      </c>
+      <c r="K13" s="19">
         <v>120</v>
       </c>
-      <c r="C12">
+      <c r="L13" s="1"/>
+      <c r="M13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15" customHeight="1">
+      <c r="A14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14">
+        <v>2018</v>
+      </c>
+      <c r="E14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F14" t="s">
+        <v>123</v>
+      </c>
+      <c r="G14">
+        <v>8</v>
+      </c>
+      <c r="H14" t="s">
+        <v>131</v>
+      </c>
+      <c r="I14">
+        <v>256</v>
+      </c>
+      <c r="J14" t="s">
+        <v>125</v>
+      </c>
+      <c r="K14" s="19">
+        <v>175</v>
+      </c>
+      <c r="L14" s="1"/>
+      <c r="M14">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15" customHeight="1">
+      <c r="A15" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15">
+        <v>2013</v>
+      </c>
+      <c r="E15" t="s">
+        <v>144</v>
+      </c>
+      <c r="F15" t="s">
+        <v>123</v>
+      </c>
+      <c r="G15">
+        <v>8</v>
+      </c>
+      <c r="H15" t="s">
+        <v>124</v>
+      </c>
+      <c r="I15">
+        <v>256</v>
+      </c>
+      <c r="J15" t="s">
+        <v>125</v>
+      </c>
+      <c r="K15" s="19">
+        <v>150</v>
+      </c>
+      <c r="L15" s="1"/>
+      <c r="M15">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15" customHeight="1">
+      <c r="A16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D16">
+        <v>2019</v>
+      </c>
+      <c r="E16" t="s">
+        <v>146</v>
+      </c>
+      <c r="F16" t="s">
+        <v>138</v>
+      </c>
+      <c r="G16">
+        <v>8</v>
+      </c>
+      <c r="H16" t="s">
+        <v>131</v>
+      </c>
+      <c r="I16">
+        <v>256</v>
+      </c>
+      <c r="J16" t="s">
+        <v>125</v>
+      </c>
+      <c r="K16" s="19">
+        <v>265</v>
+      </c>
+      <c r="L16" s="1"/>
+      <c r="M16">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15" customHeight="1">
+      <c r="A17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17">
         <v>2014</v>
-      </c>
-      <c r="D12" t="s">
-        <v>139</v>
-      </c>
-      <c r="E12" t="s">
-        <v>122</v>
-      </c>
-      <c r="F12">
-        <v>8</v>
-      </c>
-      <c r="G12" t="s">
-        <v>123</v>
-      </c>
-      <c r="H12">
-        <v>256</v>
-      </c>
-      <c r="I12" t="s">
-        <v>124</v>
-      </c>
-      <c r="J12" s="2">
-        <v>175</v>
-      </c>
-      <c r="L12">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13">
-        <v>2018</v>
-      </c>
-      <c r="D13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F13">
-        <v>8</v>
-      </c>
-      <c r="G13" t="s">
-        <v>130</v>
-      </c>
-      <c r="H13">
-        <v>256</v>
-      </c>
-      <c r="I13" t="s">
-        <v>124</v>
-      </c>
-      <c r="J13" s="19">
-        <v>120</v>
-      </c>
-      <c r="K13" s="1"/>
-      <c r="L13">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>128</v>
-      </c>
-      <c r="B14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14">
-        <v>2018</v>
-      </c>
-      <c r="D14" t="s">
-        <v>132</v>
-      </c>
-      <c r="E14" t="s">
-        <v>122</v>
-      </c>
-      <c r="F14">
-        <v>8</v>
-      </c>
-      <c r="G14" t="s">
-        <v>130</v>
-      </c>
-      <c r="H14">
-        <v>256</v>
-      </c>
-      <c r="I14" t="s">
-        <v>124</v>
-      </c>
-      <c r="J14" s="19">
-        <v>175</v>
-      </c>
-      <c r="K14" s="1"/>
-      <c r="L14">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>142</v>
-      </c>
-      <c r="B15" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15">
-        <v>2013</v>
-      </c>
-      <c r="D15" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" t="s">
-        <v>122</v>
-      </c>
-      <c r="F15">
-        <v>8</v>
-      </c>
-      <c r="G15" t="s">
-        <v>123</v>
-      </c>
-      <c r="H15">
-        <v>256</v>
-      </c>
-      <c r="I15" t="s">
-        <v>124</v>
-      </c>
-      <c r="J15" s="19">
-        <v>150</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>144</v>
-      </c>
-      <c r="B16" t="s">
-        <v>126</v>
-      </c>
-      <c r="C16">
-        <v>2019</v>
-      </c>
-      <c r="D16" t="s">
-        <v>145</v>
-      </c>
-      <c r="E16" t="s">
-        <v>137</v>
-      </c>
-      <c r="F16">
-        <v>8</v>
-      </c>
-      <c r="G16" t="s">
-        <v>130</v>
-      </c>
-      <c r="H16">
-        <v>256</v>
-      </c>
-      <c r="I16" t="s">
-        <v>124</v>
-      </c>
-      <c r="J16" s="19">
-        <v>265</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>146</v>
-      </c>
-      <c r="B17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C17">
-        <v>2014</v>
-      </c>
-      <c r="D17" t="s">
-        <v>147</v>
       </c>
       <c r="E17" t="s">
         <v>148</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="s">
+        <v>149</v>
+      </c>
+      <c r="G17">
         <v>8</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
+        <v>124</v>
+      </c>
+      <c r="I17">
+        <v>256</v>
+      </c>
+      <c r="J17" t="s">
+        <v>125</v>
+      </c>
+      <c r="K17" s="19">
+        <v>100</v>
+      </c>
+      <c r="L17" s="1"/>
+      <c r="M17">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15" customHeight="1">
+      <c r="A18" t="s">
+        <v>150</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18">
+        <v>2019</v>
+      </c>
+      <c r="E18" t="s">
+        <v>151</v>
+      </c>
+      <c r="F18" t="s">
         <v>123</v>
       </c>
-      <c r="H17">
+      <c r="G18">
+        <v>8</v>
+      </c>
+      <c r="H18" t="s">
+        <v>131</v>
+      </c>
+      <c r="I18">
         <v>256</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J18" t="s">
+        <v>125</v>
+      </c>
+      <c r="K18" s="19">
+        <v>300</v>
+      </c>
+      <c r="L18" s="1"/>
+      <c r="M18">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15" customHeight="1">
+      <c r="A19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19">
+        <v>2019</v>
+      </c>
+      <c r="E19" t="s">
+        <v>151</v>
+      </c>
+      <c r="F19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19">
+        <v>8</v>
+      </c>
+      <c r="H19" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19">
+        <v>256</v>
+      </c>
+      <c r="J19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K19" s="19">
+        <v>300</v>
+      </c>
+      <c r="L19" s="1"/>
+      <c r="M19">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="15" customHeight="1">
+      <c r="A20" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20">
+        <v>2021</v>
+      </c>
+      <c r="E20" t="s">
+        <v>153</v>
+      </c>
+      <c r="F20" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20">
+        <v>8</v>
+      </c>
+      <c r="H20" t="s">
+        <v>131</v>
+      </c>
+      <c r="I20">
+        <v>256</v>
+      </c>
+      <c r="J20" t="s">
+        <v>125</v>
+      </c>
+      <c r="K20" s="19">
+        <v>350</v>
+      </c>
+      <c r="L20" s="1"/>
+      <c r="M20">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15" customHeight="1">
+      <c r="A21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21">
+        <v>2021</v>
+      </c>
+      <c r="E21" t="s">
+        <v>153</v>
+      </c>
+      <c r="F21" t="s">
+        <v>138</v>
+      </c>
+      <c r="G21">
+        <v>8</v>
+      </c>
+      <c r="H21" t="s">
+        <v>131</v>
+      </c>
+      <c r="I21">
+        <v>256</v>
+      </c>
+      <c r="J21" t="s">
+        <v>125</v>
+      </c>
+      <c r="K21" s="19">
+        <v>350</v>
+      </c>
+      <c r="L21" s="1"/>
+      <c r="M21">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15" customHeight="1">
+      <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22">
+        <v>2016</v>
+      </c>
+      <c r="E22" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22" t="s">
+        <v>123</v>
+      </c>
+      <c r="G22">
+        <v>16</v>
+      </c>
+      <c r="H22" t="s">
+        <v>131</v>
+      </c>
+      <c r="I22">
+        <v>256</v>
+      </c>
+      <c r="J22" t="s">
+        <v>125</v>
+      </c>
+      <c r="K22" s="19">
+        <v>255</v>
+      </c>
+      <c r="L22" s="1"/>
+      <c r="M22">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15" customHeight="1">
+      <c r="A23" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23">
+        <v>2019</v>
+      </c>
+      <c r="E23" t="s">
+        <v>156</v>
+      </c>
+      <c r="F23" t="s">
+        <v>138</v>
+      </c>
+      <c r="G23">
+        <v>16</v>
+      </c>
+      <c r="H23" t="s">
+        <v>131</v>
+      </c>
+      <c r="I23">
+        <v>256</v>
+      </c>
+      <c r="J23" t="s">
+        <v>125</v>
+      </c>
+      <c r="K23" s="19">
+        <v>300</v>
+      </c>
+      <c r="L23" s="1"/>
+      <c r="M23">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15" customHeight="1">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24">
+        <v>2015</v>
+      </c>
+      <c r="E24" t="s">
+        <v>154</v>
+      </c>
+      <c r="F24" t="s">
+        <v>138</v>
+      </c>
+      <c r="G24">
+        <v>16</v>
+      </c>
+      <c r="H24" t="s">
+        <v>131</v>
+      </c>
+      <c r="I24">
+        <v>256</v>
+      </c>
+      <c r="J24" t="s">
+        <v>125</v>
+      </c>
+      <c r="K24" s="19">
+        <v>255</v>
+      </c>
+      <c r="L24" s="1"/>
+      <c r="M24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15" customHeight="1">
+      <c r="A25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25">
+        <v>2018</v>
+      </c>
+      <c r="E25" t="s">
+        <v>133</v>
+      </c>
+      <c r="F25" t="s">
+        <v>123</v>
+      </c>
+      <c r="G25">
+        <v>8</v>
+      </c>
+      <c r="H25" t="s">
+        <v>131</v>
+      </c>
+      <c r="I25">
+        <v>256</v>
+      </c>
+      <c r="J25" t="s">
+        <v>125</v>
+      </c>
+      <c r="K25" s="19">
+        <v>175</v>
+      </c>
+      <c r="L25" s="1"/>
+      <c r="M25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15" customHeight="1">
+      <c r="A26" t="s">
+        <v>157</v>
+      </c>
+      <c r="B26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26">
+        <v>2017</v>
+      </c>
+      <c r="E26" t="s">
+        <v>158</v>
+      </c>
+      <c r="F26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26">
+        <v>8</v>
+      </c>
+      <c r="H26" t="s">
+        <v>131</v>
+      </c>
+      <c r="I26">
+        <v>256</v>
+      </c>
+      <c r="J26" t="s">
+        <v>125</v>
+      </c>
+      <c r="K26" s="19">
+        <v>150</v>
+      </c>
+      <c r="L26" s="1"/>
+      <c r="M26">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15" customHeight="1">
+      <c r="A27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27">
+        <v>2017</v>
+      </c>
+      <c r="E27" t="s">
+        <v>158</v>
+      </c>
+      <c r="F27" t="s">
+        <v>138</v>
+      </c>
+      <c r="G27">
+        <v>8</v>
+      </c>
+      <c r="H27" t="s">
+        <v>131</v>
+      </c>
+      <c r="I27">
+        <v>256</v>
+      </c>
+      <c r="J27" t="s">
+        <v>125</v>
+      </c>
+      <c r="K27" s="19">
+        <v>200</v>
+      </c>
+      <c r="L27" s="1"/>
+      <c r="M27">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="15" customHeight="1">
+      <c r="A28" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28">
+        <v>2013</v>
+      </c>
+      <c r="E28" t="s">
+        <v>159</v>
+      </c>
+      <c r="F28" t="s">
+        <v>123</v>
+      </c>
+      <c r="G28">
+        <v>8</v>
+      </c>
+      <c r="H28" t="s">
         <v>124</v>
       </c>
-      <c r="J17" s="19">
+      <c r="I28">
+        <v>256</v>
+      </c>
+      <c r="J28" t="s">
+        <v>125</v>
+      </c>
+      <c r="K28" s="19">
+        <v>200</v>
+      </c>
+      <c r="L28" s="1"/>
+      <c r="M28">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="15" customHeight="1">
+      <c r="A29" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>127</v>
+      </c>
+      <c r="D29">
+        <v>2018</v>
+      </c>
+      <c r="E29" t="s">
+        <v>161</v>
+      </c>
+      <c r="F29" t="s">
+        <v>138</v>
+      </c>
+      <c r="G29">
+        <v>16</v>
+      </c>
+      <c r="H29" t="s">
+        <v>131</v>
+      </c>
+      <c r="I29">
+        <v>256</v>
+      </c>
+      <c r="J29" t="s">
+        <v>125</v>
+      </c>
+      <c r="K29" s="19">
+        <v>325</v>
+      </c>
+      <c r="L29" s="1"/>
+      <c r="M29">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15" customHeight="1">
+      <c r="A30" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="K17" s="1"/>
-      <c r="L17">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>149</v>
-      </c>
-      <c r="B18" t="s">
-        <v>126</v>
-      </c>
-      <c r="C18">
-        <v>2019</v>
-      </c>
-      <c r="D18" t="s">
-        <v>150</v>
-      </c>
-      <c r="E18" t="s">
-        <v>122</v>
-      </c>
-      <c r="F18">
+      <c r="B30" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s">
+        <v>127</v>
+      </c>
+      <c r="D30">
+        <v>2016</v>
+      </c>
+      <c r="E30" t="s">
+        <v>162</v>
+      </c>
+      <c r="F30" t="s">
+        <v>123</v>
+      </c>
+      <c r="G30">
         <v>8</v>
       </c>
-      <c r="G18" t="s">
-        <v>130</v>
-      </c>
-      <c r="H18">
+      <c r="H30" t="s">
+        <v>131</v>
+      </c>
+      <c r="I30">
         <v>256</v>
       </c>
-      <c r="I18" t="s">
-        <v>124</v>
-      </c>
-      <c r="J18" s="19">
-        <v>300</v>
-      </c>
-      <c r="K18" s="1"/>
-      <c r="L18">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B19" t="s">
-        <v>126</v>
-      </c>
-      <c r="C19">
-        <v>2019</v>
-      </c>
-      <c r="D19" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" t="s">
-        <v>137</v>
-      </c>
-      <c r="F19">
-        <v>8</v>
-      </c>
-      <c r="G19" t="s">
-        <v>130</v>
-      </c>
-      <c r="H19">
-        <v>256</v>
-      </c>
-      <c r="I19" t="s">
-        <v>124</v>
-      </c>
-      <c r="J19" s="19">
-        <v>300</v>
-      </c>
-      <c r="K19" s="1"/>
-      <c r="L19">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>151</v>
-      </c>
-      <c r="B20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C20">
-        <v>2021</v>
-      </c>
-      <c r="D20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E20" t="s">
-        <v>137</v>
-      </c>
-      <c r="F20">
-        <v>8</v>
-      </c>
-      <c r="G20" t="s">
-        <v>130</v>
-      </c>
-      <c r="H20">
-        <v>256</v>
-      </c>
-      <c r="I20" t="s">
-        <v>124</v>
-      </c>
-      <c r="J20" s="19">
-        <v>350</v>
-      </c>
-      <c r="K20" s="1"/>
-      <c r="L20">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>151</v>
-      </c>
-      <c r="B21" t="s">
-        <v>126</v>
-      </c>
-      <c r="C21">
-        <v>2021</v>
-      </c>
-      <c r="D21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E21" t="s">
-        <v>137</v>
-      </c>
-      <c r="F21">
-        <v>8</v>
-      </c>
-      <c r="G21" t="s">
-        <v>130</v>
-      </c>
-      <c r="H21">
-        <v>256</v>
-      </c>
-      <c r="I21" t="s">
-        <v>124</v>
-      </c>
-      <c r="J21" s="19">
-        <v>350</v>
-      </c>
-      <c r="K21" s="1"/>
-      <c r="L21">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C22">
-        <v>2016</v>
-      </c>
-      <c r="D22" t="s">
-        <v>153</v>
-      </c>
-      <c r="E22" t="s">
-        <v>122</v>
-      </c>
-      <c r="F22">
-        <v>16</v>
-      </c>
-      <c r="G22" t="s">
-        <v>130</v>
-      </c>
-      <c r="H22">
-        <v>256</v>
-      </c>
-      <c r="I22" t="s">
-        <v>124</v>
-      </c>
-      <c r="J22" s="19">
-        <v>255</v>
-      </c>
-      <c r="K22" s="1"/>
-      <c r="L22">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>154</v>
-      </c>
-      <c r="B23" t="s">
-        <v>126</v>
-      </c>
-      <c r="C23">
-        <v>2019</v>
-      </c>
-      <c r="D23" t="s">
-        <v>155</v>
-      </c>
-      <c r="E23" t="s">
-        <v>137</v>
-      </c>
-      <c r="F23">
-        <v>16</v>
-      </c>
-      <c r="G23" t="s">
-        <v>130</v>
-      </c>
-      <c r="H23">
-        <v>256</v>
-      </c>
-      <c r="I23" t="s">
-        <v>124</v>
-      </c>
-      <c r="J23" s="19">
-        <v>300</v>
-      </c>
-      <c r="K23" s="1"/>
-      <c r="L23">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" t="s">
-        <v>120</v>
-      </c>
-      <c r="C24">
-        <v>2015</v>
-      </c>
-      <c r="D24" t="s">
-        <v>153</v>
-      </c>
-      <c r="E24" t="s">
-        <v>137</v>
-      </c>
-      <c r="F24">
-        <v>16</v>
-      </c>
-      <c r="G24" t="s">
-        <v>130</v>
-      </c>
-      <c r="H24">
-        <v>256</v>
-      </c>
-      <c r="I24" t="s">
-        <v>124</v>
-      </c>
-      <c r="J24" s="19">
-        <v>255</v>
-      </c>
-      <c r="K24" s="1"/>
-      <c r="L24">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>128</v>
-      </c>
-      <c r="B25" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25">
-        <v>2018</v>
-      </c>
-      <c r="D25" t="s">
-        <v>132</v>
-      </c>
-      <c r="E25" t="s">
-        <v>122</v>
-      </c>
-      <c r="F25">
-        <v>8</v>
-      </c>
-      <c r="G25" t="s">
-        <v>130</v>
-      </c>
-      <c r="H25">
-        <v>256</v>
-      </c>
-      <c r="I25" t="s">
-        <v>124</v>
-      </c>
-      <c r="J25" s="19">
-        <v>175</v>
-      </c>
-      <c r="K25" s="1"/>
-      <c r="L25">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>156</v>
-      </c>
-      <c r="B26" t="s">
-        <v>126</v>
-      </c>
-      <c r="C26">
-        <v>2017</v>
-      </c>
-      <c r="D26" t="s">
-        <v>157</v>
-      </c>
-      <c r="E26" t="s">
-        <v>122</v>
-      </c>
-      <c r="F26">
-        <v>8</v>
-      </c>
-      <c r="G26" t="s">
-        <v>130</v>
-      </c>
-      <c r="H26">
-        <v>256</v>
-      </c>
-      <c r="I26" t="s">
-        <v>124</v>
-      </c>
-      <c r="J26" s="19">
-        <v>150</v>
-      </c>
-      <c r="K26" s="1"/>
-      <c r="L26">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" t="s">
-        <v>126</v>
-      </c>
-      <c r="C27">
-        <v>2017</v>
-      </c>
-      <c r="D27" t="s">
-        <v>157</v>
-      </c>
-      <c r="E27" t="s">
-        <v>137</v>
-      </c>
-      <c r="F27">
-        <v>8</v>
-      </c>
-      <c r="G27" t="s">
-        <v>130</v>
-      </c>
-      <c r="H27">
-        <v>256</v>
-      </c>
-      <c r="I27" t="s">
-        <v>124</v>
-      </c>
-      <c r="J27" s="19">
+      <c r="J30" t="s">
+        <v>125</v>
+      </c>
+      <c r="K30" s="19">
         <v>200</v>
       </c>
-      <c r="K27" s="1"/>
-      <c r="L27">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B28" t="s">
-        <v>120</v>
-      </c>
-      <c r="C28">
-        <v>2013</v>
-      </c>
-      <c r="D28" t="s">
-        <v>158</v>
-      </c>
-      <c r="E28" t="s">
-        <v>122</v>
-      </c>
-      <c r="F28">
-        <v>8</v>
-      </c>
-      <c r="G28" t="s">
-        <v>123</v>
-      </c>
-      <c r="H28">
-        <v>256</v>
-      </c>
-      <c r="I28" t="s">
-        <v>124</v>
-      </c>
-      <c r="J28" s="19">
-        <v>200</v>
-      </c>
-      <c r="K28" s="1"/>
-      <c r="L28">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>159</v>
-      </c>
-      <c r="B29" t="s">
-        <v>126</v>
-      </c>
-      <c r="C29">
-        <v>2018</v>
-      </c>
-      <c r="D29" t="s">
-        <v>160</v>
-      </c>
-      <c r="E29" t="s">
-        <v>137</v>
-      </c>
-      <c r="F29">
-        <v>16</v>
-      </c>
-      <c r="G29" t="s">
-        <v>130</v>
-      </c>
-      <c r="H29">
-        <v>256</v>
-      </c>
-      <c r="I29" t="s">
-        <v>124</v>
-      </c>
-      <c r="J29" s="19">
-        <v>325</v>
-      </c>
-      <c r="K29" s="1"/>
-      <c r="L29">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K30" s="1"/>
-    </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K31" s="1"/>
-    </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K32" s="1"/>
-    </row>
-    <row r="33" spans="11:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K33" s="1"/>
+      <c r="L30" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="M30">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="15" customHeight="1">
+      <c r="L31" s="1"/>
+    </row>
+    <row r="32" spans="1:13" ht="15" customHeight="1">
+      <c r="L32" s="1"/>
+    </row>
+    <row r="33" spans="3:12" ht="15" customHeight="1">
+      <c r="L33" s="1"/>
+    </row>
+    <row r="36" spans="3:12" ht="15" customHeight="1">
+      <c r="C36" s="26"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A27:A28">
-    <cfRule type="expression" dxfId="13" priority="17">
+  <conditionalFormatting sqref="A27:B28 A30:B30">
+    <cfRule type="expression" dxfId="24" priority="21">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="18">
+    <cfRule type="expression" dxfId="23" priority="22">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:K9 A11:K14 A15:C15 E15:K15 A16:K25">
-    <cfRule type="expression" dxfId="11" priority="21">
+  <conditionalFormatting sqref="A3:L9 A11:L14 A15:D15 F15:L15 A16:L25">
+    <cfRule type="expression" dxfId="22" priority="25">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:L9 A11:L14 A15:C15 E15:L15 A16:L25">
-    <cfRule type="expression" dxfId="10" priority="22">
+  <conditionalFormatting sqref="A3:M9 A11:M14 A15:D15 F15:M15 A16:M25">
+    <cfRule type="expression" dxfId="21" priority="26">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G26:G29">
-    <cfRule type="expression" dxfId="9" priority="9">
+  <conditionalFormatting sqref="C36:I36">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10">
+    <cfRule type="expression" dxfId="19" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H29">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="18" priority="13">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="17" priority="14">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12:L25 L3:L4" xr:uid="{BD4480FF-AB8D-4446-AB7A-01C4C2A99ADB}">
+  <conditionalFormatting sqref="I26:I29">
+    <cfRule type="expression" dxfId="16" priority="5">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="6">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M12:M25 M3:M4" xr:uid="{BD4480FF-AB8D-4446-AB7A-01C4C2A99ADB}">
       <formula1>1</formula1>
       <formula2>2000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B4 B13:B21 B23:B25" xr:uid="{23899482-37F4-4DDA-A40C-55EF7962BD79}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C4 C13:C21 C23:C25" xr:uid="{23899482-37F4-4DDA-A40C-55EF7962BD79}">
       <formula1>"Desktop,Laptop,Tablet,All-In-One"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36" xr:uid="{C368B9B8-2EFC-4D0F-9393-97EEDF8604DA}">
+      <formula1>"Not Started,In Progress,Scrapped,Unknown"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4908,56 +5093,57 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1C144A-BB57-4446-B714-000D1D9FAB4A}">
-  <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q59"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.109375" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.33203125" customWidth="1"/>
-    <col min="12" max="12" width="16.88671875" style="16" customWidth="1"/>
-    <col min="13" max="13" width="33.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.6640625" customWidth="1"/>
-    <col min="16" max="16" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" style="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.85546875" style="16" customWidth="1"/>
+    <col min="14" max="14" width="33.28515625" style="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.7109375" customWidth="1"/>
+    <col min="17" max="17" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="C1" s="18"/>
+    <row r="1" spans="1:17" ht="15" customHeight="1">
+      <c r="C1" s="17" t="s">
+        <v>164</v>
+      </c>
       <c r="D1" s="18"/>
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="22"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="18"/>
       <c r="M1" s="22"/>
-      <c r="N1" s="18"/>
-      <c r="O1" t="s">
-        <v>162</v>
-      </c>
+      <c r="N1" s="22"/>
+      <c r="O1" s="18"/>
       <c r="P1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
         <v>110</v>
@@ -4980,1813 +5166,1942 @@
       <c r="I2" t="s">
         <v>116</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" t="s">
         <v>117</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="L2" s="16" t="s">
-        <v>164</v>
+      <c r="L2" t="s">
+        <v>119</v>
       </c>
       <c r="M2" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="N2" t="s">
-        <v>249</v>
-      </c>
-      <c r="O2" s="2">
-        <f>SUM(J3:J38)</f>
+        <v>167</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="O2" t="s">
+        <v>169</v>
+      </c>
+      <c r="P2" s="2">
+        <f>SUM(K3:K38)</f>
         <v>9870</v>
       </c>
-      <c r="P2">
-        <f>COUNTIF(N3:N42,"*International*")</f>
+      <c r="Q2">
+        <f>COUNTIF(O3:O42,"*International*")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3">
+        <v>171</v>
+      </c>
+      <c r="C3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3">
         <v>2019</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>256</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K3" s="19">
+        <v>225</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="15">
+        <v>45970</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4">
+        <v>2019</v>
+      </c>
+      <c r="I4">
+        <v>256</v>
+      </c>
+      <c r="J4" t="s">
+        <v>125</v>
+      </c>
+      <c r="K4" s="19">
+        <v>225</v>
+      </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="15">
+        <v>45970</v>
+      </c>
+      <c r="N4" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5">
+        <v>2019</v>
+      </c>
+      <c r="I5">
+        <v>256</v>
+      </c>
+      <c r="J5" t="s">
+        <v>125</v>
+      </c>
+      <c r="K5" s="19">
+        <v>225</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="15">
+        <v>45970</v>
+      </c>
+      <c r="N5" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6">
+        <v>2019</v>
+      </c>
+      <c r="I6">
+        <v>256</v>
+      </c>
+      <c r="J6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K6" s="19">
+        <v>225</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="15">
+        <v>45970</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7">
+        <v>2019</v>
+      </c>
+      <c r="I7">
+        <v>256</v>
+      </c>
+      <c r="J7" t="s">
+        <v>125</v>
+      </c>
+      <c r="K7" s="19">
+        <v>225</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="15">
+        <v>45970</v>
+      </c>
+      <c r="N7" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8">
+        <v>2019</v>
+      </c>
+      <c r="I8">
+        <v>256</v>
+      </c>
+      <c r="J8" t="s">
+        <v>125</v>
+      </c>
+      <c r="K8" s="19">
+        <v>225</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="15">
+        <v>45970</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9">
+        <v>2019</v>
+      </c>
+      <c r="I9">
+        <v>256</v>
+      </c>
+      <c r="J9" t="s">
+        <v>125</v>
+      </c>
+      <c r="K9" s="19">
+        <v>225</v>
+      </c>
+      <c r="L9" s="2"/>
+      <c r="M9" s="15">
+        <v>45970</v>
+      </c>
+      <c r="N9" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10">
+        <v>2018</v>
+      </c>
+      <c r="E10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F10" t="s">
+        <v>138</v>
+      </c>
+      <c r="G10">
+        <v>16</v>
+      </c>
+      <c r="H10" t="s">
+        <v>131</v>
+      </c>
+      <c r="I10">
+        <v>256</v>
+      </c>
+      <c r="J10" t="s">
+        <v>125</v>
+      </c>
+      <c r="K10" s="21">
+        <v>325</v>
+      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="15">
+        <v>45999</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11">
+        <v>2015</v>
+      </c>
+      <c r="E11" t="s">
+        <v>177</v>
+      </c>
+      <c r="F11" t="s">
+        <v>138</v>
+      </c>
+      <c r="G11">
+        <v>8</v>
+      </c>
+      <c r="H11" t="s">
         <v>124</v>
       </c>
-      <c r="J3" s="19">
+      <c r="I11">
+        <v>256</v>
+      </c>
+      <c r="J11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K11" s="19">
         <v>225</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="15">
-        <v>45970</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4">
+      <c r="L11" s="2"/>
+      <c r="M11" s="15">
+        <v>45999</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12">
+        <v>2014</v>
+      </c>
+      <c r="E12" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G12">
+        <v>8</v>
+      </c>
+      <c r="H12" t="s">
+        <v>124</v>
+      </c>
+      <c r="I12">
+        <v>256</v>
+      </c>
+      <c r="J12" t="s">
+        <v>125</v>
+      </c>
+      <c r="K12" s="19">
+        <v>175</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="M12" s="15">
+        <v>45999</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" t="s">
+        <v>181</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13">
         <v>2019</v>
       </c>
-      <c r="H4">
+      <c r="E13" t="s">
+        <v>182</v>
+      </c>
+      <c r="F13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G13">
+        <v>16</v>
+      </c>
+      <c r="H13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I13">
         <v>256</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J13" t="s">
+        <v>125</v>
+      </c>
+      <c r="K13" s="19">
+        <v>325</v>
+      </c>
+      <c r="L13" s="2"/>
+      <c r="M13" s="15">
+        <v>45999</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14">
+        <v>2018</v>
+      </c>
+      <c r="E14" t="s">
+        <v>175</v>
+      </c>
+      <c r="F14" t="s">
+        <v>138</v>
+      </c>
+      <c r="G14">
+        <v>16</v>
+      </c>
+      <c r="H14" t="s">
+        <v>131</v>
+      </c>
+      <c r="I14">
+        <v>256</v>
+      </c>
+      <c r="J14" t="s">
+        <v>125</v>
+      </c>
+      <c r="K14" s="19">
+        <v>325</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="15">
+        <v>45999</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15">
+        <v>2021</v>
+      </c>
+      <c r="E15" t="s">
+        <v>184</v>
+      </c>
+      <c r="F15" t="s">
+        <v>138</v>
+      </c>
+      <c r="G15">
+        <v>16</v>
+      </c>
+      <c r="H15" t="s">
+        <v>131</v>
+      </c>
+      <c r="I15">
+        <v>256</v>
+      </c>
+      <c r="J15" t="s">
+        <v>125</v>
+      </c>
+      <c r="K15" s="19">
+        <v>205</v>
+      </c>
+      <c r="L15" s="2"/>
+      <c r="M15" s="15">
+        <v>45999</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D16">
+        <v>2012</v>
+      </c>
+      <c r="E16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F16" t="s">
+        <v>188</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>189</v>
+      </c>
+      <c r="I16" s="1">
+        <v>64</v>
+      </c>
+      <c r="J16" t="s">
+        <v>190</v>
+      </c>
+      <c r="K16" s="19">
+        <v>50</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="M16" s="15">
+        <v>45999</v>
+      </c>
+      <c r="N16" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O16" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>192</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17">
+        <v>2014</v>
+      </c>
+      <c r="E17" t="s">
+        <v>187</v>
+      </c>
+      <c r="F17" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17" t="s">
         <v>124</v>
       </c>
-      <c r="J4" s="19">
-        <v>225</v>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="15">
-        <v>45970</v>
-      </c>
-      <c r="M4" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C5">
-        <v>2019</v>
-      </c>
-      <c r="H5">
+      <c r="I17">
+        <v>128</v>
+      </c>
+      <c r="J17" t="s">
+        <v>190</v>
+      </c>
+      <c r="K17" s="19">
+        <v>60</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="M17" s="15">
+        <v>45999</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O17" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18">
+        <v>2018</v>
+      </c>
+      <c r="E18" t="s">
+        <v>193</v>
+      </c>
+      <c r="F18" t="s">
+        <v>138</v>
+      </c>
+      <c r="G18">
+        <v>8</v>
+      </c>
+      <c r="H18" t="s">
+        <v>131</v>
+      </c>
+      <c r="I18">
         <v>256</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J18" t="s">
+        <v>125</v>
+      </c>
+      <c r="K18" s="19">
+        <v>250</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="M18" s="16">
+        <v>46043</v>
+      </c>
+      <c r="N18" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="O18" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19">
+        <v>2013</v>
+      </c>
+      <c r="E19" t="s">
+        <v>197</v>
+      </c>
+      <c r="F19" t="s">
+        <v>123</v>
+      </c>
+      <c r="G19">
+        <v>8</v>
+      </c>
+      <c r="H19" t="s">
         <v>124</v>
       </c>
-      <c r="J5" s="19">
-        <v>225</v>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="15">
-        <v>45970</v>
-      </c>
-      <c r="M5" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6">
-        <v>2019</v>
-      </c>
-      <c r="H6">
+      <c r="I19">
         <v>256</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K19" s="19">
+        <v>290</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M19" s="16">
+        <v>46043</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="O19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="43.5">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20">
+        <v>2016</v>
+      </c>
+      <c r="E20" t="s">
+        <v>199</v>
+      </c>
+      <c r="F20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G20">
+        <v>16</v>
+      </c>
+      <c r="H20" t="s">
+        <v>131</v>
+      </c>
+      <c r="I20">
+        <v>256</v>
+      </c>
+      <c r="J20" t="s">
+        <v>125</v>
+      </c>
+      <c r="K20" s="19">
+        <v>300</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="M20" s="15">
+        <v>46056</v>
+      </c>
+      <c r="N20" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="O20" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" t="s">
+        <v>202</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21">
+        <v>2013</v>
+      </c>
+      <c r="E21" t="s">
+        <v>203</v>
+      </c>
+      <c r="F21" t="s">
+        <v>123</v>
+      </c>
+      <c r="G21">
+        <v>8</v>
+      </c>
+      <c r="H21" t="s">
         <v>124</v>
       </c>
-      <c r="J6" s="19">
-        <v>225</v>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="15">
-        <v>45970</v>
-      </c>
-      <c r="M6" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N6" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7">
-        <v>2019</v>
-      </c>
-      <c r="H7">
+      <c r="I21">
         <v>256</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J21" t="s">
+        <v>125</v>
+      </c>
+      <c r="K21" s="19">
+        <v>200</v>
+      </c>
+      <c r="L21" s="1"/>
+      <c r="M21" s="15">
+        <v>46056</v>
+      </c>
+      <c r="N21" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="O21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22">
+        <v>2013</v>
+      </c>
+      <c r="E22" t="s">
+        <v>204</v>
+      </c>
+      <c r="F22" t="s">
+        <v>123</v>
+      </c>
+      <c r="G22">
+        <v>8</v>
+      </c>
+      <c r="H22" t="s">
         <v>124</v>
       </c>
-      <c r="J7" s="19">
-        <v>225</v>
-      </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="15">
-        <v>45970</v>
-      </c>
-      <c r="M7" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N7" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>166</v>
-      </c>
-      <c r="B8" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8">
-        <v>2019</v>
-      </c>
-      <c r="H8">
+      <c r="I22">
         <v>256</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J22" t="s">
+        <v>125</v>
+      </c>
+      <c r="K22" s="19">
+        <v>200</v>
+      </c>
+      <c r="L22" s="1"/>
+      <c r="M22" s="15">
+        <v>46056</v>
+      </c>
+      <c r="N22" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="O22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23">
+        <v>2013</v>
+      </c>
+      <c r="E23" t="s">
+        <v>204</v>
+      </c>
+      <c r="F23" t="s">
+        <v>123</v>
+      </c>
+      <c r="G23">
+        <v>8</v>
+      </c>
+      <c r="H23" t="s">
         <v>124</v>
       </c>
-      <c r="J8" s="19">
-        <v>225</v>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="15">
-        <v>45970</v>
-      </c>
-      <c r="M8" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N8" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>166</v>
-      </c>
-      <c r="B9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C9">
-        <v>2019</v>
-      </c>
-      <c r="H9">
+      <c r="I23">
         <v>256</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J23" t="s">
+        <v>125</v>
+      </c>
+      <c r="K23" s="19">
+        <v>200</v>
+      </c>
+      <c r="L23" s="1"/>
+      <c r="M23" s="15">
+        <v>46056</v>
+      </c>
+      <c r="N23" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="O23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24">
+        <v>2013</v>
+      </c>
+      <c r="E24" t="s">
+        <v>204</v>
+      </c>
+      <c r="F24" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24">
+        <v>8</v>
+      </c>
+      <c r="H24" t="s">
         <v>124</v>
       </c>
-      <c r="J9" s="19">
-        <v>225</v>
-      </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="15">
-        <v>45970</v>
-      </c>
-      <c r="M9" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N9" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B10" t="s">
-        <v>126</v>
-      </c>
-      <c r="C10">
+      <c r="I24">
+        <v>256</v>
+      </c>
+      <c r="J24" t="s">
+        <v>125</v>
+      </c>
+      <c r="K24" s="19">
+        <v>200</v>
+      </c>
+      <c r="L24" s="1"/>
+      <c r="M24" s="15">
+        <v>46056</v>
+      </c>
+      <c r="N24" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="O24" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25">
+        <v>2013</v>
+      </c>
+      <c r="E25" t="s">
+        <v>204</v>
+      </c>
+      <c r="F25" t="s">
+        <v>123</v>
+      </c>
+      <c r="G25">
+        <v>16</v>
+      </c>
+      <c r="H25" t="s">
+        <v>124</v>
+      </c>
+      <c r="I25">
+        <v>256</v>
+      </c>
+      <c r="J25" t="s">
+        <v>125</v>
+      </c>
+      <c r="K25" s="19">
+        <v>200</v>
+      </c>
+      <c r="L25" s="1"/>
+      <c r="M25" s="15">
+        <v>46056</v>
+      </c>
+      <c r="N25" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="O25" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26">
+        <v>2016</v>
+      </c>
+      <c r="E26" t="s">
+        <v>199</v>
+      </c>
+      <c r="F26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26">
+        <v>16</v>
+      </c>
+      <c r="H26" t="s">
+        <v>131</v>
+      </c>
+      <c r="I26">
+        <v>256</v>
+      </c>
+      <c r="J26" t="s">
+        <v>125</v>
+      </c>
+      <c r="K26" s="19">
+        <v>300</v>
+      </c>
+      <c r="L26" s="1"/>
+      <c r="M26" s="15">
+        <v>46056</v>
+      </c>
+      <c r="N26" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="O26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27">
+        <v>2016</v>
+      </c>
+      <c r="E27" t="s">
+        <v>199</v>
+      </c>
+      <c r="F27" t="s">
+        <v>123</v>
+      </c>
+      <c r="G27">
+        <v>8</v>
+      </c>
+      <c r="H27" t="s">
+        <v>124</v>
+      </c>
+      <c r="I27">
+        <v>256</v>
+      </c>
+      <c r="J27" t="s">
+        <v>125</v>
+      </c>
+      <c r="K27" s="19">
+        <v>300</v>
+      </c>
+      <c r="L27" s="1"/>
+      <c r="M27" s="15">
+        <v>46056</v>
+      </c>
+      <c r="N27" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="O27" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" t="s">
+        <v>205</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28">
         <v>2018</v>
       </c>
-      <c r="D10" t="s">
-        <v>169</v>
-      </c>
-      <c r="E10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F10">
+      <c r="E28" t="s">
+        <v>206</v>
+      </c>
+      <c r="F28" t="s">
+        <v>138</v>
+      </c>
+      <c r="G28">
         <v>16</v>
       </c>
-      <c r="G10" t="s">
-        <v>130</v>
-      </c>
-      <c r="H10">
+      <c r="H28" t="s">
+        <v>131</v>
+      </c>
+      <c r="I28">
+        <v>512</v>
+      </c>
+      <c r="J28" t="s">
+        <v>125</v>
+      </c>
+      <c r="K28" s="19">
+        <v>445</v>
+      </c>
+      <c r="L28" s="1"/>
+      <c r="M28" s="15">
+        <v>46056</v>
+      </c>
+      <c r="N28" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="O28" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" t="s">
+        <v>205</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s">
+        <v>127</v>
+      </c>
+      <c r="D29">
+        <v>2018</v>
+      </c>
+      <c r="E29" t="s">
+        <v>206</v>
+      </c>
+      <c r="F29" t="s">
+        <v>138</v>
+      </c>
+      <c r="G29">
+        <v>16</v>
+      </c>
+      <c r="H29" t="s">
+        <v>131</v>
+      </c>
+      <c r="I29">
+        <v>512</v>
+      </c>
+      <c r="J29" t="s">
+        <v>125</v>
+      </c>
+      <c r="K29" s="19">
+        <v>445</v>
+      </c>
+      <c r="L29" s="1"/>
+      <c r="M29" s="15">
+        <v>46056</v>
+      </c>
+      <c r="N29" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="O29" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30">
+        <v>2018</v>
+      </c>
+      <c r="E30" t="s">
+        <v>207</v>
+      </c>
+      <c r="F30" t="s">
+        <v>123</v>
+      </c>
+      <c r="G30">
+        <v>8</v>
+      </c>
+      <c r="H30" t="s">
+        <v>131</v>
+      </c>
+      <c r="I30">
         <v>256</v>
       </c>
-      <c r="I10" t="s">
-        <v>124</v>
-      </c>
-      <c r="J10" s="21">
-        <v>325</v>
-      </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="15">
-        <v>45999</v>
-      </c>
-      <c r="M10" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N10" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>170</v>
-      </c>
-      <c r="B11" t="s">
-        <v>126</v>
-      </c>
-      <c r="C11">
-        <v>2015</v>
-      </c>
-      <c r="D11" t="s">
-        <v>171</v>
-      </c>
-      <c r="E11" t="s">
-        <v>137</v>
-      </c>
-      <c r="F11">
+      <c r="J30" t="s">
+        <v>125</v>
+      </c>
+      <c r="K30" s="19">
+        <v>150</v>
+      </c>
+      <c r="L30" s="1"/>
+      <c r="M30" s="15">
+        <v>46056</v>
+      </c>
+      <c r="N30" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="O30" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31">
+        <v>2016</v>
+      </c>
+      <c r="E31" t="s">
+        <v>199</v>
+      </c>
+      <c r="F31" t="s">
+        <v>123</v>
+      </c>
+      <c r="G31">
         <v>8</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H31" t="s">
+        <v>131</v>
+      </c>
+      <c r="I31">
+        <v>500</v>
+      </c>
+      <c r="J31" t="s">
+        <v>208</v>
+      </c>
+      <c r="K31" s="19">
+        <v>300</v>
+      </c>
+      <c r="L31" s="1"/>
+      <c r="M31" s="16">
+        <v>46058</v>
+      </c>
+      <c r="N31" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="O31" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32">
+        <v>2016</v>
+      </c>
+      <c r="E32" t="s">
+        <v>199</v>
+      </c>
+      <c r="F32" t="s">
         <v>123</v>
       </c>
-      <c r="H11">
+      <c r="G32">
+        <v>8</v>
+      </c>
+      <c r="H32" t="s">
+        <v>131</v>
+      </c>
+      <c r="I32">
         <v>256</v>
       </c>
-      <c r="I11" t="s">
-        <v>124</v>
-      </c>
-      <c r="J11" s="19">
-        <v>225</v>
-      </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="15">
-        <v>45999</v>
-      </c>
-      <c r="M11" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N11" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12">
-        <v>2014</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="J32" t="s">
+        <v>125</v>
+      </c>
+      <c r="K32" s="19">
+        <v>300</v>
+      </c>
+      <c r="M32" s="16">
+        <v>46058</v>
+      </c>
+      <c r="N32" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="O32" t="s">
         <v>173</v>
       </c>
-      <c r="E12" t="s">
-        <v>122</v>
-      </c>
-      <c r="F12">
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33">
+        <v>2016</v>
+      </c>
+      <c r="E33" t="s">
+        <v>199</v>
+      </c>
+      <c r="F33" t="s">
+        <v>123</v>
+      </c>
+      <c r="G33">
         <v>8</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H33" t="s">
+        <v>131</v>
+      </c>
+      <c r="I33">
+        <v>256</v>
+      </c>
+      <c r="J33" t="s">
+        <v>125</v>
+      </c>
+      <c r="K33" s="19">
+        <v>300</v>
+      </c>
+      <c r="M33" s="16">
+        <v>46058</v>
+      </c>
+      <c r="N33" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="O33" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" t="s">
+        <v>209</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34">
+        <v>2020</v>
+      </c>
+      <c r="E34" t="s">
+        <v>206</v>
+      </c>
+      <c r="F34" t="s">
+        <v>138</v>
+      </c>
+      <c r="G34">
+        <v>16</v>
+      </c>
+      <c r="H34" t="s">
+        <v>131</v>
+      </c>
+      <c r="I34">
+        <v>512</v>
+      </c>
+      <c r="J34" t="s">
+        <v>125</v>
+      </c>
+      <c r="K34" s="19">
+        <v>445</v>
+      </c>
+      <c r="M34" s="16">
+        <v>46058</v>
+      </c>
+      <c r="N34" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="O34" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" t="s">
+        <v>209</v>
+      </c>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
+        <v>127</v>
+      </c>
+      <c r="D35">
+        <v>2020</v>
+      </c>
+      <c r="E35" t="s">
+        <v>206</v>
+      </c>
+      <c r="F35" t="s">
+        <v>138</v>
+      </c>
+      <c r="G35">
+        <v>16</v>
+      </c>
+      <c r="H35" t="s">
+        <v>131</v>
+      </c>
+      <c r="I35">
+        <v>512</v>
+      </c>
+      <c r="J35" t="s">
+        <v>125</v>
+      </c>
+      <c r="K35" s="19">
+        <v>445</v>
+      </c>
+      <c r="M35" s="16">
+        <v>46058</v>
+      </c>
+      <c r="N35" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="O35" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" t="s">
+        <v>209</v>
+      </c>
+      <c r="B36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36">
+        <v>2020</v>
+      </c>
+      <c r="E36" t="s">
+        <v>206</v>
+      </c>
+      <c r="F36" t="s">
+        <v>138</v>
+      </c>
+      <c r="G36">
+        <v>16</v>
+      </c>
+      <c r="H36" t="s">
+        <v>131</v>
+      </c>
+      <c r="I36">
+        <v>512</v>
+      </c>
+      <c r="J36" t="s">
+        <v>125</v>
+      </c>
+      <c r="K36" s="19">
+        <v>445</v>
+      </c>
+      <c r="M36" s="16">
+        <v>46058</v>
+      </c>
+      <c r="N36" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="O36" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" t="s">
+        <v>209</v>
+      </c>
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>127</v>
+      </c>
+      <c r="D37">
+        <v>2020</v>
+      </c>
+      <c r="E37" t="s">
+        <v>206</v>
+      </c>
+      <c r="F37" t="s">
+        <v>138</v>
+      </c>
+      <c r="G37">
+        <v>16</v>
+      </c>
+      <c r="H37" t="s">
+        <v>131</v>
+      </c>
+      <c r="I37">
+        <v>512</v>
+      </c>
+      <c r="J37" t="s">
+        <v>125</v>
+      </c>
+      <c r="K37" s="19">
+        <v>445</v>
+      </c>
+      <c r="M37" s="16">
+        <v>46058</v>
+      </c>
+      <c r="N37" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="O37" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" t="s">
+        <v>209</v>
+      </c>
+      <c r="B38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38">
+        <v>2020</v>
+      </c>
+      <c r="E38" t="s">
+        <v>206</v>
+      </c>
+      <c r="F38" t="s">
+        <v>138</v>
+      </c>
+      <c r="G38">
+        <v>16</v>
+      </c>
+      <c r="H38" t="s">
+        <v>131</v>
+      </c>
+      <c r="I38">
+        <v>512</v>
+      </c>
+      <c r="J38" t="s">
+        <v>125</v>
+      </c>
+      <c r="K38" s="19">
+        <v>445</v>
+      </c>
+      <c r="M38" s="16">
+        <v>46058</v>
+      </c>
+      <c r="N38" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="O38" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" t="s">
+        <v>209</v>
+      </c>
+      <c r="B39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" t="s">
+        <v>127</v>
+      </c>
+      <c r="D39">
+        <v>2020</v>
+      </c>
+      <c r="E39" t="s">
+        <v>206</v>
+      </c>
+      <c r="F39" t="s">
+        <v>138</v>
+      </c>
+      <c r="G39">
+        <v>16</v>
+      </c>
+      <c r="H39" t="s">
+        <v>131</v>
+      </c>
+      <c r="I39">
+        <v>512</v>
+      </c>
+      <c r="J39" t="s">
+        <v>125</v>
+      </c>
+      <c r="K39" s="19">
+        <v>445</v>
+      </c>
+      <c r="M39" s="16">
+        <v>46058</v>
+      </c>
+      <c r="N39" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="O39" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="15" customHeight="1">
+      <c r="A40" t="s">
+        <v>209</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40">
+        <v>2020</v>
+      </c>
+      <c r="E40" t="s">
+        <v>206</v>
+      </c>
+      <c r="F40" t="s">
+        <v>138</v>
+      </c>
+      <c r="G40">
+        <v>16</v>
+      </c>
+      <c r="H40" t="s">
+        <v>131</v>
+      </c>
+      <c r="I40">
+        <v>512</v>
+      </c>
+      <c r="J40" t="s">
+        <v>125</v>
+      </c>
+      <c r="K40" s="19">
+        <v>445</v>
+      </c>
+      <c r="M40" s="16">
+        <v>46058</v>
+      </c>
+      <c r="N40" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="O40" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="15" customHeight="1">
+      <c r="A41" t="s">
+        <v>209</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41">
+        <v>2020</v>
+      </c>
+      <c r="E41" t="s">
+        <v>206</v>
+      </c>
+      <c r="F41" t="s">
+        <v>138</v>
+      </c>
+      <c r="G41">
+        <v>16</v>
+      </c>
+      <c r="H41" t="s">
+        <v>131</v>
+      </c>
+      <c r="I41">
+        <v>512</v>
+      </c>
+      <c r="J41" t="s">
+        <v>125</v>
+      </c>
+      <c r="K41" s="19">
+        <v>445</v>
+      </c>
+      <c r="M41" s="16">
+        <v>46058</v>
+      </c>
+      <c r="N41" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="O41" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="15" customHeight="1">
+      <c r="A42" t="s">
+        <v>209</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s">
+        <v>127</v>
+      </c>
+      <c r="D42">
+        <v>2020</v>
+      </c>
+      <c r="E42" t="s">
+        <v>206</v>
+      </c>
+      <c r="F42" t="s">
+        <v>138</v>
+      </c>
+      <c r="G42">
+        <v>16</v>
+      </c>
+      <c r="H42" t="s">
+        <v>131</v>
+      </c>
+      <c r="I42">
+        <v>512</v>
+      </c>
+      <c r="J42" t="s">
+        <v>125</v>
+      </c>
+      <c r="K42" s="19">
+        <v>445</v>
+      </c>
+      <c r="M42" s="16">
+        <v>46058</v>
+      </c>
+      <c r="N42" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="O42" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="15" customHeight="1">
+      <c r="A43" t="s">
+        <v>141</v>
+      </c>
+      <c r="B43" t="s">
+        <v>28</v>
+      </c>
+      <c r="C43" t="s">
+        <v>127</v>
+      </c>
+      <c r="D43">
+        <v>2018</v>
+      </c>
+      <c r="E43" t="s">
+        <v>210</v>
+      </c>
+      <c r="F43" t="s">
+        <v>138</v>
+      </c>
+      <c r="G43">
+        <v>8</v>
+      </c>
+      <c r="H43" t="s">
+        <v>131</v>
+      </c>
+      <c r="I43">
+        <v>256</v>
+      </c>
+      <c r="J43" t="s">
+        <v>125</v>
+      </c>
+      <c r="K43" s="19">
+        <v>300</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="16">
+        <v>46078</v>
+      </c>
+      <c r="N43" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="O43" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="15" customHeight="1">
+      <c r="A44" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B44" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" s="5">
+        <v>2016</v>
+      </c>
+      <c r="E44" t="s">
+        <v>154</v>
+      </c>
+      <c r="F44" t="s">
         <v>123</v>
       </c>
-      <c r="H12">
+      <c r="G44">
+        <v>8</v>
+      </c>
+      <c r="H44" t="s">
+        <v>131</v>
+      </c>
+      <c r="I44">
         <v>256</v>
       </c>
-      <c r="I12" t="s">
-        <v>124</v>
-      </c>
-      <c r="J12" s="19">
-        <v>175</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="L12" s="15">
-        <v>45999</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N12" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>175</v>
-      </c>
-      <c r="B13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13">
-        <v>2019</v>
-      </c>
-      <c r="D13" t="s">
-        <v>176</v>
-      </c>
-      <c r="E13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F13">
-        <v>16</v>
-      </c>
-      <c r="G13" t="s">
-        <v>130</v>
-      </c>
-      <c r="H13">
-        <v>256</v>
-      </c>
-      <c r="I13" t="s">
-        <v>124</v>
-      </c>
-      <c r="J13" s="19">
-        <v>325</v>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="15">
-        <v>45999</v>
-      </c>
-      <c r="M13" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N13" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>168</v>
-      </c>
-      <c r="B14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14">
-        <v>2018</v>
-      </c>
-      <c r="D14" t="s">
-        <v>169</v>
-      </c>
-      <c r="E14" t="s">
-        <v>137</v>
-      </c>
-      <c r="F14">
-        <v>16</v>
-      </c>
-      <c r="G14" t="s">
-        <v>130</v>
-      </c>
-      <c r="H14">
-        <v>256</v>
-      </c>
-      <c r="I14" t="s">
-        <v>124</v>
-      </c>
-      <c r="J14" s="19">
-        <v>325</v>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="15">
-        <v>45999</v>
-      </c>
-      <c r="M14" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N14" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>177</v>
-      </c>
-      <c r="B15" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15">
-        <v>2021</v>
-      </c>
-      <c r="D15" t="s">
-        <v>178</v>
-      </c>
-      <c r="E15" t="s">
-        <v>137</v>
-      </c>
-      <c r="F15">
-        <v>16</v>
-      </c>
-      <c r="G15" t="s">
-        <v>130</v>
-      </c>
-      <c r="H15">
-        <v>256</v>
-      </c>
-      <c r="I15" t="s">
-        <v>124</v>
-      </c>
-      <c r="J15" s="19">
-        <v>205</v>
-      </c>
-      <c r="K15" s="2"/>
-      <c r="L15" s="15">
-        <v>45999</v>
-      </c>
-      <c r="M15" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N15" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>179</v>
-      </c>
-      <c r="B16" t="s">
-        <v>180</v>
-      </c>
-      <c r="C16">
-        <v>2012</v>
-      </c>
-      <c r="D16" t="s">
-        <v>181</v>
-      </c>
-      <c r="E16" t="s">
-        <v>182</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>183</v>
-      </c>
-      <c r="H16" s="1">
-        <v>64</v>
-      </c>
-      <c r="I16" t="s">
-        <v>184</v>
-      </c>
-      <c r="J16" s="19">
-        <v>50</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="L16" s="15">
-        <v>45999</v>
-      </c>
-      <c r="M16" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N16" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>186</v>
-      </c>
-      <c r="B17" t="s">
-        <v>180</v>
-      </c>
-      <c r="C17">
-        <v>2014</v>
-      </c>
-      <c r="D17" t="s">
-        <v>181</v>
-      </c>
-      <c r="E17" t="s">
-        <v>182</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17" t="s">
-        <v>123</v>
-      </c>
-      <c r="H17">
-        <v>128</v>
-      </c>
-      <c r="I17" t="s">
-        <v>184</v>
-      </c>
-      <c r="J17" s="19">
-        <v>60</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="L17" s="15">
-        <v>45999</v>
-      </c>
-      <c r="M17" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N17" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>187</v>
-      </c>
-      <c r="B18" t="s">
-        <v>120</v>
-      </c>
-      <c r="C18">
-        <v>2018</v>
-      </c>
-      <c r="D18" t="s">
-        <v>188</v>
-      </c>
-      <c r="E18" t="s">
-        <v>137</v>
-      </c>
-      <c r="F18">
-        <v>8</v>
-      </c>
-      <c r="G18" t="s">
-        <v>130</v>
-      </c>
-      <c r="H18">
-        <v>256</v>
-      </c>
-      <c r="I18" t="s">
-        <v>124</v>
-      </c>
-      <c r="J18" s="19">
-        <v>250</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="L18" s="16">
-        <v>46043</v>
-      </c>
-      <c r="M18" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="N18" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" t="s">
-        <v>120</v>
-      </c>
-      <c r="C19">
-        <v>2013</v>
-      </c>
-      <c r="D19" t="s">
-        <v>191</v>
-      </c>
-      <c r="E19" t="s">
-        <v>122</v>
-      </c>
-      <c r="F19">
-        <v>8</v>
-      </c>
-      <c r="G19" t="s">
-        <v>123</v>
-      </c>
-      <c r="H19">
-        <v>256</v>
-      </c>
-      <c r="I19" t="s">
-        <v>124</v>
-      </c>
-      <c r="J19" s="19">
-        <v>290</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="L19" s="16">
-        <v>46043</v>
-      </c>
-      <c r="M19" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="N19" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" t="s">
-        <v>120</v>
-      </c>
-      <c r="C20">
-        <v>2016</v>
-      </c>
-      <c r="D20" t="s">
-        <v>193</v>
-      </c>
-      <c r="E20" t="s">
-        <v>122</v>
-      </c>
-      <c r="F20">
-        <v>16</v>
-      </c>
-      <c r="G20" t="s">
-        <v>130</v>
-      </c>
-      <c r="H20">
-        <v>256</v>
-      </c>
-      <c r="I20" t="s">
-        <v>124</v>
-      </c>
-      <c r="J20" s="19">
+      <c r="J44" t="s">
+        <v>125</v>
+      </c>
+      <c r="K44" s="19">
         <v>300</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L20" s="15">
-        <v>46056</v>
-      </c>
-      <c r="M20" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="N20" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="L44" s="1"/>
+      <c r="M44" s="16">
+        <v>46099</v>
+      </c>
+      <c r="N44" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="O44" t="s">
         <v>196</v>
       </c>
-      <c r="B21" t="s">
-        <v>120</v>
-      </c>
-      <c r="C21">
-        <v>2013</v>
-      </c>
-      <c r="D21" t="s">
-        <v>197</v>
-      </c>
-      <c r="E21" t="s">
-        <v>122</v>
-      </c>
-      <c r="F21">
-        <v>8</v>
-      </c>
-      <c r="G21" t="s">
-        <v>123</v>
-      </c>
-      <c r="H21">
-        <v>256</v>
-      </c>
-      <c r="I21" t="s">
-        <v>124</v>
-      </c>
-      <c r="J21" s="19">
-        <v>200</v>
-      </c>
-      <c r="K21" s="1"/>
-      <c r="L21" s="15">
-        <v>46056</v>
-      </c>
-      <c r="M21" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="N21" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" t="s">
-        <v>120</v>
-      </c>
-      <c r="C22">
-        <v>2013</v>
-      </c>
-      <c r="D22" t="s">
-        <v>198</v>
-      </c>
-      <c r="E22" t="s">
-        <v>122</v>
-      </c>
-      <c r="F22">
-        <v>8</v>
-      </c>
-      <c r="G22" t="s">
-        <v>123</v>
-      </c>
-      <c r="H22">
-        <v>256</v>
-      </c>
-      <c r="I22" t="s">
-        <v>124</v>
-      </c>
-      <c r="J22" s="19">
-        <v>200</v>
-      </c>
-      <c r="K22" s="1"/>
-      <c r="L22" s="15">
-        <v>46056</v>
-      </c>
-      <c r="M22" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="N22" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" t="s">
-        <v>120</v>
-      </c>
-      <c r="C23">
-        <v>2013</v>
-      </c>
-      <c r="D23" t="s">
-        <v>198</v>
-      </c>
-      <c r="E23" t="s">
-        <v>122</v>
-      </c>
-      <c r="F23">
-        <v>8</v>
-      </c>
-      <c r="G23" t="s">
-        <v>123</v>
-      </c>
-      <c r="H23">
-        <v>256</v>
-      </c>
-      <c r="I23" t="s">
-        <v>124</v>
-      </c>
-      <c r="J23" s="19">
-        <v>200</v>
-      </c>
-      <c r="K23" s="1"/>
-      <c r="L23" s="15">
-        <v>46056</v>
-      </c>
-      <c r="M23" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="N23" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" t="s">
-        <v>120</v>
-      </c>
-      <c r="C24">
-        <v>2013</v>
-      </c>
-      <c r="D24" t="s">
-        <v>198</v>
-      </c>
-      <c r="E24" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24">
-        <v>8</v>
-      </c>
-      <c r="G24" t="s">
-        <v>123</v>
-      </c>
-      <c r="H24">
-        <v>256</v>
-      </c>
-      <c r="I24" t="s">
-        <v>124</v>
-      </c>
-      <c r="J24" s="19">
-        <v>200</v>
-      </c>
-      <c r="K24" s="1"/>
-      <c r="L24" s="15">
-        <v>46056</v>
-      </c>
-      <c r="M24" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="N24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25">
-        <v>2013</v>
-      </c>
-      <c r="D25" t="s">
-        <v>198</v>
-      </c>
-      <c r="E25" t="s">
-        <v>122</v>
-      </c>
-      <c r="F25">
-        <v>16</v>
-      </c>
-      <c r="G25" t="s">
-        <v>123</v>
-      </c>
-      <c r="H25">
-        <v>256</v>
-      </c>
-      <c r="I25" t="s">
-        <v>124</v>
-      </c>
-      <c r="J25" s="19">
-        <v>200</v>
-      </c>
-      <c r="K25" s="1"/>
-      <c r="L25" s="15">
-        <v>46056</v>
-      </c>
-      <c r="M25" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="N25" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>61</v>
-      </c>
-      <c r="B26" t="s">
-        <v>120</v>
-      </c>
-      <c r="C26">
-        <v>2016</v>
-      </c>
-      <c r="D26" t="s">
-        <v>193</v>
-      </c>
-      <c r="E26" t="s">
-        <v>122</v>
-      </c>
-      <c r="F26">
-        <v>16</v>
-      </c>
-      <c r="G26" t="s">
-        <v>130</v>
-      </c>
-      <c r="H26">
-        <v>256</v>
-      </c>
-      <c r="I26" t="s">
-        <v>124</v>
-      </c>
-      <c r="J26" s="19">
-        <v>300</v>
-      </c>
-      <c r="K26" s="1"/>
-      <c r="L26" s="15">
-        <v>46056</v>
-      </c>
-      <c r="M26" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="N26" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" t="s">
-        <v>120</v>
-      </c>
-      <c r="C27">
-        <v>2016</v>
-      </c>
-      <c r="D27" t="s">
-        <v>193</v>
-      </c>
-      <c r="E27" t="s">
-        <v>122</v>
-      </c>
-      <c r="F27">
-        <v>8</v>
-      </c>
-      <c r="G27" t="s">
-        <v>123</v>
-      </c>
-      <c r="H27">
-        <v>256</v>
-      </c>
-      <c r="I27" t="s">
-        <v>124</v>
-      </c>
-      <c r="J27" s="19">
-        <v>300</v>
-      </c>
-      <c r="K27" s="1"/>
-      <c r="L27" s="15">
-        <v>46056</v>
-      </c>
-      <c r="M27" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="N27" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>199</v>
-      </c>
-      <c r="B28" t="s">
-        <v>126</v>
-      </c>
-      <c r="C28">
-        <v>2018</v>
-      </c>
-      <c r="D28" t="s">
-        <v>200</v>
-      </c>
-      <c r="E28" t="s">
-        <v>137</v>
-      </c>
-      <c r="F28">
-        <v>16</v>
-      </c>
-      <c r="G28" t="s">
-        <v>130</v>
-      </c>
-      <c r="H28">
-        <v>512</v>
-      </c>
-      <c r="I28" t="s">
-        <v>124</v>
-      </c>
-      <c r="J28" s="19">
-        <v>445</v>
-      </c>
-      <c r="K28" s="1"/>
-      <c r="L28" s="15">
-        <v>46056</v>
-      </c>
-      <c r="M28" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="N28" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>199</v>
-      </c>
-      <c r="B29" t="s">
-        <v>126</v>
-      </c>
-      <c r="C29">
-        <v>2018</v>
-      </c>
-      <c r="D29" t="s">
-        <v>200</v>
-      </c>
-      <c r="E29" t="s">
-        <v>137</v>
-      </c>
-      <c r="F29">
-        <v>16</v>
-      </c>
-      <c r="G29" t="s">
-        <v>130</v>
-      </c>
-      <c r="H29">
-        <v>512</v>
-      </c>
-      <c r="I29" t="s">
-        <v>124</v>
-      </c>
-      <c r="J29" s="19">
-        <v>445</v>
-      </c>
-      <c r="K29" s="1"/>
-      <c r="L29" s="15">
-        <v>46056</v>
-      </c>
-      <c r="M29" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="N29" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>128</v>
-      </c>
-      <c r="B30" t="s">
-        <v>120</v>
-      </c>
-      <c r="C30">
-        <v>2018</v>
-      </c>
-      <c r="D30" t="s">
-        <v>201</v>
-      </c>
-      <c r="E30" t="s">
-        <v>122</v>
-      </c>
-      <c r="F30">
-        <v>8</v>
-      </c>
-      <c r="G30" t="s">
-        <v>130</v>
-      </c>
-      <c r="H30">
-        <v>256</v>
-      </c>
-      <c r="I30" t="s">
-        <v>124</v>
-      </c>
-      <c r="J30" s="19">
-        <v>150</v>
-      </c>
-      <c r="K30" s="1"/>
-      <c r="L30" s="15">
-        <v>46056</v>
-      </c>
-      <c r="M30" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="N30" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" t="s">
-        <v>120</v>
-      </c>
-      <c r="C31">
-        <v>2016</v>
-      </c>
-      <c r="D31" t="s">
-        <v>193</v>
-      </c>
-      <c r="E31" t="s">
-        <v>122</v>
-      </c>
-      <c r="F31">
-        <v>8</v>
-      </c>
-      <c r="G31" t="s">
-        <v>130</v>
-      </c>
-      <c r="H31">
-        <v>500</v>
-      </c>
-      <c r="I31" t="s">
-        <v>202</v>
-      </c>
-      <c r="J31" s="19">
-        <v>300</v>
-      </c>
-      <c r="K31" s="1"/>
-      <c r="L31" s="16">
-        <v>46058</v>
-      </c>
-      <c r="M31" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="N31" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" t="s">
-        <v>120</v>
-      </c>
-      <c r="C32">
-        <v>2016</v>
-      </c>
-      <c r="D32" t="s">
-        <v>193</v>
-      </c>
-      <c r="E32" t="s">
-        <v>122</v>
-      </c>
-      <c r="F32">
-        <v>8</v>
-      </c>
-      <c r="G32" t="s">
-        <v>130</v>
-      </c>
-      <c r="H32">
-        <v>256</v>
-      </c>
-      <c r="I32" t="s">
-        <v>124</v>
-      </c>
-      <c r="J32" s="19">
-        <v>300</v>
-      </c>
-      <c r="L32" s="16">
-        <v>46058</v>
-      </c>
-      <c r="M32" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="N32" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33" t="s">
-        <v>120</v>
-      </c>
-      <c r="C33">
-        <v>2016</v>
-      </c>
-      <c r="D33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E33" t="s">
-        <v>122</v>
-      </c>
-      <c r="F33">
-        <v>8</v>
-      </c>
-      <c r="G33" t="s">
-        <v>130</v>
-      </c>
-      <c r="H33">
-        <v>256</v>
-      </c>
-      <c r="I33" t="s">
-        <v>124</v>
-      </c>
-      <c r="J33" s="19">
-        <v>300</v>
-      </c>
-      <c r="L33" s="16">
-        <v>46058</v>
-      </c>
-      <c r="M33" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="N33" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>203</v>
-      </c>
-      <c r="B34" t="s">
-        <v>126</v>
-      </c>
-      <c r="C34">
-        <v>2020</v>
-      </c>
-      <c r="D34" t="s">
-        <v>200</v>
-      </c>
-      <c r="E34" t="s">
-        <v>137</v>
-      </c>
-      <c r="F34">
-        <v>16</v>
-      </c>
-      <c r="G34" t="s">
-        <v>130</v>
-      </c>
-      <c r="H34">
-        <v>512</v>
-      </c>
-      <c r="I34" t="s">
-        <v>124</v>
-      </c>
-      <c r="J34" s="19">
-        <v>445</v>
-      </c>
-      <c r="L34" s="16">
-        <v>46058</v>
-      </c>
-      <c r="M34" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="N34" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>203</v>
-      </c>
-      <c r="B35" t="s">
-        <v>126</v>
-      </c>
-      <c r="C35">
-        <v>2020</v>
-      </c>
-      <c r="D35" t="s">
-        <v>200</v>
-      </c>
-      <c r="E35" t="s">
-        <v>137</v>
-      </c>
-      <c r="F35">
-        <v>16</v>
-      </c>
-      <c r="G35" t="s">
-        <v>130</v>
-      </c>
-      <c r="H35">
-        <v>512</v>
-      </c>
-      <c r="I35" t="s">
-        <v>124</v>
-      </c>
-      <c r="J35" s="19">
-        <v>445</v>
-      </c>
-      <c r="L35" s="16">
-        <v>46058</v>
-      </c>
-      <c r="M35" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="N35" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>203</v>
-      </c>
-      <c r="B36" t="s">
-        <v>126</v>
-      </c>
-      <c r="C36">
-        <v>2020</v>
-      </c>
-      <c r="D36" t="s">
-        <v>200</v>
-      </c>
-      <c r="E36" t="s">
-        <v>137</v>
-      </c>
-      <c r="F36">
-        <v>16</v>
-      </c>
-      <c r="G36" t="s">
-        <v>130</v>
-      </c>
-      <c r="H36">
-        <v>512</v>
-      </c>
-      <c r="I36" t="s">
-        <v>124</v>
-      </c>
-      <c r="J36" s="19">
-        <v>445</v>
-      </c>
-      <c r="L36" s="16">
-        <v>46058</v>
-      </c>
-      <c r="M36" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="N36" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>203</v>
-      </c>
-      <c r="B37" t="s">
-        <v>126</v>
-      </c>
-      <c r="C37">
-        <v>2020</v>
-      </c>
-      <c r="D37" t="s">
-        <v>200</v>
-      </c>
-      <c r="E37" t="s">
-        <v>137</v>
-      </c>
-      <c r="F37">
-        <v>16</v>
-      </c>
-      <c r="G37" t="s">
-        <v>130</v>
-      </c>
-      <c r="H37">
-        <v>512</v>
-      </c>
-      <c r="I37" t="s">
-        <v>124</v>
-      </c>
-      <c r="J37" s="19">
-        <v>445</v>
-      </c>
-      <c r="L37" s="16">
-        <v>46058</v>
-      </c>
-      <c r="M37" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="N37" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>203</v>
-      </c>
-      <c r="B38" t="s">
-        <v>126</v>
-      </c>
-      <c r="C38">
-        <v>2020</v>
-      </c>
-      <c r="D38" t="s">
-        <v>200</v>
-      </c>
-      <c r="E38" t="s">
-        <v>137</v>
-      </c>
-      <c r="F38">
-        <v>16</v>
-      </c>
-      <c r="G38" t="s">
-        <v>130</v>
-      </c>
-      <c r="H38">
-        <v>512</v>
-      </c>
-      <c r="I38" t="s">
-        <v>124</v>
-      </c>
-      <c r="J38" s="19">
-        <v>445</v>
-      </c>
-      <c r="L38" s="16">
-        <v>46058</v>
-      </c>
-      <c r="M38" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="N38" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>203</v>
-      </c>
-      <c r="B39" t="s">
-        <v>126</v>
-      </c>
-      <c r="C39">
-        <v>2020</v>
-      </c>
-      <c r="D39" t="s">
-        <v>200</v>
-      </c>
-      <c r="E39" t="s">
-        <v>137</v>
-      </c>
-      <c r="F39">
-        <v>16</v>
-      </c>
-      <c r="G39" t="s">
-        <v>130</v>
-      </c>
-      <c r="H39">
-        <v>512</v>
-      </c>
-      <c r="I39" t="s">
-        <v>124</v>
-      </c>
-      <c r="J39" s="19">
-        <v>445</v>
-      </c>
-      <c r="L39" s="16">
-        <v>46058</v>
-      </c>
-      <c r="M39" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="N39" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>203</v>
-      </c>
-      <c r="B40" t="s">
-        <v>126</v>
-      </c>
-      <c r="C40">
-        <v>2020</v>
-      </c>
-      <c r="D40" t="s">
-        <v>200</v>
-      </c>
-      <c r="E40" t="s">
-        <v>137</v>
-      </c>
-      <c r="F40">
-        <v>16</v>
-      </c>
-      <c r="G40" t="s">
-        <v>130</v>
-      </c>
-      <c r="H40">
-        <v>512</v>
-      </c>
-      <c r="I40" t="s">
-        <v>124</v>
-      </c>
-      <c r="J40" s="19">
-        <v>445</v>
-      </c>
-      <c r="L40" s="16">
-        <v>46058</v>
-      </c>
-      <c r="M40" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="N40" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>203</v>
-      </c>
-      <c r="B41" t="s">
-        <v>126</v>
-      </c>
-      <c r="C41">
-        <v>2020</v>
-      </c>
-      <c r="D41" t="s">
-        <v>200</v>
-      </c>
-      <c r="E41" t="s">
-        <v>137</v>
-      </c>
-      <c r="F41">
-        <v>16</v>
-      </c>
-      <c r="G41" t="s">
-        <v>130</v>
-      </c>
-      <c r="H41">
-        <v>512</v>
-      </c>
-      <c r="I41" t="s">
-        <v>124</v>
-      </c>
-      <c r="J41" s="19">
-        <v>445</v>
-      </c>
-      <c r="L41" s="16">
-        <v>46058</v>
-      </c>
-      <c r="M41" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="N41" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>203</v>
-      </c>
-      <c r="B42" t="s">
-        <v>126</v>
-      </c>
-      <c r="C42">
-        <v>2020</v>
-      </c>
-      <c r="D42" t="s">
-        <v>200</v>
-      </c>
-      <c r="E42" t="s">
-        <v>137</v>
-      </c>
-      <c r="F42">
-        <v>16</v>
-      </c>
-      <c r="G42" t="s">
-        <v>130</v>
-      </c>
-      <c r="H42">
-        <v>512</v>
-      </c>
-      <c r="I42" t="s">
-        <v>124</v>
-      </c>
-      <c r="J42" s="19">
-        <v>445</v>
-      </c>
-      <c r="L42" s="16">
-        <v>46058</v>
-      </c>
-      <c r="M42" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="N42" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>140</v>
-      </c>
-      <c r="B43" t="s">
-        <v>126</v>
-      </c>
-      <c r="C43">
-        <v>2018</v>
-      </c>
-      <c r="D43" t="s">
-        <v>204</v>
-      </c>
-      <c r="E43" t="s">
-        <v>137</v>
-      </c>
-      <c r="F43">
-        <v>8</v>
-      </c>
-      <c r="G43" t="s">
-        <v>130</v>
-      </c>
-      <c r="H43">
-        <v>256</v>
-      </c>
-      <c r="I43" t="s">
-        <v>124</v>
-      </c>
-      <c r="J43" s="19">
-        <v>300</v>
-      </c>
-      <c r="K43" s="1"/>
-      <c r="L43" s="16">
-        <v>46078</v>
-      </c>
-      <c r="M43" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="N43" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B44" t="s">
-        <v>120</v>
-      </c>
-      <c r="C44" s="5">
-        <v>2016</v>
-      </c>
-      <c r="D44" t="s">
-        <v>153</v>
-      </c>
-      <c r="E44" t="s">
-        <v>122</v>
-      </c>
-      <c r="F44">
-        <v>8</v>
-      </c>
-      <c r="G44" t="s">
-        <v>130</v>
-      </c>
-      <c r="H44">
-        <v>256</v>
-      </c>
-      <c r="I44" t="s">
-        <v>124</v>
-      </c>
-      <c r="J44" s="19">
-        <v>300</v>
-      </c>
-      <c r="K44" s="1"/>
-      <c r="L44" s="16">
-        <v>46099</v>
-      </c>
-      <c r="M44" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="N44" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L45" s="15"/>
+    </row>
+    <row r="45" spans="1:15" ht="15" customHeight="1">
       <c r="M45" s="15"/>
-    </row>
-    <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L46" s="15"/>
+      <c r="N45" s="15"/>
+    </row>
+    <row r="46" spans="1:15" ht="15" customHeight="1">
       <c r="M46" s="15"/>
-    </row>
-    <row r="47" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L47" s="15"/>
+      <c r="N46" s="15"/>
+    </row>
+    <row r="47" spans="1:15" ht="15" customHeight="1">
       <c r="M47" s="15"/>
-    </row>
-    <row r="48" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L48" s="15"/>
+      <c r="N47" s="15"/>
+    </row>
+    <row r="48" spans="1:15" ht="15" customHeight="1">
       <c r="M48" s="15"/>
-    </row>
-    <row r="49" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L49" s="15"/>
+      <c r="N48" s="15"/>
+    </row>
+    <row r="49" spans="13:14" ht="15" customHeight="1">
       <c r="M49" s="15"/>
-    </row>
-    <row r="50" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L50" s="15"/>
+      <c r="N49" s="15"/>
+    </row>
+    <row r="50" spans="13:14" ht="15" customHeight="1">
       <c r="M50" s="15"/>
-    </row>
-    <row r="51" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L51" s="15"/>
+      <c r="N50" s="15"/>
+    </row>
+    <row r="51" spans="13:14" ht="15" customHeight="1">
       <c r="M51" s="15"/>
-    </row>
-    <row r="52" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L52" s="15"/>
+      <c r="N51" s="15"/>
+    </row>
+    <row r="52" spans="13:14" ht="15" customHeight="1">
       <c r="M52" s="15"/>
-    </row>
-    <row r="53" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L53" s="15"/>
+      <c r="N52" s="15"/>
+    </row>
+    <row r="53" spans="13:14" ht="15" customHeight="1">
       <c r="M53" s="15"/>
-    </row>
-    <row r="54" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L54" s="15"/>
+      <c r="N53" s="15"/>
+    </row>
+    <row r="54" spans="13:14" ht="15" customHeight="1">
       <c r="M54" s="15"/>
-    </row>
-    <row r="55" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L55" s="15"/>
+      <c r="N54" s="15"/>
+    </row>
+    <row r="55" spans="13:14" ht="15" customHeight="1">
       <c r="M55" s="15"/>
-    </row>
-    <row r="56" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L56" s="15"/>
+      <c r="N55" s="15"/>
+    </row>
+    <row r="56" spans="13:14" ht="15" customHeight="1">
       <c r="M56" s="15"/>
-    </row>
-    <row r="57" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L57" s="15"/>
+      <c r="N56" s="15"/>
+    </row>
+    <row r="57" spans="13:14" ht="15" customHeight="1">
       <c r="M57" s="15"/>
-    </row>
-    <row r="58" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L58" s="15"/>
+      <c r="N57" s="15"/>
+    </row>
+    <row r="58" spans="13:14" ht="15" customHeight="1">
       <c r="M58" s="15"/>
-    </row>
-    <row r="59" spans="12:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L59" s="15"/>
+      <c r="N58" s="15"/>
+    </row>
+    <row r="59" spans="13:14" ht="15" customHeight="1">
       <c r="M59" s="15"/>
+      <c r="N59" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A44:F44 H44:K44">
-    <cfRule type="expression" dxfId="5" priority="5">
+  <conditionalFormatting sqref="A44:G44 I44:L44">
+    <cfRule type="expression" dxfId="11" priority="5">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A44:F44 H44:M44">
-    <cfRule type="expression" dxfId="4" priority="6">
+  <conditionalFormatting sqref="A44:G44 I44:N44">
+    <cfRule type="expression" dxfId="10" priority="6">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:N9 A10:G15 I10:N15 A16:N43 N44 A45:N59">
+  <conditionalFormatting sqref="A3:O9 A10:H15 J10:O15 O44 A45:O59 A16:O43">
     <cfRule type="expression" priority="7">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="9" priority="8">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G44">
+  <conditionalFormatting sqref="H44">
     <cfRule type="expression" priority="3">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:H15">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="I10:I15">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K32:K42" xr:uid="{9E34EFD6-6288-43CE-B05D-35BC10E05685}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L32:L42" xr:uid="{9E34EFD6-6288-43CE-B05D-35BC10E05685}">
       <formula1>1</formula1>
       <formula2>2000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1 L1:M42 L45:M1048576" xr:uid="{A9EBE1C3-8923-4578-8214-596FAC33FDB8}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B17 B19 B21:B29 B31:B42" xr:uid="{C7FD23E6-3E08-4DF7-8556-C07E455C4835}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1 M1:N42 M45:N1048576" xr:uid="{A9EBE1C3-8923-4578-8214-596FAC33FDB8}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C17 C19 C21:C29 C31:C42" xr:uid="{C7FD23E6-3E08-4DF7-8556-C07E455C4835}">
       <formula1>"Desktop,Laptop,Tablet,All-In-One"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6800,280 +7115,280 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6146040A-3AF4-440D-9E03-57379B2EC394}">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-    </row>
-    <row r="2" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
+      <c r="A1" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E3" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E4" s="2">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E5" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B6" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E6" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B7" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B8" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C8">
         <v>18</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>221</v>
+        <v>173</v>
       </c>
       <c r="E8" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>221</v>
+        <v>173</v>
       </c>
       <c r="E9" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E10" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B11" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E11" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B12" t="s">
         <v>225</v>
-      </c>
-      <c r="B12" t="s">
-        <v>220</v>
       </c>
       <c r="C12">
         <v>6</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E12" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B13" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E13" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B14" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E14" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B15" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C15">
         <v>11</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E15" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="15" customHeight="1">
       <c r="A16" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B16" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C16">
         <v>4</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E16" s="2">
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:4" ht="15" customHeight="1">
       <c r="D17" s="23"/>
     </row>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:4" ht="15" customHeight="1">
       <c r="D18" s="23"/>
     </row>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:4" ht="15" customHeight="1">
       <c r="D19" s="23"/>
     </row>
   </sheetData>
@@ -7089,43 +7404,43 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F77F78-0898-4060-A2C7-C1A84336B28A}">
-  <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="33.109375" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" style="19" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
+    <row r="1" spans="1:4" ht="15" customHeight="1">
+      <c r="A1" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
       <c r="D1" s="24"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -7134,12 +7449,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -7148,12 +7463,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -7162,12 +7477,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B6" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -7176,12 +7491,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B7" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -7190,12 +7505,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B8" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -7204,12 +7519,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B9" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -7218,12 +7533,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B10" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -7232,12 +7547,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C11">
         <v>14</v>
@@ -7246,12 +7561,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B12" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -7260,12 +7575,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B13" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -7274,12 +7589,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" customHeight="1">
       <c r="A14" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B14" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -7288,26 +7603,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3"/>
-    <row r="17" x14ac:dyDescent="0.3"/>
-    <row r="18" x14ac:dyDescent="0.3"/>
-    <row r="19" x14ac:dyDescent="0.3"/>
-    <row r="20" x14ac:dyDescent="0.3"/>
-    <row r="21" x14ac:dyDescent="0.3"/>
-    <row r="22" x14ac:dyDescent="0.3"/>
-    <row r="23" x14ac:dyDescent="0.3"/>
-    <row r="24" x14ac:dyDescent="0.3"/>
-    <row r="25" x14ac:dyDescent="0.3"/>
-    <row r="26" x14ac:dyDescent="0.3"/>
-    <row r="27" x14ac:dyDescent="0.3"/>
-    <row r="28" x14ac:dyDescent="0.3"/>
-    <row r="29" x14ac:dyDescent="0.3"/>
-    <row r="30" x14ac:dyDescent="0.3"/>
-    <row r="31" x14ac:dyDescent="0.3"/>
-    <row r="32" x14ac:dyDescent="0.3"/>
-    <row r="33" x14ac:dyDescent="0.3"/>
-    <row r="34" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/data/OldInventorySystem.xlsx
+++ b/data/OldInventorySystem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rosehulman-my.sharepoint.com/personal/lucasja_rose-hulman_edu/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{556398BC-9AA0-4613-9E16-7C15B14402EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3822" documentId="8_{A0F2C8DF-695D-4A53-BA74-C2F5D1F57A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5D3BD5F-2075-44A1-91B0-CD25A0336B48}"/>
   <bookViews>
-    <workbookView xWindow="-315" yWindow="3510" windowWidth="19665" windowHeight="11055" firstSheet="1" activeTab="4" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="6" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Laptops" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="247">
   <si>
     <t>LAPTOPS</t>
   </si>
@@ -764,49 +764,31 @@
     <t>iFixit Moray Kit (complete)</t>
   </si>
   <si>
-    <t>Screwdriver Kit</t>
-  </si>
-  <si>
     <t>iFixit Pro Tech Toolkit (complete)</t>
   </si>
   <si>
     <t>iFixit Magnetic Screw Organizer</t>
   </si>
   <si>
-    <t>Screw Organizer</t>
-  </si>
-  <si>
     <t>Magnetic Parts Tray</t>
   </si>
   <si>
     <t>Anker Power Strip</t>
   </si>
   <si>
-    <t>Power Strip</t>
-  </si>
-  <si>
     <t>Generic Power Strip</t>
   </si>
   <si>
     <t>USB A to Ethernet</t>
   </si>
   <si>
-    <t>Adapter</t>
-  </si>
-  <si>
     <t>Duster</t>
   </si>
   <si>
-    <t>Miscellaneous</t>
-  </si>
-  <si>
     <t>USB Drive</t>
   </si>
   <si>
     <t>Goo Gone</t>
-  </si>
-  <si>
-    <t>Cleaning Supplies</t>
   </si>
   <si>
     <t>Isopropyl Alcohol</t>
@@ -824,7 +806,7 @@
     <numFmt numFmtId="164" formatCode="00000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -968,7 +950,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1026,6 +1008,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1038,41 +1022,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="30">
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1126,19 +1080,6 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
     </dxf>
     <dxf>
       <fill>
@@ -1242,12 +1183,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="00000"/>
-    </dxf>
-    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1273,7 +1208,50 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="00000"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1299,7 +1277,7 @@
     <tableColumn id="13" xr3:uid="{5BEE40AD-E450-4A13-BFB5-1D0CED084DB3}" name="ID"/>
     <tableColumn id="8" xr3:uid="{E9AB9B46-3541-4715-8E5B-024096D78342}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{F7DAC8DD-8096-40F1-8780-1DB9CB4EC72F}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="25"/>
     <tableColumn id="5" xr3:uid="{5338F6FB-43B0-44AF-AF8B-542FAC6CEDF0}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{64D6C993-8518-4A7C-9BDA-A54D7DBFBA8E}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{E5D987A3-C54A-4907-B710-79DB224E0008}" name="Current Status" totalsRowFunction="count"/>
@@ -1318,7 +1296,7 @@
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F96A3CC8-25D1-4CF8-877D-2816B26B7DC4}" name="Item Name" totalsRowLabel="Total"/>
-    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="24"/>
     <tableColumn id="8" xr3:uid="{7D8F815E-A974-42A8-AC0B-AB8B951599A2}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{FEA94C75-B538-448A-A9F5-46F5A27E863D}" name="Year released"/>
     <tableColumn id="4" xr3:uid="{24998D92-36B7-4553-81E7-CB33711B31BB}" name="Special Reqs/Notes"/>
@@ -1340,7 +1318,7 @@
     <tableColumn id="13" xr3:uid="{EFFF3477-1A58-41CD-BFF3-45CE299505A7}" name="ID"/>
     <tableColumn id="8" xr3:uid="{C694899F-E385-4DE2-972A-7395A9633019}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{13C54556-A90A-4F9C-800D-3D838462DF46}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="23"/>
     <tableColumn id="5" xr3:uid="{6DE19FBC-9BD8-456E-9FC5-F633F61E4A34}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{68546225-0A78-43C1-A4F9-4D2E1DC008A3}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{0D7FD365-4F73-4A57-B8A1-CFAC47267923}" name="Current Status" totalsRowFunction="count"/>
@@ -1351,7 +1329,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:M33" totalsRowShown="0" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:M33" totalsRowShown="0" tableBorderDxfId="22">
   <autoFilter ref="A2:M33" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{73648E04-2EA1-4ADB-8E24-E7DDE01C0462}" name="Item"/>
@@ -1364,8 +1342,8 @@
     <tableColumn id="2" xr3:uid="{C85B34EB-06B2-40A8-BBCB-B5F170EF3F82}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{A686D1B3-031E-4544-A98D-8F3144FA62B0}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{AB29939A-0AF4-4451-A6F4-2144F8957E73}" name="SSD/HDD"/>
-    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="20"/>
     <tableColumn id="12" xr3:uid="{67EC036F-98F6-4C6B-BDD7-99DB9B6ADF97}" name="ID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1373,7 +1351,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10100501-D05A-423B-A036-4B5D9B2ECD20}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:O59" totalsRowShown="0" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10100501-D05A-423B-A036-4B5D9B2ECD20}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:O59" totalsRowShown="0" tableBorderDxfId="29">
   <autoFilter ref="A2:O59" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{549BC727-085C-45F5-9520-711A34B50F51}" name="Item"/>
@@ -1386,10 +1364,10 @@
     <tableColumn id="13" xr3:uid="{A9DF335A-A163-4AA9-8879-B5B359D716CC}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{03AC00D8-5308-407D-9BAC-3303A2B380B3}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{CFFC1B93-1DA0-40C5-BC8E-01F5CAD8DB66}" name="SSD/HDD"/>
-    <tableColumn id="10" xr3:uid="{71AF2E6E-D071-4784-865B-CA65E73CD28D}" name="Est. Value" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{71AF2E6E-D071-4784-865B-CA65E73CD28D}" name="Est. Value" dataDxfId="28"/>
     <tableColumn id="12" xr3:uid="{EFA4DB39-7CD3-4AA7-9335-2FEE3F14CF55}" name="Notes"/>
-    <tableColumn id="9" xr3:uid="{2DC095C6-494B-405F-9E1B-C8849C64E6F1}" name="Date Donated" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{4D76F748-9FDA-4C94-B04F-D8250CE6CE08}" name="Recipient" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{2DC095C6-494B-405F-9E1B-C8849C64E6F1}" name="Date Donated" dataDxfId="27"/>
+    <tableColumn id="14" xr3:uid="{4D76F748-9FDA-4C94-B04F-D8250CE6CE08}" name="Recipient" dataDxfId="26"/>
     <tableColumn id="2" xr3:uid="{77D1B06F-E180-45FD-ACE9-4BA0C5955E95}" name="Org?"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1403,7 +1381,7 @@
     <tableColumn id="1" xr3:uid="{A07F4B01-C838-4D46-AE29-85BAC951AA36}" name="Type"/>
     <tableColumn id="3" xr3:uid="{9AC978C2-FD83-43AA-9C69-BC026B4E6411}" name="Description"/>
     <tableColumn id="4" xr3:uid="{9B2129F6-659A-4DD2-94CF-8EC39B827718}" name="Qty"/>
-    <tableColumn id="5" xr3:uid="{C24221AA-BF54-4384-AC51-1C5D1D76BE99}" name="Donated?" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{C24221AA-BF54-4384-AC51-1C5D1D76BE99}" name="Donated?" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{1B36C5CD-E753-4327-9D04-48D37AAB944F}" name="Value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1411,13 +1389,12 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1921E586-F6B8-46BF-BE64-CE91A4EEE8D6}" name="Parts56" displayName="Parts56" ref="A2:D34" totalsRowShown="0">
-  <autoFilter ref="A2:D34" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1921E586-F6B8-46BF-BE64-CE91A4EEE8D6}" name="Parts56" displayName="Parts56" ref="A2:C34" totalsRowShown="0">
+  <autoFilter ref="A2:C34" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}"/>
+  <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{C29E963F-354B-4750-B17F-22461F6DC5F4}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{7C7B0B32-2D9C-4EDB-8E56-4C2ADECB5869}" name="Type"/>
     <tableColumn id="2" xr3:uid="{1155C0CA-025A-4922-8B0E-F2A817B3BB60}" name="Qty"/>
-    <tableColumn id="8" xr3:uid="{D743202E-D377-4920-815B-09F9ED9CC36B}" name="Value" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{D743202E-D377-4920-815B-09F9ED9CC36B}" name="Value" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1741,33 +1718,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5AA6A1-7D43-4966-8813-F497D895A5C2}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.109375" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="7" max="7" width="19.44140625" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1799,11 +1776,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E3" s="1"/>
       <c r="I3" s="16"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1829,11 +1806,11 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E5" s="1"/>
       <c r="I5" s="16"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1859,7 +1836,7 @@
         <v>45673</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1886,7 +1863,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1910,7 +1887,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1934,7 +1911,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1958,7 +1935,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1982,7 +1959,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -2006,7 +1983,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="30">
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -2032,7 +2009,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -2061,7 +2038,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="45">
+    <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2087,7 +2064,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -2111,7 +2088,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="30">
+    <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2137,7 +2114,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="30">
+    <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2163,7 +2140,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="30">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -2189,7 +2166,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -2213,7 +2190,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="30">
+    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -2242,11 +2219,11 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E22" s="1"/>
       <c r="I22" s="16"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -2275,11 +2252,11 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E25" s="1"/>
       <c r="I25" s="16"/>
     </row>
-    <row r="26" spans="1:9" ht="30">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -2305,7 +2282,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -2329,7 +2306,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -2353,7 +2330,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>55</v>
       </c>
@@ -2379,34 +2356,34 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="5:5">
+    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="5:5">
+    <row r="34" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="5:5">
+    <row r="35" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="5:5">
+    <row r="36" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="5:5">
+    <row r="37" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="5:5">
+    <row r="38" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="5:5">
+    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E39" s="1"/>
     </row>
   </sheetData>
@@ -2439,29 +2416,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEA6183-B753-401C-B21E-C502785DFA3D}">
   <dimension ref="A1:G63"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2484,7 +2461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>59</v>
       </c>
@@ -2505,7 +2482,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>59</v>
       </c>
@@ -2526,7 +2503,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1">
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>59</v>
       </c>
@@ -2549,7 +2526,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>59</v>
       </c>
@@ -2572,7 +2549,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>59</v>
       </c>
@@ -2593,7 +2570,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>59</v>
       </c>
@@ -2616,7 +2593,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>59</v>
       </c>
@@ -2637,7 +2614,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="B10" s="14"/>
       <c r="C10" s="9"/>
@@ -2646,7 +2623,7 @@
       <c r="F10" s="9"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>59</v>
       </c>
@@ -2667,7 +2644,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="60">
+    <row r="12" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>63</v>
       </c>
@@ -2690,7 +2667,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>63</v>
       </c>
@@ -2713,7 +2690,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>63</v>
       </c>
@@ -2734,7 +2711,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>63</v>
       </c>
@@ -2755,7 +2732,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>63</v>
       </c>
@@ -2776,7 +2753,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>63</v>
       </c>
@@ -2797,7 +2774,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>63</v>
       </c>
@@ -2818,7 +2795,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>63</v>
       </c>
@@ -2839,7 +2816,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>63</v>
       </c>
@@ -2860,7 +2837,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>63</v>
       </c>
@@ -2881,7 +2858,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>66</v>
       </c>
@@ -2902,7 +2879,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>67</v>
       </c>
@@ -2925,7 +2902,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>66</v>
       </c>
@@ -2946,7 +2923,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>66</v>
       </c>
@@ -2967,7 +2944,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="13"/>
       <c r="C26" s="5"/>
@@ -2976,7 +2953,7 @@
       <c r="F26" s="5"/>
       <c r="G26" s="7"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>66</v>
       </c>
@@ -2999,7 +2976,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>70</v>
       </c>
@@ -3020,7 +2997,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>71</v>
       </c>
@@ -3043,7 +3020,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>73</v>
       </c>
@@ -3064,7 +3041,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>74</v>
       </c>
@@ -3085,7 +3062,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>75</v>
       </c>
@@ -3106,7 +3083,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>73</v>
       </c>
@@ -3127,7 +3104,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>76</v>
       </c>
@@ -3148,7 +3125,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>77</v>
       </c>
@@ -3171,7 +3148,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>66</v>
       </c>
@@ -3194,7 +3171,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>80</v>
       </c>
@@ -3214,7 +3191,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -3234,7 +3211,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>66</v>
       </c>
@@ -3257,7 +3234,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -3280,10 +3257,10 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G42" s="16"/>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>81</v>
       </c>
@@ -3303,7 +3280,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>81</v>
       </c>
@@ -3323,7 +3300,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>81</v>
       </c>
@@ -3343,7 +3320,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>86</v>
       </c>
@@ -3366,7 +3343,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>86</v>
       </c>
@@ -3389,7 +3366,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>88</v>
       </c>
@@ -3409,7 +3386,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>89</v>
       </c>
@@ -3426,10 +3403,10 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G50" s="16"/>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>91</v>
       </c>
@@ -3449,7 +3426,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>92</v>
       </c>
@@ -3469,7 +3446,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>93</v>
       </c>
@@ -3492,7 +3469,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>95</v>
       </c>
@@ -3515,7 +3492,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>97</v>
       </c>
@@ -3538,7 +3515,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>99</v>
       </c>
@@ -3561,7 +3538,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>100</v>
       </c>
@@ -3581,7 +3558,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>75</v>
       </c>
@@ -3601,7 +3578,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -3624,7 +3601,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>102</v>
       </c>
@@ -3647,24 +3624,24 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G61" s="16"/>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G62" s="16"/>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G63" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:G28 A30:G59 A61:G63 B60:G60">
-    <cfRule type="expression" dxfId="28" priority="1">
+  <conditionalFormatting sqref="A3:G28 A30:G59 B60:G60 A61:G63">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3684,33 +3661,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F948288C-1730-49D1-BD4C-FC704F167D22}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5703125" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.109375" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3739,7 +3716,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>105</v>
       </c>
@@ -3768,7 +3745,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>105</v>
       </c>
@@ -3797,91 +3774,91 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="5:5">
+    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="5:5">
+    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="5:5">
+    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="5:5">
+    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="5:5">
+    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="5:5">
+    <row r="22" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="5:5">
+    <row r="23" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="5:5">
+    <row r="24" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="5:5">
+    <row r="25" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="5:5">
+    <row r="26" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="5:5">
+    <row r="27" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="5:5">
+    <row r="28" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="5:5">
+    <row r="29" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="5:5">
+    <row r="30" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="5:5">
+    <row r="31" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="5:5">
+    <row r="32" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="5:5">
+    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E33" s="1"/>
     </row>
   </sheetData>
@@ -3913,40 +3890,40 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFE86381-3E33-4CB8-A62B-E48A74AB9667}">
   <dimension ref="A1:M36"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.33203125" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" style="19" customWidth="1"/>
-    <col min="12" max="12" width="21.28515625" customWidth="1"/>
+    <col min="8" max="8" width="17.109375" customWidth="1"/>
+    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" customWidth="1"/>
+    <col min="11" max="11" width="18.6640625" style="19" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+    </row>
+    <row r="2" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>109</v>
       </c>
@@ -3987,7 +3964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>120</v>
       </c>
@@ -4026,7 +4003,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>126</v>
       </c>
@@ -4065,7 +4042,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -4104,10 +4081,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>129</v>
       </c>
@@ -4146,7 +4123,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -4185,7 +4162,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>134</v>
       </c>
@@ -4224,10 +4201,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>136</v>
       </c>
@@ -4266,7 +4243,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>139</v>
       </c>
@@ -4304,7 +4281,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>141</v>
       </c>
@@ -4343,7 +4320,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>129</v>
       </c>
@@ -4382,7 +4359,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>143</v>
       </c>
@@ -4421,7 +4398,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>145</v>
       </c>
@@ -4460,7 +4437,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15" customHeight="1">
+    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>147</v>
       </c>
@@ -4499,7 +4476,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15" customHeight="1">
+    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>150</v>
       </c>
@@ -4538,7 +4515,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1">
+    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>150</v>
       </c>
@@ -4577,7 +4554,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1">
+    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>152</v>
       </c>
@@ -4616,7 +4593,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15" customHeight="1">
+    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>152</v>
       </c>
@@ -4655,7 +4632,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15" customHeight="1">
+    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -4694,7 +4671,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15" customHeight="1">
+    <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>155</v>
       </c>
@@ -4733,7 +4710,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15" customHeight="1">
+    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -4772,7 +4749,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15" customHeight="1">
+    <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>129</v>
       </c>
@@ -4811,7 +4788,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15" customHeight="1">
+    <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>157</v>
       </c>
@@ -4850,7 +4827,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15" customHeight="1">
+    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>47</v>
       </c>
@@ -4889,11 +4866,11 @@
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15" customHeight="1">
+    <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="36" t="s">
+      <c r="B28" s="31" t="s">
         <v>28</v>
       </c>
       <c r="C28" t="s">
@@ -4928,7 +4905,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="15" customHeight="1">
+    <row r="29" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>160</v>
       </c>
@@ -4967,11 +4944,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15" customHeight="1">
+    <row r="30" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="B30" s="37" t="s">
+      <c r="B30" t="s">
         <v>12</v>
       </c>
       <c r="C30" t="s">
@@ -5008,16 +4985,16 @@
         <v>127</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15" customHeight="1">
+    <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L31" s="1"/>
     </row>
-    <row r="32" spans="1:13" ht="15" customHeight="1">
+    <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="3:12" ht="15" customHeight="1">
+    <row r="33" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L33" s="1"/>
     </row>
-    <row r="36" spans="3:12" ht="15" customHeight="1">
+    <row r="36" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="26"/>
       <c r="D36" s="27"/>
       <c r="E36" s="28"/>
@@ -5031,44 +5008,44 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <conditionalFormatting sqref="A27:B28 A30:B30">
-    <cfRule type="expression" dxfId="24" priority="21">
+    <cfRule type="expression" dxfId="15" priority="21">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="22">
+    <cfRule type="expression" dxfId="14" priority="22">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:L9 A11:L14 A15:D15 F15:L15 A16:L25">
-    <cfRule type="expression" dxfId="22" priority="25">
+    <cfRule type="expression" dxfId="13" priority="25">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:M9 A11:M14 A15:D15 F15:M15 A16:M25">
-    <cfRule type="expression" dxfId="21" priority="26">
+    <cfRule type="expression" dxfId="12" priority="26">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:I36">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H29">
-    <cfRule type="expression" dxfId="18" priority="13">
+    <cfRule type="expression" dxfId="9" priority="13">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="14">
+    <cfRule type="expression" dxfId="8" priority="14">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I29">
-    <cfRule type="expression" dxfId="16" priority="5">
+    <cfRule type="expression" dxfId="7" priority="5">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="6">
+    <cfRule type="expression" dxfId="6" priority="6">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5094,28 +5071,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1C144A-BB57-4446-B714-000D1D9FAB4A}">
   <dimension ref="A1:Q59"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.28515625" style="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.28515625" customWidth="1"/>
-    <col min="13" max="13" width="16.85546875" style="16" customWidth="1"/>
-    <col min="14" max="14" width="33.28515625" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.33203125" customWidth="1"/>
+    <col min="13" max="13" width="16.88671875" style="16" customWidth="1"/>
+    <col min="14" max="14" width="33.33203125" style="16" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27.7109375" customWidth="1"/>
-    <col min="17" max="17" width="28.28515625" customWidth="1"/>
+    <col min="16" max="16" width="27.6640625" customWidth="1"/>
+    <col min="17" max="17" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" customHeight="1">
+    <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C1" s="17" t="s">
         <v>164</v>
       </c>
@@ -5138,7 +5115,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>109</v>
       </c>
@@ -5193,7 +5170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>170</v>
       </c>
@@ -5226,7 +5203,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>170</v>
       </c>
@@ -5259,7 +5236,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>170</v>
       </c>
@@ -5292,7 +5269,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>170</v>
       </c>
@@ -5325,7 +5302,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>170</v>
       </c>
@@ -5358,7 +5335,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>170</v>
       </c>
@@ -5391,7 +5368,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>170</v>
       </c>
@@ -5424,7 +5401,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>174</v>
       </c>
@@ -5469,7 +5446,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>176</v>
       </c>
@@ -5514,7 +5491,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>178</v>
       </c>
@@ -5561,7 +5538,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>181</v>
       </c>
@@ -5606,7 +5583,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>174</v>
       </c>
@@ -5651,7 +5628,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>183</v>
       </c>
@@ -5696,7 +5673,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>185</v>
       </c>
@@ -5743,7 +5720,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>192</v>
       </c>
@@ -5790,7 +5767,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>102</v>
       </c>
@@ -5818,8 +5795,8 @@
       <c r="I18">
         <v>256</v>
       </c>
-      <c r="J18" t="s">
-        <v>125</v>
+      <c r="J18">
+        <v>256</v>
       </c>
       <c r="K18" s="19">
         <v>250</v>
@@ -5837,7 +5814,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -5884,7 +5861,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="43.5">
+    <row r="20" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -5931,7 +5908,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>202</v>
       </c>
@@ -5976,7 +5953,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>66</v>
       </c>
@@ -6021,7 +5998,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -6066,7 +6043,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -6111,7 +6088,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -6156,7 +6133,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -6201,7 +6178,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -6246,7 +6223,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>205</v>
       </c>
@@ -6291,7 +6268,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>205</v>
       </c>
@@ -6336,7 +6313,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>129</v>
       </c>
@@ -6381,11 +6358,11 @@
         <v>173</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="38" t="s">
+      <c r="B31" s="32" t="s">
         <v>28</v>
       </c>
       <c r="C31" t="s">
@@ -6426,7 +6403,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -6470,7 +6447,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -6514,7 +6491,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>209</v>
       </c>
@@ -6558,7 +6535,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>209</v>
       </c>
@@ -6602,7 +6579,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>209</v>
       </c>
@@ -6646,7 +6623,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>209</v>
       </c>
@@ -6690,7 +6667,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>209</v>
       </c>
@@ -6734,7 +6711,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>209</v>
       </c>
@@ -6778,7 +6755,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="15" customHeight="1">
+    <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>209</v>
       </c>
@@ -6822,7 +6799,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="15" customHeight="1">
+    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>209</v>
       </c>
@@ -6866,7 +6843,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="15" customHeight="1">
+    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>209</v>
       </c>
@@ -6910,7 +6887,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="15" customHeight="1">
+    <row r="43" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -6955,11 +6932,11 @@
         <v>196</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="15" customHeight="1">
+    <row r="44" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="36" t="s">
+      <c r="B44" s="31" t="s">
         <v>28</v>
       </c>
       <c r="C44" t="s">
@@ -7000,82 +6977,82 @@
         <v>196</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="15" customHeight="1">
+    <row r="45" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M45" s="15"/>
       <c r="N45" s="15"/>
     </row>
-    <row r="46" spans="1:15" ht="15" customHeight="1">
+    <row r="46" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M46" s="15"/>
       <c r="N46" s="15"/>
     </row>
-    <row r="47" spans="1:15" ht="15" customHeight="1">
+    <row r="47" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M47" s="15"/>
       <c r="N47" s="15"/>
     </row>
-    <row r="48" spans="1:15" ht="15" customHeight="1">
+    <row r="48" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M48" s="15"/>
       <c r="N48" s="15"/>
     </row>
-    <row r="49" spans="13:14" ht="15" customHeight="1">
+    <row r="49" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M49" s="15"/>
       <c r="N49" s="15"/>
     </row>
-    <row r="50" spans="13:14" ht="15" customHeight="1">
+    <row r="50" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M50" s="15"/>
       <c r="N50" s="15"/>
     </row>
-    <row r="51" spans="13:14" ht="15" customHeight="1">
+    <row r="51" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M51" s="15"/>
       <c r="N51" s="15"/>
     </row>
-    <row r="52" spans="13:14" ht="15" customHeight="1">
+    <row r="52" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M52" s="15"/>
       <c r="N52" s="15"/>
     </row>
-    <row r="53" spans="13:14" ht="15" customHeight="1">
+    <row r="53" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M53" s="15"/>
       <c r="N53" s="15"/>
     </row>
-    <row r="54" spans="13:14" ht="15" customHeight="1">
+    <row r="54" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M54" s="15"/>
       <c r="N54" s="15"/>
     </row>
-    <row r="55" spans="13:14" ht="15" customHeight="1">
+    <row r="55" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M55" s="15"/>
       <c r="N55" s="15"/>
     </row>
-    <row r="56" spans="13:14" ht="15" customHeight="1">
+    <row r="56" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M56" s="15"/>
       <c r="N56" s="15"/>
     </row>
-    <row r="57" spans="13:14" ht="15" customHeight="1">
+    <row r="57" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M57" s="15"/>
       <c r="N57" s="15"/>
     </row>
-    <row r="58" spans="13:14" ht="15" customHeight="1">
+    <row r="58" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M58" s="15"/>
       <c r="N58" s="15"/>
     </row>
-    <row r="59" spans="13:14" ht="15" customHeight="1">
+    <row r="59" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M59" s="15"/>
       <c r="N59" s="15"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A44:G44 I44:L44">
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:G44 I44:N44">
-    <cfRule type="expression" dxfId="10" priority="6">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:O9 A10:H15 J10:O15 O44 A45:O59 A16:O43">
+  <conditionalFormatting sqref="A3:O9 A10:H15 J10:O15 A16:O43 O44 A45:O59">
     <cfRule type="expression" priority="7">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="8">
+    <cfRule type="expression" dxfId="3" priority="8">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7083,15 +7060,15 @@
     <cfRule type="expression" priority="3">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:I15">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7115,25 +7092,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6146040A-3AF4-440D-9E03-57379B2EC394}">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+    </row>
+    <row r="2" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>214</v>
       </c>
@@ -7150,7 +7127,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>219</v>
       </c>
@@ -7164,7 +7141,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>220</v>
       </c>
@@ -7178,7 +7155,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>221</v>
       </c>
@@ -7195,7 +7172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>221</v>
       </c>
@@ -7212,7 +7189,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>221</v>
       </c>
@@ -7229,7 +7206,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>221</v>
       </c>
@@ -7246,7 +7223,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>221</v>
       </c>
@@ -7263,7 +7240,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>221</v>
       </c>
@@ -7280,7 +7257,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>221</v>
       </c>
@@ -7297,7 +7274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>229</v>
       </c>
@@ -7314,7 +7291,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>229</v>
       </c>
@@ -7331,7 +7308,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>229</v>
       </c>
@@ -7348,7 +7325,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>229</v>
       </c>
@@ -7365,7 +7342,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1">
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>231</v>
       </c>
@@ -7382,13 +7359,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="4:4" ht="15" customHeight="1">
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D17" s="23"/>
     </row>
-    <row r="18" spans="4:4" ht="15" customHeight="1">
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D18" s="23"/>
     </row>
-    <row r="19" spans="4:4" ht="15" customHeight="1">
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D19" s="23"/>
     </row>
   </sheetData>
@@ -7404,208 +7381,167 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F77F78-0898-4060-A2C7-C1A84336B28A}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="19" customWidth="1"/>
+    <col min="1" max="1" width="33.109375" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="24"/>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1">
+      <c r="B1" s="36"/>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>234</v>
       </c>
-      <c r="B2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="C2" s="21" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>235</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3" s="19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>236</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3" s="19">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="19">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="19">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" s="19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="19">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B4" t="s">
-        <v>236</v>
-      </c>
-      <c r="C4">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B11">
+        <v>14</v>
+      </c>
+      <c r="C11" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="D4" s="19">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1">
-      <c r="A5" t="s">
-        <v>238</v>
-      </c>
-      <c r="B5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5" s="19">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1">
-      <c r="A6" t="s">
-        <v>240</v>
-      </c>
-      <c r="B6" t="s">
-        <v>239</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6" s="19">
+      <c r="C12" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>245</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="19">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1">
-      <c r="A7" t="s">
-        <v>241</v>
-      </c>
-      <c r="B7" t="s">
-        <v>242</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7" s="19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1">
-      <c r="A8" t="s">
-        <v>243</v>
-      </c>
-      <c r="B8" t="s">
-        <v>242</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1">
-      <c r="A9" t="s">
-        <v>244</v>
-      </c>
-      <c r="B9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C9">
-        <v>5</v>
-      </c>
-      <c r="D9" s="19">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1">
-      <c r="A10" t="s">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>246</v>
       </c>
-      <c r="B10" t="s">
-        <v>247</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" s="19">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1">
-      <c r="A11" t="s">
-        <v>248</v>
-      </c>
-      <c r="B11" t="s">
-        <v>247</v>
-      </c>
-      <c r="C11">
-        <v>14</v>
-      </c>
-      <c r="D11" s="19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1">
-      <c r="A12" t="s">
-        <v>249</v>
-      </c>
-      <c r="B12" t="s">
-        <v>250</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" s="19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1">
-      <c r="A13" t="s">
-        <v>251</v>
-      </c>
-      <c r="B13" t="s">
-        <v>250</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" t="s">
-        <v>252</v>
-      </c>
-      <c r="B14" t="s">
-        <v>245</v>
-      </c>
-      <c r="C14">
+      <c r="B14">
         <v>6</v>
       </c>
-      <c r="D14" s="19">
+      <c r="C14" s="19">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/OldInventorySystem.xlsx
+++ b/data/OldInventorySystem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30105"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rosehulman-my.sharepoint.com/personal/lucasja_rose-hulman_edu/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3822" documentId="8_{A0F2C8DF-695D-4A53-BA74-C2F5D1F57A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5D3BD5F-2075-44A1-91B0-CD25A0336B48}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F93733CB-E6FB-4BA1-B4B3-CC6466AACE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="6" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Laptops" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="255">
   <si>
     <t>LAPTOPS</t>
   </si>
@@ -74,9 +74,6 @@
     <t>Date Updated</t>
   </si>
   <si>
-    <t>Column1</t>
-  </si>
-  <si>
     <t>100e Chromebook 2nd Gen</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
     <t>Not Started</t>
   </si>
   <si>
-    <t>bv</t>
-  </si>
-  <si>
     <t>MacBook Air A2179</t>
   </si>
   <si>
@@ -194,15 +188,6 @@
     <t>Windows 11 w/ all updates, battery no work :(</t>
   </si>
   <si>
-    <t>Edge 15</t>
-  </si>
-  <si>
-    <t>Needs Vinilla OS</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>Precision 5540</t>
   </si>
   <si>
@@ -273,12 +258,6 @@
   </si>
   <si>
     <t>Ryzen 4000 Desktop</t>
-  </si>
-  <si>
-    <t>Optiplex 5050 Micro</t>
-  </si>
-  <si>
-    <t>Installed SSD</t>
   </si>
   <si>
     <r>
@@ -332,220 +311,250 @@
     <t>ProDesk 400 G5 Desktop Mini</t>
   </si>
   <si>
+    <t>Mini PC ZBox-CI323NANO</t>
+  </si>
+  <si>
+    <t>Has Vanilla OS, can discover eduroam but not rhit open, ethernet works</t>
+  </si>
+  <si>
+    <t>Z2 Mini G5 Workstation</t>
+  </si>
+  <si>
+    <t>Needs power supply; expensive!!!! MXM P620</t>
+  </si>
+  <si>
+    <t>Optiplex 7070 micro</t>
+  </si>
+  <si>
+    <t>Windows Updates</t>
+  </si>
+  <si>
+    <t>ThinkCentre M700</t>
+  </si>
+  <si>
+    <t>Needs to play dugdug video, make clinky when moved</t>
+  </si>
+  <si>
+    <t>Optiplex 3070</t>
+  </si>
+  <si>
+    <t>TABLETS</t>
+  </si>
+  <si>
+    <t>iPad A1397</t>
+  </si>
+  <si>
+    <t>Wifi + Cellular, Cracked screen</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Wifi + Cellular</t>
+  </si>
+  <si>
+    <t>READY TO DONATE</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Type of Device</t>
+  </si>
+  <si>
+    <t>Est. Year</t>
+  </si>
+  <si>
+    <t>CPU</t>
+  </si>
+  <si>
+    <t>OS</t>
+  </si>
+  <si>
+    <t>RAM Amount</t>
+  </si>
+  <si>
+    <t>RAM Generation</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>SSD/HDD</t>
+  </si>
+  <si>
+    <t>Est. Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Thinkcenter E73</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>Intel i3-4130</t>
+  </si>
+  <si>
+    <t>Vanilla OS</t>
+  </si>
+  <si>
+    <t>DDR3</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>Inspiron 15 3552</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Inspiron 15-3552</t>
+  </si>
+  <si>
+    <t>Chromebox Thin Cilent 3</t>
+  </si>
+  <si>
+    <t>Intel Celeron 3865U</t>
+  </si>
+  <si>
+    <t>DDR4</t>
+  </si>
+  <si>
+    <t>intel core i3-7100</t>
+  </si>
+  <si>
+    <t>Intel core i3-7100</t>
+  </si>
+  <si>
+    <t>ThinkCentre M625q</t>
+  </si>
+  <si>
+    <t>AMD A9-9420e</t>
+  </si>
+  <si>
+    <t>Latitude 5510</t>
+  </si>
+  <si>
+    <t>Intel Core i7-10610U</t>
+  </si>
+  <si>
+    <t>Windows 11</t>
+  </si>
+  <si>
+    <t>Inspiron 3847</t>
+  </si>
+  <si>
+    <t>Intel Core i3-4170</t>
+  </si>
+  <si>
+    <t>Latitude 5490</t>
+  </si>
+  <si>
+    <t>Intel Core i7-8650U</t>
+  </si>
+  <si>
+    <t>Inspiron 15 3537</t>
+  </si>
+  <si>
+    <t>Intel Core i3 ULV</t>
+  </si>
+  <si>
+    <t>Latitude 5410</t>
+  </si>
+  <si>
+    <t>Intel Core i5-10210U</t>
+  </si>
+  <si>
+    <t>MacBook Pro A1502</t>
+  </si>
+  <si>
+    <t>2.6 GHz Dual-Core Intel Core i5</t>
+  </si>
+  <si>
+    <t>macOS</t>
+  </si>
+  <si>
+    <t>ProBook 450 G6</t>
+  </si>
+  <si>
+    <t>Intel Core i5-8265U</t>
+  </si>
+  <si>
+    <t>ProBook 450 G8</t>
+  </si>
+  <si>
+    <t>Intel Core i5-1135G7</t>
+  </si>
+  <si>
+    <t>Intel Core i7-6700</t>
+  </si>
+  <si>
+    <t>Elitebook 850 G6</t>
+  </si>
+  <si>
+    <t>Intel Core i7-8565U</t>
+  </si>
+  <si>
+    <t>ProBook 650 G3</t>
+  </si>
+  <si>
+    <t>Intel Core i5-7300u</t>
+  </si>
+  <si>
+    <t>Intel Core i7-4770</t>
+  </si>
+  <si>
+    <t>Latitude 5580</t>
+  </si>
+  <si>
+    <t>Intel Core i7-7820</t>
+  </si>
+  <si>
+    <t>Intel Core i5-6400t</t>
+  </si>
+  <si>
+    <t>Needs charger</t>
+  </si>
+  <si>
+    <t>Edge 15</t>
+  </si>
+  <si>
+    <t>Intel Core i3-5020U</t>
+  </si>
+  <si>
+    <t>DRR3</t>
+  </si>
+  <si>
+    <t>Optiplex 5060</t>
+  </si>
+  <si>
+    <t>Intel Core i5-8400</t>
+  </si>
+  <si>
+    <t>Optiplex 5050 Micro</t>
+  </si>
+  <si>
+    <t>Intel Core i5-7600</t>
+  </si>
+  <si>
+    <t>ProDesk 600 G5 Desktop Mini</t>
+  </si>
+  <si>
+    <t>Intel core i5-9500</t>
+  </si>
+  <si>
     <t>ProDesk 600 G3 Desktop Mini</t>
   </si>
   <si>
-    <t>Mini PC ZBox-CI323NANO</t>
-  </si>
-  <si>
-    <t>Has Vanilla OS, can discover eduroam but not rhit open, ethernet works</t>
-  </si>
-  <si>
-    <t>ProDesk 600 G5 Desktop Mini</t>
-  </si>
-  <si>
-    <t>Windows Updates</t>
-  </si>
-  <si>
-    <t>Z2 Mini G5 Workstation</t>
-  </si>
-  <si>
-    <t>Needs power supply; expensive!!!! MXM P620</t>
-  </si>
-  <si>
-    <t>Optiplex 7070 micro</t>
-  </si>
-  <si>
-    <t>ThinkCentre M700</t>
-  </si>
-  <si>
-    <t>Needs to play dugdug video, make clinky when moved</t>
-  </si>
-  <si>
-    <t>Optiplex 5060</t>
-  </si>
-  <si>
-    <t>Needs Windows 11, Has Vanilla OS</t>
-  </si>
-  <si>
-    <t>TABLETS</t>
-  </si>
-  <si>
-    <t>iPad A1397</t>
-  </si>
-  <si>
-    <t>Wifi + Cellular, Cracked screen</t>
-  </si>
-  <si>
-    <t>Wifi + Cellular</t>
-  </si>
-  <si>
-    <t>READY TO DONATE</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Type of Device</t>
-  </si>
-  <si>
-    <t>Est. Year</t>
-  </si>
-  <si>
-    <t>CPU</t>
-  </si>
-  <si>
-    <t>OS</t>
-  </si>
-  <si>
-    <t>RAM Amount</t>
-  </si>
-  <si>
-    <t>RAM Generation</t>
-  </si>
-  <si>
-    <t>Storage</t>
-  </si>
-  <si>
-    <t>SSD/HDD</t>
-  </si>
-  <si>
-    <t>Est. Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Thinkcenter E73</t>
-  </si>
-  <si>
-    <t>Desktop</t>
-  </si>
-  <si>
-    <t>Intel i3-4130</t>
-  </si>
-  <si>
-    <t>Vanilla OS</t>
-  </si>
-  <si>
-    <t>DDR3</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>Inspiron 15 3552</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>Inspiron 15-3552</t>
-  </si>
-  <si>
-    <t>Chromebox Thin Cilent 3</t>
-  </si>
-  <si>
-    <t>Intel Celeron 3865U</t>
-  </si>
-  <si>
-    <t>DDR4</t>
-  </si>
-  <si>
-    <t>intel core i3-7100</t>
-  </si>
-  <si>
-    <t>Intel core i3-7100</t>
-  </si>
-  <si>
-    <t>ThinkCentre M625q</t>
-  </si>
-  <si>
-    <t>AMD A9-9420e</t>
-  </si>
-  <si>
-    <t>Latitude 5510</t>
-  </si>
-  <si>
-    <t>Intel Core i7-10610U</t>
-  </si>
-  <si>
-    <t>Windows 11</t>
-  </si>
-  <si>
-    <t>Inspiron 3847</t>
-  </si>
-  <si>
-    <t>Intel Core i3-4170</t>
-  </si>
-  <si>
-    <t>Latitude 5490</t>
-  </si>
-  <si>
-    <t>Intel Core i7-8650U</t>
-  </si>
-  <si>
-    <t>Inspiron 15 3537</t>
-  </si>
-  <si>
-    <t>Intel Core i3 ULV</t>
-  </si>
-  <si>
-    <t>Latitude 5410</t>
-  </si>
-  <si>
-    <t>Intel Core i5-10210U</t>
-  </si>
-  <si>
-    <t>MacBook Pro A1502</t>
-  </si>
-  <si>
-    <t>2.6 GHz Dual-Core Intel Core i5</t>
-  </si>
-  <si>
-    <t>macOS</t>
-  </si>
-  <si>
-    <t>ProBook 450 G6</t>
-  </si>
-  <si>
-    <t>Intel Core i5-8265U</t>
-  </si>
-  <si>
-    <t>ProBook 450 G8</t>
-  </si>
-  <si>
-    <t>Intel Core i5-1135G7</t>
-  </si>
-  <si>
-    <t>Intel Core i7-6700</t>
-  </si>
-  <si>
-    <t>Elitebook 850 G6</t>
-  </si>
-  <si>
-    <t>Intel Core i7-8565U</t>
-  </si>
-  <si>
-    <t>ProBook 650 G3</t>
-  </si>
-  <si>
-    <t>Intel Core i5-7300u</t>
-  </si>
-  <si>
-    <t>Intel Core i7-4770</t>
-  </si>
-  <si>
-    <t>Latitude 5580</t>
-  </si>
-  <si>
-    <t>Intel Core i7-7820</t>
-  </si>
-  <si>
-    <t>Intel Core i5 6400t</t>
-  </si>
-  <si>
-    <t>Needs charger</t>
+    <t>Intel core i5-7500t</t>
+  </si>
+  <si>
+    <t>Intel core i5-1210u</t>
   </si>
   <si>
     <t>Donated Devices</t>
@@ -695,6 +704,18 @@
     <t>Wabash Activity Center</t>
   </si>
   <si>
+    <t>ASUS</t>
+  </si>
+  <si>
+    <t>Intel Core i3-4010U</t>
+  </si>
+  <si>
+    <t>Archlinux</t>
+  </si>
+  <si>
+    <t>Linux User Group</t>
+  </si>
+  <si>
     <t>PARTS</t>
   </si>
   <si>
@@ -716,6 +737,9 @@
     <t>SATA SSD</t>
   </si>
   <si>
+    <t>256GB</t>
+  </si>
+  <si>
     <t>M2 SSD</t>
   </si>
   <si>
@@ -743,10 +767,10 @@
     <t>4GB DDR3</t>
   </si>
   <si>
+    <t>16GB DDR4</t>
+  </si>
+  <si>
     <t>DIMM</t>
-  </si>
-  <si>
-    <t>16GB DDR4</t>
   </si>
   <si>
     <t>GPU</t>
@@ -806,7 +830,7 @@
     <numFmt numFmtId="164" formatCode="00000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -950,7 +974,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1001,15 +1025,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1026,7 +1048,31 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="36">
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1080,6 +1126,94 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -1183,6 +1317,12 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="00000"/>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1208,50 +1348,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="00000"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1267,36 +1364,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}" name="In_Progress" displayName="In_Progress" ref="A2:J39">
-  <autoFilter ref="A2:J39" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:J16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}" name="In_Progress" displayName="In_Progress" ref="A2:I39">
+  <autoFilter ref="A2:I39" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I16">
     <sortCondition ref="B2:B16"/>
   </sortState>
-  <tableColumns count="10">
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{ED14BD60-C1E9-46C1-80A5-0D5E395AF078}" name="Item Name" totalsRowLabel="Total"/>
     <tableColumn id="13" xr3:uid="{5BEE40AD-E450-4A13-BFB5-1D0CED084DB3}" name="ID"/>
     <tableColumn id="8" xr3:uid="{E9AB9B46-3541-4715-8E5B-024096D78342}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{F7DAC8DD-8096-40F1-8780-1DB9CB4EC72F}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="35"/>
     <tableColumn id="5" xr3:uid="{5338F6FB-43B0-44AF-AF8B-542FAC6CEDF0}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{64D6C993-8518-4A7C-9BDA-A54D7DBFBA8E}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{E5D987A3-C54A-4907-B710-79DB224E0008}" name="Current Status" totalsRowFunction="count"/>
     <tableColumn id="14" xr3:uid="{CBD4AC90-B0AA-4722-BB52-11B8B47FEEAF}" name="Date Updated"/>
-    <tableColumn id="2" xr3:uid="{FA824550-7946-45DC-83FC-FF24AB7D40C1}" name="Column1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1B9E2046-2B17-40F3-B52D-EAF68E47122D}" name="In_Progress8" displayName="In_Progress8" ref="A2:G63">
-  <autoFilter ref="A2:G63" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G63">
-    <sortCondition ref="B2:B63"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1B9E2046-2B17-40F3-B52D-EAF68E47122D}" name="In_Progress8" displayName="In_Progress8" ref="A2:G59">
+  <autoFilter ref="A2:G59" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G59">
+    <sortCondition ref="B2:B59"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F96A3CC8-25D1-4CF8-877D-2816B26B7DC4}" name="Item Name" totalsRowLabel="Total"/>
-    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="32"/>
     <tableColumn id="8" xr3:uid="{7D8F815E-A974-42A8-AC0B-AB8B951599A2}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{FEA94C75-B538-448A-A9F5-46F5A27E863D}" name="Year released"/>
     <tableColumn id="4" xr3:uid="{24998D92-36B7-4553-81E7-CB33711B31BB}" name="Special Reqs/Notes"/>
@@ -1318,7 +1414,7 @@
     <tableColumn id="13" xr3:uid="{EFFF3477-1A58-41CD-BFF3-45CE299505A7}" name="ID"/>
     <tableColumn id="8" xr3:uid="{C694899F-E385-4DE2-972A-7395A9633019}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{13C54556-A90A-4F9C-800D-3D838462DF46}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="31"/>
     <tableColumn id="5" xr3:uid="{6DE19FBC-9BD8-456E-9FC5-F633F61E4A34}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{68546225-0A78-43C1-A4F9-4D2E1DC008A3}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{0D7FD365-4F73-4A57-B8A1-CFAC47267923}" name="Current Status" totalsRowFunction="count"/>
@@ -1329,8 +1425,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:M33" totalsRowShown="0" tableBorderDxfId="22">
-  <autoFilter ref="A2:M33" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:M44" totalsRowShown="0" tableBorderDxfId="14">
+  <autoFilter ref="A2:M44" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{73648E04-2EA1-4ADB-8E24-E7DDE01C0462}" name="Item"/>
     <tableColumn id="13" xr3:uid="{DB867F70-87B5-4AE3-B35F-568639EAF10F}" name="Manufacturer"/>
@@ -1342,8 +1438,8 @@
     <tableColumn id="2" xr3:uid="{C85B34EB-06B2-40A8-BBCB-B5F170EF3F82}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{A686D1B3-031E-4544-A98D-8F3144FA62B0}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{AB29939A-0AF4-4451-A6F4-2144F8957E73}" name="SSD/HDD"/>
-    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="12"/>
     <tableColumn id="12" xr3:uid="{67EC036F-98F6-4C6B-BDD7-99DB9B6ADF97}" name="ID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1351,7 +1447,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10100501-D05A-423B-A036-4B5D9B2ECD20}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:O59" totalsRowShown="0" tableBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10100501-D05A-423B-A036-4B5D9B2ECD20}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:O59" totalsRowShown="0" tableBorderDxfId="5">
   <autoFilter ref="A2:O59" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{549BC727-085C-45F5-9520-711A34B50F51}" name="Item"/>
@@ -1364,10 +1460,10 @@
     <tableColumn id="13" xr3:uid="{A9DF335A-A163-4AA9-8879-B5B359D716CC}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{03AC00D8-5308-407D-9BAC-3303A2B380B3}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{CFFC1B93-1DA0-40C5-BC8E-01F5CAD8DB66}" name="SSD/HDD"/>
-    <tableColumn id="10" xr3:uid="{71AF2E6E-D071-4784-865B-CA65E73CD28D}" name="Est. Value" dataDxfId="28"/>
+    <tableColumn id="10" xr3:uid="{71AF2E6E-D071-4784-865B-CA65E73CD28D}" name="Est. Value" dataDxfId="4"/>
     <tableColumn id="12" xr3:uid="{EFA4DB39-7CD3-4AA7-9335-2FEE3F14CF55}" name="Notes"/>
-    <tableColumn id="9" xr3:uid="{2DC095C6-494B-405F-9E1B-C8849C64E6F1}" name="Date Donated" dataDxfId="27"/>
-    <tableColumn id="14" xr3:uid="{4D76F748-9FDA-4C94-B04F-D8250CE6CE08}" name="Recipient" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{2DC095C6-494B-405F-9E1B-C8849C64E6F1}" name="Date Donated" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{4D76F748-9FDA-4C94-B04F-D8250CE6CE08}" name="Recipient" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{77D1B06F-E180-45FD-ACE9-4BA0C5955E95}" name="Org?"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1375,13 +1471,13 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5027EC0E-CEEE-4641-ADD0-AA27230F7EC3}" name="Parts5" displayName="Parts5" ref="A2:E19" totalsRowShown="0">
-  <autoFilter ref="A2:E19" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5027EC0E-CEEE-4641-ADD0-AA27230F7EC3}" name="Parts5" displayName="Parts5" ref="A2:E20" totalsRowShown="0">
+  <autoFilter ref="A2:E20" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A07F4B01-C838-4D46-AE29-85BAC951AA36}" name="Type"/>
     <tableColumn id="3" xr3:uid="{9AC978C2-FD83-43AA-9C69-BC026B4E6411}" name="Description"/>
     <tableColumn id="4" xr3:uid="{9B2129F6-659A-4DD2-94CF-8EC39B827718}" name="Qty"/>
-    <tableColumn id="5" xr3:uid="{C24221AA-BF54-4384-AC51-1C5D1D76BE99}" name="Donated?" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{C24221AA-BF54-4384-AC51-1C5D1D76BE99}" name="Donated?" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{1B36C5CD-E753-4327-9D04-48D37AAB944F}" name="Value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1394,7 +1490,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{C29E963F-354B-4750-B17F-22461F6DC5F4}" name="Name"/>
     <tableColumn id="2" xr3:uid="{1155C0CA-025A-4922-8B0E-F2A817B3BB60}" name="Qty"/>
-    <tableColumn id="8" xr3:uid="{D743202E-D377-4920-815B-09F9ED9CC36B}" name="Value" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{D743202E-D377-4920-815B-09F9ED9CC36B}" name="Value" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1717,34 +1813,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5AA6A1-7D43-4966-8813-F497D895A5C2}">
-  <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.109375" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5546875" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
-    <col min="7" max="7" width="19.44140625" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1772,618 +1868,587 @@
       <c r="I2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:9">
       <c r="E3" s="1"/>
       <c r="I3" s="16"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>2019</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
       </c>
       <c r="I4" s="16">
         <v>46045</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="E5" s="1"/>
       <c r="I5" s="16"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>2010</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
         <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
       </c>
       <c r="I6" s="16">
         <v>45673</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7">
         <v>2010</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I7" s="16">
         <v>46001</v>
       </c>
-      <c r="J7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>2020</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I8" s="16">
         <v>46001</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9">
         <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9">
         <v>2013</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I9" s="16">
         <v>46001</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10">
         <v>2014</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I10" s="16">
         <v>46001</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>2012</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I11" s="16">
         <v>46001</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B12">
         <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2016</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I12" s="16">
         <v>46001</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="30">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B13">
         <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>2011</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
         <v>14</v>
-      </c>
-      <c r="H13" t="s">
-        <v>15</v>
       </c>
       <c r="I13" s="16">
         <v>46038</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B14">
         <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14">
         <v>2023</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" t="s">
         <v>14</v>
-      </c>
-      <c r="G14" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" t="s">
-        <v>15</v>
       </c>
       <c r="I14" s="16">
         <v>46001</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="45">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B15">
         <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D15">
         <v>2011</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
         <v>14</v>
-      </c>
-      <c r="H15" t="s">
-        <v>15</v>
       </c>
       <c r="I15" s="16">
         <v>46101</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16">
         <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16">
         <v>2018</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I16" s="16">
         <v>46001</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="30">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B17">
         <v>116</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D17">
         <v>2020</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" t="s">
         <v>14</v>
-      </c>
-      <c r="H17" t="s">
-        <v>15</v>
       </c>
       <c r="I17" s="16">
         <v>46094</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="30">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B18">
         <v>118</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18">
         <v>2020</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I18" s="16">
         <v>46136</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="30">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B19">
         <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19">
         <v>2012</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
         <v>14</v>
-      </c>
-      <c r="H19" t="s">
-        <v>15</v>
       </c>
       <c r="I19" s="16">
         <v>46108</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B20">
         <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D20">
         <v>2017</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I20" s="16">
         <v>46094</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="30">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B21">
         <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D21">
         <v>2017</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" t="s">
         <v>14</v>
-      </c>
-      <c r="G21" t="s">
-        <v>35</v>
-      </c>
-      <c r="H21" t="s">
-        <v>15</v>
       </c>
       <c r="I21" s="16">
         <v>46108</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9">
       <c r="E22" s="1"/>
       <c r="I22" s="16"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24">
-        <v>122</v>
-      </c>
-      <c r="C24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24">
-        <v>2015</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F24" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" t="s">
-        <v>52</v>
-      </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="16">
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9">
+      <c r="E24" s="1"/>
+      <c r="I24" s="16"/>
+    </row>
+    <row r="25" spans="1:9">
       <c r="E25" s="1"/>
       <c r="I25" s="16"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="30">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B26">
         <v>134</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D26">
         <v>2019</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I26" s="16">
         <v>46094</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B27">
         <v>137</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D27">
         <v>2017</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I27" s="16">
         <v>46108</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B28">
         <v>138</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D28">
         <v>2017</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I28" s="16">
         <v>46108</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B29">
         <v>136</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D29">
         <v>2017</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
         <v>14</v>
-      </c>
-      <c r="H29" t="s">
-        <v>15</v>
       </c>
       <c r="I29" s="16">
         <v>46108</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9">
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:5">
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:5">
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="5:5">
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:5">
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="5:5">
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="5:5">
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="5:5">
       <c r="E39" s="1"/>
     </row>
   </sheetData>
@@ -2402,7 +2467,7 @@
       <formula1>0</formula1>
       <formula2>2000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F19 F21:F22 F24:F25" xr:uid="{B98105AE-173E-4A15-99FD-BB956E15C3C9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F19 F21:F22 F25" xr:uid="{B98105AE-173E-4A15-99FD-BB956E15C3C9}">
       <formula1>"Included, Not Included"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2415,30 +2480,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEA6183-B753-401C-B21E-C502785DFA3D}">
-  <dimension ref="A1:G63"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G59"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="2" width="7.5546875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5546875" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
+      <c r="A1" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2461,160 +2526,160 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B3" s="13">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" s="5">
         <v>2015</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" s="7">
         <v>46000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B4" s="14">
         <v>2</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" s="9">
         <v>2015</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4" s="11">
         <v>46000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B5" s="13">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D5" s="5">
         <v>2015</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" s="7">
         <v>46094</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="45">
       <c r="A6" s="8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B6" s="14">
         <v>4</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6" s="9">
         <v>2015</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6" s="11">
         <v>46115</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B7" s="13">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D7" s="5">
         <v>2015</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G7" s="7">
         <v>46000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30">
       <c r="A8" s="8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B8" s="14">
         <v>6</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D8" s="9">
         <v>2015</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G8" s="11">
         <v>46057</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B9" s="13">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D9" s="5">
         <v>2015</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G9" s="7">
         <v>46000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" s="8"/>
       <c r="B10" s="14"/>
       <c r="C10" s="9"/>
@@ -2623,328 +2688,328 @@
       <c r="F10" s="9"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B11" s="13">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D11" s="5">
         <v>2015</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11" s="7">
         <v>46000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="60">
       <c r="A12" s="8" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B12" s="14">
         <v>12</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D12" s="9">
         <v>2016</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G12" s="11">
         <v>46000</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" s="8" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B13" s="14">
         <v>14</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D13" s="9">
         <v>2016</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G13" s="11">
         <v>46000</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B14" s="13">
         <v>18</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D14" s="5">
         <v>2016</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G14" s="7">
         <v>46000</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" s="8" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B15" s="14">
         <v>19</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D15" s="9">
         <v>2016</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G15" s="11">
         <v>46000</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B16" s="13">
         <v>20</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D16" s="5">
         <v>2016</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G16" s="7">
         <v>46000</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B17" s="14">
         <v>21</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D17" s="9">
         <v>2016</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G17" s="11">
         <v>46000</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B18" s="13">
         <v>23</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D18" s="5">
         <v>2016</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G18" s="7">
         <v>46057</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19" s="8" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B19" s="14">
         <v>24</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D19" s="9">
         <v>2016</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G19" s="11">
         <v>46000</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B20" s="13">
         <v>25</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D20" s="5">
         <v>2016</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G20" s="7">
         <v>46000</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21" s="8" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B21" s="14">
         <v>27</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D21" s="9">
         <v>2016</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G21" s="11">
         <v>46000</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B22" s="13">
         <v>28</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D22" s="5">
         <v>2013</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G22" s="7">
         <v>46000</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23" s="8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B23" s="14">
         <v>31</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D23" s="9">
         <v>2017</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G23" s="11">
         <v>46132</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B24" s="13">
         <v>32</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D24" s="5">
         <v>2013</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G24" s="7">
         <v>46052</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B25" s="14">
         <v>33</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D25" s="9">
         <v>2013</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G25" s="11">
         <v>46000</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26" s="4"/>
       <c r="B26" s="13"/>
       <c r="C26" s="5"/>
@@ -2953,700 +3018,645 @@
       <c r="F26" s="5"/>
       <c r="G26" s="7"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B27" s="14">
         <v>37</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D27" s="9">
         <v>2013</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G27" s="11">
         <v>46122</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B28" s="13">
         <v>38</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D28" s="5">
         <v>2009</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G28" s="7">
         <v>46000</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B30" s="14">
         <v>41</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D30" s="9">
         <v>2012</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G30" s="11">
         <v>46073</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31" s="8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B31" s="14">
         <v>42</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D31" s="9">
         <v>2017</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G31" s="11">
         <v>46000</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32" s="8" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B32" s="14">
         <v>43</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D32" s="9">
         <v>2014</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G32" s="11">
         <v>46000</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33" s="8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B33" s="14">
         <v>44</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D33" s="9">
         <v>2017</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G33" s="11">
         <v>46000</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34" s="8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B34" s="14">
         <v>45</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D34" s="9">
         <v>2017</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G34" s="11">
         <v>46000</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35" s="8" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B35" s="14">
         <v>46</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D35" s="9">
         <v>2020</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G35" s="11">
         <v>46000</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B36" s="12">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D36">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="E36" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G36" s="16">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B37" s="12">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C37" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D37">
-        <v>2013</v>
-      </c>
-      <c r="E37" t="s">
-        <v>79</v>
+        <v>2014</v>
       </c>
       <c r="F37" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G37" s="16">
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B38" s="12">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C38" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="D38">
         <v>2014</v>
       </c>
       <c r="F38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G38" s="16">
-        <v>46001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B39" s="12">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="C39" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="D39">
+        <v>2013</v>
+      </c>
+      <c r="E39" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="16">
+        <v>46057</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="12">
+        <v>102</v>
+      </c>
+      <c r="C40" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40">
+        <v>2018</v>
+      </c>
+      <c r="E40" t="s">
+        <v>78</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" s="16">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="G41" s="16"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>74</v>
+      </c>
+      <c r="B42" s="12">
+        <v>104</v>
+      </c>
+      <c r="C42" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42">
         <v>2014</v>
       </c>
-      <c r="F39" t="s">
-        <v>21</v>
-      </c>
-      <c r="G39" s="16">
-        <v>46031</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>66</v>
-      </c>
-      <c r="B40" s="12">
-        <v>35</v>
-      </c>
-      <c r="C40" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40">
-        <v>2013</v>
-      </c>
-      <c r="E40" t="s">
-        <v>83</v>
-      </c>
-      <c r="F40" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" s="16">
-        <v>46057</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>84</v>
-      </c>
-      <c r="B41" s="12">
-        <v>102</v>
-      </c>
-      <c r="C41" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41">
-        <v>2018</v>
-      </c>
-      <c r="E41" t="s">
-        <v>85</v>
-      </c>
-      <c r="F41" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" s="16">
-        <v>46122</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G42" s="16"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F42" t="s">
+        <v>20</v>
+      </c>
+      <c r="G42" s="16">
+        <v>46066</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B43" s="12">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C43" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D43">
         <v>2014</v>
       </c>
       <c r="F43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G43" s="16">
         <v>46066</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B44" s="12">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C44" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D44">
         <v>2014</v>
       </c>
       <c r="F44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G44" s="16">
         <v>46066</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B45" s="12">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C45" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="D45">
         <v>2014</v>
       </c>
+      <c r="E45" t="s">
+        <v>56</v>
+      </c>
       <c r="F45" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G45" s="16">
-        <v>46066</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B46" s="12">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D46">
         <v>2014</v>
       </c>
       <c r="E46" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G46" s="16">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B47" s="12">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D47">
-        <v>2014</v>
-      </c>
-      <c r="E47" t="s">
-        <v>87</v>
+        <v>2018</v>
       </c>
       <c r="F47" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G47" s="16">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B48" s="12">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
-        <v>37</v>
-      </c>
-      <c r="D48">
-        <v>2018</v>
+        <v>83</v>
       </c>
       <c r="F48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G48" s="16">
         <v>46092</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    <row r="49" spans="1:7">
+      <c r="G49" s="16"/>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>84</v>
+      </c>
+      <c r="B50" s="12">
+        <v>128</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50">
+        <v>2018</v>
+      </c>
+      <c r="F50" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="16">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>85</v>
+      </c>
+      <c r="B51" s="12">
+        <v>130</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51">
+        <v>2015</v>
+      </c>
+      <c r="E51" t="s">
+        <v>86</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="16">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52" s="12">
+        <v>132</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52">
+        <v>2020</v>
+      </c>
+      <c r="E52" t="s">
+        <v>88</v>
+      </c>
+      <c r="F52" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" s="16">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
         <v>89</v>
       </c>
-      <c r="B49" s="12">
-        <v>112</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="B53" s="12">
+        <v>133</v>
+      </c>
+      <c r="C53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53">
+        <v>2019</v>
+      </c>
+      <c r="E53" t="s">
         <v>90</v>
       </c>
-      <c r="F49" t="s">
-        <v>21</v>
-      </c>
-      <c r="G49" s="16">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G50" s="16"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="F53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" s="16">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
         <v>91</v>
       </c>
-      <c r="B51" s="12">
-        <v>128</v>
-      </c>
-      <c r="C51" t="s">
-        <v>12</v>
-      </c>
-      <c r="D51">
+      <c r="B54" s="12">
+        <v>135</v>
+      </c>
+      <c r="C54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54">
+        <v>2016</v>
+      </c>
+      <c r="F54" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" s="16">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" s="12">
+        <v>139</v>
+      </c>
+      <c r="C55" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55">
         <v>2018</v>
       </c>
-      <c r="F51" t="s">
-        <v>21</v>
-      </c>
-      <c r="G51" s="16">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="F55" t="s">
+        <v>20</v>
+      </c>
+      <c r="G55" s="16">
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="12">
+        <v>142</v>
+      </c>
+      <c r="C56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56">
+        <v>2013</v>
+      </c>
+      <c r="E56" t="s">
         <v>92</v>
       </c>
-      <c r="B52" s="12">
-        <v>129</v>
-      </c>
-      <c r="C52" t="s">
-        <v>12</v>
-      </c>
-      <c r="D52">
-        <v>2017</v>
-      </c>
-      <c r="F52" t="s">
-        <v>15</v>
-      </c>
-      <c r="G52" s="16">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="F56" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" s="16">
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
         <v>93</v>
       </c>
-      <c r="B53" s="12">
-        <v>130</v>
-      </c>
-      <c r="C53" t="s">
-        <v>12</v>
-      </c>
-      <c r="D53">
-        <v>2015</v>
-      </c>
-      <c r="E53" t="s">
-        <v>94</v>
-      </c>
-      <c r="F53" t="s">
-        <v>15</v>
-      </c>
-      <c r="G53" s="16">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>95</v>
-      </c>
-      <c r="B54" s="12">
-        <v>131</v>
-      </c>
-      <c r="C54" t="s">
-        <v>12</v>
-      </c>
-      <c r="D54">
+      <c r="B57" s="12">
+        <v>143</v>
+      </c>
+      <c r="C57" t="s">
+        <v>26</v>
+      </c>
+      <c r="D57">
         <v>2019</v>
       </c>
-      <c r="E54" t="s">
-        <v>96</v>
-      </c>
-      <c r="F54" t="s">
-        <v>15</v>
-      </c>
-      <c r="G54" s="16">
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>97</v>
-      </c>
-      <c r="B55" s="12">
-        <v>132</v>
-      </c>
-      <c r="C55" t="s">
-        <v>12</v>
-      </c>
-      <c r="D55">
-        <v>2020</v>
-      </c>
-      <c r="E55" t="s">
-        <v>98</v>
-      </c>
-      <c r="F55" t="s">
-        <v>15</v>
-      </c>
-      <c r="G55" s="16">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>99</v>
-      </c>
-      <c r="B56" s="12">
-        <v>133</v>
-      </c>
-      <c r="C56" t="s">
-        <v>12</v>
-      </c>
-      <c r="D56">
+      <c r="F57" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" s="16">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>93</v>
+      </c>
+      <c r="B58" s="12">
+        <v>144</v>
+      </c>
+      <c r="C58" t="s">
+        <v>26</v>
+      </c>
+      <c r="D58">
         <v>2019</v>
       </c>
-      <c r="E56" t="s">
-        <v>96</v>
-      </c>
-      <c r="F56" t="s">
-        <v>15</v>
-      </c>
-      <c r="G56" s="16">
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>100</v>
-      </c>
-      <c r="B57" s="12">
-        <v>135</v>
-      </c>
-      <c r="C57" t="s">
-        <v>12</v>
-      </c>
-      <c r="D57">
-        <v>2016</v>
-      </c>
-      <c r="F57" t="s">
-        <v>21</v>
-      </c>
-      <c r="G57" s="16">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>75</v>
-      </c>
-      <c r="B58" s="12">
-        <v>139</v>
-      </c>
-      <c r="C58" t="s">
-        <v>12</v>
-      </c>
-      <c r="D58">
-        <v>2018</v>
-      </c>
       <c r="F58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G58" s="16">
-        <v>46115</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>66</v>
-      </c>
-      <c r="B59" s="12">
-        <v>142</v>
-      </c>
-      <c r="C59" t="s">
-        <v>12</v>
-      </c>
-      <c r="D59">
-        <v>2013</v>
-      </c>
-      <c r="E59" t="s">
-        <v>101</v>
-      </c>
-      <c r="F59" t="s">
-        <v>15</v>
-      </c>
-      <c r="G59" s="16">
-        <v>46115</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>102</v>
-      </c>
-      <c r="B60" s="12">
-        <v>39</v>
-      </c>
-      <c r="C60" t="s">
-        <v>28</v>
-      </c>
-      <c r="D60">
-        <v>2018</v>
-      </c>
-      <c r="E60" t="s">
-        <v>103</v>
-      </c>
-      <c r="F60" t="s">
-        <v>15</v>
-      </c>
-      <c r="G60" s="16">
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G61" s="16"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G62" s="16"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G63" s="16"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="G59" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:G28 A30:G59 B60:G60 A61:G63">
-    <cfRule type="expression" dxfId="17" priority="1">
+  <conditionalFormatting sqref="A3:G28 A30:G59">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="33" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F44:F46 F49:F63 F3:F28 F30:F39" xr:uid="{6630553F-92E4-427F-9784-13858DB7D720}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F43:F45 F3:F28 F30:F38 F48:F59" xr:uid="{6630553F-92E4-427F-9784-13858DB7D720}">
       <formula1>"Not Started,In Progress,Scrapped,Unknown"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3661,33 +3671,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F948288C-1730-49D1-BD4C-FC704F167D22}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.109375" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5546875" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
+      <c r="A1" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3716,149 +3726,149 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B3">
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>2011</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" s="16">
         <v>46001</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B4">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>2011</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I4" s="16">
         <v>46001</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:5">
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:5">
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:5">
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:5">
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:5">
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:5">
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:5">
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="5:5">
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="5:5">
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="5:5">
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:5">
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="5:5">
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="5:5">
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="5:5">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="5:5">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="5:5">
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:5">
       <c r="E33" s="1"/>
     </row>
   </sheetData>
@@ -3889,111 +3899,111 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFE86381-3E33-4CB8-A62B-E48A74AB9667}">
-  <dimension ref="A1:M36"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M44"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.28515625" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="17.109375" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.109375" customWidth="1"/>
-    <col min="11" max="11" width="18.6640625" style="19" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" style="19" customWidth="1"/>
+    <col min="12" max="12" width="21.28515625" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-    </row>
-    <row r="2" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13">
+      <c r="A1" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="L2" t="s">
         <v>110</v>
-      </c>
-      <c r="D2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J2" t="s">
-        <v>117</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="L2" t="s">
-        <v>119</v>
       </c>
       <c r="M2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D3">
         <v>2013</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I3">
         <v>256</v>
       </c>
       <c r="J3" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K3" s="19">
         <v>100</v>
@@ -4003,36 +4013,36 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D4">
         <v>2017</v>
       </c>
       <c r="E4" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F4" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G4">
         <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I4">
         <v>256</v>
       </c>
       <c r="J4" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K4" s="19">
         <v>200</v>
@@ -4042,36 +4052,36 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D5">
         <v>2018</v>
       </c>
       <c r="E5" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="F5" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G5">
         <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I5">
         <v>256</v>
       </c>
       <c r="J5" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K5" s="19">
         <v>175</v>
@@ -4081,39 +4091,39 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13">
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D7">
         <v>2018</v>
       </c>
       <c r="E7" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F7" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G7">
         <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I7">
         <v>256</v>
       </c>
       <c r="J7" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K7" s="19">
         <v>175</v>
@@ -4123,36 +4133,36 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D8">
         <v>2018</v>
       </c>
       <c r="E8" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="F8" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G8">
         <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I8">
         <v>256</v>
       </c>
       <c r="J8" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K8" s="19">
         <v>175</v>
@@ -4162,36 +4172,36 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D9">
         <v>2018</v>
       </c>
       <c r="E9" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="F9" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G9">
         <v>8</v>
       </c>
       <c r="H9" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I9">
         <v>256</v>
       </c>
       <c r="J9" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K9" s="19">
         <v>150</v>
@@ -4201,39 +4211,39 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13">
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D11">
         <v>2020</v>
       </c>
       <c r="E11" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="F11" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G11">
         <v>8</v>
       </c>
       <c r="H11" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I11">
         <v>256</v>
       </c>
       <c r="J11" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K11" s="19">
         <v>300</v>
@@ -4243,36 +4253,36 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D12">
         <v>2014</v>
       </c>
       <c r="E12" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="F12" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G12">
         <v>8</v>
       </c>
       <c r="H12" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I12">
         <v>256</v>
       </c>
       <c r="J12" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K12" s="2">
         <v>175</v>
@@ -4281,36 +4291,36 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D13">
         <v>2018</v>
       </c>
       <c r="E13" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="F13" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G13">
         <v>8</v>
       </c>
       <c r="H13" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I13">
         <v>256</v>
       </c>
       <c r="J13" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K13" s="19">
         <v>120</v>
@@ -4320,36 +4330,36 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15" customHeight="1">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D14">
         <v>2018</v>
       </c>
       <c r="E14" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="F14" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G14">
         <v>8</v>
       </c>
       <c r="H14" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I14">
         <v>256</v>
       </c>
       <c r="J14" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K14" s="19">
         <v>175</v>
@@ -4359,36 +4369,36 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="15" customHeight="1">
       <c r="A15" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D15">
         <v>2013</v>
       </c>
       <c r="E15" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="F15" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G15">
         <v>8</v>
       </c>
       <c r="H15" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I15">
         <v>256</v>
       </c>
       <c r="J15" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K15" s="19">
         <v>150</v>
@@ -4398,36 +4408,36 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="15" customHeight="1">
       <c r="A16" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D16">
         <v>2019</v>
       </c>
       <c r="E16" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="F16" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G16">
         <v>8</v>
       </c>
       <c r="H16" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I16">
         <v>256</v>
       </c>
       <c r="J16" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K16" s="19">
         <v>265</v>
@@ -4437,36 +4447,36 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="15" customHeight="1">
       <c r="A17" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D17">
         <v>2014</v>
       </c>
       <c r="E17" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F17" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G17">
         <v>8</v>
       </c>
       <c r="H17" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I17">
         <v>256</v>
       </c>
       <c r="J17" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K17" s="19">
         <v>100</v>
@@ -4476,36 +4486,36 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="15" customHeight="1">
       <c r="A18" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D18">
         <v>2019</v>
       </c>
       <c r="E18" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F18" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G18">
         <v>8</v>
       </c>
       <c r="H18" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I18">
         <v>256</v>
       </c>
       <c r="J18" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K18" s="19">
         <v>300</v>
@@ -4515,36 +4525,36 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="15" customHeight="1">
       <c r="A19" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D19">
         <v>2019</v>
       </c>
       <c r="E19" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F19" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G19">
         <v>8</v>
       </c>
       <c r="H19" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I19">
         <v>256</v>
       </c>
       <c r="J19" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K19" s="19">
         <v>300</v>
@@ -4554,36 +4564,36 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="15" customHeight="1">
       <c r="A20" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D20">
         <v>2021</v>
       </c>
       <c r="E20" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="F20" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G20">
         <v>8</v>
       </c>
       <c r="H20" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I20">
         <v>256</v>
       </c>
       <c r="J20" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K20" s="19">
         <v>350</v>
@@ -4593,36 +4603,36 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="15" customHeight="1">
       <c r="A21" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D21">
         <v>2021</v>
       </c>
       <c r="E21" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="F21" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G21">
         <v>8</v>
       </c>
       <c r="H21" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I21">
         <v>256</v>
       </c>
       <c r="J21" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K21" s="19">
         <v>350</v>
@@ -4632,36 +4642,36 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="15" customHeight="1">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D22">
         <v>2016</v>
       </c>
       <c r="E22" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F22" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G22">
         <v>16</v>
       </c>
       <c r="H22" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I22">
         <v>256</v>
       </c>
       <c r="J22" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K22" s="19">
         <v>255</v>
@@ -4671,36 +4681,36 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="15" customHeight="1">
       <c r="A23" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D23">
         <v>2019</v>
       </c>
       <c r="E23" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F23" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G23">
         <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I23">
         <v>256</v>
       </c>
       <c r="J23" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K23" s="19">
         <v>300</v>
@@ -4710,36 +4720,36 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="15" customHeight="1">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D24">
         <v>2015</v>
       </c>
       <c r="E24" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F24" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G24">
         <v>16</v>
       </c>
       <c r="H24" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I24">
         <v>256</v>
       </c>
       <c r="J24" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K24" s="19">
         <v>255</v>
@@ -4749,36 +4759,36 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="15" customHeight="1">
       <c r="A25" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D25">
         <v>2018</v>
       </c>
       <c r="E25" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="F25" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G25">
         <v>8</v>
       </c>
       <c r="H25" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I25">
         <v>256</v>
       </c>
       <c r="J25" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K25" s="19">
         <v>175</v>
@@ -4788,36 +4798,36 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="15" customHeight="1">
       <c r="A26" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D26">
         <v>2017</v>
       </c>
       <c r="E26" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F26" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G26">
         <v>8</v>
       </c>
       <c r="H26" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I26">
         <v>256</v>
       </c>
       <c r="J26" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K26" s="19">
         <v>150</v>
@@ -4827,36 +4837,36 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="15" customHeight="1">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D27">
         <v>2017</v>
       </c>
       <c r="E27" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F27" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G27">
         <v>8</v>
       </c>
       <c r="H27" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I27">
         <v>256</v>
       </c>
       <c r="J27" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K27" s="19">
         <v>200</v>
@@ -4866,36 +4876,36 @@
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="15" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="31" t="s">
-        <v>28</v>
+        <v>61</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D28">
         <v>2013</v>
       </c>
       <c r="E28" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="F28" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G28">
         <v>8</v>
       </c>
       <c r="H28" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I28">
         <v>256</v>
       </c>
       <c r="J28" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K28" s="19">
         <v>200</v>
@@ -4905,36 +4915,36 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" ht="15" customHeight="1">
       <c r="A29" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D29">
         <v>2018</v>
       </c>
       <c r="E29" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="F29" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G29">
         <v>16</v>
       </c>
       <c r="H29" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I29">
         <v>256</v>
       </c>
       <c r="J29" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K29" s="19">
         <v>325</v>
@@ -4944,112 +4954,361 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="15" customHeight="1">
       <c r="A30" s="25" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D30">
         <v>2016</v>
       </c>
       <c r="E30" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F30" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G30">
         <v>8</v>
       </c>
       <c r="H30" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I30">
         <v>256</v>
       </c>
       <c r="J30" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K30" s="19">
         <v>200</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="M30">
         <v>127</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L31" s="1"/>
-    </row>
-    <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" ht="15" customHeight="1">
+      <c r="A31" t="s">
+        <v>155</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>2015</v>
+      </c>
+      <c r="E31" t="s">
+        <v>156</v>
+      </c>
+      <c r="F31" t="s">
+        <v>114</v>
+      </c>
+      <c r="G31">
+        <v>8</v>
+      </c>
+      <c r="H31" t="s">
+        <v>157</v>
+      </c>
+      <c r="I31">
+        <v>256</v>
+      </c>
+      <c r="J31" t="s">
+        <v>116</v>
+      </c>
+      <c r="L31" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15" customHeight="1">
+      <c r="A32" t="s">
+        <v>158</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32">
+        <v>2018</v>
+      </c>
+      <c r="E32" t="s">
+        <v>159</v>
+      </c>
+      <c r="F32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G32">
+        <v>8</v>
+      </c>
+      <c r="H32" t="s">
+        <v>122</v>
+      </c>
+      <c r="I32">
+        <v>256</v>
+      </c>
+      <c r="J32" t="s">
+        <v>116</v>
+      </c>
+      <c r="K32" s="19">
+        <f>_xlfn.SINGLE(200)</f>
+        <v>200</v>
+      </c>
       <c r="L32" s="1"/>
-    </row>
-    <row r="33" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M32">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15" customHeight="1">
+      <c r="A33" t="s">
+        <v>160</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33">
+        <v>2017</v>
+      </c>
+      <c r="E33" t="s">
+        <v>161</v>
+      </c>
+      <c r="F33" t="s">
+        <v>129</v>
+      </c>
+      <c r="G33">
+        <v>16</v>
+      </c>
+      <c r="H33" t="s">
+        <v>122</v>
+      </c>
+      <c r="I33">
+        <v>256</v>
+      </c>
+      <c r="J33" t="s">
+        <v>116</v>
+      </c>
       <c r="L33" s="1"/>
-    </row>
-    <row r="36" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="26"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="30"/>
+      <c r="M33">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15" customHeight="1">
+      <c r="A34" t="s">
+        <v>162</v>
+      </c>
+      <c r="B34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D34">
+        <v>2019</v>
+      </c>
+      <c r="E34" t="s">
+        <v>163</v>
+      </c>
+      <c r="F34" t="s">
+        <v>129</v>
+      </c>
+      <c r="G34">
+        <v>16</v>
+      </c>
+      <c r="H34" t="s">
+        <v>122</v>
+      </c>
+      <c r="I34">
+        <v>256</v>
+      </c>
+      <c r="J34" t="s">
+        <v>116</v>
+      </c>
+      <c r="L34" s="1"/>
+      <c r="M34">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15" customHeight="1">
+      <c r="A35" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35">
+        <v>2017</v>
+      </c>
+      <c r="E35" t="s">
+        <v>165</v>
+      </c>
+      <c r="F35" t="s">
+        <v>129</v>
+      </c>
+      <c r="G35">
+        <v>8</v>
+      </c>
+      <c r="H35" t="s">
+        <v>122</v>
+      </c>
+      <c r="I35">
+        <v>256</v>
+      </c>
+      <c r="J35" t="s">
+        <v>116</v>
+      </c>
+      <c r="L35" s="1"/>
+      <c r="M35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="15" customHeight="1">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D36" s="29">
+        <v>2020</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="F36" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G36" s="30">
+        <v>8</v>
+      </c>
+      <c r="H36" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="I36" s="28">
+        <v>256</v>
+      </c>
+      <c r="J36" t="s">
+        <v>116</v>
+      </c>
+      <c r="L36" s="1"/>
+      <c r="M36">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="15" customHeight="1">
+      <c r="L37" s="1"/>
+    </row>
+    <row r="38" spans="1:13" ht="15" customHeight="1">
+      <c r="L38" s="1"/>
+    </row>
+    <row r="39" spans="1:13" ht="15" customHeight="1">
+      <c r="L39" s="1"/>
+    </row>
+    <row r="40" spans="1:13" ht="15" customHeight="1">
+      <c r="L40" s="1"/>
+    </row>
+    <row r="41" spans="1:13" ht="15" customHeight="1">
+      <c r="L41" s="1"/>
+    </row>
+    <row r="42" spans="1:13" ht="15" customHeight="1">
+      <c r="L42" s="1"/>
+    </row>
+    <row r="43" spans="1:13" ht="15" customHeight="1">
+      <c r="L43" s="1"/>
+    </row>
+    <row r="44" spans="1:13" ht="15" customHeight="1">
+      <c r="L44" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <conditionalFormatting sqref="A27:B28 A30:B30">
-    <cfRule type="expression" dxfId="15" priority="21">
+    <cfRule type="expression" dxfId="30" priority="27">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="22">
+    <cfRule type="expression" dxfId="29" priority="28">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:L9 A11:L14 A15:D15 F15:L15 A16:L25">
-    <cfRule type="expression" dxfId="13" priority="25">
+    <cfRule type="expression" dxfId="28" priority="31">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:M9 A11:M14 A15:D15 F15:M15 A16:M25">
-    <cfRule type="expression" dxfId="12" priority="26">
+    <cfRule type="expression" dxfId="27" priority="32">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:I36">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="26" priority="7">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="25" priority="8">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H29">
-    <cfRule type="expression" dxfId="9" priority="13">
+    <cfRule type="expression" dxfId="24" priority="19">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="14">
+    <cfRule type="expression" dxfId="23" priority="20">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I29">
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" dxfId="22" priority="11">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="21" priority="12">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <conditionalFormatting sqref="A33">
+    <cfRule type="expression" dxfId="20" priority="5">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="6">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A34">
+    <cfRule type="expression" dxfId="18" priority="3">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="4">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35">
+    <cfRule type="expression" dxfId="16" priority="1">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="2">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M12:M25 M3:M4" xr:uid="{BD4480FF-AB8D-4446-AB7A-01C4C2A99ADB}">
       <formula1>1</formula1>
       <formula2>2000</formula2>
@@ -5057,8 +5316,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C4 C13:C21 C23:C25" xr:uid="{23899482-37F4-4DDA-A40C-55EF7962BD79}">
       <formula1>"Desktop,Laptop,Tablet,All-In-One"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36" xr:uid="{C368B9B8-2EFC-4D0F-9393-97EEDF8604DA}">
-      <formula1>"Not Started,In Progress,Scrapped,Unknown"</formula1>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36" xr:uid="{C368B9B8-2EFC-4D0F-9393-97EEDF8604DA}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L31" xr:uid="{B98105AE-173E-4A15-99FD-BB956E15C3C9}">
+      <formula1>"Included, Not Included"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5071,30 +5331,30 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1C144A-BB57-4446-B714-000D1D9FAB4A}">
   <dimension ref="A1:Q59"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.109375" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.33203125" customWidth="1"/>
-    <col min="13" max="13" width="16.88671875" style="16" customWidth="1"/>
-    <col min="14" max="14" width="33.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" style="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.85546875" style="16" customWidth="1"/>
+    <col min="14" max="14" width="33.28515625" style="16" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27.6640625" customWidth="1"/>
-    <col min="17" max="17" width="28.33203125" customWidth="1"/>
+    <col min="16" max="16" width="27.7109375" customWidth="1"/>
+    <col min="17" max="17" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="15" customHeight="1">
       <c r="C1" s="17" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D1" s="18"/>
       <c r="E1" s="18"/>
@@ -5109,57 +5369,57 @@
       <c r="N1" s="22"/>
       <c r="O1" s="18"/>
       <c r="P1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="L2" t="s">
         <v>110</v>
       </c>
-      <c r="D2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J2" t="s">
-        <v>117</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="L2" t="s">
-        <v>119</v>
-      </c>
       <c r="M2" s="16" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N2" s="16" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="P2" s="2">
         <f>SUM(K3:K38)</f>
@@ -5170,15 +5430,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D3">
         <v>2019</v>
@@ -5187,7 +5447,7 @@
         <v>256</v>
       </c>
       <c r="J3" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K3" s="19">
         <v>225</v>
@@ -5197,21 +5457,21 @@
         <v>45970</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>170</v>
-      </c>
       <c r="B4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D4">
         <v>2019</v>
@@ -5220,7 +5480,7 @@
         <v>256</v>
       </c>
       <c r="J4" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K4" s="19">
         <v>225</v>
@@ -5230,21 +5490,21 @@
         <v>45970</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>170</v>
-      </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D5">
         <v>2019</v>
@@ -5253,7 +5513,7 @@
         <v>256</v>
       </c>
       <c r="J5" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K5" s="19">
         <v>225</v>
@@ -5263,21 +5523,21 @@
         <v>45970</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>170</v>
-      </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D6">
         <v>2019</v>
@@ -5286,7 +5546,7 @@
         <v>256</v>
       </c>
       <c r="J6" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K6" s="19">
         <v>225</v>
@@ -5296,21 +5556,21 @@
         <v>45970</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>170</v>
-      </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D7">
         <v>2019</v>
@@ -5319,7 +5579,7 @@
         <v>256</v>
       </c>
       <c r="J7" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K7" s="19">
         <v>225</v>
@@ -5329,21 +5589,21 @@
         <v>45970</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>170</v>
-      </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D8">
         <v>2019</v>
@@ -5352,7 +5612,7 @@
         <v>256</v>
       </c>
       <c r="J8" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K8" s="19">
         <v>225</v>
@@ -5362,21 +5622,21 @@
         <v>45970</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>170</v>
-      </c>
       <c r="B9" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D9">
         <v>2019</v>
@@ -5385,7 +5645,7 @@
         <v>256</v>
       </c>
       <c r="J9" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K9" s="19">
         <v>225</v>
@@ -5395,42 +5655,42 @@
         <v>45970</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D10">
         <v>2018</v>
       </c>
       <c r="E10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F10" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G10">
         <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I10">
         <v>256</v>
       </c>
       <c r="J10" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K10" s="21">
         <v>325</v>
@@ -5440,42 +5700,42 @@
         <v>45999</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D11">
         <v>2015</v>
       </c>
       <c r="E11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F11" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G11">
         <v>8</v>
       </c>
       <c r="H11" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I11">
         <v>256</v>
       </c>
       <c r="J11" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K11" s="19">
         <v>225</v>
@@ -5485,89 +5745,89 @@
         <v>45999</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O11" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D12">
         <v>2014</v>
       </c>
       <c r="E12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F12" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G12">
         <v>8</v>
       </c>
       <c r="H12" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I12">
         <v>256</v>
       </c>
       <c r="J12" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K12" s="19">
         <v>175</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="M12" s="15">
         <v>45999</v>
       </c>
       <c r="N12" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D13">
         <v>2019</v>
       </c>
       <c r="E13" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F13" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G13">
         <v>16</v>
       </c>
       <c r="H13" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I13">
         <v>256</v>
       </c>
       <c r="J13" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K13" s="19">
         <v>325</v>
@@ -5577,42 +5837,42 @@
         <v>45999</v>
       </c>
       <c r="N13" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O13" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D14">
         <v>2018</v>
       </c>
       <c r="E14" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F14" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G14">
         <v>16</v>
       </c>
       <c r="H14" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I14">
         <v>256</v>
       </c>
       <c r="J14" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K14" s="19">
         <v>325</v>
@@ -5622,42 +5882,42 @@
         <v>45999</v>
       </c>
       <c r="N14" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D15">
         <v>2021</v>
       </c>
       <c r="E15" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F15" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G15">
         <v>16</v>
       </c>
       <c r="H15" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I15">
         <v>256</v>
       </c>
       <c r="J15" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K15" s="19">
         <v>205</v>
@@ -5667,277 +5927,277 @@
         <v>45999</v>
       </c>
       <c r="N15" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O15" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D16">
         <v>2012</v>
       </c>
       <c r="E16" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F16" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="I16" s="1">
         <v>64</v>
       </c>
       <c r="J16" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K16" s="19">
         <v>50</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M16" s="15">
         <v>45999</v>
       </c>
       <c r="N16" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O16" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D17">
         <v>2014</v>
       </c>
       <c r="E17" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F17" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G17">
         <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I17">
         <v>128</v>
       </c>
       <c r="J17" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K17" s="19">
         <v>60</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M17" s="15">
         <v>45999</v>
       </c>
       <c r="N17" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O17" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D18">
         <v>2018</v>
       </c>
       <c r="E18" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F18" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G18">
         <v>8</v>
       </c>
       <c r="H18" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I18">
         <v>256</v>
       </c>
-      <c r="J18">
-        <v>256</v>
+      <c r="J18" t="s">
+        <v>116</v>
       </c>
       <c r="K18" s="19">
         <v>250</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="M18" s="16">
         <v>46043</v>
       </c>
       <c r="N18" s="16" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="O18" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D19">
         <v>2013</v>
       </c>
       <c r="E19" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F19" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G19">
         <v>8</v>
       </c>
       <c r="H19" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I19">
         <v>256</v>
       </c>
       <c r="J19" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K19" s="19">
         <v>290</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="M19" s="16">
         <v>46043</v>
       </c>
       <c r="N19" s="16" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="O19" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="45">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D20">
         <v>2016</v>
       </c>
       <c r="E20" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F20" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G20">
         <v>16</v>
       </c>
       <c r="H20" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I20">
         <v>256</v>
       </c>
       <c r="J20" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K20" s="19">
         <v>300</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="M20" s="15">
         <v>46056</v>
       </c>
       <c r="N20" s="15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O20" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D21">
         <v>2013</v>
       </c>
       <c r="E21" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F21" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G21">
         <v>8</v>
       </c>
       <c r="H21" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I21">
         <v>256</v>
       </c>
       <c r="J21" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K21" s="19">
         <v>200</v>
@@ -5947,42 +6207,42 @@
         <v>46056</v>
       </c>
       <c r="N21" s="15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O21" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D22">
         <v>2013</v>
       </c>
       <c r="E22" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F22" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G22">
         <v>8</v>
       </c>
       <c r="H22" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I22">
         <v>256</v>
       </c>
       <c r="J22" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K22" s="19">
         <v>200</v>
@@ -5992,42 +6252,42 @@
         <v>46056</v>
       </c>
       <c r="N22" s="15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O22" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D23">
         <v>2013</v>
       </c>
       <c r="E23" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F23" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G23">
         <v>8</v>
       </c>
       <c r="H23" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I23">
         <v>256</v>
       </c>
       <c r="J23" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K23" s="19">
         <v>200</v>
@@ -6037,42 +6297,42 @@
         <v>46056</v>
       </c>
       <c r="N23" s="15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O23" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D24">
         <v>2013</v>
       </c>
       <c r="E24" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F24" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G24">
         <v>8</v>
       </c>
       <c r="H24" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I24">
         <v>256</v>
       </c>
       <c r="J24" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K24" s="19">
         <v>200</v>
@@ -6082,42 +6342,42 @@
         <v>46056</v>
       </c>
       <c r="N24" s="15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O24" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D25">
         <v>2013</v>
       </c>
       <c r="E25" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F25" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G25">
         <v>16</v>
       </c>
       <c r="H25" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I25">
         <v>256</v>
       </c>
       <c r="J25" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K25" s="19">
         <v>200</v>
@@ -6127,42 +6387,42 @@
         <v>46056</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O25" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D26">
         <v>2016</v>
       </c>
       <c r="E26" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F26" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G26">
         <v>16</v>
       </c>
       <c r="H26" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I26">
         <v>256</v>
       </c>
       <c r="J26" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K26" s="19">
         <v>300</v>
@@ -6172,42 +6432,42 @@
         <v>46056</v>
       </c>
       <c r="N26" s="15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O26" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D27">
         <v>2016</v>
       </c>
       <c r="E27" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F27" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G27">
         <v>8</v>
       </c>
       <c r="H27" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I27">
         <v>256</v>
       </c>
       <c r="J27" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K27" s="19">
         <v>300</v>
@@ -6217,42 +6477,42 @@
         <v>46056</v>
       </c>
       <c r="N27" s="15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O27" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D28">
         <v>2018</v>
       </c>
       <c r="E28" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F28" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G28">
         <v>16</v>
       </c>
       <c r="H28" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I28">
         <v>512</v>
       </c>
       <c r="J28" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K28" s="19">
         <v>445</v>
@@ -6262,42 +6522,42 @@
         <v>46056</v>
       </c>
       <c r="N28" s="15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O28" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D29">
         <v>2018</v>
       </c>
       <c r="E29" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F29" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G29">
         <v>16</v>
       </c>
       <c r="H29" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I29">
         <v>512</v>
       </c>
       <c r="J29" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K29" s="19">
         <v>445</v>
@@ -6307,42 +6567,42 @@
         <v>46056</v>
       </c>
       <c r="N29" s="15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O29" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D30">
         <v>2018</v>
       </c>
       <c r="E30" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F30" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G30">
         <v>8</v>
       </c>
       <c r="H30" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I30">
         <v>256</v>
       </c>
       <c r="J30" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K30" s="19">
         <v>150</v>
@@ -6352,42 +6612,42 @@
         <v>46056</v>
       </c>
       <c r="N30" s="15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O30" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="32" t="s">
-        <v>28</v>
+        <v>58</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D31">
         <v>2016</v>
       </c>
       <c r="E31" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F31" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G31">
         <v>8</v>
       </c>
       <c r="H31" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I31">
         <v>500</v>
       </c>
       <c r="J31" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K31" s="19">
         <v>300</v>
@@ -6397,42 +6657,42 @@
         <v>46058</v>
       </c>
       <c r="N31" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O31" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D32">
         <v>2016</v>
       </c>
       <c r="E32" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F32" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G32">
         <v>8</v>
       </c>
       <c r="H32" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I32">
         <v>256</v>
       </c>
       <c r="J32" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K32" s="19">
         <v>300</v>
@@ -6441,42 +6701,42 @@
         <v>46058</v>
       </c>
       <c r="N32" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O32" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D33">
         <v>2016</v>
       </c>
       <c r="E33" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F33" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G33">
         <v>8</v>
       </c>
       <c r="H33" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I33">
         <v>256</v>
       </c>
       <c r="J33" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K33" s="19">
         <v>300</v>
@@ -6485,42 +6745,42 @@
         <v>46058</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O33" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D34">
         <v>2020</v>
       </c>
       <c r="E34" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F34" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G34">
         <v>16</v>
       </c>
       <c r="H34" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I34">
         <v>512</v>
       </c>
       <c r="J34" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K34" s="19">
         <v>445</v>
@@ -6529,42 +6789,42 @@
         <v>46058</v>
       </c>
       <c r="N34" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O34" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D35">
         <v>2020</v>
       </c>
       <c r="E35" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F35" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G35">
         <v>16</v>
       </c>
       <c r="H35" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I35">
         <v>512</v>
       </c>
       <c r="J35" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K35" s="19">
         <v>445</v>
@@ -6573,42 +6833,42 @@
         <v>46058</v>
       </c>
       <c r="N35" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D36">
         <v>2020</v>
       </c>
       <c r="E36" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F36" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G36">
         <v>16</v>
       </c>
       <c r="H36" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I36">
         <v>512</v>
       </c>
       <c r="J36" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K36" s="19">
         <v>445</v>
@@ -6617,42 +6877,42 @@
         <v>46058</v>
       </c>
       <c r="N36" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O36" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D37">
         <v>2020</v>
       </c>
       <c r="E37" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F37" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G37">
         <v>16</v>
       </c>
       <c r="H37" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I37">
         <v>512</v>
       </c>
       <c r="J37" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K37" s="19">
         <v>445</v>
@@ -6661,42 +6921,42 @@
         <v>46058</v>
       </c>
       <c r="N37" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O37" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D38">
         <v>2020</v>
       </c>
       <c r="E38" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F38" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G38">
         <v>16</v>
       </c>
       <c r="H38" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I38">
         <v>512</v>
       </c>
       <c r="J38" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K38" s="19">
         <v>445</v>
@@ -6705,42 +6965,42 @@
         <v>46058</v>
       </c>
       <c r="N38" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O38" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D39">
         <v>2020</v>
       </c>
       <c r="E39" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F39" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G39">
         <v>16</v>
       </c>
       <c r="H39" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I39">
         <v>512</v>
       </c>
       <c r="J39" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K39" s="19">
         <v>445</v>
@@ -6749,42 +7009,42 @@
         <v>46058</v>
       </c>
       <c r="N39" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O39" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="15" customHeight="1">
       <c r="A40" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D40">
         <v>2020</v>
       </c>
       <c r="E40" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F40" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G40">
         <v>16</v>
       </c>
       <c r="H40" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I40">
         <v>512</v>
       </c>
       <c r="J40" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K40" s="19">
         <v>445</v>
@@ -6793,42 +7053,42 @@
         <v>46058</v>
       </c>
       <c r="N40" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O40" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="15" customHeight="1">
       <c r="A41" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D41">
         <v>2020</v>
       </c>
       <c r="E41" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F41" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G41">
         <v>16</v>
       </c>
       <c r="H41" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I41">
         <v>512</v>
       </c>
       <c r="J41" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K41" s="19">
         <v>445</v>
@@ -6837,42 +7097,42 @@
         <v>46058</v>
       </c>
       <c r="N41" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O41" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="15" customHeight="1">
       <c r="A42" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D42">
         <v>2020</v>
       </c>
       <c r="E42" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F42" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G42">
         <v>16</v>
       </c>
       <c r="H42" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I42">
         <v>512</v>
       </c>
       <c r="J42" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K42" s="19">
         <v>445</v>
@@ -6881,42 +7141,42 @@
         <v>46058</v>
       </c>
       <c r="N42" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O42" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="15" customHeight="1">
       <c r="A43" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D43">
         <v>2018</v>
       </c>
       <c r="E43" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F43" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G43">
         <v>8</v>
       </c>
       <c r="H43" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I43">
         <v>256</v>
       </c>
       <c r="J43" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K43" s="19">
         <v>300</v>
@@ -6926,42 +7186,42 @@
         <v>46078</v>
       </c>
       <c r="N43" s="16" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="O43" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="15" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B44" s="31" t="s">
-        <v>28</v>
+        <v>58</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="C44" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D44" s="5">
         <v>2016</v>
       </c>
       <c r="E44" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F44" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G44">
         <v>8</v>
       </c>
       <c r="H44" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I44">
         <v>256</v>
       </c>
       <c r="J44" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K44" s="19">
         <v>300</v>
@@ -6971,80 +7231,120 @@
         <v>46099</v>
       </c>
       <c r="N44" s="16" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="O44" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M45" s="15"/>
-      <c r="N45" s="15"/>
-    </row>
-    <row r="46" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="15" customHeight="1">
+      <c r="A45" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" t="s">
+        <v>216</v>
+      </c>
+      <c r="C45" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45">
+        <v>2014</v>
+      </c>
+      <c r="E45" t="s">
+        <v>217</v>
+      </c>
+      <c r="F45" t="s">
+        <v>218</v>
+      </c>
+      <c r="G45">
+        <v>32</v>
+      </c>
+      <c r="H45" t="s">
+        <v>115</v>
+      </c>
+      <c r="I45">
+        <v>512</v>
+      </c>
+      <c r="J45" t="s">
+        <v>116</v>
+      </c>
+      <c r="K45" s="19">
+        <v>300</v>
+      </c>
+      <c r="M45" s="15">
+        <v>46143</v>
+      </c>
+      <c r="N45" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="O45" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="15" customHeight="1">
       <c r="M46" s="15"/>
       <c r="N46" s="15"/>
     </row>
-    <row r="47" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" ht="15" customHeight="1">
       <c r="M47" s="15"/>
       <c r="N47" s="15"/>
     </row>
-    <row r="48" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" ht="15" customHeight="1">
       <c r="M48" s="15"/>
       <c r="N48" s="15"/>
     </row>
-    <row r="49" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="13:14" ht="15" customHeight="1">
       <c r="M49" s="15"/>
       <c r="N49" s="15"/>
     </row>
-    <row r="50" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="13:14" ht="15" customHeight="1">
       <c r="M50" s="15"/>
       <c r="N50" s="15"/>
     </row>
-    <row r="51" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="13:14" ht="15" customHeight="1">
       <c r="M51" s="15"/>
       <c r="N51" s="15"/>
     </row>
-    <row r="52" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="13:14" ht="15" customHeight="1">
       <c r="M52" s="15"/>
       <c r="N52" s="15"/>
     </row>
-    <row r="53" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="13:14" ht="15" customHeight="1">
       <c r="M53" s="15"/>
       <c r="N53" s="15"/>
     </row>
-    <row r="54" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="13:14" ht="15" customHeight="1">
       <c r="M54" s="15"/>
       <c r="N54" s="15"/>
     </row>
-    <row r="55" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="13:14" ht="15" customHeight="1">
       <c r="M55" s="15"/>
       <c r="N55" s="15"/>
     </row>
-    <row r="56" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="13:14" ht="15" customHeight="1">
       <c r="M56" s="15"/>
       <c r="N56" s="15"/>
     </row>
-    <row r="57" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="13:14" ht="15" customHeight="1">
       <c r="M57" s="15"/>
       <c r="N57" s="15"/>
     </row>
-    <row r="58" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="13:14" ht="15" customHeight="1">
       <c r="M58" s="15"/>
       <c r="N58" s="15"/>
     </row>
-    <row r="59" spans="13:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="13:14" ht="15" customHeight="1">
       <c r="M59" s="15"/>
       <c r="N59" s="15"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A44:G44 I44:L44">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="11" priority="5">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:G44 I44:N44">
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="10" priority="6">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7052,7 +7352,7 @@
     <cfRule type="expression" priority="7">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="8">
+    <cfRule type="expression" dxfId="9" priority="8">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7060,15 +7360,15 @@
     <cfRule type="expression" priority="3">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:I15">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7091,282 +7391,305 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6146040A-3AF4-440D-9E03-57379B2EC394}">
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-    </row>
-    <row r="2" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
+      <c r="A1" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C2" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D2" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>219</v>
+        <v>226</v>
+      </c>
+      <c r="B3" t="s">
+        <v>227</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="E3" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>220</v>
+        <v>228</v>
+      </c>
+      <c r="B4" t="s">
+        <v>227</v>
       </c>
       <c r="C4">
         <v>7</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="E4" s="2">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B5" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E5" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B6" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E6" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B7" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B8" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C8">
         <v>18</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E8" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E9" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B10" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E10" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C11">
         <v>15</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E11" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>229</v>
       </c>
       <c r="B12" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E12" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>238</v>
+      </c>
+      <c r="B13" t="s">
+        <v>233</v>
+      </c>
+      <c r="C13">
         <v>6</v>
       </c>
-      <c r="D12" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="E12" s="2">
+      <c r="D13" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E13" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>229</v>
-      </c>
-      <c r="B13" t="s">
-        <v>226</v>
-      </c>
-      <c r="C13">
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>238</v>
+      </c>
+      <c r="B14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14">
         <v>3</v>
       </c>
-      <c r="D13" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="E13" s="2">
+      <c r="D14" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E14" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>229</v>
-      </c>
-      <c r="B14" t="s">
-        <v>230</v>
-      </c>
-      <c r="C14">
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>238</v>
+      </c>
+      <c r="B15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C15">
         <v>0</v>
       </c>
-      <c r="D14" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="E14" s="2">
+      <c r="D15" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E15" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>229</v>
-      </c>
-      <c r="B15" t="s">
-        <v>228</v>
-      </c>
-      <c r="C15">
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B16" t="s">
+        <v>236</v>
+      </c>
+      <c r="C16">
         <v>11</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="E15" s="2">
+      <c r="D16" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E16" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>231</v>
-      </c>
-      <c r="B16" t="s">
-        <v>232</v>
-      </c>
-      <c r="C16">
+    <row r="17" spans="1:5" ht="15" customHeight="1">
+      <c r="A17" t="s">
+        <v>239</v>
+      </c>
+      <c r="B17" t="s">
+        <v>240</v>
+      </c>
+      <c r="C17">
         <v>4</v>
       </c>
-      <c r="D16" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="E16" s="2">
+      <c r="D17" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E17" s="2">
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D17" s="23"/>
-    </row>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="15" customHeight="1">
       <c r="D18" s="23"/>
     </row>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="15" customHeight="1">
       <c r="D19" s="23"/>
+    </row>
+    <row r="20" spans="1:5" ht="15" customHeight="1">
+      <c r="D20" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7382,34 +7705,34 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F77F78-0898-4060-A2C7-C1A84336B28A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="33.109375" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="19" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="B1" s="36"/>
+    <row r="1" spans="1:3" ht="15" customHeight="1">
+      <c r="A1" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="B1" s="34"/>
       <c r="C1" s="24"/>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1">
       <c r="A3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -7418,9 +7741,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -7429,9 +7752,9 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="15" customHeight="1">
       <c r="A5" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -7440,9 +7763,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -7451,9 +7774,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="15" customHeight="1">
       <c r="A7" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -7462,9 +7785,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -7473,9 +7796,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -7484,9 +7807,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -7495,9 +7818,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B11">
         <v>14</v>
@@ -7506,9 +7829,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -7517,9 +7840,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="15" customHeight="1">
       <c r="A13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -7528,9 +7851,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="15" customHeight="1">
       <c r="A14" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B14">
         <v>6</v>

--- a/data/OldInventorySystem.xlsx
+++ b/data/OldInventorySystem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rosehulman-my.sharepoint.com/personal/lucasja_rose-hulman_edu/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F93733CB-E6FB-4BA1-B4B3-CC6466AACE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{112BB916-2D75-4BC5-8521-46D837D93EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Laptops" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="254">
   <si>
     <t>LAPTOPS</t>
   </si>
@@ -162,12 +162,6 @@
   </si>
   <si>
     <t>Screen does not turn on but power light does, SSD installed</t>
-  </si>
-  <si>
-    <t>ThinkPad P15s Gen 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> needs Windows updates needs usbc charger</t>
   </si>
   <si>
     <t>Thinkpad S230u</t>
@@ -552,6 +546,9 @@
   </si>
   <si>
     <t>Intel core i5-7500t</t>
+  </si>
+  <si>
+    <t>ThinkPad P15s Gen 1</t>
   </si>
   <si>
     <t>Intel core i5-1210u</t>
@@ -1364,8 +1361,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}" name="In_Progress" displayName="In_Progress" ref="A2:I39">
-  <autoFilter ref="A2:I39" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}" name="In_Progress" displayName="In_Progress" ref="A2:I38">
+  <autoFilter ref="A2:I38" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I16">
     <sortCondition ref="B2:B16"/>
   </sortState>
@@ -1813,7 +1810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5AA6A1-7D43-4966-8813-F497D895A5C2}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.28515625" customWidth="1"/>
@@ -2209,153 +2206,151 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
       </c>
       <c r="D18">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H18" t="s">
         <v>14</v>
       </c>
       <c r="I18" s="16">
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="30">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>42</v>
       </c>
       <c r="B19">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D19">
-        <v>2012</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>43</v>
-      </c>
+        <v>2017</v>
+      </c>
+      <c r="E19" s="1"/>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I19" s="16">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="30">
       <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20">
+        <v>124</v>
+      </c>
+      <c r="C20" t="s">
         <v>44</v>
-      </c>
-      <c r="B20">
-        <v>121</v>
-      </c>
-      <c r="C20" t="s">
-        <v>19</v>
       </c>
       <c r="D20">
         <v>2017</v>
       </c>
-      <c r="E20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
+      <c r="G20" t="s">
+        <v>33</v>
+      </c>
       <c r="H20" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I20" s="16">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="30">
-      <c r="A21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21">
-        <v>124</v>
-      </c>
-      <c r="C21" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21">
-        <v>2017</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" t="s">
-        <v>33</v>
-      </c>
-      <c r="H21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21" s="16">
         <v>46108</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
-      <c r="E22" s="1"/>
-      <c r="I22" s="16"/>
+    <row r="21" spans="1:9">
+      <c r="E21" s="1"/>
+      <c r="I21" s="16"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="E23" s="1"/>
+      <c r="I23" s="16"/>
     </row>
     <row r="24" spans="1:9">
       <c r="E24" s="1"/>
       <c r="I24" s="16"/>
     </row>
-    <row r="25" spans="1:9">
-      <c r="E25" s="1"/>
-      <c r="I25" s="16"/>
-    </row>
-    <row r="26" spans="1:9" ht="30">
+    <row r="25" spans="1:9" ht="30">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25">
+        <v>134</v>
+      </c>
+      <c r="C25" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25">
+        <v>2019</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="16">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>48</v>
       </c>
       <c r="B26">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D26">
-        <v>2019</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>49</v>
-      </c>
+        <v>2017</v>
+      </c>
+      <c r="E26" s="1"/>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H26" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I26" s="16">
-        <v>46094</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B27">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D27">
         <v>2017</v>
@@ -2373,53 +2368,32 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B28">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D28">
         <v>2017</v>
       </c>
-      <c r="E28" s="1"/>
+      <c r="E28" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="F28" t="s">
         <v>13</v>
       </c>
       <c r="H28" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I28" s="16">
         <v>46108</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29">
-        <v>136</v>
-      </c>
-      <c r="C29" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29">
-        <v>2017</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F29" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="16">
-        <v>46108</v>
-      </c>
+      <c r="E29" s="1"/>
     </row>
     <row r="30" spans="1:9">
       <c r="E30" s="1"/>
@@ -2447,9 +2421,6 @@
     </row>
     <row r="38" spans="5:5">
       <c r="E38" s="1"/>
-    </row>
-    <row r="39" spans="5:5">
-      <c r="E39" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2457,17 +2428,17 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H19 H21:H22 H24:H25" xr:uid="{BDBDE7E9-9FC3-44B3-919F-CEEE026A72CD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20:H21 H23:H24 H3:H18" xr:uid="{BDBDE7E9-9FC3-44B3-919F-CEEE026A72CD}">
       <formula1>"Not Started, In Progress, Scrapped, Unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G19 G21:G22 G24:G25" xr:uid="{B3C7309D-E7FF-4409-A545-48D8D2AB8658}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G20:G21 G23:G24 G3:G18" xr:uid="{B3C7309D-E7FF-4409-A545-48D8D2AB8658}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B19 B21:B22 B24:B25" xr:uid="{16B18C16-4889-4A0C-A4CE-D22AA5030E8B}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20:B21 B23:B24 B3:B18" xr:uid="{16B18C16-4889-4A0C-A4CE-D22AA5030E8B}">
       <formula1>0</formula1>
       <formula2>2000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F19 F21:F22 F25" xr:uid="{B98105AE-173E-4A15-99FD-BB956E15C3C9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F20:F21 F24 F3:F18" xr:uid="{B98105AE-173E-4A15-99FD-BB956E15C3C9}">
       <formula1>"Included, Not Included"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2494,7 +2465,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="31" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -2528,7 +2499,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B3" s="13">
         <v>1</v>
@@ -2549,7 +2520,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B4" s="14">
         <v>2</v>
@@ -2570,7 +2541,7 @@
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B5" s="13">
         <v>3</v>
@@ -2582,7 +2553,7 @@
         <v>2015</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>14</v>
@@ -2593,7 +2564,7 @@
     </row>
     <row r="6" spans="1:7" ht="45">
       <c r="A6" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B6" s="14">
         <v>4</v>
@@ -2605,7 +2576,7 @@
         <v>2015</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>14</v>
@@ -2616,7 +2587,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B7" s="13">
         <v>5</v>
@@ -2637,7 +2608,7 @@
     </row>
     <row r="8" spans="1:7" ht="30">
       <c r="A8" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B8" s="14">
         <v>6</v>
@@ -2649,7 +2620,7 @@
         <v>2015</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>14</v>
@@ -2660,7 +2631,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B9" s="13">
         <v>7</v>
@@ -2690,7 +2661,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B11" s="13">
         <v>9</v>
@@ -2711,7 +2682,7 @@
     </row>
     <row r="12" spans="1:7" ht="60">
       <c r="A12" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B12" s="14">
         <v>12</v>
@@ -2723,7 +2694,7 @@
         <v>2016</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>14</v>
@@ -2734,7 +2705,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B13" s="14">
         <v>14</v>
@@ -2746,7 +2717,7 @@
         <v>2016</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>14</v>
@@ -2757,7 +2728,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B14" s="13">
         <v>18</v>
@@ -2778,7 +2749,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B15" s="14">
         <v>19</v>
@@ -2799,7 +2770,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B16" s="13">
         <v>20</v>
@@ -2820,7 +2791,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B17" s="14">
         <v>21</v>
@@ -2841,7 +2812,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B18" s="13">
         <v>23</v>
@@ -2862,7 +2833,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B19" s="14">
         <v>24</v>
@@ -2883,7 +2854,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B20" s="13">
         <v>25</v>
@@ -2904,7 +2875,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B21" s="14">
         <v>27</v>
@@ -2925,7 +2896,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B22" s="13">
         <v>28</v>
@@ -2946,7 +2917,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B23" s="14">
         <v>31</v>
@@ -2958,7 +2929,7 @@
         <v>2017</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>14</v>
@@ -2969,7 +2940,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B24" s="13">
         <v>32</v>
@@ -2990,7 +2961,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B25" s="14">
         <v>33</v>
@@ -3020,7 +2991,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B27" s="14">
         <v>37</v>
@@ -3032,7 +3003,7 @@
         <v>2013</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>14</v>
@@ -3043,7 +3014,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B28" s="13">
         <v>38</v>
@@ -3064,7 +3035,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B30" s="14">
         <v>41</v>
@@ -3076,7 +3047,7 @@
         <v>2012</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>14</v>
@@ -3087,7 +3058,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B31" s="14">
         <v>42</v>
@@ -3108,7 +3079,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B32" s="14">
         <v>43</v>
@@ -3129,7 +3100,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B33" s="14">
         <v>44</v>
@@ -3150,7 +3121,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B34" s="14">
         <v>45</v>
@@ -3171,7 +3142,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B35" s="14">
         <v>46</v>
@@ -3192,7 +3163,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B36" s="12">
         <v>80</v>
@@ -3204,7 +3175,7 @@
         <v>2013</v>
       </c>
       <c r="E36" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F36" t="s">
         <v>14</v>
@@ -3215,7 +3186,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B37" s="12">
         <v>82</v>
@@ -3235,13 +3206,13 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B38" s="12">
         <v>89</v>
       </c>
       <c r="C38" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D38">
         <v>2014</v>
@@ -3255,7 +3226,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B39" s="12">
         <v>35</v>
@@ -3267,7 +3238,7 @@
         <v>2013</v>
       </c>
       <c r="E39" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F39" t="s">
         <v>14</v>
@@ -3278,19 +3249,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B40" s="12">
         <v>102</v>
       </c>
       <c r="C40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D40">
         <v>2018</v>
       </c>
       <c r="E40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F40" t="s">
         <v>14</v>
@@ -3304,13 +3275,13 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B42" s="12">
         <v>104</v>
       </c>
       <c r="C42" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D42">
         <v>2014</v>
@@ -3324,13 +3295,13 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B43" s="12">
         <v>105</v>
       </c>
       <c r="C43" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D43">
         <v>2014</v>
@@ -3344,13 +3315,13 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B44" s="12">
         <v>106</v>
       </c>
       <c r="C44" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D44">
         <v>2014</v>
@@ -3364,7 +3335,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B45" s="12">
         <v>107</v>
@@ -3376,7 +3347,7 @@
         <v>2014</v>
       </c>
       <c r="E45" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
@@ -3387,7 +3358,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B46" s="12">
         <v>109</v>
@@ -3399,7 +3370,7 @@
         <v>2014</v>
       </c>
       <c r="E46" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
@@ -3410,7 +3381,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B47" s="12">
         <v>111</v>
@@ -3430,13 +3401,13 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B48" s="12">
         <v>112</v>
       </c>
       <c r="C48" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F48" t="s">
         <v>20</v>
@@ -3450,7 +3421,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B50" s="12">
         <v>128</v>
@@ -3470,7 +3441,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B51" s="12">
         <v>130</v>
@@ -3482,7 +3453,7 @@
         <v>2015</v>
       </c>
       <c r="E51" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
@@ -3493,7 +3464,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B52" s="12">
         <v>132</v>
@@ -3505,7 +3476,7 @@
         <v>2020</v>
       </c>
       <c r="E52" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F52" t="s">
         <v>14</v>
@@ -3516,7 +3487,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B53" s="12">
         <v>133</v>
@@ -3528,7 +3499,7 @@
         <v>2019</v>
       </c>
       <c r="E53" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F53" t="s">
         <v>14</v>
@@ -3539,7 +3510,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B54" s="12">
         <v>135</v>
@@ -3559,7 +3530,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B55" s="12">
         <v>139</v>
@@ -3579,7 +3550,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B56" s="12">
         <v>142</v>
@@ -3591,7 +3562,7 @@
         <v>2013</v>
       </c>
       <c r="E56" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F56" t="s">
         <v>14</v>
@@ -3602,7 +3573,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B57" s="12">
         <v>143</v>
@@ -3622,7 +3593,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B58" s="12">
         <v>144</v>
@@ -3686,7 +3657,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -3728,7 +3699,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B3">
         <v>74</v>
@@ -3740,13 +3711,13 @@
         <v>2011</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H3" t="s">
         <v>20</v>
@@ -3757,7 +3728,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B4">
         <v>75</v>
@@ -3769,13 +3740,13 @@
         <v>2011</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H4" t="s">
         <v>20</v>
@@ -3918,7 +3889,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
@@ -3935,40 +3906,40 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" t="s">
         <v>101</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>102</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>103</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>104</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>105</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>106</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>108</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="L2" t="s">
-        <v>110</v>
       </c>
       <c r="M2" t="s">
         <v>2</v>
@@ -3976,34 +3947,34 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D3">
         <v>2013</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I3">
         <v>256</v>
       </c>
       <c r="J3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K3" s="19">
         <v>100</v>
@@ -4015,34 +3986,34 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D4">
         <v>2017</v>
       </c>
       <c r="E4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G4">
         <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I4">
         <v>256</v>
       </c>
       <c r="J4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K4" s="19">
         <v>200</v>
@@ -4054,34 +4025,34 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D5">
         <v>2018</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G5">
         <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I5">
         <v>256</v>
       </c>
       <c r="J5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K5" s="19">
         <v>175</v>
@@ -4096,34 +4067,34 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D7">
         <v>2018</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G7">
         <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I7">
         <v>256</v>
       </c>
       <c r="J7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K7" s="19">
         <v>175</v>
@@ -4135,34 +4106,34 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D8">
         <v>2018</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G8">
         <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I8">
         <v>256</v>
       </c>
       <c r="J8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K8" s="19">
         <v>175</v>
@@ -4174,34 +4145,34 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D9">
         <v>2018</v>
       </c>
       <c r="E9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G9">
         <v>8</v>
       </c>
       <c r="H9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I9">
         <v>256</v>
       </c>
       <c r="J9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K9" s="19">
         <v>150</v>
@@ -4216,34 +4187,34 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D11">
         <v>2020</v>
       </c>
       <c r="E11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G11">
         <v>8</v>
       </c>
       <c r="H11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I11">
         <v>256</v>
       </c>
       <c r="J11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K11" s="19">
         <v>300</v>
@@ -4255,34 +4226,34 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D12">
         <v>2014</v>
       </c>
       <c r="E12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G12">
         <v>8</v>
       </c>
       <c r="H12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I12">
         <v>256</v>
       </c>
       <c r="J12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K12" s="2">
         <v>175</v>
@@ -4293,34 +4264,34 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D13">
         <v>2018</v>
       </c>
       <c r="E13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G13">
         <v>8</v>
       </c>
       <c r="H13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I13">
         <v>256</v>
       </c>
       <c r="J13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K13" s="19">
         <v>120</v>
@@ -4332,34 +4303,34 @@
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1">
       <c r="A14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D14">
         <v>2018</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G14">
         <v>8</v>
       </c>
       <c r="H14" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I14">
         <v>256</v>
       </c>
       <c r="J14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K14" s="19">
         <v>175</v>
@@ -4371,34 +4342,34 @@
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1">
       <c r="A15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D15">
         <v>2013</v>
       </c>
       <c r="E15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G15">
         <v>8</v>
       </c>
       <c r="H15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I15">
         <v>256</v>
       </c>
       <c r="J15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K15" s="19">
         <v>150</v>
@@ -4410,34 +4381,34 @@
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1">
       <c r="A16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D16">
         <v>2019</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F16" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G16">
         <v>8</v>
       </c>
       <c r="H16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I16">
         <v>256</v>
       </c>
       <c r="J16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K16" s="19">
         <v>265</v>
@@ -4449,34 +4420,34 @@
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D17">
         <v>2014</v>
       </c>
       <c r="E17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G17">
         <v>8</v>
       </c>
       <c r="H17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I17">
         <v>256</v>
       </c>
       <c r="J17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K17" s="19">
         <v>100</v>
@@ -4488,34 +4459,34 @@
     </row>
     <row r="18" spans="1:13" ht="15" customHeight="1">
       <c r="A18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D18">
         <v>2019</v>
       </c>
       <c r="E18" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F18" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G18">
         <v>8</v>
       </c>
       <c r="H18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I18">
         <v>256</v>
       </c>
       <c r="J18" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K18" s="19">
         <v>300</v>
@@ -4527,34 +4498,34 @@
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1">
       <c r="A19" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D19">
         <v>2019</v>
       </c>
       <c r="E19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G19">
         <v>8</v>
       </c>
       <c r="H19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I19">
         <v>256</v>
       </c>
       <c r="J19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K19" s="19">
         <v>300</v>
@@ -4566,34 +4537,34 @@
     </row>
     <row r="20" spans="1:13" ht="15" customHeight="1">
       <c r="A20" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s">
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D20">
         <v>2021</v>
       </c>
       <c r="E20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F20" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G20">
         <v>8</v>
       </c>
       <c r="H20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I20">
         <v>256</v>
       </c>
       <c r="J20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K20" s="19">
         <v>350</v>
@@ -4605,34 +4576,34 @@
     </row>
     <row r="21" spans="1:13" ht="15" customHeight="1">
       <c r="A21" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B21" t="s">
         <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D21">
         <v>2021</v>
       </c>
       <c r="E21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G21">
         <v>8</v>
       </c>
       <c r="H21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I21">
         <v>256</v>
       </c>
       <c r="J21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K21" s="19">
         <v>350</v>
@@ -4644,34 +4615,34 @@
     </row>
     <row r="22" spans="1:13" ht="15" customHeight="1">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D22">
         <v>2016</v>
       </c>
       <c r="E22" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F22" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G22">
         <v>16</v>
       </c>
       <c r="H22" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I22">
         <v>256</v>
       </c>
       <c r="J22" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K22" s="19">
         <v>255</v>
@@ -4683,34 +4654,34 @@
     </row>
     <row r="23" spans="1:13" ht="15" customHeight="1">
       <c r="A23" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D23">
         <v>2019</v>
       </c>
       <c r="E23" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G23">
         <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I23">
         <v>256</v>
       </c>
       <c r="J23" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K23" s="19">
         <v>300</v>
@@ -4722,34 +4693,34 @@
     </row>
     <row r="24" spans="1:13" ht="15" customHeight="1">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D24">
         <v>2015</v>
       </c>
       <c r="E24" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F24" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G24">
         <v>16</v>
       </c>
       <c r="H24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I24">
         <v>256</v>
       </c>
       <c r="J24" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K24" s="19">
         <v>255</v>
@@ -4761,34 +4732,34 @@
     </row>
     <row r="25" spans="1:13" ht="15" customHeight="1">
       <c r="A25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D25">
         <v>2018</v>
       </c>
       <c r="E25" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G25">
         <v>8</v>
       </c>
       <c r="H25" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I25">
         <v>256</v>
       </c>
       <c r="J25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K25" s="19">
         <v>175</v>
@@ -4800,34 +4771,34 @@
     </row>
     <row r="26" spans="1:13" ht="15" customHeight="1">
       <c r="A26" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D26">
         <v>2017</v>
       </c>
       <c r="E26" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G26">
         <v>8</v>
       </c>
       <c r="H26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I26">
         <v>256</v>
       </c>
       <c r="J26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K26" s="19">
         <v>150</v>
@@ -4839,34 +4810,34 @@
     </row>
     <row r="27" spans="1:13" ht="15" customHeight="1">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D27">
         <v>2017</v>
       </c>
       <c r="E27" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F27" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G27">
         <v>8</v>
       </c>
       <c r="H27" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I27">
         <v>256</v>
       </c>
       <c r="J27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K27" s="19">
         <v>200</v>
@@ -4878,34 +4849,34 @@
     </row>
     <row r="28" spans="1:13" ht="15" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B28" s="26" t="s">
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D28">
         <v>2013</v>
       </c>
       <c r="E28" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F28" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G28">
         <v>8</v>
       </c>
       <c r="H28" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I28">
         <v>256</v>
       </c>
       <c r="J28" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K28" s="19">
         <v>200</v>
@@ -4917,34 +4888,34 @@
     </row>
     <row r="29" spans="1:13" ht="15" customHeight="1">
       <c r="A29" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B29" t="s">
         <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D29">
         <v>2018</v>
       </c>
       <c r="E29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G29">
         <v>16</v>
       </c>
       <c r="H29" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I29">
         <v>256</v>
       </c>
       <c r="J29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K29" s="19">
         <v>325</v>
@@ -4956,40 +4927,40 @@
     </row>
     <row r="30" spans="1:13" ht="15" customHeight="1">
       <c r="A30" s="25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D30">
         <v>2016</v>
       </c>
       <c r="E30" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F30" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G30">
         <v>8</v>
       </c>
       <c r="H30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I30">
         <v>256</v>
       </c>
       <c r="J30" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K30" s="19">
         <v>200</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="M30">
         <v>127</v>
@@ -4997,31 +4968,37 @@
     </row>
     <row r="31" spans="1:13" ht="15" customHeight="1">
       <c r="A31" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B31" t="s">
         <v>11</v>
       </c>
+      <c r="C31" t="s">
+        <v>116</v>
+      </c>
       <c r="D31">
         <v>2015</v>
       </c>
       <c r="E31" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F31" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G31">
         <v>8</v>
       </c>
       <c r="H31" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I31">
         <v>256</v>
       </c>
       <c r="J31" t="s">
-        <v>116</v>
+        <v>114</v>
+      </c>
+      <c r="K31" s="19">
+        <v>175</v>
       </c>
       <c r="L31" t="s">
         <v>23</v>
@@ -5032,34 +5009,34 @@
     </row>
     <row r="32" spans="1:13" ht="15" customHeight="1">
       <c r="A32" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B32" t="s">
         <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D32">
         <v>2018</v>
       </c>
       <c r="E32" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F32" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G32">
         <v>8</v>
       </c>
       <c r="H32" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I32">
         <v>256</v>
       </c>
       <c r="J32" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K32" s="19">
         <f>_xlfn.SINGLE(200)</f>
@@ -5072,34 +5049,37 @@
     </row>
     <row r="33" spans="1:13" ht="15" customHeight="1">
       <c r="A33" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B33" t="s">
         <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D33">
         <v>2017</v>
       </c>
       <c r="E33" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F33" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G33">
         <v>16</v>
       </c>
       <c r="H33" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I33">
         <v>256</v>
       </c>
       <c r="J33" t="s">
-        <v>116</v>
+        <v>114</v>
+      </c>
+      <c r="K33" s="19">
+        <v>200</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33">
@@ -5108,34 +5088,37 @@
     </row>
     <row r="34" spans="1:13" ht="15" customHeight="1">
       <c r="A34" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D34">
         <v>2019</v>
       </c>
       <c r="E34" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G34">
         <v>16</v>
       </c>
       <c r="H34" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I34">
         <v>256</v>
       </c>
       <c r="J34" t="s">
-        <v>116</v>
+        <v>114</v>
+      </c>
+      <c r="K34" s="19">
+        <v>350</v>
       </c>
       <c r="L34" s="1"/>
       <c r="M34">
@@ -5144,34 +5127,37 @@
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1">
       <c r="A35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B35" t="s">
         <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D35">
         <v>2017</v>
       </c>
       <c r="E35" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F35" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G35">
         <v>8</v>
       </c>
       <c r="H35" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I35">
         <v>256</v>
       </c>
       <c r="J35" t="s">
-        <v>116</v>
+        <v>114</v>
+      </c>
+      <c r="K35" s="19">
+        <v>300</v>
       </c>
       <c r="L35" s="1"/>
       <c r="M35">
@@ -5180,34 +5166,37 @@
     </row>
     <row r="36" spans="1:13" ht="15" customHeight="1">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>164</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D36" s="29">
         <v>2020</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G36" s="30">
         <v>8</v>
       </c>
       <c r="H36" s="28" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I36" s="28">
         <v>256</v>
       </c>
       <c r="J36" t="s">
-        <v>116</v>
+        <v>114</v>
+      </c>
+      <c r="K36" s="19">
+        <v>400</v>
       </c>
       <c r="L36" s="1"/>
       <c r="M36">
@@ -5354,7 +5343,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15" customHeight="1">
       <c r="C1" s="17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D1" s="18"/>
       <c r="E1" s="18"/>
@@ -5369,57 +5358,57 @@
       <c r="N1" s="22"/>
       <c r="O1" s="18"/>
       <c r="P1" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q1" t="s">
         <v>168</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" t="s">
         <v>101</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>102</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>103</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>104</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>105</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>106</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>108</v>
       </c>
-      <c r="K2" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="L2" t="s">
-        <v>110</v>
-      </c>
       <c r="M2" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="N2" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="O2" t="s">
         <v>171</v>
-      </c>
-      <c r="O2" t="s">
-        <v>172</v>
       </c>
       <c r="P2" s="2">
         <f>SUM(K3:K38)</f>
@@ -5432,13 +5421,13 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" t="s">
         <v>173</v>
       </c>
-      <c r="B3" t="s">
-        <v>174</v>
-      </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D3">
         <v>2019</v>
@@ -5447,7 +5436,7 @@
         <v>256</v>
       </c>
       <c r="J3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K3" s="19">
         <v>225</v>
@@ -5457,21 +5446,21 @@
         <v>45970</v>
       </c>
       <c r="N3" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="O3" t="s">
         <v>175</v>
-      </c>
-      <c r="O3" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" t="s">
         <v>173</v>
       </c>
-      <c r="B4" t="s">
-        <v>174</v>
-      </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D4">
         <v>2019</v>
@@ -5480,7 +5469,7 @@
         <v>256</v>
       </c>
       <c r="J4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K4" s="19">
         <v>225</v>
@@ -5490,21 +5479,21 @@
         <v>45970</v>
       </c>
       <c r="N4" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="O4" t="s">
         <v>175</v>
-      </c>
-      <c r="O4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" t="s">
         <v>173</v>
       </c>
-      <c r="B5" t="s">
-        <v>174</v>
-      </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D5">
         <v>2019</v>
@@ -5513,7 +5502,7 @@
         <v>256</v>
       </c>
       <c r="J5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K5" s="19">
         <v>225</v>
@@ -5523,21 +5512,21 @@
         <v>45970</v>
       </c>
       <c r="N5" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="O5" t="s">
         <v>175</v>
-      </c>
-      <c r="O5" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" t="s">
         <v>173</v>
       </c>
-      <c r="B6" t="s">
-        <v>174</v>
-      </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D6">
         <v>2019</v>
@@ -5546,7 +5535,7 @@
         <v>256</v>
       </c>
       <c r="J6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K6" s="19">
         <v>225</v>
@@ -5556,21 +5545,21 @@
         <v>45970</v>
       </c>
       <c r="N6" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="O6" t="s">
         <v>175</v>
-      </c>
-      <c r="O6" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" t="s">
         <v>173</v>
       </c>
-      <c r="B7" t="s">
-        <v>174</v>
-      </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D7">
         <v>2019</v>
@@ -5579,7 +5568,7 @@
         <v>256</v>
       </c>
       <c r="J7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K7" s="19">
         <v>225</v>
@@ -5589,21 +5578,21 @@
         <v>45970</v>
       </c>
       <c r="N7" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="O7" t="s">
         <v>175</v>
-      </c>
-      <c r="O7" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" t="s">
         <v>173</v>
       </c>
-      <c r="B8" t="s">
-        <v>174</v>
-      </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D8">
         <v>2019</v>
@@ -5612,7 +5601,7 @@
         <v>256</v>
       </c>
       <c r="J8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K8" s="19">
         <v>225</v>
@@ -5622,21 +5611,21 @@
         <v>45970</v>
       </c>
       <c r="N8" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="O8" t="s">
         <v>175</v>
-      </c>
-      <c r="O8" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" t="s">
         <v>173</v>
       </c>
-      <c r="B9" t="s">
-        <v>174</v>
-      </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D9">
         <v>2019</v>
@@ -5645,7 +5634,7 @@
         <v>256</v>
       </c>
       <c r="J9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K9" s="19">
         <v>225</v>
@@ -5655,42 +5644,42 @@
         <v>45970</v>
       </c>
       <c r="N9" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="O9" t="s">
         <v>175</v>
-      </c>
-      <c r="O9" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D10">
         <v>2018</v>
       </c>
       <c r="E10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G10">
         <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I10">
         <v>256</v>
       </c>
       <c r="J10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K10" s="21">
         <v>325</v>
@@ -5700,42 +5689,42 @@
         <v>45999</v>
       </c>
       <c r="N10" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="O10" t="s">
         <v>175</v>
-      </c>
-      <c r="O10" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
         <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D11">
         <v>2015</v>
       </c>
       <c r="E11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G11">
         <v>8</v>
       </c>
       <c r="H11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I11">
         <v>256</v>
       </c>
       <c r="J11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K11" s="19">
         <v>225</v>
@@ -5745,89 +5734,89 @@
         <v>45999</v>
       </c>
       <c r="N11" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="O11" t="s">
         <v>175</v>
-      </c>
-      <c r="O11" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D12">
         <v>2014</v>
       </c>
       <c r="E12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G12">
         <v>8</v>
       </c>
       <c r="H12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I12">
         <v>256</v>
       </c>
       <c r="J12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K12" s="19">
         <v>175</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M12" s="15">
         <v>45999</v>
       </c>
       <c r="N12" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="O12" t="s">
         <v>175</v>
-      </c>
-      <c r="O12" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D13">
         <v>2019</v>
       </c>
       <c r="E13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G13">
         <v>16</v>
       </c>
       <c r="H13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I13">
         <v>256</v>
       </c>
       <c r="J13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K13" s="19">
         <v>325</v>
@@ -5837,42 +5826,42 @@
         <v>45999</v>
       </c>
       <c r="N13" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="O13" t="s">
         <v>175</v>
-      </c>
-      <c r="O13" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D14">
         <v>2018</v>
       </c>
       <c r="E14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F14" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G14">
         <v>16</v>
       </c>
       <c r="H14" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I14">
         <v>256</v>
       </c>
       <c r="J14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K14" s="19">
         <v>325</v>
@@ -5882,42 +5871,42 @@
         <v>45999</v>
       </c>
       <c r="N14" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="O14" t="s">
         <v>175</v>
-      </c>
-      <c r="O14" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D15">
         <v>2021</v>
       </c>
       <c r="E15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G15">
         <v>16</v>
       </c>
       <c r="H15" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I15">
         <v>256</v>
       </c>
       <c r="J15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K15" s="19">
         <v>205</v>
@@ -5927,277 +5916,277 @@
         <v>45999</v>
       </c>
       <c r="N15" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="O15" t="s">
         <v>175</v>
-      </c>
-      <c r="O15" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D16">
         <v>2012</v>
       </c>
       <c r="E16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F16" t="s">
         <v>190</v>
-      </c>
-      <c r="F16" t="s">
-        <v>191</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I16" s="1">
         <v>64</v>
       </c>
       <c r="J16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K16" s="19">
         <v>50</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M16" s="15">
         <v>45999</v>
       </c>
       <c r="N16" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="O16" t="s">
         <v>175</v>
-      </c>
-      <c r="O16" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D17">
         <v>2014</v>
       </c>
       <c r="E17" t="s">
+        <v>189</v>
+      </c>
+      <c r="F17" t="s">
         <v>190</v>
-      </c>
-      <c r="F17" t="s">
-        <v>191</v>
       </c>
       <c r="G17">
         <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I17">
         <v>128</v>
       </c>
       <c r="J17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K17" s="19">
         <v>60</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M17" s="15">
         <v>45999</v>
       </c>
       <c r="N17" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="O17" t="s">
         <v>175</v>
-      </c>
-      <c r="O17" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D18">
         <v>2018</v>
       </c>
       <c r="E18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F18" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G18">
         <v>8</v>
       </c>
       <c r="H18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I18">
         <v>256</v>
       </c>
       <c r="J18" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K18" s="19">
         <v>250</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M18" s="16">
         <v>46043</v>
       </c>
       <c r="N18" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="O18" t="s">
         <v>198</v>
-      </c>
-      <c r="O18" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D19">
         <v>2013</v>
       </c>
       <c r="E19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G19">
         <v>8</v>
       </c>
       <c r="H19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I19">
         <v>256</v>
       </c>
       <c r="J19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K19" s="19">
         <v>290</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M19" s="16">
         <v>46043</v>
       </c>
       <c r="N19" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="O19" t="s">
         <v>198</v>
-      </c>
-      <c r="O19" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="45">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D20">
         <v>2016</v>
       </c>
       <c r="E20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F20" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G20">
         <v>16</v>
       </c>
       <c r="H20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I20">
         <v>256</v>
       </c>
       <c r="J20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K20" s="19">
         <v>300</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M20" s="15">
         <v>46056</v>
       </c>
       <c r="N20" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D21">
         <v>2013</v>
       </c>
       <c r="E21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G21">
         <v>8</v>
       </c>
       <c r="H21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I21">
         <v>256</v>
       </c>
       <c r="J21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K21" s="19">
         <v>200</v>
@@ -6207,42 +6196,42 @@
         <v>46056</v>
       </c>
       <c r="N21" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D22">
         <v>2013</v>
       </c>
       <c r="E22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F22" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G22">
         <v>8</v>
       </c>
       <c r="H22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I22">
         <v>256</v>
       </c>
       <c r="J22" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K22" s="19">
         <v>200</v>
@@ -6252,42 +6241,42 @@
         <v>46056</v>
       </c>
       <c r="N22" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O22" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D23">
         <v>2013</v>
       </c>
       <c r="E23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F23" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G23">
         <v>8</v>
       </c>
       <c r="H23" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I23">
         <v>256</v>
       </c>
       <c r="J23" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K23" s="19">
         <v>200</v>
@@ -6297,42 +6286,42 @@
         <v>46056</v>
       </c>
       <c r="N23" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O23" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D24">
         <v>2013</v>
       </c>
       <c r="E24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F24" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G24">
         <v>8</v>
       </c>
       <c r="H24" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I24">
         <v>256</v>
       </c>
       <c r="J24" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K24" s="19">
         <v>200</v>
@@ -6342,42 +6331,42 @@
         <v>46056</v>
       </c>
       <c r="N24" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D25">
         <v>2013</v>
       </c>
       <c r="E25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G25">
         <v>16</v>
       </c>
       <c r="H25" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I25">
         <v>256</v>
       </c>
       <c r="J25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K25" s="19">
         <v>200</v>
@@ -6387,42 +6376,42 @@
         <v>46056</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D26">
         <v>2016</v>
       </c>
       <c r="E26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G26">
         <v>16</v>
       </c>
       <c r="H26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I26">
         <v>256</v>
       </c>
       <c r="J26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K26" s="19">
         <v>300</v>
@@ -6432,42 +6421,42 @@
         <v>46056</v>
       </c>
       <c r="N26" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O26" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B27" t="s">
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D27">
         <v>2016</v>
       </c>
       <c r="E27" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G27">
         <v>8</v>
       </c>
       <c r="H27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I27">
         <v>256</v>
       </c>
       <c r="J27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K27" s="19">
         <v>300</v>
@@ -6477,42 +6466,42 @@
         <v>46056</v>
       </c>
       <c r="N27" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D28">
         <v>2018</v>
       </c>
       <c r="E28" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G28">
         <v>16</v>
       </c>
       <c r="H28" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I28">
         <v>512</v>
       </c>
       <c r="J28" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K28" s="19">
         <v>445</v>
@@ -6522,42 +6511,42 @@
         <v>46056</v>
       </c>
       <c r="N28" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O28" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B29" t="s">
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D29">
         <v>2018</v>
       </c>
       <c r="E29" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G29">
         <v>16</v>
       </c>
       <c r="H29" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I29">
         <v>512</v>
       </c>
       <c r="J29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K29" s="19">
         <v>445</v>
@@ -6567,42 +6556,42 @@
         <v>46056</v>
       </c>
       <c r="N29" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O29" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D30">
         <v>2018</v>
       </c>
       <c r="E30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F30" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G30">
         <v>8</v>
       </c>
       <c r="H30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I30">
         <v>256</v>
       </c>
       <c r="J30" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K30" s="19">
         <v>150</v>
@@ -6612,42 +6601,42 @@
         <v>46056</v>
       </c>
       <c r="N30" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B31" s="27" t="s">
         <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D31">
         <v>2016</v>
       </c>
       <c r="E31" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F31" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G31">
         <v>8</v>
       </c>
       <c r="H31" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I31">
         <v>500</v>
       </c>
       <c r="J31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K31" s="19">
         <v>300</v>
@@ -6657,42 +6646,42 @@
         <v>46058</v>
       </c>
       <c r="N31" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O31" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B32" t="s">
         <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D32">
         <v>2016</v>
       </c>
       <c r="E32" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F32" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G32">
         <v>8</v>
       </c>
       <c r="H32" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I32">
         <v>256</v>
       </c>
       <c r="J32" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K32" s="19">
         <v>300</v>
@@ -6701,42 +6690,42 @@
         <v>46058</v>
       </c>
       <c r="N32" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O32" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B33" t="s">
         <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D33">
         <v>2016</v>
       </c>
       <c r="E33" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F33" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G33">
         <v>8</v>
       </c>
       <c r="H33" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I33">
         <v>256</v>
       </c>
       <c r="J33" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K33" s="19">
         <v>300</v>
@@ -6745,42 +6734,42 @@
         <v>46058</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O33" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D34">
         <v>2020</v>
       </c>
       <c r="E34" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G34">
         <v>16</v>
       </c>
       <c r="H34" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I34">
         <v>512</v>
       </c>
       <c r="J34" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K34" s="19">
         <v>445</v>
@@ -6789,42 +6778,42 @@
         <v>46058</v>
       </c>
       <c r="N34" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B35" t="s">
         <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D35">
         <v>2020</v>
       </c>
       <c r="E35" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F35" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G35">
         <v>16</v>
       </c>
       <c r="H35" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I35">
         <v>512</v>
       </c>
       <c r="J35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K35" s="19">
         <v>445</v>
@@ -6833,42 +6822,42 @@
         <v>46058</v>
       </c>
       <c r="N35" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O35" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D36">
         <v>2020</v>
       </c>
       <c r="E36" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F36" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G36">
         <v>16</v>
       </c>
       <c r="H36" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I36">
         <v>512</v>
       </c>
       <c r="J36" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K36" s="19">
         <v>445</v>
@@ -6877,42 +6866,42 @@
         <v>46058</v>
       </c>
       <c r="N36" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O36" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B37" t="s">
         <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D37">
         <v>2020</v>
       </c>
       <c r="E37" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G37">
         <v>16</v>
       </c>
       <c r="H37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I37">
         <v>512</v>
       </c>
       <c r="J37" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K37" s="19">
         <v>445</v>
@@ -6921,42 +6910,42 @@
         <v>46058</v>
       </c>
       <c r="N37" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O37" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D38">
         <v>2020</v>
       </c>
       <c r="E38" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F38" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G38">
         <v>16</v>
       </c>
       <c r="H38" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I38">
         <v>512</v>
       </c>
       <c r="J38" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K38" s="19">
         <v>445</v>
@@ -6965,42 +6954,42 @@
         <v>46058</v>
       </c>
       <c r="N38" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D39">
         <v>2020</v>
       </c>
       <c r="E39" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F39" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G39">
         <v>16</v>
       </c>
       <c r="H39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I39">
         <v>512</v>
       </c>
       <c r="J39" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K39" s="19">
         <v>445</v>
@@ -7009,42 +6998,42 @@
         <v>46058</v>
       </c>
       <c r="N39" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O39" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="15" customHeight="1">
       <c r="A40" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D40">
         <v>2020</v>
       </c>
       <c r="E40" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G40">
         <v>16</v>
       </c>
       <c r="H40" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I40">
         <v>512</v>
       </c>
       <c r="J40" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K40" s="19">
         <v>445</v>
@@ -7053,42 +7042,42 @@
         <v>46058</v>
       </c>
       <c r="N40" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="15" customHeight="1">
       <c r="A41" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D41">
         <v>2020</v>
       </c>
       <c r="E41" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F41" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G41">
         <v>16</v>
       </c>
       <c r="H41" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I41">
         <v>512</v>
       </c>
       <c r="J41" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K41" s="19">
         <v>445</v>
@@ -7097,42 +7086,42 @@
         <v>46058</v>
       </c>
       <c r="N41" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O41" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="15" customHeight="1">
       <c r="A42" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D42">
         <v>2020</v>
       </c>
       <c r="E42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F42" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G42">
         <v>16</v>
       </c>
       <c r="H42" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I42">
         <v>512</v>
       </c>
       <c r="J42" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K42" s="19">
         <v>445</v>
@@ -7141,42 +7130,42 @@
         <v>46058</v>
       </c>
       <c r="N42" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="15" customHeight="1">
       <c r="A43" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B43" t="s">
         <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D43">
         <v>2018</v>
       </c>
       <c r="E43" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G43">
         <v>8</v>
       </c>
       <c r="H43" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I43">
         <v>256</v>
       </c>
       <c r="J43" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K43" s="19">
         <v>300</v>
@@ -7186,42 +7175,42 @@
         <v>46078</v>
       </c>
       <c r="N43" s="16" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O43" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="15" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B44" s="26" t="s">
         <v>26</v>
       </c>
       <c r="C44" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D44" s="5">
         <v>2016</v>
       </c>
       <c r="E44" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F44" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G44">
         <v>8</v>
       </c>
       <c r="H44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I44">
         <v>256</v>
       </c>
       <c r="J44" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K44" s="19">
         <v>300</v>
@@ -7231,42 +7220,42 @@
         <v>46099</v>
       </c>
       <c r="N44" s="16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="15" customHeight="1">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B45" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C45" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D45">
         <v>2014</v>
       </c>
       <c r="E45" t="s">
+        <v>216</v>
+      </c>
+      <c r="F45" t="s">
         <v>217</v>
-      </c>
-      <c r="F45" t="s">
-        <v>218</v>
       </c>
       <c r="G45">
         <v>32</v>
       </c>
       <c r="H45" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I45">
         <v>512</v>
       </c>
       <c r="J45" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K45" s="19">
         <v>300</v>
@@ -7275,10 +7264,10 @@
         <v>46143</v>
       </c>
       <c r="N45" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O45" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="15" customHeight="1">
@@ -7403,7 +7392,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="33" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
@@ -7412,33 +7401,33 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" t="s">
         <v>221</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>222</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>223</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B3" t="s">
         <v>226</v>
-      </c>
-      <c r="B3" t="s">
-        <v>227</v>
       </c>
       <c r="C3">
         <v>12</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E3" s="2">
         <v>50</v>
@@ -7446,16 +7435,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C4">
         <v>7</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E4" s="2">
         <v>55</v>
@@ -7463,16 +7452,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" t="s">
         <v>229</v>
-      </c>
-      <c r="B5" t="s">
-        <v>230</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E5" s="2">
         <v>5</v>
@@ -7480,16 +7469,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E6" s="2">
         <v>10</v>
@@ -7497,16 +7486,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
@@ -7514,16 +7503,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C8">
         <v>18</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E8" s="2">
         <v>35</v>
@@ -7531,16 +7520,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E9" s="2">
         <v>20</v>
@@ -7548,16 +7537,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E10" s="2">
         <v>20</v>
@@ -7565,16 +7554,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C11">
         <v>15</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E11" s="2">
         <v>15</v>
@@ -7582,16 +7571,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E12" s="2">
         <v>50</v>
@@ -7599,16 +7588,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C13">
         <v>6</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E13" s="2">
         <v>30</v>
@@ -7616,16 +7605,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E14" s="2">
         <v>25</v>
@@ -7633,16 +7622,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E15" s="2">
         <v>50</v>
@@ -7650,16 +7639,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C16">
         <v>11</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E16" s="2">
         <v>10</v>
@@ -7667,16 +7656,16 @@
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1">
       <c r="A17" t="s">
+        <v>238</v>
+      </c>
+      <c r="B17" t="s">
         <v>239</v>
-      </c>
-      <c r="B17" t="s">
-        <v>240</v>
       </c>
       <c r="C17">
         <v>4</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E17" s="2">
         <v>60</v>
@@ -7714,25 +7703,25 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1">
       <c r="A1" s="33" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1">
       <c r="A3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -7743,7 +7732,7 @@
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -7754,7 +7743,7 @@
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
       <c r="A5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -7765,7 +7754,7 @@
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -7776,7 +7765,7 @@
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
       <c r="A7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -7787,7 +7776,7 @@
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -7798,7 +7787,7 @@
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -7809,7 +7798,7 @@
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -7820,7 +7809,7 @@
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B11">
         <v>14</v>
@@ -7831,7 +7820,7 @@
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -7842,7 +7831,7 @@
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1">
       <c r="A13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -7853,7 +7842,7 @@
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1">
       <c r="A14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B14">
         <v>6</v>

--- a/data/OldInventorySystem.xlsx
+++ b/data/OldInventorySystem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rosehulman-my.sharepoint.com/personal/lucasja_rose-hulman_edu/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{112BB916-2D75-4BC5-8521-46D837D93EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D9739BD-6947-495D-A632-4B17D9A929FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{5168A3A3-41E7-40C2-87C5-8FD5FAD669C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Laptops" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="283">
   <si>
     <t>LAPTOPS</t>
   </si>
@@ -74,6 +74,18 @@
     <t>Date Updated</t>
   </si>
   <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>Column4</t>
+  </si>
+  <si>
     <t>100e Chromebook 2nd Gen</t>
   </si>
   <si>
@@ -104,21 +116,21 @@
     <t>Apple</t>
   </si>
   <si>
+    <t>Reconnect and potentially replace battrey, completely unresponsive</t>
+  </si>
+  <si>
+    <t>MacBook Air A2179</t>
+  </si>
+  <si>
     <t>Not Started</t>
   </si>
   <si>
-    <t>MacBook Air A2179</t>
-  </si>
-  <si>
     <t>Satellite Click W35Dt-A3300</t>
   </si>
   <si>
     <t>Not Included</t>
   </si>
   <si>
-    <t>Satellite C55t-C5300</t>
-  </si>
-  <si>
     <t>Precision M6700</t>
   </si>
   <si>
@@ -197,6 +209,15 @@
     <t>Arc Linux Minecraft Installed</t>
   </si>
   <si>
+    <t>ProBook 450 G6</t>
+  </si>
+  <si>
+    <t>Intel Core i5-8265U; currently has vanilla os, should have windows 11</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>DESKTOPS</t>
   </si>
   <si>
@@ -215,9 +236,6 @@
     <t>Precision Tower 3420</t>
   </si>
   <si>
-    <t>Being used as a 2.5" SSD eraser; Tal accidentally ripped the sata power port off the motherboard, so if it doesn't work that's why</t>
-  </si>
-  <si>
     <t>Has SSD, no bootable device found</t>
   </si>
   <si>
@@ -234,12 +252,6 @@
   </si>
   <si>
     <t>Optiplex 960</t>
-  </si>
-  <si>
-    <t>Precision T3600</t>
-  </si>
-  <si>
-    <t>No OS, needs Vanilla; Ready to install</t>
   </si>
   <si>
     <t>Precision 7920</t>
@@ -287,430 +299,517 @@
     <t>Doesnt display video</t>
   </si>
   <si>
-    <t>Precision T7810</t>
-  </si>
-  <si>
-    <t>"No bootable devices" still a problem</t>
+    <t>Custom Build</t>
+  </si>
+  <si>
+    <t>CoolerMaster</t>
+  </si>
+  <si>
+    <t>ProDesk 400 G5 Desktop Mini</t>
+  </si>
+  <si>
+    <t>Needs Windows updates</t>
+  </si>
+  <si>
+    <t>Mini PC ZBox-CI323NANO</t>
+  </si>
+  <si>
+    <t>Has Vanilla OS, can discover eduroam but not rhit open, ethernet works</t>
+  </si>
+  <si>
+    <t>Z2 Mini G5 Workstation</t>
+  </si>
+  <si>
+    <t>Needs power supply; expensive!!!! MXM P620</t>
+  </si>
+  <si>
+    <t>ThinkCentre M700</t>
+  </si>
+  <si>
+    <t>Needs to play dugdug video, make clinky when moved</t>
+  </si>
+  <si>
+    <t>Optiplex 3070</t>
+  </si>
+  <si>
+    <t>Need Windows NEED better Charger</t>
+  </si>
+  <si>
+    <t>TABLETS</t>
+  </si>
+  <si>
+    <t>iPad A1397</t>
+  </si>
+  <si>
+    <t>Wifi + Cellular, Cracked screen</t>
+  </si>
+  <si>
+    <t>Wifi + Cellular</t>
+  </si>
+  <si>
+    <t>READY TO DONATE</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Type of Device</t>
+  </si>
+  <si>
+    <t>Est. Year</t>
+  </si>
+  <si>
+    <t>CPU</t>
+  </si>
+  <si>
+    <t>OS</t>
+  </si>
+  <si>
+    <t>RAM Amount</t>
+  </si>
+  <si>
+    <t>RAM Generation</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>SSD/HDD</t>
+  </si>
+  <si>
+    <t>Est. Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Thinkcenter E73</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>Intel i3-4130</t>
+  </si>
+  <si>
+    <t>Vanilla OS</t>
+  </si>
+  <si>
+    <t>DDR3</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>Inspiron 15 3552</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Inspiron 15-3552</t>
+  </si>
+  <si>
+    <t>Chromebox Thin Cilent 3</t>
+  </si>
+  <si>
+    <t>Intel Celeron 3865U</t>
+  </si>
+  <si>
+    <t>DDR4</t>
+  </si>
+  <si>
+    <t>intel core i3-7100</t>
+  </si>
+  <si>
+    <t>Intel core i3-7100</t>
+  </si>
+  <si>
+    <t>ThinkCentre M625q</t>
+  </si>
+  <si>
+    <t>AMD A9-9420e</t>
+  </si>
+  <si>
+    <t>Latitude 5510</t>
+  </si>
+  <si>
+    <t>Intel Core i7-10610U</t>
+  </si>
+  <si>
+    <t>Windows 11</t>
+  </si>
+  <si>
+    <t>Inspiron 3847</t>
+  </si>
+  <si>
+    <t>Intel Core i3-4170</t>
+  </si>
+  <si>
+    <t>Inspiron 15 3537</t>
+  </si>
+  <si>
+    <t>Intel Core i3 ULV</t>
+  </si>
+  <si>
+    <t>MacBook Pro A1502</t>
+  </si>
+  <si>
+    <t>2.6 GHz Dual-Core Intel Core i5</t>
+  </si>
+  <si>
+    <t>macOS</t>
+  </si>
+  <si>
+    <t>ProBook 450 G8</t>
+  </si>
+  <si>
+    <t>Intel Core i5-1135G7</t>
+  </si>
+  <si>
+    <t>Intel Core i7-6700</t>
+  </si>
+  <si>
+    <t>ProBook 650 G3</t>
+  </si>
+  <si>
+    <t>Intel Core i5-7300u</t>
+  </si>
+  <si>
+    <t>Intel Core i7-4770</t>
+  </si>
+  <si>
+    <t>Latitude 5580</t>
+  </si>
+  <si>
+    <t>Intel Core i7-7820</t>
+  </si>
+  <si>
+    <t>Intel Core i5-6400t</t>
+  </si>
+  <si>
+    <t>Needs charger</t>
+  </si>
+  <si>
+    <t>Edge 15</t>
+  </si>
+  <si>
+    <t>Intel Core i3-5020U</t>
+  </si>
+  <si>
+    <t>DRR3</t>
+  </si>
+  <si>
+    <t>Optiplex 5050 Micro</t>
+  </si>
+  <si>
+    <t>Intel Core i5-7600</t>
+  </si>
+  <si>
+    <t>ProDesk 600 G5 Desktop Mini</t>
+  </si>
+  <si>
+    <t>Intel core i5-9500</t>
+  </si>
+  <si>
+    <t>ProDesk 600 G3 Desktop Mini</t>
+  </si>
+  <si>
+    <t>Intel core i5-7500t</t>
   </si>
   <si>
     <t>EliteDesk 800 G4 TWR</t>
   </si>
   <si>
-    <t>Custom Build</t>
-  </si>
-  <si>
-    <t>CoolerMaster</t>
-  </si>
-  <si>
-    <t>ProDesk 400 G5 Desktop Mini</t>
-  </si>
-  <si>
-    <t>Mini PC ZBox-CI323NANO</t>
-  </si>
-  <si>
-    <t>Has Vanilla OS, can discover eduroam but not rhit open, ethernet works</t>
-  </si>
-  <si>
-    <t>Z2 Mini G5 Workstation</t>
-  </si>
-  <si>
-    <t>Needs power supply; expensive!!!! MXM P620</t>
+    <t>Intel i5-8500</t>
   </si>
   <si>
     <t>Optiplex 7070 micro</t>
   </si>
   <si>
-    <t>Windows Updates</t>
-  </si>
-  <si>
-    <t>ThinkCentre M700</t>
-  </si>
-  <si>
-    <t>Needs to play dugdug video, make clinky when moved</t>
-  </si>
-  <si>
-    <t>Optiplex 3070</t>
-  </si>
-  <si>
-    <t>TABLETS</t>
-  </si>
-  <si>
-    <t>iPad A1397</t>
-  </si>
-  <si>
-    <t>Wifi + Cellular, Cracked screen</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Wifi + Cellular</t>
-  </si>
-  <si>
-    <t>READY TO DONATE</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Type of Device</t>
-  </si>
-  <si>
-    <t>Est. Year</t>
-  </si>
-  <si>
-    <t>CPU</t>
-  </si>
-  <si>
-    <t>OS</t>
-  </si>
-  <si>
-    <t>RAM Amount</t>
-  </si>
-  <si>
-    <t>RAM Generation</t>
-  </si>
-  <si>
-    <t>Storage</t>
-  </si>
-  <si>
-    <t>SSD/HDD</t>
-  </si>
-  <si>
-    <t>Est. Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Thinkcenter E73</t>
-  </si>
-  <si>
-    <t>Desktop</t>
-  </si>
-  <si>
-    <t>Intel i3-4130</t>
-  </si>
-  <si>
-    <t>Vanilla OS</t>
-  </si>
-  <si>
-    <t>DDR3</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>Inspiron 15 3552</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>Inspiron 15-3552</t>
-  </si>
-  <si>
-    <t>Chromebox Thin Cilent 3</t>
-  </si>
-  <si>
-    <t>Intel Celeron 3865U</t>
-  </si>
-  <si>
-    <t>DDR4</t>
-  </si>
-  <si>
-    <t>intel core i3-7100</t>
-  </si>
-  <si>
-    <t>Intel core i3-7100</t>
-  </si>
-  <si>
-    <t>ThinkCentre M625q</t>
-  </si>
-  <si>
-    <t>AMD A9-9420e</t>
-  </si>
-  <si>
-    <t>Latitude 5510</t>
-  </si>
-  <si>
-    <t>Intel Core i7-10610U</t>
-  </si>
-  <si>
-    <t>Windows 11</t>
-  </si>
-  <si>
-    <t>Inspiron 3847</t>
-  </si>
-  <si>
-    <t>Intel Core i3-4170</t>
+    <t>ProBook 640 GB</t>
+  </si>
+  <si>
+    <t>Intel i5-1135G7</t>
+  </si>
+  <si>
+    <t>Google Pixel 7 Phone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google </t>
+  </si>
+  <si>
+    <t>Tablet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tensor G2 </t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>LPDDR5</t>
+  </si>
+  <si>
+    <t>USF</t>
+  </si>
+  <si>
+    <t>Precision T3600</t>
+  </si>
+  <si>
+    <t>Intel Xeon E5-1650</t>
+  </si>
+  <si>
+    <t>Satellite C55t-C5300</t>
+  </si>
+  <si>
+    <t>Intel i3-5020u</t>
+  </si>
+  <si>
+    <t>Donated Devices</t>
+  </si>
+  <si>
+    <t>Total Estimated Value</t>
+  </si>
+  <si>
+    <t>International donations:</t>
+  </si>
+  <si>
+    <t>Date Donated</t>
+  </si>
+  <si>
+    <t>Recipient</t>
+  </si>
+  <si>
+    <t>Org?</t>
+  </si>
+  <si>
+    <t>Laptop given to Tarrant</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>International, via Wayne Tarrant</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Latitude 5500</t>
+  </si>
+  <si>
+    <t>Intel core i7-8665U</t>
+  </si>
+  <si>
+    <t>15-AC113CL</t>
+  </si>
+  <si>
+    <t>Intel core i3-5005U</t>
+  </si>
+  <si>
+    <t>Satellite C55-B5296</t>
+  </si>
+  <si>
+    <t>Intel Celeron N2830</t>
+  </si>
+  <si>
+    <t>Low battery health</t>
+  </si>
+  <si>
+    <t>EliteBook 850 G6</t>
+  </si>
+  <si>
+    <t>Intel core i7-8565U</t>
+  </si>
+  <si>
+    <t>Latitude 5420</t>
+  </si>
+  <si>
+    <t>Intel core i5-1145G7</t>
+  </si>
+  <si>
+    <t>iPad Mini A1455</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>iOS</t>
+  </si>
+  <si>
+    <t>DDR2</t>
+  </si>
+  <si>
+    <t>eMMC</t>
+  </si>
+  <si>
+    <t>WiFi + Cellular</t>
+  </si>
+  <si>
+    <t>iPad Air 2 A1566</t>
+  </si>
+  <si>
+    <t>Optiplex 5060</t>
+  </si>
+  <si>
+    <t>Intel core i5-8500</t>
+  </si>
+  <si>
+    <t>No wifi, Ethernet only</t>
+  </si>
+  <si>
+    <t>The Learning Center, Terre Haute</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Intel core i7-4770</t>
+  </si>
+  <si>
+    <t>Wifi included</t>
+  </si>
+  <si>
+    <t>Intel i7-6700</t>
+  </si>
+  <si>
+    <t>built in ethernet doesn't work. Donate with usb-wifi adapter</t>
+  </si>
+  <si>
+    <t>International, via Dr. Onyancha</t>
+  </si>
+  <si>
+    <t>Optiplex 9010</t>
+  </si>
+  <si>
+    <t>Intel i7-3770</t>
+  </si>
+  <si>
+    <t>Intel i7-4770</t>
+  </si>
+  <si>
+    <t>ThinkPad P1 Gen 1</t>
+  </si>
+  <si>
+    <t>Intel i7 10750H</t>
+  </si>
+  <si>
+    <t>Intel i3-7100</t>
+  </si>
+  <si>
+    <t>HDD</t>
+  </si>
+  <si>
+    <t>ThinkPad P1 Gen 3</t>
   </si>
   <si>
     <t>Latitude 5490</t>
   </si>
   <si>
+    <t>Intel  i7-865OU</t>
+  </si>
+  <si>
+    <t>Given to Enzo at NU, for Deborah's Place</t>
+  </si>
+  <si>
+    <t>Wabash Activity Center</t>
+  </si>
+  <si>
+    <t>ASUS</t>
+  </si>
+  <si>
+    <t>Intel Core i3-4010U</t>
+  </si>
+  <si>
+    <t>Archlinux</t>
+  </si>
+  <si>
+    <t>Linux User Group</t>
+  </si>
+  <si>
+    <t>Chromebook 11 N7 C731</t>
+  </si>
+  <si>
+    <t>Intel Celeron N3060</t>
+  </si>
+  <si>
+    <t>Chrome OS</t>
+  </si>
+  <si>
+    <t>The Excel Center of Terre Haute</t>
+  </si>
+  <si>
+    <t>Intel Core i5-8400</t>
+  </si>
+  <si>
+    <t>Elitebook 850 G6</t>
+  </si>
+  <si>
+    <t>Intel Core i7-8565U</t>
+  </si>
+  <si>
+    <t>Jessalynn Boone</t>
+  </si>
+  <si>
+    <t>boonebee22@gmail.com</t>
+  </si>
+  <si>
+    <t>Intel Core i5-8265U</t>
+  </si>
+  <si>
+    <t>Brayden Smith</t>
+  </si>
+  <si>
+    <t>smittyjr629@gmail.com</t>
+  </si>
+  <si>
     <t>Intel Core i7-8650U</t>
   </si>
   <si>
-    <t>Inspiron 15 3537</t>
-  </si>
-  <si>
-    <t>Intel Core i3 ULV</t>
-  </si>
-  <si>
     <t>Latitude 5410</t>
   </si>
   <si>
     <t>Intel Core i5-10210U</t>
   </si>
   <si>
-    <t>MacBook Pro A1502</t>
-  </si>
-  <si>
-    <t>2.6 GHz Dual-Core Intel Core i5</t>
-  </si>
-  <si>
-    <t>macOS</t>
-  </si>
-  <si>
-    <t>ProBook 450 G6</t>
-  </si>
-  <si>
-    <t>Intel Core i5-8265U</t>
-  </si>
-  <si>
-    <t>ProBook 450 G8</t>
-  </si>
-  <si>
-    <t>Intel Core i5-1135G7</t>
-  </si>
-  <si>
-    <t>Intel Core i7-6700</t>
-  </si>
-  <si>
-    <t>Elitebook 850 G6</t>
-  </si>
-  <si>
-    <t>Intel Core i7-8565U</t>
-  </si>
-  <si>
-    <t>ProBook 650 G3</t>
-  </si>
-  <si>
-    <t>Intel Core i5-7300u</t>
-  </si>
-  <si>
-    <t>Intel Core i7-4770</t>
-  </si>
-  <si>
-    <t>Latitude 5580</t>
-  </si>
-  <si>
-    <t>Intel Core i7-7820</t>
-  </si>
-  <si>
-    <t>Intel Core i5-6400t</t>
-  </si>
-  <si>
-    <t>Needs charger</t>
-  </si>
-  <si>
-    <t>Edge 15</t>
-  </si>
-  <si>
-    <t>Intel Core i3-5020U</t>
-  </si>
-  <si>
-    <t>DRR3</t>
-  </si>
-  <si>
-    <t>Optiplex 5060</t>
-  </si>
-  <si>
-    <t>Intel Core i5-8400</t>
-  </si>
-  <si>
-    <t>Optiplex 5050 Micro</t>
-  </si>
-  <si>
-    <t>Intel Core i5-7600</t>
-  </si>
-  <si>
-    <t>ProDesk 600 G5 Desktop Mini</t>
-  </si>
-  <si>
-    <t>Intel core i5-9500</t>
-  </si>
-  <si>
-    <t>ProDesk 600 G3 Desktop Mini</t>
-  </si>
-  <si>
-    <t>Intel core i5-7500t</t>
-  </si>
-  <si>
     <t>ThinkPad P15s Gen 1</t>
   </si>
   <si>
-    <t>Intel core i5-1210u</t>
-  </si>
-  <si>
-    <t>Donated Devices</t>
-  </si>
-  <si>
-    <t>Total Estimated Value</t>
-  </si>
-  <si>
-    <t>International donations:</t>
-  </si>
-  <si>
-    <t>Date Donated</t>
-  </si>
-  <si>
-    <t>Recipient</t>
-  </si>
-  <si>
-    <t>Org?</t>
-  </si>
-  <si>
-    <t>Laptop given to Tarrant</t>
-  </si>
-  <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>International, via Wayne Tarrant</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Latitude 5500</t>
-  </si>
-  <si>
-    <t>Intel core i7-8665U</t>
-  </si>
-  <si>
-    <t>15-AC113CL</t>
-  </si>
-  <si>
-    <t>Intel core i3-5005U</t>
-  </si>
-  <si>
-    <t>Satellite C55-B5296</t>
-  </si>
-  <si>
-    <t>Intel Celeron N2830</t>
-  </si>
-  <si>
-    <t>Low battery health</t>
-  </si>
-  <si>
-    <t>EliteBook 850 G6</t>
-  </si>
-  <si>
-    <t>Intel core i7-8565U</t>
-  </si>
-  <si>
-    <t>Latitude 5420</t>
-  </si>
-  <si>
-    <t>Intel core i5-1145G7</t>
-  </si>
-  <si>
-    <t>iPad Mini A1455</t>
-  </si>
-  <si>
-    <t>Tablet</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>iOS</t>
-  </si>
-  <si>
-    <t>DDR2</t>
-  </si>
-  <si>
-    <t>eMMC</t>
-  </si>
-  <si>
-    <t>WiFi + Cellular</t>
-  </si>
-  <si>
-    <t>iPad Air 2 A1566</t>
-  </si>
-  <si>
-    <t>Intel core i5-8500</t>
-  </si>
-  <si>
-    <t>No wifi, Ethernet only</t>
-  </si>
-  <si>
-    <t>The Learning Center, Terre Haute</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Intel core i7-4770</t>
-  </si>
-  <si>
-    <t>Wifi included</t>
-  </si>
-  <si>
-    <t>Intel i7-6700</t>
-  </si>
-  <si>
-    <t>built in ethernet doesn't work. Donate with usb-wifi adapter</t>
-  </si>
-  <si>
-    <t>International, via Dr. Onyancha</t>
-  </si>
-  <si>
-    <t>Optiplex 9010</t>
-  </si>
-  <si>
-    <t>Intel i7-3770</t>
-  </si>
-  <si>
-    <t>Intel i7-4770</t>
-  </si>
-  <si>
-    <t>ThinkPad P1 Gen 1</t>
-  </si>
-  <si>
-    <t>Intel i7 10750H</t>
-  </si>
-  <si>
-    <t>Intel i3-7100</t>
-  </si>
-  <si>
-    <t>HDD</t>
-  </si>
-  <si>
-    <t>ThinkPad P1 Gen 3</t>
-  </si>
-  <si>
-    <t>Intel  i7-865OU</t>
-  </si>
-  <si>
-    <t>Given to Enzo at NU, for Deborah's Place</t>
-  </si>
-  <si>
-    <t>Wabash Activity Center</t>
-  </si>
-  <si>
-    <t>ASUS</t>
-  </si>
-  <si>
-    <t>Intel Core i3-4010U</t>
-  </si>
-  <si>
-    <t>Archlinux</t>
-  </si>
-  <si>
-    <t>Linux User Group</t>
+    <t>Intel core i5-10210u</t>
+  </si>
+  <si>
+    <t>Chromebook 13 CB5-311 series</t>
+  </si>
+  <si>
+    <t>Nvidia Tegra K1</t>
+  </si>
+  <si>
+    <t>Chromebook 13 C810 series</t>
+  </si>
+  <si>
+    <t>Nvidia Tegra K2</t>
+  </si>
+  <si>
+    <t>Nvidia Tegra K3</t>
+  </si>
+  <si>
+    <t>Nvidia Tegra K4</t>
+  </si>
+  <si>
+    <t>DDR5</t>
+  </si>
+  <si>
+    <t>Nvidia Tegra K5</t>
+  </si>
+  <si>
+    <t>DDR6</t>
+  </si>
+  <si>
+    <t>Nvidia Tegra K6</t>
+  </si>
+  <si>
+    <t>DDR7</t>
   </si>
   <si>
     <t>PARTS</t>
@@ -797,22 +896,10 @@
     <t>Anker Power Strip</t>
   </si>
   <si>
-    <t>Generic Power Strip</t>
-  </si>
-  <si>
     <t>USB A to Ethernet</t>
   </si>
   <si>
     <t>Duster</t>
-  </si>
-  <si>
-    <t>USB Drive</t>
-  </si>
-  <si>
-    <t>Goo Gone</t>
-  </si>
-  <si>
-    <t>Isopropyl Alcohol</t>
   </si>
   <si>
     <t>USB Wifi Adapter</t>
@@ -827,7 +914,7 @@
     <numFmt numFmtId="164" formatCode="00000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -858,6 +945,22 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -968,10 +1071,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1025,10 +1129,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1042,10 +1149,11 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="44">
     <dxf>
       <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
@@ -1069,23 +1177,6 @@
           <color theme="4" tint="0.39997558519241921"/>
         </top>
       </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1125,17 +1216,14 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1178,14 +1266,9 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="0"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1198,6 +1281,13 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1206,10 +1296,52 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -1314,6 +1446,31 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1347,6 +1504,23 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1361,35 +1535,39 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}" name="In_Progress" displayName="In_Progress" ref="A2:I38">
-  <autoFilter ref="A2:I38" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I16">
-    <sortCondition ref="B2:B16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}" name="In_Progress" displayName="In_Progress" ref="A2:M31">
+  <autoFilter ref="A2:M31" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I14">
+    <sortCondition ref="B2:B14"/>
   </sortState>
-  <tableColumns count="9">
+  <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{ED14BD60-C1E9-46C1-80A5-0D5E395AF078}" name="Item Name" totalsRowLabel="Total"/>
     <tableColumn id="13" xr3:uid="{5BEE40AD-E450-4A13-BFB5-1D0CED084DB3}" name="ID"/>
     <tableColumn id="8" xr3:uid="{E9AB9B46-3541-4715-8E5B-024096D78342}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{F7DAC8DD-8096-40F1-8780-1DB9CB4EC72F}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{C5D14689-5BE8-4F27-9815-298E6CAC6990}" name="Special Reqs/Notes" dataDxfId="41"/>
     <tableColumn id="5" xr3:uid="{5338F6FB-43B0-44AF-AF8B-542FAC6CEDF0}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{64D6C993-8518-4A7C-9BDA-A54D7DBFBA8E}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{E5D987A3-C54A-4907-B710-79DB224E0008}" name="Current Status" totalsRowFunction="count"/>
     <tableColumn id="14" xr3:uid="{CBD4AC90-B0AA-4722-BB52-11B8B47FEEAF}" name="Date Updated"/>
+    <tableColumn id="2" xr3:uid="{37627AD7-E085-4E4A-B466-1A160D855596}" name="Column1"/>
+    <tableColumn id="3" xr3:uid="{CBA297C3-3F4B-485B-892B-6D603F77FA9F}" name="Column2"/>
+    <tableColumn id="10" xr3:uid="{1B5601B3-07F5-42D9-80E6-14EBD7B95B0E}" name="Column3"/>
+    <tableColumn id="11" xr3:uid="{22887553-46A7-4FAE-A752-5DE64C9CFAB1}" name="Column4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1B9E2046-2B17-40F3-B52D-EAF68E47122D}" name="In_Progress8" displayName="In_Progress8" ref="A2:G59">
-  <autoFilter ref="A2:G59" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G59">
-    <sortCondition ref="B2:B59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1B9E2046-2B17-40F3-B52D-EAF68E47122D}" name="In_Progress8" displayName="In_Progress8" ref="A2:G52">
+  <autoFilter ref="A2:G52" xr:uid="{45A14D1D-80BB-4248-9A8B-692D6686C6DC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G52">
+    <sortCondition ref="B2:B52"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F96A3CC8-25D1-4CF8-877D-2816B26B7DC4}" name="Item Name" totalsRowLabel="Total"/>
-    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{CC95B79B-E9C6-4478-8268-7B5E0708443A}" name="ID" dataDxfId="38"/>
     <tableColumn id="8" xr3:uid="{7D8F815E-A974-42A8-AC0B-AB8B951599A2}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{FEA94C75-B538-448A-A9F5-46F5A27E863D}" name="Year released"/>
     <tableColumn id="4" xr3:uid="{24998D92-36B7-4553-81E7-CB33711B31BB}" name="Special Reqs/Notes"/>
@@ -1411,7 +1589,7 @@
     <tableColumn id="13" xr3:uid="{EFFF3477-1A58-41CD-BFF3-45CE299505A7}" name="ID"/>
     <tableColumn id="8" xr3:uid="{C694899F-E385-4DE2-972A-7395A9633019}" name="Manufacturer"/>
     <tableColumn id="9" xr3:uid="{13C54556-A90A-4F9C-800D-3D838462DF46}" name="Year released"/>
-    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{EB0C81D5-20B7-428A-9A74-64C6C59A39B6}" name="Special Reqs/Notes" dataDxfId="37"/>
     <tableColumn id="5" xr3:uid="{6DE19FBC-9BD8-456E-9FC5-F633F61E4A34}" name="Charger"/>
     <tableColumn id="6" xr3:uid="{68546225-0A78-43C1-A4F9-4D2E1DC008A3}" name="Working Battery"/>
     <tableColumn id="7" xr3:uid="{0D7FD365-4F73-4A57-B8A1-CFAC47267923}" name="Current Status" totalsRowFunction="count"/>
@@ -1422,8 +1600,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:M44" totalsRowShown="0" tableBorderDxfId="14">
-  <autoFilter ref="A2:M44" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}" name="Ready_To_Donate7" displayName="Ready_To_Donate7" ref="A2:M34" totalsRowShown="0" tableBorderDxfId="24">
+  <autoFilter ref="A2:M34" xr:uid="{D92D5D5D-191C-4D78-B08D-0ABFBE06D7B2}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{73648E04-2EA1-4ADB-8E24-E7DDE01C0462}" name="Item"/>
     <tableColumn id="13" xr3:uid="{DB867F70-87B5-4AE3-B35F-568639EAF10F}" name="Manufacturer"/>
@@ -1435,8 +1613,8 @@
     <tableColumn id="2" xr3:uid="{C85B34EB-06B2-40A8-BBCB-B5F170EF3F82}" name="RAM Generation"/>
     <tableColumn id="7" xr3:uid="{A686D1B3-031E-4544-A98D-8F3144FA62B0}" name="Storage"/>
     <tableColumn id="8" xr3:uid="{AB29939A-0AF4-4451-A6F4-2144F8957E73}" name="SSD/HDD"/>
-    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{80B69989-1A34-4B32-B100-006B113A12B3}" name="Est. Value" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{46DBF7E9-A65E-495E-A2E7-C18169DE9637}" name="Notes" dataDxfId="22"/>
     <tableColumn id="12" xr3:uid="{67EC036F-98F6-4C6B-BDD7-99DB9B6ADF97}" name="ID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1444,8 +1622,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10100501-D05A-423B-A036-4B5D9B2ECD20}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:O59" totalsRowShown="0" tableBorderDxfId="5">
-  <autoFilter ref="A2:O59" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10100501-D05A-423B-A036-4B5D9B2ECD20}" name="Ready_To_Donate" displayName="Ready_To_Donate" ref="A2:O104" totalsRowShown="0" tableBorderDxfId="5">
+  <autoFilter ref="A2:O104" xr:uid="{06396574-0271-4522-ADDB-9465953585FF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{549BC727-085C-45F5-9520-711A34B50F51}" name="Item"/>
     <tableColumn id="15" xr3:uid="{1796B66C-9564-4ED9-A973-A3E6CA0C2A0C}" name="Manufacturer"/>
@@ -1482,8 +1660,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1921E586-F6B8-46BF-BE64-CE91A4EEE8D6}" name="Parts56" displayName="Parts56" ref="A2:C34" totalsRowShown="0">
-  <autoFilter ref="A2:C34" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1921E586-F6B8-46BF-BE64-CE91A4EEE8D6}" name="Parts56" displayName="Parts56" ref="A2:C30" totalsRowShown="0">
+  <autoFilter ref="A2:C30" xr:uid="{56EE61A1-6164-4CDE-8E4E-0C4F2D11BFE3}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{C29E963F-354B-4750-B17F-22461F6DC5F4}" name="Name"/>
     <tableColumn id="2" xr3:uid="{1155C0CA-025A-4922-8B0E-F2A817B3BB60}" name="Qty"/>
@@ -1810,7 +1988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5AA6A1-7D43-4966-8813-F497D895A5C2}">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.28515625" customWidth="1"/>
@@ -1824,20 +2002,20 @@
     <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1865,581 +2043,548 @@
       <c r="I2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="E3" s="1"/>
-      <c r="I3" s="16"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3">
+        <v>2019</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="16">
+        <v>46045</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B4">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I4" s="16">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="E5" s="1"/>
-      <c r="I5" s="16"/>
-    </row>
-    <row r="6" spans="1:9">
+        <v>45673</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="30">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5">
+        <v>64</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>2010</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="16">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D6">
-        <v>2010</v>
-      </c>
-      <c r="E6" s="1" t="s">
+        <v>2020</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" t="s">
         <v>17</v>
       </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I6" s="16">
-        <v>45673</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B7">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I7" s="16">
-        <v>46001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8">
-        <v>66</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8">
-        <v>2020</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="16">
-        <v>46001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B9">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D9">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I9" s="16">
         <v>46001</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D10">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H10" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I10" s="16">
         <v>46001</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:13" ht="30">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B11">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D11">
-        <v>2012</v>
-      </c>
-      <c r="E11" s="1"/>
+        <v>2011</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I11" s="16">
-        <v>46001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>46038</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B12">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D12">
-        <v>2016</v>
-      </c>
-      <c r="E12" s="1"/>
+        <v>2023</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>37</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I12" s="16">
         <v>46001</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="30">
+    <row r="13" spans="1:13" ht="45">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B13">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D13">
         <v>2011</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I13" s="16">
-        <v>46038</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B14">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D14">
-        <v>2023</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>32</v>
-      </c>
+        <v>2018</v>
+      </c>
+      <c r="E14" s="1"/>
       <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I14" s="16">
         <v>46001</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="45">
+    <row r="15" spans="1:13" ht="30">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B15">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D15">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I15" s="16">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="30">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B16">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D16">
-        <v>2018</v>
-      </c>
-      <c r="E16" s="1"/>
+        <v>2012</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I16" s="16">
-        <v>46001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="30">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B17">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D17">
-        <v>2020</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>2017</v>
+      </c>
+      <c r="E17" s="1"/>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I17" s="16">
         <v>46094</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="30">
+    <row r="18" spans="1:12" ht="30">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B18">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="D18">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="G18" t="s">
+        <v>37</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I18" s="16">
         <v>46108</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:12" ht="30">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B19">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D19">
-        <v>2017</v>
-      </c>
-      <c r="E19" s="1"/>
+        <v>2019</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I19" s="16">
         <v>46094</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="30">
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B20">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D20">
         <v>2017</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I20" s="16">
         <v>46108</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
-      <c r="E21" s="1"/>
-      <c r="I21" s="16"/>
-    </row>
-    <row r="23" spans="1:9">
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21">
+        <v>115</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21">
+        <v>2019</v>
+      </c>
+      <c r="E21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" t="s">
+        <v>57</v>
+      </c>
+      <c r="H21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="16">
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:12">
       <c r="E23" s="1"/>
-      <c r="I23" s="16"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="E24" s="1"/>
-      <c r="I24" s="16"/>
-    </row>
-    <row r="25" spans="1:9" ht="30">
-      <c r="A25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25">
-        <v>134</v>
-      </c>
-      <c r="C25" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25">
-        <v>2019</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="16">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26">
-        <v>137</v>
-      </c>
-      <c r="C26" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26">
-        <v>2017</v>
-      </c>
+      <c r="K23" s="19"/>
+      <c r="L23" s="1"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="E24" s="30"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:12">
       <c r="E26" s="1"/>
-      <c r="F26" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" t="s">
-        <v>20</v>
-      </c>
-      <c r="I26" s="16">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27">
-        <v>138</v>
-      </c>
-      <c r="C27" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27">
-        <v>2017</v>
-      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="E27" s="1"/>
-      <c r="F27" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" t="s">
-        <v>20</v>
-      </c>
-      <c r="I27" s="16">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28">
-        <v>136</v>
-      </c>
-      <c r="C28" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28">
-        <v>2017</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F28" t="s">
-        <v>13</v>
-      </c>
-      <c r="H28" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="16">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+    </row>
+    <row r="28" spans="1:12">
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" spans="1:12">
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:12">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:12">
       <c r="E31" s="1"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="5:5">
-      <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="5:5">
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="5:5">
-      <c r="E35" s="1"/>
-    </row>
-    <row r="36" spans="5:5">
-      <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="5:5">
-      <c r="E37" s="1"/>
-    </row>
-    <row r="38" spans="5:5">
-      <c r="E38" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20:H21 H23:H24 H3:H18" xr:uid="{BDBDE7E9-9FC3-44B3-919F-CEEE026A72CD}">
+  <conditionalFormatting sqref="A21:B21 D21:I21 J23:L23">
+    <cfRule type="expression" dxfId="43" priority="1">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21:B21 D21:I21 J23:M23">
+    <cfRule type="expression" dxfId="42" priority="2">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18 H3:H7 H9:H16" xr:uid="{BDBDE7E9-9FC3-44B3-919F-CEEE026A72CD}">
       <formula1>"Not Started, In Progress, Scrapped, Unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G20:G21 G23:G24 G3:G18" xr:uid="{B3C7309D-E7FF-4409-A545-48D8D2AB8658}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G18 G3:G7 G9:G16" xr:uid="{B3C7309D-E7FF-4409-A545-48D8D2AB8658}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20:B21 B23:B24 B3:B18" xr:uid="{16B18C16-4889-4A0C-A4CE-D22AA5030E8B}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18 B3:B7 B9:B16" xr:uid="{16B18C16-4889-4A0C-A4CE-D22AA5030E8B}">
       <formula1>0</formula1>
       <formula2>2000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F20:F21 F24 F3:F18" xr:uid="{B98105AE-173E-4A15-99FD-BB956E15C3C9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F18 F3:F7 F9:F16" xr:uid="{B98105AE-173E-4A15-99FD-BB956E15C3C9}">
       <formula1>"Included, Not Included"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M23" xr:uid="{BD4480FF-AB8D-4446-AB7A-01C4C2A99ADB}">
+      <formula1>1</formula1>
+      <formula2>2000</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2451,7 +2596,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEA6183-B753-401C-B21E-C502785DFA3D}">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.28515625" customWidth="1"/>
@@ -2464,8 +2609,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="31" t="s">
-        <v>51</v>
+      <c r="A1" s="32" t="s">
+        <v>58</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -2499,20 +2644,20 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B3" s="13">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D3" s="5">
         <v>2015</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G3" s="7">
         <v>46000</v>
@@ -2520,20 +2665,20 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="8" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="14">
         <v>2</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D4" s="9">
         <v>2015</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G4" s="11">
         <v>46000</v>
@@ -2541,22 +2686,22 @@
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B5" s="13">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D5" s="5">
         <v>2015</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G5" s="7">
         <v>46094</v>
@@ -2564,22 +2709,22 @@
     </row>
     <row r="6" spans="1:7" ht="45">
       <c r="A6" s="8" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B6" s="14">
         <v>4</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D6" s="9">
         <v>2015</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G6" s="11">
         <v>46115</v>
@@ -2587,20 +2732,20 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B7" s="13">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D7" s="5">
         <v>2015</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G7" s="7">
         <v>46000</v>
@@ -2608,22 +2753,22 @@
     </row>
     <row r="8" spans="1:7" ht="30">
       <c r="A8" s="8" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B8" s="14">
         <v>6</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D8" s="9">
         <v>2015</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G8" s="11">
         <v>46057</v>
@@ -2631,20 +2776,20 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B9" s="13">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D9" s="5">
         <v>2015</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G9" s="7">
         <v>46000</v>
@@ -2661,66 +2806,52 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B11" s="13">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D11" s="5">
         <v>2015</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G11" s="7">
         <v>46000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="60">
-      <c r="A12" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="14">
-        <v>12</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="9">
-        <v>2016</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="11">
-        <v>46000</v>
-      </c>
+    <row r="12" spans="1:7">
+      <c r="A12" s="8"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="8" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B13" s="14">
         <v>14</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D13" s="9">
         <v>2016</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G13" s="11">
         <v>46000</v>
@@ -2728,20 +2859,20 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B14" s="13">
         <v>18</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D14" s="5">
         <v>2016</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G14" s="7">
         <v>46000</v>
@@ -2749,20 +2880,20 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="8" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B15" s="14">
         <v>19</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D15" s="9">
         <v>2016</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G15" s="11">
         <v>46000</v>
@@ -2770,20 +2901,20 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B16" s="13">
         <v>20</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D16" s="5">
         <v>2016</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G16" s="7">
         <v>46000</v>
@@ -2791,20 +2922,20 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B17" s="14">
         <v>21</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D17" s="9">
         <v>2016</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G17" s="11">
         <v>46000</v>
@@ -2812,20 +2943,20 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B18" s="13">
         <v>23</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D18" s="5">
         <v>2016</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G18" s="7">
         <v>46057</v>
@@ -2833,20 +2964,20 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="8" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B19" s="14">
         <v>24</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D19" s="9">
         <v>2016</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G19" s="11">
         <v>46000</v>
@@ -2854,20 +2985,20 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B20" s="13">
         <v>25</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D20" s="5">
         <v>2016</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G20" s="7">
         <v>46000</v>
@@ -2875,20 +3006,20 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="8" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B21" s="14">
         <v>27</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D21" s="9">
         <v>2016</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G21" s="11">
         <v>46000</v>
@@ -2896,20 +3027,20 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B22" s="13">
         <v>28</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D22" s="5">
         <v>2013</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G22" s="7">
         <v>46000</v>
@@ -2917,22 +3048,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="8" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B23" s="14">
         <v>31</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D23" s="9">
         <v>2017</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G23" s="11">
         <v>46132</v>
@@ -2940,20 +3071,20 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B24" s="13">
         <v>32</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D24" s="5">
         <v>2013</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G24" s="7">
         <v>46052</v>
@@ -2961,117 +3092,148 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="8" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B25" s="14">
         <v>33</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D25" s="9">
         <v>2013</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G25" s="11">
         <v>46000</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="4"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="7"/>
+      <c r="A26" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="14">
+        <v>37</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="9">
+        <v>2013</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="11">
+        <v>46122</v>
+      </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B27" s="14">
-        <v>37</v>
-      </c>
-      <c r="C27" s="9" t="s">
+      <c r="A27" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="13">
+        <v>38</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="5">
+        <v>2009</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="9">
-        <v>2013</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" s="11">
-        <v>46122</v>
+      <c r="G27" s="7">
+        <v>46000</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="13">
-        <v>38</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="A28" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="14">
+        <v>42</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="9">
+        <v>2017</v>
+      </c>
+      <c r="E28" s="10"/>
+      <c r="F28" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="5">
-        <v>2009</v>
-      </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="7">
+      <c r="G28" s="11">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="14">
+        <v>43</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="9">
+        <v>2014</v>
+      </c>
+      <c r="E29" s="10"/>
+      <c r="F29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="11">
         <v>46000</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="8" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B30" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C30" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="9">
+        <v>2017</v>
+      </c>
+      <c r="E30" s="10"/>
+      <c r="F30" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="9">
-        <v>2012</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="G30" s="11">
-        <v>46073</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B31" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D31" s="9">
         <v>2017</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G31" s="11">
         <v>46000</v>
@@ -3079,555 +3241,406 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="8" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B32" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D32" s="9">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G32" s="11">
         <v>46000</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B33" s="14">
-        <v>44</v>
-      </c>
-      <c r="C33" s="9" t="s">
+      <c r="A33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="12">
+        <v>80</v>
+      </c>
+      <c r="C33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33">
+        <v>2013</v>
+      </c>
+      <c r="E33" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="16">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="12">
+        <v>82</v>
+      </c>
+      <c r="C34" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34">
+        <v>2014</v>
+      </c>
+      <c r="F34" t="s">
         <v>26</v>
       </c>
-      <c r="D33" s="9">
-        <v>2017</v>
-      </c>
-      <c r="E33" s="10"/>
-      <c r="F33" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" s="11">
-        <v>46000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="14">
-        <v>45</v>
-      </c>
-      <c r="C34" s="9" t="s">
+      <c r="G34" s="16">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" s="12">
+        <v>89</v>
+      </c>
+      <c r="C35" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35">
+        <v>2014</v>
+      </c>
+      <c r="F35" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="9">
-        <v>2017</v>
-      </c>
-      <c r="E34" s="10"/>
-      <c r="F34" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G34" s="11">
-        <v>46000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="14">
-        <v>46</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D35" s="9">
-        <v>2020</v>
-      </c>
-      <c r="E35" s="10"/>
-      <c r="F35" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="11">
-        <v>46000</v>
+      <c r="G35" s="16">
+        <v>46031</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B36" s="12">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D36">
         <v>2013</v>
       </c>
       <c r="E36" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G36" s="16">
-        <v>46136</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B37" s="12">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C37" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="D37">
-        <v>2014</v>
+        <v>2018</v>
+      </c>
+      <c r="E37" t="s">
+        <v>80</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G37" s="16">
-        <v>46001</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B38" s="12">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C38" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D38">
         <v>2014</v>
       </c>
       <c r="F38" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G38" s="16">
-        <v>46031</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B39" s="12">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39">
+        <v>2014</v>
+      </c>
+      <c r="F39" t="s">
         <v>26</v>
       </c>
-      <c r="D39">
-        <v>2013</v>
-      </c>
-      <c r="E39" t="s">
-        <v>74</v>
-      </c>
-      <c r="F39" t="s">
-        <v>14</v>
-      </c>
       <c r="G39" s="16">
-        <v>46057</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B40" s="12">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D40">
-        <v>2018</v>
-      </c>
-      <c r="E40" t="s">
-        <v>76</v>
+        <v>2014</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G40" s="16">
-        <v>46122</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="G41" s="16"/>
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="12">
+        <v>112</v>
+      </c>
+      <c r="C41" t="s">
+        <v>82</v>
+      </c>
+      <c r="F41" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="16">
+        <v>46092</v>
+      </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="B42" s="12">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="C42" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="D42">
-        <v>2014</v>
+        <v>2018</v>
+      </c>
+      <c r="E42" t="s">
+        <v>84</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G42" s="16">
-        <v>46066</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="B43" s="12">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C43" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="D43">
-        <v>2014</v>
+        <v>2015</v>
+      </c>
+      <c r="E43" t="s">
+        <v>86</v>
       </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G43" s="16">
-        <v>46066</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="B44" s="12">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="C44" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="D44">
-        <v>2014</v>
+        <v>2020</v>
+      </c>
+      <c r="E44" t="s">
+        <v>88</v>
       </c>
       <c r="F44" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G44" s="16">
-        <v>46066</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B45" s="12">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45">
+        <v>2016</v>
+      </c>
+      <c r="F45" t="s">
         <v>26</v>
       </c>
-      <c r="D45">
-        <v>2014</v>
-      </c>
-      <c r="E45" t="s">
-        <v>54</v>
-      </c>
-      <c r="F45" t="s">
-        <v>14</v>
-      </c>
       <c r="G45" s="16">
-        <v>46073</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B46" s="12">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46">
+        <v>2018</v>
+      </c>
+      <c r="F46" t="s">
         <v>26</v>
       </c>
-      <c r="D46">
-        <v>2014</v>
-      </c>
-      <c r="E46" t="s">
-        <v>78</v>
-      </c>
-      <c r="F46" t="s">
-        <v>14</v>
-      </c>
       <c r="G46" s="16">
-        <v>46108</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B47" s="12">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C47" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D47">
-        <v>2018</v>
+        <v>2013</v>
+      </c>
+      <c r="E47" t="s">
+        <v>90</v>
       </c>
       <c r="F47" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G47" s="16">
-        <v>46092</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B48" s="12">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="C48" t="s">
-        <v>81</v>
+        <v>30</v>
+      </c>
+      <c r="D48">
+        <v>2019</v>
+      </c>
+      <c r="E48" t="s">
+        <v>92</v>
       </c>
       <c r="F48" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G48" s="16">
-        <v>46092</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="G49" s="16"/>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" t="s">
-        <v>82</v>
-      </c>
-      <c r="B50" s="12">
-        <v>128</v>
-      </c>
-      <c r="C50" t="s">
-        <v>11</v>
-      </c>
-      <c r="D50">
-        <v>2018</v>
-      </c>
-      <c r="F50" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" s="16">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" t="s">
-        <v>83</v>
-      </c>
-      <c r="B51" s="12">
-        <v>130</v>
-      </c>
-      <c r="C51" t="s">
-        <v>11</v>
-      </c>
-      <c r="D51">
-        <v>2015</v>
-      </c>
-      <c r="E51" t="s">
-        <v>84</v>
-      </c>
-      <c r="F51" t="s">
-        <v>14</v>
-      </c>
-      <c r="G51" s="16">
-        <v>46101</v>
+      <c r="A49" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" s="12">
+        <v>144</v>
+      </c>
+      <c r="C49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49">
+        <v>2019</v>
+      </c>
+      <c r="E49" t="s">
+        <v>92</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="16">
+        <v>46157</v>
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" t="s">
-        <v>85</v>
-      </c>
-      <c r="B52" s="12">
-        <v>132</v>
-      </c>
-      <c r="C52" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52">
-        <v>2020</v>
-      </c>
-      <c r="E52" t="s">
-        <v>86</v>
-      </c>
-      <c r="F52" t="s">
-        <v>14</v>
-      </c>
-      <c r="G52" s="16">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" t="s">
-        <v>87</v>
-      </c>
-      <c r="B53" s="12">
-        <v>133</v>
-      </c>
-      <c r="C53" t="s">
-        <v>11</v>
-      </c>
-      <c r="D53">
-        <v>2019</v>
-      </c>
-      <c r="E53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F53" t="s">
-        <v>14</v>
-      </c>
-      <c r="G53" s="16">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" t="s">
-        <v>89</v>
-      </c>
-      <c r="B54" s="12">
-        <v>135</v>
-      </c>
-      <c r="C54" t="s">
-        <v>11</v>
-      </c>
-      <c r="D54">
-        <v>2016</v>
-      </c>
-      <c r="F54" t="s">
-        <v>20</v>
-      </c>
-      <c r="G54" s="16">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" t="s">
-        <v>68</v>
-      </c>
-      <c r="B55" s="12">
-        <v>139</v>
-      </c>
-      <c r="C55" t="s">
-        <v>11</v>
-      </c>
-      <c r="D55">
-        <v>2018</v>
-      </c>
-      <c r="F55" t="s">
-        <v>20</v>
-      </c>
-      <c r="G55" s="16">
-        <v>46115</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" t="s">
-        <v>59</v>
-      </c>
-      <c r="B56" s="12">
-        <v>142</v>
-      </c>
-      <c r="C56" t="s">
-        <v>11</v>
-      </c>
-      <c r="D56">
-        <v>2013</v>
-      </c>
-      <c r="E56" t="s">
-        <v>90</v>
-      </c>
-      <c r="F56" t="s">
-        <v>14</v>
-      </c>
-      <c r="G56" s="16">
-        <v>46115</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" t="s">
-        <v>91</v>
-      </c>
-      <c r="B57" s="12">
-        <v>143</v>
-      </c>
-      <c r="C57" t="s">
-        <v>26</v>
-      </c>
-      <c r="D57">
-        <v>2019</v>
-      </c>
-      <c r="F57" t="s">
-        <v>20</v>
-      </c>
-      <c r="G57" s="16">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" t="s">
-        <v>91</v>
-      </c>
-      <c r="B58" s="12">
-        <v>144</v>
-      </c>
-      <c r="C58" t="s">
-        <v>26</v>
-      </c>
-      <c r="D58">
-        <v>2019</v>
-      </c>
-      <c r="F58" t="s">
-        <v>20</v>
-      </c>
-      <c r="G58" s="16">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="G59" s="16"/>
+      <c r="G52" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:G28 A30:G59">
-    <cfRule type="expression" dxfId="34" priority="1">
+  <conditionalFormatting sqref="A52:G52 A3:G49">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="2">
+    <cfRule type="expression" dxfId="39" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F43:F45 F3:F28 F30:F38 F48:F59" xr:uid="{6630553F-92E4-427F-9784-13858DB7D720}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F35 F52 F39:F49" xr:uid="{6630553F-92E4-427F-9784-13858DB7D720}">
       <formula1>"Not Started,In Progress,Scrapped,Unknown"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3656,17 +3669,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
+      <c r="A1" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
@@ -3699,28 +3712,28 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B3">
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D3">
         <v>2011</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I3" s="16">
         <v>46001</v>
@@ -3728,13 +3741,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>2011</v>
@@ -3743,20 +3756,17 @@
         <v>96</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I4" s="16">
         <v>46001</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:9">
       <c r="E6" s="1"/>
@@ -3847,18 +3857,18 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F33" xr:uid="{DC839142-B4EB-40C5-A87E-16E886C982C3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H33" xr:uid="{E5C6D861-9704-4A24-A373-266C3767845A}">
+      <formula1>"Not Started, In Progress, Scrapped, Unknown"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F4 F6:F33" xr:uid="{DC839142-B4EB-40C5-A87E-16E886C982C3}">
       <formula1>"Included, Not Included"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B33" xr:uid="{5D9F521D-9556-4B0B-98FA-700A425B326D}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B4 B6:B33" xr:uid="{5D9F521D-9556-4B0B-98FA-700A425B326D}">
       <formula1>0</formula1>
       <formula2>2000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G33" xr:uid="{5C3E82F6-F480-4C1E-B342-7BEF40999310}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G4 G6:G33" xr:uid="{5C3E82F6-F480-4C1E-B342-7BEF40999310}">
       <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H33" xr:uid="{E5C6D861-9704-4A24-A373-266C3767845A}">
-      <formula1>"Not Started, In Progress, Scrapped, Unknown"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3870,7 +3880,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFE86381-3E33-4CB8-A62B-E48A74AB9667}">
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -3888,21 +3898,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
@@ -3950,7 +3960,7 @@
         <v>109</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>110</v>
@@ -3989,7 +3999,7 @@
         <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
         <v>116</v>
@@ -4028,7 +4038,7 @@
         <v>118</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
         <v>110</v>
@@ -4063,14 +4073,50 @@
       </c>
     </row>
     <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6">
+        <v>2018</v>
+      </c>
+      <c r="E6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6">
+        <v>256</v>
+      </c>
+      <c r="J6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K6" s="19">
+        <v>175</v>
+      </c>
       <c r="L6" s="1"/>
+      <c r="M6">
+        <v>85</v>
+      </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
         <v>110</v>
@@ -4079,7 +4125,7 @@
         <v>2018</v>
       </c>
       <c r="E7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F7" t="s">
         <v>112</v>
@@ -4101,15 +4147,15 @@
       </c>
       <c r="L7" s="1"/>
       <c r="M7">
-        <v>85</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>110</v>
@@ -4118,7 +4164,7 @@
         <v>2018</v>
       </c>
       <c r="E8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F8" t="s">
         <v>112</v>
@@ -4136,31 +4182,31 @@
         <v>114</v>
       </c>
       <c r="K8" s="19">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D9">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F9" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -4175,34 +4221,69 @@
         <v>114</v>
       </c>
       <c r="K9" s="19">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9">
-        <v>83</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="L10" s="1"/>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="A10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10">
+        <v>2014</v>
+      </c>
+      <c r="E10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+      <c r="H10" t="s">
+        <v>113</v>
+      </c>
+      <c r="I10">
+        <v>256</v>
+      </c>
+      <c r="J10" t="s">
+        <v>114</v>
+      </c>
+      <c r="K10" s="2">
+        <v>175</v>
+      </c>
+      <c r="M10">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15" customHeight="1">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D11">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="E11" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F11" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="G11">
         <v>8</v>
@@ -4217,28 +4298,28 @@
         <v>114</v>
       </c>
       <c r="K11" s="19">
-        <v>300</v>
+        <v>175</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15" customHeight="1">
       <c r="A12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D12">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="E12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F12" t="s">
         <v>112</v>
@@ -4255,37 +4336,38 @@
       <c r="J12" t="s">
         <v>114</v>
       </c>
-      <c r="K12" s="2">
-        <v>175</v>
-      </c>
+      <c r="K12" s="19">
+        <v>150</v>
+      </c>
+      <c r="L12" s="1"/>
       <c r="M12">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15" customHeight="1">
       <c r="A13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>116</v>
       </c>
       <c r="D13">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="E13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F13" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="G13">
         <v>8</v>
       </c>
       <c r="H13" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I13">
         <v>256</v>
@@ -4294,31 +4376,31 @@
         <v>114</v>
       </c>
       <c r="K13" s="19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13">
-        <v>61</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D14">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="E14" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="F14" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="G14">
         <v>8</v>
@@ -4333,37 +4415,37 @@
         <v>114</v>
       </c>
       <c r="K14" s="19">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14">
-        <v>88</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1">
       <c r="A15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
         <v>116</v>
       </c>
       <c r="D15">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="E15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F15" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="G15">
         <v>8</v>
       </c>
       <c r="H15" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I15">
         <v>256</v>
@@ -4372,34 +4454,34 @@
         <v>114</v>
       </c>
       <c r="K15" s="19">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15">
-        <v>57</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1">
       <c r="A16" t="s">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>116</v>
+        <v>30</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="D16">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="E16" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F16" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="G16">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H16" t="s">
         <v>120</v>
@@ -4411,37 +4493,37 @@
         <v>114</v>
       </c>
       <c r="K16" s="19">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16">
-        <v>56</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1">
       <c r="A17" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D17">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="E17" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="F17" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="G17">
         <v>8</v>
       </c>
       <c r="H17" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I17">
         <v>256</v>
@@ -4450,28 +4532,28 @@
         <v>114</v>
       </c>
       <c r="K17" s="19">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17">
-        <v>108</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15" customHeight="1">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
         <v>116</v>
       </c>
       <c r="D18">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="E18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F18" t="s">
         <v>112</v>
@@ -4489,28 +4571,28 @@
         <v>114</v>
       </c>
       <c r="K18" s="19">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
         <v>116</v>
       </c>
       <c r="D19">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F19" t="s">
         <v>127</v>
@@ -4528,37 +4610,37 @@
         <v>114</v>
       </c>
       <c r="K19" s="19">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15" customHeight="1">
-      <c r="A20" t="s">
-        <v>141</v>
-      </c>
-      <c r="B20" t="s">
-        <v>35</v>
+      <c r="A20" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D20">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="E20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F20" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="G20">
         <v>8</v>
       </c>
       <c r="H20" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I20">
         <v>256</v>
@@ -4567,11 +4649,11 @@
         <v>114</v>
       </c>
       <c r="K20" s="19">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20">
-        <v>113</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15" customHeight="1">
@@ -4579,13 +4661,13 @@
         <v>141</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
         <v>116</v>
       </c>
       <c r="D21">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="E21" t="s">
         <v>142</v>
@@ -4594,7 +4676,7 @@
         <v>127</v>
       </c>
       <c r="G21">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H21" t="s">
         <v>120</v>
@@ -4606,22 +4688,22 @@
         <v>114</v>
       </c>
       <c r="K21" s="19">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15" customHeight="1">
-      <c r="A22" t="s">
-        <v>56</v>
+      <c r="A22" s="25" t="s">
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>110</v>
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
+        <v>116</v>
       </c>
       <c r="D22">
         <v>2016</v>
@@ -4633,7 +4715,7 @@
         <v>112</v>
       </c>
       <c r="G22">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H22" t="s">
         <v>120</v>
@@ -4645,37 +4727,39 @@
         <v>114</v>
       </c>
       <c r="K22" s="19">
-        <v>255</v>
-      </c>
-      <c r="L22" s="1"/>
+        <v>200</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="M22">
-        <v>11</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15" customHeight="1">
       <c r="A23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
         <v>116</v>
       </c>
       <c r="D23">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="E23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F23" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="G23">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H23" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="I23">
         <v>256</v>
@@ -4684,28 +4768,30 @@
         <v>114</v>
       </c>
       <c r="K23" s="19">
-        <v>300</v>
-      </c>
-      <c r="L23" s="1"/>
+        <v>175</v>
+      </c>
+      <c r="L23" t="s">
+        <v>28</v>
+      </c>
       <c r="M23">
-        <v>55</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15" customHeight="1">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
         <v>110</v>
       </c>
       <c r="D24">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="E24" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F24" t="s">
         <v>127</v>
@@ -4723,34 +4809,34 @@
         <v>114</v>
       </c>
       <c r="K24" s="19">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15" customHeight="1">
       <c r="A25" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
         <v>110</v>
       </c>
       <c r="D25">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E25" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="F25" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="G25">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H25" t="s">
         <v>120</v>
@@ -4762,31 +4848,31 @@
         <v>114</v>
       </c>
       <c r="K25" s="19">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25">
-        <v>86</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15" customHeight="1">
       <c r="A26" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D26">
         <v>2017</v>
       </c>
       <c r="E26" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F26" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="G26">
         <v>8</v>
@@ -4801,28 +4887,28 @@
         <v>114</v>
       </c>
       <c r="K26" s="19">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="L26" s="1"/>
       <c r="M26">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="15" customHeight="1">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D27">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E27" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="F27" t="s">
         <v>127</v>
@@ -4840,37 +4926,34 @@
         <v>114</v>
       </c>
       <c r="K27" s="19">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>26</v>
+      <c r="A28" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
       </c>
       <c r="C28" t="s">
         <v>110</v>
       </c>
       <c r="D28">
-        <v>2013</v>
-      </c>
-      <c r="E28" t="s">
-        <v>148</v>
+        <v>2019</v>
       </c>
       <c r="F28" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="G28">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H28" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I28">
         <v>256</v>
@@ -4883,24 +4966,24 @@
       </c>
       <c r="L28" s="1"/>
       <c r="M28">
-        <v>34</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="15" customHeight="1">
       <c r="A29" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C29" t="s">
         <v>116</v>
       </c>
       <c r="D29">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="E29" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="F29" t="s">
         <v>127</v>
@@ -4918,78 +5001,76 @@
         <v>114</v>
       </c>
       <c r="K29" s="19">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="L29" s="1"/>
       <c r="M29">
-        <v>126</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15" customHeight="1">
-      <c r="A30" s="25" t="s">
-        <v>89</v>
+      <c r="A30" t="s">
+        <v>159</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="D30">
-        <v>2016</v>
-      </c>
-      <c r="E30" t="s">
-        <v>151</v>
+        <v>2022</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="F30" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="G30">
         <v>8</v>
       </c>
       <c r="H30" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="I30">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="J30" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="K30" s="19">
-        <v>200</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>152</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="L30" s="1"/>
       <c r="M30">
-        <v>127</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15" customHeight="1">
       <c r="A31" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D31">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="E31" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F31" t="s">
         <v>112</v>
       </c>
       <c r="G31">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H31" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="I31">
         <v>256</v>
@@ -4998,316 +5079,127 @@
         <v>114</v>
       </c>
       <c r="K31" s="19">
-        <v>175</v>
-      </c>
-      <c r="L31" t="s">
-        <v>23</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="L31" s="1"/>
       <c r="M31">
-        <v>122</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="15" customHeight="1">
       <c r="A32" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D32">
-        <v>2018</v>
-      </c>
-      <c r="E32" t="s">
-        <v>157</v>
+        <v>2014</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="F32" t="s">
         <v>127</v>
       </c>
       <c r="G32">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H32" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I32">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="J32" t="s">
         <v>114</v>
       </c>
       <c r="K32" s="19">
-        <f>_xlfn.SINGLE(200)</f>
         <v>200</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="15" customHeight="1">
-      <c r="A33" t="s">
-        <v>158</v>
-      </c>
-      <c r="B33" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" t="s">
-        <v>110</v>
-      </c>
-      <c r="D33">
-        <v>2017</v>
-      </c>
-      <c r="E33" t="s">
-        <v>159</v>
-      </c>
-      <c r="F33" t="s">
-        <v>127</v>
-      </c>
-      <c r="G33">
-        <v>16</v>
-      </c>
-      <c r="H33" t="s">
-        <v>120</v>
-      </c>
-      <c r="I33">
-        <v>256</v>
-      </c>
-      <c r="J33" t="s">
-        <v>114</v>
-      </c>
-      <c r="K33" s="19">
-        <v>200</v>
-      </c>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="12:12" ht="15" customHeight="1">
       <c r="L33" s="1"/>
-      <c r="M33">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="15" customHeight="1">
-      <c r="A34" t="s">
-        <v>160</v>
-      </c>
-      <c r="B34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" t="s">
-        <v>110</v>
-      </c>
-      <c r="D34">
-        <v>2019</v>
-      </c>
-      <c r="E34" t="s">
-        <v>161</v>
-      </c>
-      <c r="F34" t="s">
-        <v>127</v>
-      </c>
-      <c r="G34">
-        <v>16</v>
-      </c>
-      <c r="H34" t="s">
-        <v>120</v>
-      </c>
-      <c r="I34">
-        <v>256</v>
-      </c>
-      <c r="J34" t="s">
-        <v>114</v>
-      </c>
-      <c r="K34" s="19">
-        <v>350</v>
-      </c>
+    </row>
+    <row r="34" spans="12:12" ht="15" customHeight="1">
       <c r="L34" s="1"/>
-      <c r="M34">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="15" customHeight="1">
-      <c r="A35" t="s">
-        <v>162</v>
-      </c>
-      <c r="B35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35">
-        <v>2017</v>
-      </c>
-      <c r="E35" t="s">
-        <v>163</v>
-      </c>
-      <c r="F35" t="s">
-        <v>127</v>
-      </c>
-      <c r="G35">
-        <v>8</v>
-      </c>
-      <c r="H35" t="s">
-        <v>120</v>
-      </c>
-      <c r="I35">
-        <v>256</v>
-      </c>
-      <c r="J35" t="s">
-        <v>114</v>
-      </c>
-      <c r="K35" s="19">
-        <v>300</v>
-      </c>
-      <c r="L35" s="1"/>
-      <c r="M35">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="15" customHeight="1">
-      <c r="A36" t="s">
-        <v>164</v>
-      </c>
-      <c r="B36" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="D36" s="29">
-        <v>2020</v>
-      </c>
-      <c r="E36" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="F36" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="G36" s="30">
-        <v>8</v>
-      </c>
-      <c r="H36" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="I36" s="28">
-        <v>256</v>
-      </c>
-      <c r="J36" t="s">
-        <v>114</v>
-      </c>
-      <c r="K36" s="19">
-        <v>400</v>
-      </c>
-      <c r="L36" s="1"/>
-      <c r="M36">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="15" customHeight="1">
-      <c r="L37" s="1"/>
-    </row>
-    <row r="38" spans="1:13" ht="15" customHeight="1">
-      <c r="L38" s="1"/>
-    </row>
-    <row r="39" spans="1:13" ht="15" customHeight="1">
-      <c r="L39" s="1"/>
-    </row>
-    <row r="40" spans="1:13" ht="15" customHeight="1">
-      <c r="L40" s="1"/>
-    </row>
-    <row r="41" spans="1:13" ht="15" customHeight="1">
-      <c r="L41" s="1"/>
-    </row>
-    <row r="42" spans="1:13" ht="15" customHeight="1">
-      <c r="L42" s="1"/>
-    </row>
-    <row r="43" spans="1:13" ht="15" customHeight="1">
-      <c r="L43" s="1"/>
-    </row>
-    <row r="44" spans="1:13" ht="15" customHeight="1">
-      <c r="L44" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A27:B28 A30:B30">
-    <cfRule type="expression" dxfId="30" priority="27">
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="A24:A28">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="28">
+    <cfRule type="expression" dxfId="35" priority="2">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:L9 A11:L14 A15:D15 F15:L15 A16:L25">
-    <cfRule type="expression" dxfId="28" priority="31">
+  <conditionalFormatting sqref="A19:B20 A22:B22">
+    <cfRule type="expression" dxfId="34" priority="33">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="34">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:L11 A12:D12 F12:L12 A13:L17">
+    <cfRule type="expression" dxfId="32" priority="37">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:M9 A11:M14 A15:D15 F15:M15 A16:M25">
-    <cfRule type="expression" dxfId="27" priority="32">
+  <conditionalFormatting sqref="A3:M11 A12:D12 F12:M12 A13:M17">
+    <cfRule type="expression" dxfId="31" priority="38">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C36:I36">
-    <cfRule type="expression" dxfId="26" priority="7">
+  <conditionalFormatting sqref="D27">
+    <cfRule type="expression" dxfId="30" priority="3">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="8">
+    <cfRule type="expression" dxfId="29" priority="4">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H26:H29">
-    <cfRule type="expression" dxfId="24" priority="19">
+  <conditionalFormatting sqref="H18:H21">
+    <cfRule type="expression" dxfId="28" priority="25">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="20">
+    <cfRule type="expression" dxfId="27" priority="26">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I26:I29">
-    <cfRule type="expression" dxfId="22" priority="11">
+  <conditionalFormatting sqref="I18:I21">
+    <cfRule type="expression" dxfId="26" priority="17">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="12">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A33">
-    <cfRule type="expression" dxfId="20" priority="5">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="6">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A34">
-    <cfRule type="expression" dxfId="18" priority="3">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="4">
-      <formula>ISODD(ROW())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35">
-    <cfRule type="expression" dxfId="16" priority="1">
-      <formula>ISEVEN(ROW())</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="2">
+    <cfRule type="expression" dxfId="25" priority="18">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M12:M25 M3:M4" xr:uid="{BD4480FF-AB8D-4446-AB7A-01C4C2A99ADB}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M4 M10:M17" xr:uid="{BD4480FF-AB8D-4446-AB7A-01C4C2A99ADB}">
       <formula1>1</formula1>
       <formula2>2000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C4 C13:C21 C23:C25" xr:uid="{23899482-37F4-4DDA-A40C-55EF7962BD79}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C4 C17 C11:C15" xr:uid="{23899482-37F4-4DDA-A40C-55EF7962BD79}">
       <formula1>"Desktop,Laptop,Tablet,All-In-One"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36" xr:uid="{C368B9B8-2EFC-4D0F-9393-97EEDF8604DA}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L31" xr:uid="{B98105AE-173E-4A15-99FD-BB956E15C3C9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L23" xr:uid="{B98105AE-173E-4A15-99FD-BB956E15C3C9}">
       <formula1>"Included, Not Included"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M30 M32" xr:uid="{5D9F521D-9556-4B0B-98FA-700A425B326D}">
+      <formula1>0</formula1>
+      <formula2>2000</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5319,7 +5211,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1C144A-BB57-4446-B714-000D1D9FAB4A}">
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q104"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
@@ -5343,7 +5235,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15" customHeight="1">
       <c r="C1" s="17" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D1" s="18"/>
       <c r="E1" s="18"/>
@@ -5358,10 +5250,10 @@
       <c r="N1" s="22"/>
       <c r="O1" s="18"/>
       <c r="P1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -5402,13 +5294,13 @@
         <v>108</v>
       </c>
       <c r="M2" s="16" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N2" s="16" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="O2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="P2" s="2">
         <f>SUM(K3:K38)</f>
@@ -5421,10 +5313,10 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C3" t="s">
         <v>116</v>
@@ -5446,18 +5338,18 @@
         <v>45970</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C4" t="s">
         <v>116</v>
@@ -5479,18 +5371,18 @@
         <v>45970</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O4" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C5" t="s">
         <v>116</v>
@@ -5512,18 +5404,18 @@
         <v>45970</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C6" t="s">
         <v>116</v>
@@ -5545,18 +5437,18 @@
         <v>45970</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O6" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C7" t="s">
         <v>116</v>
@@ -5578,18 +5470,18 @@
         <v>45970</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O7" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B8" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C8" t="s">
         <v>116</v>
@@ -5611,18 +5503,18 @@
         <v>45970</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O8" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C9" t="s">
         <v>116</v>
@@ -5644,18 +5536,18 @@
         <v>45970</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O9" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>116</v>
@@ -5664,7 +5556,7 @@
         <v>2018</v>
       </c>
       <c r="E10" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F10" t="s">
         <v>127</v>
@@ -5689,18 +5581,18 @@
         <v>45999</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O10" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
         <v>116</v>
@@ -5709,7 +5601,7 @@
         <v>2015</v>
       </c>
       <c r="E11" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F11" t="s">
         <v>127</v>
@@ -5734,18 +5626,18 @@
         <v>45999</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
         <v>116</v>
@@ -5754,7 +5646,7 @@
         <v>2014</v>
       </c>
       <c r="E12" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F12" t="s">
         <v>112</v>
@@ -5775,24 +5667,24 @@
         <v>175</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="M12" s="15">
         <v>45999</v>
       </c>
       <c r="N12" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O12" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
         <v>116</v>
@@ -5801,7 +5693,7 @@
         <v>2019</v>
       </c>
       <c r="E13" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F13" t="s">
         <v>127</v>
@@ -5826,18 +5718,18 @@
         <v>45999</v>
       </c>
       <c r="N13" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O13" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
         <v>116</v>
@@ -5846,7 +5738,7 @@
         <v>2018</v>
       </c>
       <c r="E14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F14" t="s">
         <v>127</v>
@@ -5871,18 +5763,18 @@
         <v>45999</v>
       </c>
       <c r="N14" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O14" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
         <v>116</v>
@@ -5891,7 +5783,7 @@
         <v>2021</v>
       </c>
       <c r="E15" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F15" t="s">
         <v>127</v>
@@ -5916,77 +5808,77 @@
         <v>45999</v>
       </c>
       <c r="N15" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O15" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="D16">
         <v>2012</v>
       </c>
       <c r="E16" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F16" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I16" s="1">
         <v>64</v>
       </c>
       <c r="J16" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K16" s="19">
         <v>50</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="M16" s="15">
         <v>45999</v>
       </c>
       <c r="N16" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O16" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="D17">
         <v>2014</v>
       </c>
       <c r="E17" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F17" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -5998,30 +5890,30 @@
         <v>128</v>
       </c>
       <c r="J17" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K17" s="19">
         <v>60</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="M17" s="15">
         <v>45999</v>
       </c>
       <c r="N17" s="15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O17" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
         <v>110</v>
@@ -6030,7 +5922,7 @@
         <v>2018</v>
       </c>
       <c r="E18" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F18" t="s">
         <v>127</v>
@@ -6051,24 +5943,24 @@
         <v>250</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="M18" s="16">
         <v>46043</v>
       </c>
       <c r="N18" s="16" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="O18" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
         <v>110</v>
@@ -6077,7 +5969,7 @@
         <v>2013</v>
       </c>
       <c r="E19" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F19" t="s">
         <v>112</v>
@@ -6098,24 +5990,24 @@
         <v>290</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="M19" s="16">
         <v>46043</v>
       </c>
       <c r="N19" s="16" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="O19" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="45">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
         <v>110</v>
@@ -6124,7 +6016,7 @@
         <v>2016</v>
       </c>
       <c r="E20" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F20" t="s">
         <v>112</v>
@@ -6145,24 +6037,24 @@
         <v>300</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M20" s="15">
         <v>46056</v>
       </c>
       <c r="N20" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O20" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
         <v>110</v>
@@ -6171,7 +6063,7 @@
         <v>2013</v>
       </c>
       <c r="E21" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F21" t="s">
         <v>112</v>
@@ -6196,18 +6088,18 @@
         <v>46056</v>
       </c>
       <c r="N21" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O21" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
         <v>110</v>
@@ -6216,7 +6108,7 @@
         <v>2013</v>
       </c>
       <c r="E22" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F22" t="s">
         <v>112</v>
@@ -6241,18 +6133,18 @@
         <v>46056</v>
       </c>
       <c r="N22" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O22" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
         <v>110</v>
@@ -6261,7 +6153,7 @@
         <v>2013</v>
       </c>
       <c r="E23" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F23" t="s">
         <v>112</v>
@@ -6286,18 +6178,18 @@
         <v>46056</v>
       </c>
       <c r="N23" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
         <v>110</v>
@@ -6306,7 +6198,7 @@
         <v>2013</v>
       </c>
       <c r="E24" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F24" t="s">
         <v>112</v>
@@ -6331,18 +6223,18 @@
         <v>46056</v>
       </c>
       <c r="N24" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O24" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
         <v>110</v>
@@ -6351,7 +6243,7 @@
         <v>2013</v>
       </c>
       <c r="E25" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F25" t="s">
         <v>112</v>
@@ -6376,18 +6268,18 @@
         <v>46056</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O25" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
         <v>110</v>
@@ -6396,7 +6288,7 @@
         <v>2016</v>
       </c>
       <c r="E26" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F26" t="s">
         <v>112</v>
@@ -6421,18 +6313,18 @@
         <v>46056</v>
       </c>
       <c r="N26" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O26" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
         <v>110</v>
@@ -6441,7 +6333,7 @@
         <v>2016</v>
       </c>
       <c r="E27" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F27" t="s">
         <v>112</v>
@@ -6466,18 +6358,18 @@
         <v>46056</v>
       </c>
       <c r="N27" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O27" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
         <v>116</v>
@@ -6486,7 +6378,7 @@
         <v>2018</v>
       </c>
       <c r="E28" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F28" t="s">
         <v>127</v>
@@ -6511,18 +6403,18 @@
         <v>46056</v>
       </c>
       <c r="N28" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O28" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
         <v>116</v>
@@ -6531,7 +6423,7 @@
         <v>2018</v>
       </c>
       <c r="E29" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F29" t="s">
         <v>127</v>
@@ -6556,10 +6448,10 @@
         <v>46056</v>
       </c>
       <c r="N29" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O29" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:15">
@@ -6567,7 +6459,7 @@
         <v>118</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
         <v>110</v>
@@ -6576,7 +6468,7 @@
         <v>2018</v>
       </c>
       <c r="E30" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F30" t="s">
         <v>112</v>
@@ -6601,18 +6493,18 @@
         <v>46056</v>
       </c>
       <c r="N30" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O30" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="8" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
         <v>110</v>
@@ -6621,7 +6513,7 @@
         <v>2016</v>
       </c>
       <c r="E31" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F31" t="s">
         <v>112</v>
@@ -6636,7 +6528,7 @@
         <v>500</v>
       </c>
       <c r="J31" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K31" s="19">
         <v>300</v>
@@ -6646,18 +6538,18 @@
         <v>46058</v>
       </c>
       <c r="N31" s="16" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O31" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
         <v>110</v>
@@ -6666,7 +6558,7 @@
         <v>2016</v>
       </c>
       <c r="E32" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F32" t="s">
         <v>112</v>
@@ -6690,18 +6582,18 @@
         <v>46058</v>
       </c>
       <c r="N32" s="16" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O32" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
         <v>110</v>
@@ -6710,7 +6602,7 @@
         <v>2016</v>
       </c>
       <c r="E33" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F33" t="s">
         <v>112</v>
@@ -6734,18 +6626,18 @@
         <v>46058</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O33" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
         <v>116</v>
@@ -6754,7 +6646,7 @@
         <v>2020</v>
       </c>
       <c r="E34" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F34" t="s">
         <v>127</v>
@@ -6778,18 +6670,18 @@
         <v>46058</v>
       </c>
       <c r="N34" s="16" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O34" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C35" t="s">
         <v>116</v>
@@ -6798,7 +6690,7 @@
         <v>2020</v>
       </c>
       <c r="E35" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F35" t="s">
         <v>127</v>
@@ -6822,18 +6714,18 @@
         <v>46058</v>
       </c>
       <c r="N35" s="16" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O35" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C36" t="s">
         <v>116</v>
@@ -6842,7 +6734,7 @@
         <v>2020</v>
       </c>
       <c r="E36" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F36" t="s">
         <v>127</v>
@@ -6866,18 +6758,18 @@
         <v>46058</v>
       </c>
       <c r="N36" s="16" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O36" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C37" t="s">
         <v>116</v>
@@ -6886,7 +6778,7 @@
         <v>2020</v>
       </c>
       <c r="E37" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F37" t="s">
         <v>127</v>
@@ -6910,18 +6802,18 @@
         <v>46058</v>
       </c>
       <c r="N37" s="16" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O37" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
         <v>116</v>
@@ -6930,7 +6822,7 @@
         <v>2020</v>
       </c>
       <c r="E38" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F38" t="s">
         <v>127</v>
@@ -6954,18 +6846,18 @@
         <v>46058</v>
       </c>
       <c r="N38" s="16" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O38" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C39" t="s">
         <v>116</v>
@@ -6974,7 +6866,7 @@
         <v>2020</v>
       </c>
       <c r="E39" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F39" t="s">
         <v>127</v>
@@ -6998,18 +6890,18 @@
         <v>46058</v>
       </c>
       <c r="N39" s="16" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O39" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="15" customHeight="1">
       <c r="A40" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
         <v>116</v>
@@ -7018,7 +6910,7 @@
         <v>2020</v>
       </c>
       <c r="E40" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F40" t="s">
         <v>127</v>
@@ -7042,18 +6934,18 @@
         <v>46058</v>
       </c>
       <c r="N40" s="16" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O40" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="15" customHeight="1">
       <c r="A41" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C41" t="s">
         <v>116</v>
@@ -7062,7 +6954,7 @@
         <v>2020</v>
       </c>
       <c r="E41" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F41" t="s">
         <v>127</v>
@@ -7086,18 +6978,18 @@
         <v>46058</v>
       </c>
       <c r="N41" s="16" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O41" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="15" customHeight="1">
       <c r="A42" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
         <v>116</v>
@@ -7106,7 +6998,7 @@
         <v>2020</v>
       </c>
       <c r="E42" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F42" t="s">
         <v>127</v>
@@ -7130,18 +7022,18 @@
         <v>46058</v>
       </c>
       <c r="N42" s="16" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O42" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="15" customHeight="1">
       <c r="A43" t="s">
-        <v>130</v>
+        <v>216</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C43" t="s">
         <v>116</v>
@@ -7150,7 +7042,7 @@
         <v>2018</v>
       </c>
       <c r="E43" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F43" t="s">
         <v>127</v>
@@ -7175,18 +7067,18 @@
         <v>46078</v>
       </c>
       <c r="N43" s="16" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="O43" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="15" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C44" t="s">
         <v>110</v>
@@ -7195,7 +7087,7 @@
         <v>2016</v>
       </c>
       <c r="E44" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F44" t="s">
         <v>112</v>
@@ -7220,18 +7112,18 @@
         <v>46099</v>
       </c>
       <c r="N44" s="16" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="O44" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="15" customHeight="1">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B45" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C45" t="s">
         <v>110</v>
@@ -7240,13 +7132,13 @@
         <v>2014</v>
       </c>
       <c r="E45" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F45" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="G45">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H45" t="s">
         <v>113</v>
@@ -7264,100 +7156,2271 @@
         <v>46143</v>
       </c>
       <c r="N45" s="15" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="O45" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="15" customHeight="1">
+      <c r="A46" t="s">
+        <v>224</v>
+      </c>
+      <c r="B46" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" t="s">
+        <v>116</v>
+      </c>
+      <c r="D46">
+        <v>2017</v>
+      </c>
+      <c r="E46" t="s">
+        <v>225</v>
+      </c>
+      <c r="F46" t="s">
+        <v>226</v>
+      </c>
+      <c r="G46">
+        <v>4</v>
+      </c>
+      <c r="H46" t="s">
+        <v>113</v>
+      </c>
+      <c r="I46">
+        <v>16</v>
+      </c>
+      <c r="J46" t="s">
+        <v>195</v>
+      </c>
+      <c r="K46" s="19">
+        <v>15</v>
+      </c>
+      <c r="M46" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N46" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O46" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="15" customHeight="1">
+      <c r="A47" t="s">
+        <v>224</v>
+      </c>
+      <c r="B47" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47">
+        <v>2017</v>
+      </c>
+      <c r="E47" t="s">
+        <v>225</v>
+      </c>
+      <c r="F47" t="s">
+        <v>226</v>
+      </c>
+      <c r="G47">
+        <v>4</v>
+      </c>
+      <c r="H47" t="s">
+        <v>113</v>
+      </c>
+      <c r="I47">
+        <v>16</v>
+      </c>
+      <c r="J47" t="s">
+        <v>195</v>
+      </c>
+      <c r="K47" s="19">
+        <v>15</v>
+      </c>
+      <c r="M47" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N47" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O47" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="15" customHeight="1">
+      <c r="A48" t="s">
+        <v>224</v>
+      </c>
+      <c r="B48" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" t="s">
+        <v>116</v>
+      </c>
+      <c r="D48">
+        <v>2017</v>
+      </c>
+      <c r="E48" t="s">
+        <v>225</v>
+      </c>
+      <c r="F48" t="s">
+        <v>226</v>
+      </c>
+      <c r="G48">
+        <v>4</v>
+      </c>
+      <c r="H48" t="s">
+        <v>113</v>
+      </c>
+      <c r="I48">
+        <v>16</v>
+      </c>
+      <c r="J48" t="s">
+        <v>195</v>
+      </c>
+      <c r="K48" s="19">
+        <v>15</v>
+      </c>
+      <c r="M48" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N48" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O48" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="15" customHeight="1">
+      <c r="A49" t="s">
+        <v>224</v>
+      </c>
+      <c r="B49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" t="s">
+        <v>116</v>
+      </c>
+      <c r="D49">
+        <v>2017</v>
+      </c>
+      <c r="E49" t="s">
+        <v>225</v>
+      </c>
+      <c r="F49" t="s">
+        <v>226</v>
+      </c>
+      <c r="G49">
+        <v>4</v>
+      </c>
+      <c r="H49" t="s">
+        <v>113</v>
+      </c>
+      <c r="I49">
+        <v>16</v>
+      </c>
+      <c r="J49" t="s">
+        <v>195</v>
+      </c>
+      <c r="K49" s="19">
+        <v>15</v>
+      </c>
+      <c r="M49" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N49" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O49" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="15" customHeight="1">
+      <c r="A50" t="s">
+        <v>224</v>
+      </c>
+      <c r="B50" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50">
+        <v>2017</v>
+      </c>
+      <c r="E50" t="s">
+        <v>225</v>
+      </c>
+      <c r="F50" t="s">
+        <v>226</v>
+      </c>
+      <c r="G50">
+        <v>4</v>
+      </c>
+      <c r="H50" t="s">
+        <v>113</v>
+      </c>
+      <c r="I50">
+        <v>16</v>
+      </c>
+      <c r="J50" t="s">
+        <v>195</v>
+      </c>
+      <c r="K50" s="19">
+        <v>15</v>
+      </c>
+      <c r="M50" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N50" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O50" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="15" customHeight="1">
+      <c r="A51" t="s">
+        <v>224</v>
+      </c>
+      <c r="B51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" t="s">
+        <v>116</v>
+      </c>
+      <c r="D51">
+        <v>2017</v>
+      </c>
+      <c r="E51" t="s">
+        <v>225</v>
+      </c>
+      <c r="F51" t="s">
+        <v>226</v>
+      </c>
+      <c r="G51">
+        <v>4</v>
+      </c>
+      <c r="H51" t="s">
+        <v>113</v>
+      </c>
+      <c r="I51">
+        <v>16</v>
+      </c>
+      <c r="J51" t="s">
+        <v>195</v>
+      </c>
+      <c r="K51" s="19">
+        <v>15</v>
+      </c>
+      <c r="M51" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N51" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O51" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="15" customHeight="1">
+      <c r="A52" t="s">
+        <v>224</v>
+      </c>
+      <c r="B52" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" t="s">
+        <v>116</v>
+      </c>
+      <c r="D52">
+        <v>2017</v>
+      </c>
+      <c r="E52" t="s">
+        <v>225</v>
+      </c>
+      <c r="F52" t="s">
+        <v>226</v>
+      </c>
+      <c r="G52">
+        <v>4</v>
+      </c>
+      <c r="H52" t="s">
+        <v>113</v>
+      </c>
+      <c r="I52">
+        <v>16</v>
+      </c>
+      <c r="J52" t="s">
+        <v>195</v>
+      </c>
+      <c r="K52" s="19">
+        <v>15</v>
+      </c>
+      <c r="M52" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N52" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O52" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="15" customHeight="1">
+      <c r="A53" t="s">
+        <v>224</v>
+      </c>
+      <c r="B53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" t="s">
+        <v>116</v>
+      </c>
+      <c r="D53">
+        <v>2017</v>
+      </c>
+      <c r="E53" t="s">
+        <v>225</v>
+      </c>
+      <c r="F53" t="s">
+        <v>226</v>
+      </c>
+      <c r="G53">
+        <v>4</v>
+      </c>
+      <c r="H53" t="s">
+        <v>113</v>
+      </c>
+      <c r="I53">
+        <v>16</v>
+      </c>
+      <c r="J53" t="s">
+        <v>195</v>
+      </c>
+      <c r="K53" s="19">
+        <v>15</v>
+      </c>
+      <c r="M53" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N53" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O53" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="15" customHeight="1">
+      <c r="A54" t="s">
+        <v>224</v>
+      </c>
+      <c r="B54" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" t="s">
+        <v>116</v>
+      </c>
+      <c r="D54">
+        <v>2017</v>
+      </c>
+      <c r="E54" t="s">
+        <v>225</v>
+      </c>
+      <c r="F54" t="s">
+        <v>226</v>
+      </c>
+      <c r="G54">
+        <v>4</v>
+      </c>
+      <c r="H54" t="s">
+        <v>113</v>
+      </c>
+      <c r="I54">
+        <v>16</v>
+      </c>
+      <c r="J54" t="s">
+        <v>195</v>
+      </c>
+      <c r="K54" s="19">
+        <v>15</v>
+      </c>
+      <c r="M54" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N54" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O54" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="15" customHeight="1">
+      <c r="A55" t="s">
+        <v>224</v>
+      </c>
+      <c r="B55" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" t="s">
+        <v>116</v>
+      </c>
+      <c r="D55">
+        <v>2017</v>
+      </c>
+      <c r="E55" t="s">
+        <v>225</v>
+      </c>
+      <c r="F55" t="s">
+        <v>226</v>
+      </c>
+      <c r="G55">
+        <v>4</v>
+      </c>
+      <c r="H55" t="s">
+        <v>113</v>
+      </c>
+      <c r="I55">
+        <v>16</v>
+      </c>
+      <c r="J55" t="s">
+        <v>195</v>
+      </c>
+      <c r="K55" s="19">
+        <v>15</v>
+      </c>
+      <c r="M55" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N55" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O55" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="15" customHeight="1">
+      <c r="A56" t="s">
+        <v>224</v>
+      </c>
+      <c r="B56" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56">
+        <v>2017</v>
+      </c>
+      <c r="E56" t="s">
+        <v>225</v>
+      </c>
+      <c r="F56" t="s">
+        <v>226</v>
+      </c>
+      <c r="G56">
+        <v>4</v>
+      </c>
+      <c r="H56" t="s">
+        <v>113</v>
+      </c>
+      <c r="I56">
+        <v>16</v>
+      </c>
+      <c r="J56" t="s">
+        <v>195</v>
+      </c>
+      <c r="K56" s="19">
+        <v>15</v>
+      </c>
+      <c r="M56" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N56" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O56" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="15" customHeight="1">
+      <c r="A57" t="s">
+        <v>224</v>
+      </c>
+      <c r="B57" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" t="s">
+        <v>116</v>
+      </c>
+      <c r="D57">
+        <v>2017</v>
+      </c>
+      <c r="E57" t="s">
+        <v>225</v>
+      </c>
+      <c r="F57" t="s">
+        <v>226</v>
+      </c>
+      <c r="G57">
+        <v>4</v>
+      </c>
+      <c r="H57" t="s">
+        <v>113</v>
+      </c>
+      <c r="I57">
+        <v>16</v>
+      </c>
+      <c r="J57" t="s">
+        <v>195</v>
+      </c>
+      <c r="K57" s="19">
+        <v>15</v>
+      </c>
+      <c r="M57" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N57" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O57" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="15" customHeight="1">
+      <c r="A58" t="s">
+        <v>224</v>
+      </c>
+      <c r="B58" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" t="s">
+        <v>116</v>
+      </c>
+      <c r="D58">
+        <v>2017</v>
+      </c>
+      <c r="E58" t="s">
+        <v>225</v>
+      </c>
+      <c r="F58" t="s">
+        <v>226</v>
+      </c>
+      <c r="G58">
+        <v>4</v>
+      </c>
+      <c r="H58" t="s">
+        <v>113</v>
+      </c>
+      <c r="I58">
+        <v>16</v>
+      </c>
+      <c r="J58" t="s">
+        <v>195</v>
+      </c>
+      <c r="K58" s="19">
+        <v>15</v>
+      </c>
+      <c r="M58" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N58" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O58" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="15" customHeight="1">
+      <c r="A59" t="s">
+        <v>224</v>
+      </c>
+      <c r="B59" t="s">
+        <v>53</v>
+      </c>
+      <c r="C59" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59">
+        <v>2017</v>
+      </c>
+      <c r="E59" t="s">
+        <v>225</v>
+      </c>
+      <c r="F59" t="s">
+        <v>226</v>
+      </c>
+      <c r="G59">
+        <v>4</v>
+      </c>
+      <c r="H59" t="s">
+        <v>113</v>
+      </c>
+      <c r="I59">
+        <v>16</v>
+      </c>
+      <c r="J59" t="s">
+        <v>195</v>
+      </c>
+      <c r="K59" s="19">
+        <v>15</v>
+      </c>
+      <c r="M59" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N59" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O59" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="15" customHeight="1">
+      <c r="A60" t="s">
+        <v>224</v>
+      </c>
+      <c r="B60" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" t="s">
+        <v>116</v>
+      </c>
+      <c r="D60">
+        <v>2017</v>
+      </c>
+      <c r="E60" t="s">
+        <v>225</v>
+      </c>
+      <c r="F60" t="s">
+        <v>226</v>
+      </c>
+      <c r="G60">
+        <v>4</v>
+      </c>
+      <c r="H60" t="s">
+        <v>113</v>
+      </c>
+      <c r="I60">
+        <v>16</v>
+      </c>
+      <c r="J60" t="s">
+        <v>195</v>
+      </c>
+      <c r="K60" s="19">
+        <v>15</v>
+      </c>
+      <c r="M60" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N60" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O60" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="15" customHeight="1">
+      <c r="A61" t="s">
+        <v>224</v>
+      </c>
+      <c r="B61" t="s">
+        <v>53</v>
+      </c>
+      <c r="C61" t="s">
+        <v>116</v>
+      </c>
+      <c r="D61">
+        <v>2017</v>
+      </c>
+      <c r="E61" t="s">
+        <v>225</v>
+      </c>
+      <c r="F61" t="s">
+        <v>226</v>
+      </c>
+      <c r="G61">
+        <v>4</v>
+      </c>
+      <c r="H61" t="s">
+        <v>113</v>
+      </c>
+      <c r="I61">
+        <v>16</v>
+      </c>
+      <c r="J61" t="s">
+        <v>195</v>
+      </c>
+      <c r="K61" s="19">
+        <v>15</v>
+      </c>
+      <c r="M61" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N61" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O61" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="15" customHeight="1">
+      <c r="A62" t="s">
+        <v>224</v>
+      </c>
+      <c r="B62" t="s">
+        <v>53</v>
+      </c>
+      <c r="C62" t="s">
+        <v>116</v>
+      </c>
+      <c r="D62">
+        <v>2017</v>
+      </c>
+      <c r="E62" t="s">
+        <v>225</v>
+      </c>
+      <c r="F62" t="s">
+        <v>226</v>
+      </c>
+      <c r="G62">
+        <v>4</v>
+      </c>
+      <c r="H62" t="s">
+        <v>113</v>
+      </c>
+      <c r="I62">
+        <v>16</v>
+      </c>
+      <c r="J62" t="s">
+        <v>195</v>
+      </c>
+      <c r="K62" s="19">
+        <v>15</v>
+      </c>
+      <c r="M62" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N62" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O62" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="15" customHeight="1">
+      <c r="A63" t="s">
+        <v>224</v>
+      </c>
+      <c r="B63" t="s">
+        <v>53</v>
+      </c>
+      <c r="C63" t="s">
+        <v>116</v>
+      </c>
+      <c r="D63">
+        <v>2017</v>
+      </c>
+      <c r="E63" t="s">
+        <v>225</v>
+      </c>
+      <c r="F63" t="s">
+        <v>226</v>
+      </c>
+      <c r="G63">
+        <v>4</v>
+      </c>
+      <c r="H63" t="s">
+        <v>113</v>
+      </c>
+      <c r="I63">
+        <v>16</v>
+      </c>
+      <c r="J63" t="s">
+        <v>195</v>
+      </c>
+      <c r="K63" s="19">
+        <v>15</v>
+      </c>
+      <c r="M63" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N63" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O63" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="15" customHeight="1">
+      <c r="A64" t="s">
+        <v>224</v>
+      </c>
+      <c r="B64" t="s">
+        <v>53</v>
+      </c>
+      <c r="C64" t="s">
+        <v>116</v>
+      </c>
+      <c r="D64">
+        <v>2017</v>
+      </c>
+      <c r="E64" t="s">
+        <v>225</v>
+      </c>
+      <c r="F64" t="s">
+        <v>226</v>
+      </c>
+      <c r="G64">
+        <v>4</v>
+      </c>
+      <c r="H64" t="s">
+        <v>113</v>
+      </c>
+      <c r="I64">
+        <v>16</v>
+      </c>
+      <c r="J64" t="s">
+        <v>195</v>
+      </c>
+      <c r="K64" s="19">
+        <v>15</v>
+      </c>
+      <c r="M64" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N64" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O64" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="15" customHeight="1">
+      <c r="A65" t="s">
+        <v>224</v>
+      </c>
+      <c r="B65" t="s">
+        <v>53</v>
+      </c>
+      <c r="C65" t="s">
+        <v>116</v>
+      </c>
+      <c r="D65">
+        <v>2017</v>
+      </c>
+      <c r="E65" t="s">
+        <v>225</v>
+      </c>
+      <c r="F65" t="s">
+        <v>226</v>
+      </c>
+      <c r="G65">
+        <v>4</v>
+      </c>
+      <c r="H65" t="s">
+        <v>113</v>
+      </c>
+      <c r="I65">
+        <v>16</v>
+      </c>
+      <c r="J65" t="s">
+        <v>195</v>
+      </c>
+      <c r="K65" s="19">
+        <v>15</v>
+      </c>
+      <c r="M65" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N65" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O65" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="15" customHeight="1">
+      <c r="A66" t="s">
+        <v>224</v>
+      </c>
+      <c r="B66" t="s">
+        <v>53</v>
+      </c>
+      <c r="C66" t="s">
+        <v>116</v>
+      </c>
+      <c r="D66">
+        <v>2017</v>
+      </c>
+      <c r="E66" t="s">
+        <v>225</v>
+      </c>
+      <c r="F66" t="s">
+        <v>226</v>
+      </c>
+      <c r="G66">
+        <v>4</v>
+      </c>
+      <c r="H66" t="s">
+        <v>113</v>
+      </c>
+      <c r="I66">
+        <v>16</v>
+      </c>
+      <c r="J66" t="s">
+        <v>195</v>
+      </c>
+      <c r="K66" s="19">
+        <v>15</v>
+      </c>
+      <c r="M66" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N66" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O66" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="15" customHeight="1">
+      <c r="A67" t="s">
+        <v>224</v>
+      </c>
+      <c r="B67" t="s">
+        <v>53</v>
+      </c>
+      <c r="C67" t="s">
+        <v>116</v>
+      </c>
+      <c r="D67">
+        <v>2017</v>
+      </c>
+      <c r="E67" t="s">
+        <v>225</v>
+      </c>
+      <c r="F67" t="s">
+        <v>226</v>
+      </c>
+      <c r="G67">
+        <v>4</v>
+      </c>
+      <c r="H67" t="s">
+        <v>113</v>
+      </c>
+      <c r="I67">
+        <v>16</v>
+      </c>
+      <c r="J67" t="s">
+        <v>195</v>
+      </c>
+      <c r="K67" s="19">
+        <v>15</v>
+      </c>
+      <c r="M67" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N67" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O67" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="15" customHeight="1">
+      <c r="A68" t="s">
+        <v>224</v>
+      </c>
+      <c r="B68" t="s">
+        <v>53</v>
+      </c>
+      <c r="C68" t="s">
+        <v>116</v>
+      </c>
+      <c r="D68">
+        <v>2017</v>
+      </c>
+      <c r="E68" t="s">
+        <v>225</v>
+      </c>
+      <c r="F68" t="s">
+        <v>226</v>
+      </c>
+      <c r="G68">
+        <v>4</v>
+      </c>
+      <c r="H68" t="s">
+        <v>113</v>
+      </c>
+      <c r="I68">
+        <v>16</v>
+      </c>
+      <c r="J68" t="s">
+        <v>195</v>
+      </c>
+      <c r="K68" s="19">
+        <v>15</v>
+      </c>
+      <c r="M68" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N68" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O68" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="15" customHeight="1">
+      <c r="A69" t="s">
+        <v>224</v>
+      </c>
+      <c r="B69" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" t="s">
+        <v>116</v>
+      </c>
+      <c r="D69">
+        <v>2017</v>
+      </c>
+      <c r="E69" t="s">
+        <v>225</v>
+      </c>
+      <c r="F69" t="s">
+        <v>226</v>
+      </c>
+      <c r="G69">
+        <v>4</v>
+      </c>
+      <c r="H69" t="s">
+        <v>113</v>
+      </c>
+      <c r="I69">
+        <v>16</v>
+      </c>
+      <c r="J69" t="s">
+        <v>195</v>
+      </c>
+      <c r="K69" s="19">
+        <v>15</v>
+      </c>
+      <c r="M69" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N69" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O69" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="15" customHeight="1">
+      <c r="A70" t="s">
+        <v>224</v>
+      </c>
+      <c r="B70" t="s">
+        <v>53</v>
+      </c>
+      <c r="C70" t="s">
+        <v>116</v>
+      </c>
+      <c r="D70">
+        <v>2017</v>
+      </c>
+      <c r="E70" t="s">
+        <v>225</v>
+      </c>
+      <c r="F70" t="s">
+        <v>226</v>
+      </c>
+      <c r="G70">
+        <v>4</v>
+      </c>
+      <c r="H70" t="s">
+        <v>113</v>
+      </c>
+      <c r="I70">
+        <v>16</v>
+      </c>
+      <c r="J70" t="s">
+        <v>195</v>
+      </c>
+      <c r="K70" s="19">
+        <v>15</v>
+      </c>
+      <c r="M70" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N70" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O70" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="15" customHeight="1">
+      <c r="A71" t="s">
+        <v>224</v>
+      </c>
+      <c r="B71" t="s">
+        <v>53</v>
+      </c>
+      <c r="C71" t="s">
+        <v>116</v>
+      </c>
+      <c r="D71">
+        <v>2017</v>
+      </c>
+      <c r="E71" t="s">
+        <v>225</v>
+      </c>
+      <c r="F71" t="s">
+        <v>226</v>
+      </c>
+      <c r="G71">
+        <v>4</v>
+      </c>
+      <c r="H71" t="s">
+        <v>113</v>
+      </c>
+      <c r="I71">
+        <v>16</v>
+      </c>
+      <c r="J71" t="s">
+        <v>195</v>
+      </c>
+      <c r="K71" s="19">
+        <v>15</v>
+      </c>
+      <c r="M71" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N71" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O71" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="15" customHeight="1">
+      <c r="A72" t="s">
+        <v>224</v>
+      </c>
+      <c r="B72" t="s">
+        <v>53</v>
+      </c>
+      <c r="C72" t="s">
+        <v>116</v>
+      </c>
+      <c r="D72">
+        <v>2017</v>
+      </c>
+      <c r="E72" t="s">
+        <v>225</v>
+      </c>
+      <c r="F72" t="s">
+        <v>226</v>
+      </c>
+      <c r="G72">
+        <v>4</v>
+      </c>
+      <c r="H72" t="s">
+        <v>113</v>
+      </c>
+      <c r="I72">
+        <v>16</v>
+      </c>
+      <c r="J72" t="s">
+        <v>195</v>
+      </c>
+      <c r="K72" s="19">
+        <v>15</v>
+      </c>
+      <c r="M72" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N72" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O72" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="15" customHeight="1">
+      <c r="A73" t="s">
+        <v>224</v>
+      </c>
+      <c r="B73" t="s">
+        <v>53</v>
+      </c>
+      <c r="C73" t="s">
+        <v>116</v>
+      </c>
+      <c r="D73">
+        <v>2017</v>
+      </c>
+      <c r="E73" t="s">
+        <v>225</v>
+      </c>
+      <c r="F73" t="s">
+        <v>226</v>
+      </c>
+      <c r="G73">
+        <v>4</v>
+      </c>
+      <c r="H73" t="s">
+        <v>113</v>
+      </c>
+      <c r="I73">
+        <v>16</v>
+      </c>
+      <c r="J73" t="s">
+        <v>195</v>
+      </c>
+      <c r="K73" s="19">
+        <v>15</v>
+      </c>
+      <c r="M73" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N73" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O73" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="15" customHeight="1">
+      <c r="A74" t="s">
+        <v>224</v>
+      </c>
+      <c r="B74" t="s">
+        <v>53</v>
+      </c>
+      <c r="C74" t="s">
+        <v>116</v>
+      </c>
+      <c r="D74">
+        <v>2017</v>
+      </c>
+      <c r="E74" t="s">
+        <v>225</v>
+      </c>
+      <c r="F74" t="s">
+        <v>226</v>
+      </c>
+      <c r="G74">
+        <v>4</v>
+      </c>
+      <c r="H74" t="s">
+        <v>113</v>
+      </c>
+      <c r="I74">
+        <v>16</v>
+      </c>
+      <c r="J74" t="s">
+        <v>195</v>
+      </c>
+      <c r="K74" s="19">
+        <v>15</v>
+      </c>
+      <c r="M74" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N74" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O74" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" ht="15" customHeight="1">
+      <c r="A75" t="s">
+        <v>224</v>
+      </c>
+      <c r="B75" t="s">
+        <v>53</v>
+      </c>
+      <c r="C75" t="s">
+        <v>116</v>
+      </c>
+      <c r="D75">
+        <v>2017</v>
+      </c>
+      <c r="E75" t="s">
+        <v>225</v>
+      </c>
+      <c r="F75" t="s">
+        <v>226</v>
+      </c>
+      <c r="G75">
+        <v>4</v>
+      </c>
+      <c r="H75" t="s">
+        <v>113</v>
+      </c>
+      <c r="I75">
+        <v>16</v>
+      </c>
+      <c r="J75" t="s">
+        <v>195</v>
+      </c>
+      <c r="K75" s="19">
+        <v>15</v>
+      </c>
+      <c r="M75" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N75" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O75" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="15" customHeight="1">
+      <c r="A76" t="s">
+        <v>224</v>
+      </c>
+      <c r="B76" t="s">
+        <v>53</v>
+      </c>
+      <c r="C76" t="s">
+        <v>116</v>
+      </c>
+      <c r="D76">
+        <v>2017</v>
+      </c>
+      <c r="E76" t="s">
+        <v>225</v>
+      </c>
+      <c r="F76" t="s">
+        <v>226</v>
+      </c>
+      <c r="G76">
+        <v>4</v>
+      </c>
+      <c r="H76" t="s">
+        <v>113</v>
+      </c>
+      <c r="I76">
+        <v>16</v>
+      </c>
+      <c r="J76" t="s">
+        <v>195</v>
+      </c>
+      <c r="K76" s="19">
+        <v>15</v>
+      </c>
+      <c r="M76" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N76" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O76" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" ht="15" customHeight="1">
+      <c r="A77" t="s">
+        <v>224</v>
+      </c>
+      <c r="B77" t="s">
+        <v>53</v>
+      </c>
+      <c r="C77" t="s">
+        <v>116</v>
+      </c>
+      <c r="D77">
+        <v>2017</v>
+      </c>
+      <c r="E77" t="s">
+        <v>225</v>
+      </c>
+      <c r="F77" t="s">
+        <v>226</v>
+      </c>
+      <c r="G77">
+        <v>4</v>
+      </c>
+      <c r="H77" t="s">
+        <v>113</v>
+      </c>
+      <c r="I77">
+        <v>16</v>
+      </c>
+      <c r="J77" t="s">
+        <v>195</v>
+      </c>
+      <c r="K77" s="19">
+        <v>15</v>
+      </c>
+      <c r="M77" s="15">
+        <v>46153</v>
+      </c>
+      <c r="N77" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O77" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="15" customHeight="1">
+      <c r="A78" t="s">
+        <v>59</v>
+      </c>
+      <c r="B78" t="s">
+        <v>30</v>
+      </c>
+      <c r="C78" t="s">
+        <v>110</v>
+      </c>
+      <c r="D78">
+        <v>2015</v>
+      </c>
+      <c r="E78" t="s">
+        <v>137</v>
+      </c>
+      <c r="F78" t="s">
+        <v>127</v>
+      </c>
+      <c r="G78">
+        <v>16</v>
+      </c>
+      <c r="H78" t="s">
+        <v>120</v>
+      </c>
+      <c r="I78">
+        <v>256</v>
+      </c>
+      <c r="J78" t="s">
+        <v>114</v>
+      </c>
+      <c r="K78" s="19">
+        <v>255</v>
+      </c>
+      <c r="L78" s="1"/>
+      <c r="M78" s="15">
+        <v>46155</v>
+      </c>
+      <c r="N78" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="O78" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="15" customHeight="1">
+      <c r="A79" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" ht="15" customHeight="1">
-      <c r="M46" s="15"/>
-      <c r="N46" s="15"/>
-    </row>
-    <row r="47" spans="1:15" ht="15" customHeight="1">
-      <c r="M47" s="15"/>
-      <c r="N47" s="15"/>
-    </row>
-    <row r="48" spans="1:15" ht="15" customHeight="1">
-      <c r="M48" s="15"/>
-      <c r="N48" s="15"/>
-    </row>
-    <row r="49" spans="13:14" ht="15" customHeight="1">
-      <c r="M49" s="15"/>
-      <c r="N49" s="15"/>
-    </row>
-    <row r="50" spans="13:14" ht="15" customHeight="1">
-      <c r="M50" s="15"/>
-      <c r="N50" s="15"/>
-    </row>
-    <row r="51" spans="13:14" ht="15" customHeight="1">
-      <c r="M51" s="15"/>
-      <c r="N51" s="15"/>
-    </row>
-    <row r="52" spans="13:14" ht="15" customHeight="1">
-      <c r="M52" s="15"/>
-      <c r="N52" s="15"/>
-    </row>
-    <row r="53" spans="13:14" ht="15" customHeight="1">
-      <c r="M53" s="15"/>
-      <c r="N53" s="15"/>
-    </row>
-    <row r="54" spans="13:14" ht="15" customHeight="1">
-      <c r="M54" s="15"/>
-      <c r="N54" s="15"/>
-    </row>
-    <row r="55" spans="13:14" ht="15" customHeight="1">
-      <c r="M55" s="15"/>
-      <c r="N55" s="15"/>
-    </row>
-    <row r="56" spans="13:14" ht="15" customHeight="1">
-      <c r="M56" s="15"/>
-      <c r="N56" s="15"/>
-    </row>
-    <row r="57" spans="13:14" ht="15" customHeight="1">
-      <c r="M57" s="15"/>
-      <c r="N57" s="15"/>
-    </row>
-    <row r="58" spans="13:14" ht="15" customHeight="1">
-      <c r="M58" s="15"/>
-      <c r="N58" s="15"/>
-    </row>
-    <row r="59" spans="13:14" ht="15" customHeight="1">
-      <c r="M59" s="15"/>
-      <c r="N59" s="15"/>
+      <c r="B79" t="s">
+        <v>30</v>
+      </c>
+      <c r="C79" t="s">
+        <v>110</v>
+      </c>
+      <c r="D79">
+        <v>2018</v>
+      </c>
+      <c r="E79" t="s">
+        <v>228</v>
+      </c>
+      <c r="F79" t="s">
+        <v>127</v>
+      </c>
+      <c r="G79">
+        <v>8</v>
+      </c>
+      <c r="H79" t="s">
+        <v>120</v>
+      </c>
+      <c r="I79">
+        <v>256</v>
+      </c>
+      <c r="J79" t="s">
+        <v>114</v>
+      </c>
+      <c r="K79" s="19">
+        <f>_xlfn.SINGLE(200)</f>
+        <v>200</v>
+      </c>
+      <c r="L79" s="1"/>
+      <c r="M79" s="15">
+        <v>46155</v>
+      </c>
+      <c r="N79" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="O79" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="15" customHeight="1">
+      <c r="A80" t="s">
+        <v>229</v>
+      </c>
+      <c r="B80" t="s">
+        <v>39</v>
+      </c>
+      <c r="C80" t="s">
+        <v>116</v>
+      </c>
+      <c r="D80">
+        <v>2019</v>
+      </c>
+      <c r="E80" t="s">
+        <v>230</v>
+      </c>
+      <c r="F80" t="s">
+        <v>127</v>
+      </c>
+      <c r="G80">
+        <v>16</v>
+      </c>
+      <c r="H80" t="s">
+        <v>120</v>
+      </c>
+      <c r="I80">
+        <v>256</v>
+      </c>
+      <c r="J80" t="s">
+        <v>114</v>
+      </c>
+      <c r="K80" s="19">
+        <v>300</v>
+      </c>
+      <c r="L80" s="1"/>
+      <c r="M80" s="15">
+        <v>46155</v>
+      </c>
+      <c r="N80" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="O80" t="s">
+        <v>179</v>
+      </c>
+      <c r="P80" s="31" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="15" customHeight="1">
+      <c r="A81" t="s">
+        <v>55</v>
+      </c>
+      <c r="B81" t="s">
+        <v>39</v>
+      </c>
+      <c r="C81" t="s">
+        <v>116</v>
+      </c>
+      <c r="D81">
+        <v>2019</v>
+      </c>
+      <c r="E81" t="s">
+        <v>233</v>
+      </c>
+      <c r="F81" t="s">
+        <v>127</v>
+      </c>
+      <c r="G81">
+        <v>8</v>
+      </c>
+      <c r="H81" t="s">
+        <v>120</v>
+      </c>
+      <c r="I81">
+        <v>256</v>
+      </c>
+      <c r="J81" t="s">
+        <v>114</v>
+      </c>
+      <c r="K81" s="19">
+        <v>300</v>
+      </c>
+      <c r="L81" s="1"/>
+      <c r="M81" s="15">
+        <v>46155</v>
+      </c>
+      <c r="N81" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="O81" t="s">
+        <v>179</v>
+      </c>
+      <c r="P81" s="31" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="15" customHeight="1">
+      <c r="A82" t="s">
+        <v>216</v>
+      </c>
+      <c r="B82" t="s">
+        <v>30</v>
+      </c>
+      <c r="C82" t="s">
+        <v>116</v>
+      </c>
+      <c r="D82">
+        <v>2018</v>
+      </c>
+      <c r="E82" t="s">
+        <v>236</v>
+      </c>
+      <c r="F82" t="s">
+        <v>127</v>
+      </c>
+      <c r="G82">
+        <v>8</v>
+      </c>
+      <c r="H82" t="s">
+        <v>120</v>
+      </c>
+      <c r="I82">
+        <v>256</v>
+      </c>
+      <c r="J82" t="s">
+        <v>114</v>
+      </c>
+      <c r="K82" s="19">
+        <v>120</v>
+      </c>
+      <c r="L82" s="1"/>
+      <c r="M82" s="15">
+        <v>46155</v>
+      </c>
+      <c r="N82" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="O82" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" ht="15" customHeight="1">
+      <c r="A83" t="s">
+        <v>237</v>
+      </c>
+      <c r="B83" t="s">
+        <v>30</v>
+      </c>
+      <c r="C83" t="s">
+        <v>116</v>
+      </c>
+      <c r="D83">
+        <v>2019</v>
+      </c>
+      <c r="E83" t="s">
+        <v>238</v>
+      </c>
+      <c r="F83" t="s">
+        <v>127</v>
+      </c>
+      <c r="G83">
+        <v>8</v>
+      </c>
+      <c r="H83" t="s">
+        <v>120</v>
+      </c>
+      <c r="I83">
+        <v>256</v>
+      </c>
+      <c r="J83" t="s">
+        <v>114</v>
+      </c>
+      <c r="K83" s="19">
+        <v>265</v>
+      </c>
+      <c r="L83" s="1"/>
+      <c r="M83" s="15">
+        <v>46155</v>
+      </c>
+      <c r="N83" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="O83" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="15" customHeight="1">
+      <c r="A84" t="s">
+        <v>239</v>
+      </c>
+      <c r="B84" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="D84">
+        <v>2020</v>
+      </c>
+      <c r="E84" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="F84" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="G84" s="29">
+        <v>8</v>
+      </c>
+      <c r="H84" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="I84" s="28">
+        <v>256</v>
+      </c>
+      <c r="J84" t="s">
+        <v>114</v>
+      </c>
+      <c r="K84" s="19">
+        <v>400</v>
+      </c>
+      <c r="L84" s="1"/>
+      <c r="M84" s="15">
+        <v>46155</v>
+      </c>
+      <c r="N84" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="O84" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="15" customHeight="1">
+      <c r="A85" t="s">
+        <v>241</v>
+      </c>
+      <c r="B85" t="s">
+        <v>53</v>
+      </c>
+      <c r="C85" t="s">
+        <v>116</v>
+      </c>
+      <c r="D85">
+        <v>2014</v>
+      </c>
+      <c r="E85" t="s">
+        <v>242</v>
+      </c>
+      <c r="F85" t="s">
+        <v>226</v>
+      </c>
+      <c r="G85">
+        <v>4</v>
+      </c>
+      <c r="H85" t="s">
+        <v>113</v>
+      </c>
+      <c r="I85">
+        <v>16</v>
+      </c>
+      <c r="J85" t="s">
+        <v>195</v>
+      </c>
+      <c r="K85" s="19">
+        <v>15</v>
+      </c>
+      <c r="M85" s="15">
+        <v>46157</v>
+      </c>
+      <c r="N85" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O85" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="15" customHeight="1">
+      <c r="A86" t="s">
+        <v>243</v>
+      </c>
+      <c r="B86" t="s">
+        <v>53</v>
+      </c>
+      <c r="C86" t="s">
+        <v>116</v>
+      </c>
+      <c r="D86">
+        <v>2015</v>
+      </c>
+      <c r="E86" t="s">
+        <v>244</v>
+      </c>
+      <c r="F86" t="s">
+        <v>226</v>
+      </c>
+      <c r="G86">
+        <v>4</v>
+      </c>
+      <c r="H86" t="s">
+        <v>113</v>
+      </c>
+      <c r="I86">
+        <v>16</v>
+      </c>
+      <c r="J86" t="s">
+        <v>195</v>
+      </c>
+      <c r="K86" s="19">
+        <v>15</v>
+      </c>
+      <c r="M86" s="15">
+        <v>46157</v>
+      </c>
+      <c r="N86" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O86" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="15" customHeight="1">
+      <c r="A87" t="s">
+        <v>243</v>
+      </c>
+      <c r="B87" t="s">
+        <v>53</v>
+      </c>
+      <c r="C87" t="s">
+        <v>116</v>
+      </c>
+      <c r="D87">
+        <v>2015</v>
+      </c>
+      <c r="E87" t="s">
+        <v>245</v>
+      </c>
+      <c r="F87" t="s">
+        <v>226</v>
+      </c>
+      <c r="G87">
+        <v>4</v>
+      </c>
+      <c r="H87" t="s">
+        <v>120</v>
+      </c>
+      <c r="I87">
+        <v>16</v>
+      </c>
+      <c r="J87" t="s">
+        <v>195</v>
+      </c>
+      <c r="K87" s="19">
+        <v>15</v>
+      </c>
+      <c r="M87" s="15">
+        <v>46158</v>
+      </c>
+      <c r="N87" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O87" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="15" customHeight="1">
+      <c r="A88" t="s">
+        <v>243</v>
+      </c>
+      <c r="B88" t="s">
+        <v>53</v>
+      </c>
+      <c r="C88" t="s">
+        <v>116</v>
+      </c>
+      <c r="D88">
+        <v>2015</v>
+      </c>
+      <c r="E88" t="s">
+        <v>246</v>
+      </c>
+      <c r="F88" t="s">
+        <v>226</v>
+      </c>
+      <c r="G88">
+        <v>4</v>
+      </c>
+      <c r="H88" t="s">
+        <v>247</v>
+      </c>
+      <c r="I88">
+        <v>16</v>
+      </c>
+      <c r="J88" t="s">
+        <v>195</v>
+      </c>
+      <c r="K88" s="19">
+        <v>15</v>
+      </c>
+      <c r="M88" s="15">
+        <v>46159</v>
+      </c>
+      <c r="N88" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O88" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="15" customHeight="1">
+      <c r="A89" t="s">
+        <v>243</v>
+      </c>
+      <c r="B89" t="s">
+        <v>53</v>
+      </c>
+      <c r="C89" t="s">
+        <v>116</v>
+      </c>
+      <c r="D89">
+        <v>2015</v>
+      </c>
+      <c r="E89" t="s">
+        <v>248</v>
+      </c>
+      <c r="F89" t="s">
+        <v>226</v>
+      </c>
+      <c r="G89">
+        <v>4</v>
+      </c>
+      <c r="H89" t="s">
+        <v>249</v>
+      </c>
+      <c r="I89">
+        <v>16</v>
+      </c>
+      <c r="J89" t="s">
+        <v>195</v>
+      </c>
+      <c r="K89" s="19">
+        <v>15</v>
+      </c>
+      <c r="M89" s="15">
+        <v>46160</v>
+      </c>
+      <c r="N89" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O89" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" ht="15" customHeight="1">
+      <c r="A90" t="s">
+        <v>243</v>
+      </c>
+      <c r="B90" t="s">
+        <v>53</v>
+      </c>
+      <c r="C90" t="s">
+        <v>116</v>
+      </c>
+      <c r="D90">
+        <v>2015</v>
+      </c>
+      <c r="E90" t="s">
+        <v>250</v>
+      </c>
+      <c r="F90" t="s">
+        <v>226</v>
+      </c>
+      <c r="G90">
+        <v>4</v>
+      </c>
+      <c r="H90" t="s">
+        <v>251</v>
+      </c>
+      <c r="I90">
+        <v>16</v>
+      </c>
+      <c r="J90" t="s">
+        <v>195</v>
+      </c>
+      <c r="K90" s="19">
+        <v>15</v>
+      </c>
+      <c r="M90" s="15">
+        <v>46161</v>
+      </c>
+      <c r="N90" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O90" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" ht="15" customHeight="1">
+      <c r="A91" t="s">
+        <v>224</v>
+      </c>
+      <c r="B91" t="s">
+        <v>53</v>
+      </c>
+      <c r="C91" t="s">
+        <v>116</v>
+      </c>
+      <c r="D91">
+        <v>2017</v>
+      </c>
+      <c r="E91" t="s">
+        <v>225</v>
+      </c>
+      <c r="F91" t="s">
+        <v>226</v>
+      </c>
+      <c r="G91">
+        <v>4</v>
+      </c>
+      <c r="H91" t="s">
+        <v>113</v>
+      </c>
+      <c r="I91">
+        <v>16</v>
+      </c>
+      <c r="J91" t="s">
+        <v>195</v>
+      </c>
+      <c r="K91" s="19">
+        <v>15</v>
+      </c>
+      <c r="M91" s="15">
+        <v>46157</v>
+      </c>
+      <c r="N91" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O91" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="15" customHeight="1">
+      <c r="A92" t="s">
+        <v>224</v>
+      </c>
+      <c r="B92" t="s">
+        <v>53</v>
+      </c>
+      <c r="C92" t="s">
+        <v>116</v>
+      </c>
+      <c r="D92">
+        <v>2017</v>
+      </c>
+      <c r="E92" t="s">
+        <v>225</v>
+      </c>
+      <c r="F92" t="s">
+        <v>226</v>
+      </c>
+      <c r="G92">
+        <v>4</v>
+      </c>
+      <c r="H92" t="s">
+        <v>113</v>
+      </c>
+      <c r="I92">
+        <v>16</v>
+      </c>
+      <c r="J92" t="s">
+        <v>195</v>
+      </c>
+      <c r="K92" s="19">
+        <v>15</v>
+      </c>
+      <c r="M92" s="15">
+        <v>46157</v>
+      </c>
+      <c r="N92" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O92" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" ht="15" customHeight="1">
+      <c r="A93" t="s">
+        <v>224</v>
+      </c>
+      <c r="B93" t="s">
+        <v>53</v>
+      </c>
+      <c r="C93" t="s">
+        <v>116</v>
+      </c>
+      <c r="D93">
+        <v>2017</v>
+      </c>
+      <c r="E93" t="s">
+        <v>225</v>
+      </c>
+      <c r="F93" t="s">
+        <v>226</v>
+      </c>
+      <c r="G93">
+        <v>4</v>
+      </c>
+      <c r="H93" t="s">
+        <v>113</v>
+      </c>
+      <c r="I93">
+        <v>16</v>
+      </c>
+      <c r="J93" t="s">
+        <v>195</v>
+      </c>
+      <c r="K93" s="19">
+        <v>15</v>
+      </c>
+      <c r="M93" s="15">
+        <v>46157</v>
+      </c>
+      <c r="N93" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="O93" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" ht="15" customHeight="1">
+      <c r="M94" s="15"/>
+      <c r="N94" s="15"/>
+    </row>
+    <row r="95" spans="1:16" ht="15" customHeight="1">
+      <c r="M95" s="15"/>
+      <c r="N95" s="15"/>
+    </row>
+    <row r="96" spans="1:16" ht="15" customHeight="1">
+      <c r="M96" s="15"/>
+      <c r="N96" s="15"/>
+    </row>
+    <row r="97" spans="13:14" ht="15" customHeight="1">
+      <c r="M97" s="15"/>
+      <c r="N97" s="15"/>
+    </row>
+    <row r="98" spans="13:14" ht="15" customHeight="1">
+      <c r="M98" s="15"/>
+      <c r="N98" s="15"/>
+    </row>
+    <row r="99" spans="13:14" ht="15" customHeight="1">
+      <c r="M99" s="15"/>
+      <c r="N99" s="15"/>
+    </row>
+    <row r="100" spans="13:14" ht="15" customHeight="1">
+      <c r="M100" s="15"/>
+      <c r="N100" s="15"/>
+    </row>
+    <row r="101" spans="13:14" ht="15" customHeight="1">
+      <c r="M101" s="15"/>
+      <c r="N101" s="15"/>
+    </row>
+    <row r="102" spans="13:14" ht="15" customHeight="1">
+      <c r="M102" s="15"/>
+      <c r="N102" s="15"/>
+    </row>
+    <row r="103" spans="13:14" ht="15" customHeight="1">
+      <c r="M103" s="15"/>
+      <c r="N103" s="15"/>
+    </row>
+    <row r="104" spans="13:14" ht="15" customHeight="1">
+      <c r="M104" s="15"/>
+      <c r="N104" s="15"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A44:G44 I44:L44">
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="21" priority="65">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:G44 I44:N44">
-    <cfRule type="expression" dxfId="10" priority="6">
+    <cfRule type="expression" dxfId="20" priority="66">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:O9 A10:H15 J10:O15 A16:O43 O44 A45:O59">
-    <cfRule type="expression" priority="7">
+  <conditionalFormatting sqref="A78:L78">
+    <cfRule type="expression" dxfId="19" priority="19">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="8">
+    <cfRule type="expression" dxfId="18" priority="20">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A80:L83">
+    <cfRule type="expression" dxfId="17" priority="9">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="10">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:O9 A10:H15 J10:O15 A16:O43 O44 A45:O45">
+    <cfRule type="expression" priority="67">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="68">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46:D77 F46:I77 K46:O77">
+    <cfRule type="expression" priority="21">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="22">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B91:D93 F91:I93 K91:O93">
+    <cfRule type="expression" priority="1">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C84 E84:I84">
+    <cfRule type="expression" dxfId="12" priority="7">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="8">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H44">
-    <cfRule type="expression" priority="3">
+    <cfRule type="expression" priority="63">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="10" priority="64">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:I15">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="9" priority="61">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="8" priority="62">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M78:M84">
+    <cfRule type="expression" priority="17">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="18">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N85:N90">
+    <cfRule type="expression" priority="5">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="6">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7366,14 +9429,18 @@
       <formula1>1</formula1>
       <formula2>2000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1 M1:N42 M45:N1048576" xr:uid="{A9EBE1C3-8923-4578-8214-596FAC33FDB8}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C17 C19 C21:C29 C31:C42" xr:uid="{C7FD23E6-3E08-4DF7-8556-C07E455C4835}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1 M1:N42 H84 M45:N1048576" xr:uid="{A9EBE1C3-8923-4578-8214-596FAC33FDB8}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C17 C19 C21:C29 C31:C42 C78 C80:C83" xr:uid="{C7FD23E6-3E08-4DF7-8556-C07E455C4835}">
       <formula1>"Desktop,Laptop,Tablet,All-In-One"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="P80" r:id="rId1" xr:uid="{88E36221-050A-4484-95D7-E396668D9595}"/>
+    <hyperlink ref="P81" r:id="rId2" xr:uid="{ADE433DC-94EB-4AAD-9404-DB569BB97262}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7391,43 +9458,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
+      <c r="A1" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>220</v>
+        <v>253</v>
       </c>
       <c r="B2" t="s">
-        <v>221</v>
+        <v>254</v>
       </c>
       <c r="C2" t="s">
-        <v>222</v>
+        <v>255</v>
       </c>
       <c r="D2" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>224</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E3" s="2">
         <v>50</v>
@@ -7435,16 +9502,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>227</v>
+        <v>260</v>
       </c>
       <c r="B4" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E4" s="2">
         <v>55</v>
@@ -7452,16 +9519,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="B5" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E5" s="2">
         <v>5</v>
@@ -7469,16 +9536,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="B6" t="s">
-        <v>230</v>
+        <v>263</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E6" s="2">
         <v>10</v>
@@ -7486,16 +9553,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="B7" t="s">
-        <v>231</v>
+        <v>264</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
@@ -7503,16 +9570,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="B8" t="s">
-        <v>232</v>
+        <v>265</v>
       </c>
       <c r="C8">
         <v>18</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E8" s="2">
         <v>35</v>
@@ -7520,16 +9587,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="B9" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E9" s="2">
         <v>20</v>
@@ -7537,16 +9604,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="B10" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E10" s="2">
         <v>20</v>
@@ -7554,16 +9621,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="B11" t="s">
-        <v>235</v>
+        <v>268</v>
       </c>
       <c r="C11">
         <v>15</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E11" s="2">
         <v>15</v>
@@ -7571,16 +9638,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="B12" t="s">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E12" s="2">
         <v>50</v>
@@ -7588,16 +9655,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="B13" t="s">
-        <v>232</v>
+        <v>265</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E13" s="2">
         <v>30</v>
@@ -7605,16 +9672,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="B14" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E14" s="2">
         <v>25</v>
@@ -7622,16 +9689,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="B15" t="s">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E15" s="2">
         <v>50</v>
@@ -7639,16 +9706,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="B16" t="s">
-        <v>235</v>
+        <v>268</v>
       </c>
       <c r="C16">
         <v>11</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E16" s="2">
         <v>10</v>
@@ -7656,16 +9723,16 @@
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1">
       <c r="A17" t="s">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="B17" t="s">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="C17">
         <v>4</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E17" s="2">
         <v>60</v>
@@ -7693,7 +9760,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F77F78-0898-4060-A2C7-C1A84336B28A}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -7702,26 +9769,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="B1" s="34"/>
+      <c r="A1" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="B1" s="35"/>
       <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" t="s">
-        <v>241</v>
+        <v>274</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>222</v>
+        <v>255</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>224</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1">
       <c r="A3" t="s">
-        <v>242</v>
+        <v>275</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -7732,7 +9799,7 @@
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -7743,7 +9810,7 @@
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
       <c r="A5" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -7754,7 +9821,7 @@
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" t="s">
-        <v>245</v>
+        <v>278</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -7765,7 +9832,7 @@
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
       <c r="A7" t="s">
-        <v>246</v>
+        <v>279</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -7776,78 +9843,34 @@
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" t="s">
-        <v>247</v>
+        <v>280</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C8" s="19">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C9" s="19">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" t="s">
-        <v>249</v>
+        <v>282</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C10" s="19">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1">
-      <c r="A11" t="s">
-        <v>250</v>
-      </c>
-      <c r="B11">
-        <v>14</v>
-      </c>
-      <c r="C11" s="19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1">
-      <c r="A12" t="s">
-        <v>251</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" s="19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1">
-      <c r="A13" t="s">
-        <v>252</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1">
-      <c r="A14" t="s">
-        <v>253</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14" s="19">
         <v>15</v>
       </c>
     </row>
